--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3905EFC-24B6-4566-BA72-C92A1B9861F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20F817A-035B-4939-8602-0BD953CB0032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -34,8 +34,8 @@
     <sheet name="Week 18" sheetId="22" r:id="rId19"/>
     <sheet name="Week 19" sheetId="23" r:id="rId20"/>
     <sheet name="Week 20" sheetId="24" r:id="rId21"/>
-    <sheet name="Week 21" sheetId="25" r:id="rId22"/>
-    <sheet name="Week 22" sheetId="26" r:id="rId23"/>
+    <sheet name="Week 22" sheetId="26" r:id="rId22"/>
+    <sheet name="Week 21" sheetId="25" r:id="rId23"/>
     <sheet name="Week 23" sheetId="27" r:id="rId24"/>
     <sheet name="Week 24" sheetId="28" r:id="rId25"/>
     <sheet name="Week 25" sheetId="29" r:id="rId26"/>
@@ -1505,7 +1505,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="291">
+  <dxfs count="286">
     <dxf>
       <font>
         <color theme="1"/>
@@ -1517,6 +1517,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1547,6 +1571,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1567,6 +1615,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1729,6 +1787,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1837,6 +1915,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1857,6 +1959,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1911,6 +2023,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1955,6 +2077,54 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1965,6 +2135,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2019,6 +2209,46 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2083,6 +2313,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2127,6 +2367,56 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2151,6 +2441,56 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2205,6 +2545,46 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2279,26 +2659,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2319,416 +2679,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4887,47 +4837,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="237" priority="17">
+    <cfRule type="expression" dxfId="232" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="236" priority="25">
+    <cfRule type="expression" dxfId="231" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="235" priority="24">
+    <cfRule type="expression" dxfId="230" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="234" priority="5">
+    <cfRule type="expression" dxfId="229" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="233" priority="9">
+    <cfRule type="expression" dxfId="228" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="232" priority="8">
+    <cfRule type="expression" dxfId="227" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="231" priority="11">
+    <cfRule type="expression" dxfId="226" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="230" priority="15">
+    <cfRule type="expression" dxfId="225" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="229" priority="2">
+    <cfRule type="expression" dxfId="224" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5386,42 +5336,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="228" priority="15">
+    <cfRule type="expression" dxfId="223" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="227" priority="10">
+    <cfRule type="expression" dxfId="222" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="226" priority="24">
+    <cfRule type="expression" dxfId="221" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="225" priority="23">
+    <cfRule type="expression" dxfId="220" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="224" priority="1">
+    <cfRule type="expression" dxfId="219" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="223" priority="7">
+    <cfRule type="expression" dxfId="218" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="222" priority="3">
+    <cfRule type="expression" dxfId="217" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="221" priority="14">
+    <cfRule type="expression" dxfId="216" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5860,47 +5810,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="220" priority="10">
+    <cfRule type="expression" dxfId="215" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="219" priority="1">
+    <cfRule type="expression" dxfId="214" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="218" priority="25">
+    <cfRule type="expression" dxfId="213" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="217" priority="24">
+    <cfRule type="expression" dxfId="212" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="216" priority="4">
+    <cfRule type="expression" dxfId="211" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="215" priority="3">
+    <cfRule type="expression" dxfId="210" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="214" priority="6">
+    <cfRule type="expression" dxfId="209" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="213" priority="9">
+    <cfRule type="expression" dxfId="208" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="212" priority="11">
+    <cfRule type="expression" dxfId="207" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6363,57 +6313,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="211" priority="36">
+    <cfRule type="expression" dxfId="206" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="210" priority="51">
+    <cfRule type="expression" dxfId="205" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="209" priority="50">
+    <cfRule type="expression" dxfId="204" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="208" priority="9">
+    <cfRule type="expression" dxfId="203" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="207" priority="28">
+    <cfRule type="expression" dxfId="202" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="206" priority="11">
+    <cfRule type="expression" dxfId="201" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="205" priority="24">
+    <cfRule type="expression" dxfId="200" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="204" priority="31">
+    <cfRule type="expression" dxfId="199" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="203" priority="7">
+    <cfRule type="expression" dxfId="198" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="202" priority="35">
+    <cfRule type="expression" dxfId="197" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="201" priority="1">
+    <cfRule type="expression" dxfId="196" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6845,59 +6795,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="200" priority="35">
+    <cfRule type="expression" dxfId="195" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="199" priority="42">
+    <cfRule type="expression" dxfId="194" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="198" priority="54">
+    <cfRule type="expression" dxfId="193" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="197" priority="53">
+    <cfRule type="expression" dxfId="192" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="196" priority="5">
+    <cfRule type="expression" dxfId="191" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="195" priority="30">
+    <cfRule type="expression" dxfId="190" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="194" priority="33">
+    <cfRule type="expression" dxfId="189" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="193" priority="37">
+    <cfRule type="expression" dxfId="188" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="192" priority="41">
+    <cfRule type="expression" dxfId="187" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="191" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="189" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="188" priority="1">
+    <cfRule type="expression" dxfId="183" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7363,57 +7313,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="187" priority="1">
+    <cfRule type="expression" dxfId="182" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="186" priority="18">
+    <cfRule type="expression" dxfId="181" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="185" priority="41">
+    <cfRule type="expression" dxfId="180" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="184" priority="40">
+    <cfRule type="expression" dxfId="179" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="183" priority="13">
+    <cfRule type="expression" dxfId="178" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="182" priority="3">
+    <cfRule type="expression" dxfId="177" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="181" priority="5">
+    <cfRule type="expression" dxfId="176" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="180" priority="19">
+    <cfRule type="expression" dxfId="175" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="179" priority="7">
+    <cfRule type="expression" dxfId="174" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="178" priority="27">
+    <cfRule type="expression" dxfId="173" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="177" priority="8">
+    <cfRule type="expression" dxfId="172" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7873,32 +7823,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="176" priority="21">
+    <cfRule type="expression" dxfId="171" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="175" priority="43">
+    <cfRule type="expression" dxfId="170" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="174" priority="42">
+    <cfRule type="expression" dxfId="169" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="173" priority="1">
+    <cfRule type="expression" dxfId="168" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="172" priority="16">
+    <cfRule type="expression" dxfId="167" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="171" priority="24">
+    <cfRule type="expression" dxfId="166" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8314,32 +8264,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="170" priority="30">
+    <cfRule type="expression" dxfId="165" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="169" priority="29">
+    <cfRule type="expression" dxfId="164" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="168" priority="16">
+    <cfRule type="expression" dxfId="163" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="167" priority="1">
+    <cfRule type="expression" dxfId="162" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="166" priority="4">
+    <cfRule type="expression" dxfId="161" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="165" priority="5">
+    <cfRule type="expression" dxfId="160" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8749,32 +8699,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="164" priority="39">
+    <cfRule type="expression" dxfId="159" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="163" priority="38">
+    <cfRule type="expression" dxfId="158" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="162" priority="20">
+    <cfRule type="expression" dxfId="157" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="161" priority="1">
+    <cfRule type="expression" dxfId="156" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="160" priority="3">
+    <cfRule type="expression" dxfId="155" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="159" priority="2">
+    <cfRule type="expression" dxfId="154" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9194,37 +9144,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="158" priority="18">
+    <cfRule type="expression" dxfId="153" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="157" priority="2">
+    <cfRule type="expression" dxfId="152" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="156" priority="32">
+    <cfRule type="expression" dxfId="151" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="155" priority="31">
+    <cfRule type="expression" dxfId="150" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="154" priority="5">
+    <cfRule type="expression" dxfId="149" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="153" priority="1">
+    <cfRule type="expression" dxfId="148" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="152" priority="3">
+    <cfRule type="expression" dxfId="147" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9640,22 +9590,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="290" priority="14">
+    <cfRule type="expression" dxfId="285" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="289" priority="6">
+    <cfRule type="expression" dxfId="284" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="288" priority="15">
+    <cfRule type="expression" dxfId="283" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="287" priority="1">
+    <cfRule type="expression" dxfId="282" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10055,22 +10005,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="151" priority="32">
+    <cfRule type="expression" dxfId="146" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="150" priority="31">
+    <cfRule type="expression" dxfId="145" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="149" priority="12">
+    <cfRule type="expression" dxfId="144" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="148" priority="1">
+    <cfRule type="expression" dxfId="143" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10436,22 +10386,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="147" priority="17">
+    <cfRule type="expression" dxfId="142" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="146" priority="16">
+    <cfRule type="expression" dxfId="141" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="145" priority="2">
+    <cfRule type="expression" dxfId="140" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="144" priority="1">
+    <cfRule type="expression" dxfId="139" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10460,6 +10410,438 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1003C9-1B1D-4C87-A4F1-C57BF5E9D303}">
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="6" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4">
+        <v>22</v>
+      </c>
+      <c r="D1" s="18">
+        <f>C1/Data!B2</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8">
+        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
+        <v>45705</v>
+      </c>
+      <c r="C3" s="8">
+        <f>B3+1</f>
+        <v>45706</v>
+      </c>
+      <c r="D3" s="8">
+        <f>C3+1</f>
+        <v>45707</v>
+      </c>
+      <c r="E3" s="8">
+        <f>D3+1</f>
+        <v>45708</v>
+      </c>
+      <c r="F3" s="8">
+        <f>E3+1</f>
+        <v>45709</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="H4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>0.54166666666666696</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D15" s="36"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="33"/>
+      <c r="F16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+    </row>
+    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+    </row>
+    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+    </row>
+    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+    </row>
+    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+    </row>
+    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+    </row>
+    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+    </row>
+    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+    </row>
+    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4 F5:F14 B15:B25">
+    <cfRule type="expression" dxfId="129" priority="10">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="128" priority="27">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
+    <cfRule type="expression" dxfId="127" priority="26">
+      <formula>B3 = TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="126" priority="25">
+      <formula>NOT(ISBLANK(B28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C25">
+    <cfRule type="expression" dxfId="125" priority="6">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:D15">
+    <cfRule type="expression" dxfId="124" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E25">
+    <cfRule type="expression" dxfId="123" priority="7">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:F25">
+    <cfRule type="expression" dxfId="122" priority="22">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H19 J17:J21">
+    <cfRule type="expression" dxfId="121" priority="28">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5250EE95-0BED-45B5-9E71-085C4126A053}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10851,484 +11233,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="143" priority="28">
+    <cfRule type="expression" dxfId="138" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="142" priority="27">
+    <cfRule type="expression" dxfId="137" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="141" priority="26">
+    <cfRule type="expression" dxfId="136" priority="26">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="140" priority="6">
+    <cfRule type="expression" dxfId="135" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D11:D15">
-    <cfRule type="expression" dxfId="139" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="138" priority="8">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 B5:B25">
-    <cfRule type="expression" dxfId="137" priority="14">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="136" priority="23">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="135" priority="29">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D10">
+  <conditionalFormatting sqref="D5:D15">
     <cfRule type="expression" dxfId="134" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1003C9-1B1D-4C87-A4F1-C57BF5E9D303}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="6" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4">
-        <v>22</v>
-      </c>
-      <c r="D1" s="18">
-        <f>C1/Data!B2</f>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="8">
-        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
-        <v>45705</v>
-      </c>
-      <c r="C3" s="8">
-        <f>B3+1</f>
-        <v>45706</v>
-      </c>
-      <c r="D3" s="8">
-        <f>C3+1</f>
-        <v>45707</v>
-      </c>
-      <c r="E3" s="8">
-        <f>D3+1</f>
-        <v>45708</v>
-      </c>
-      <c r="F3" s="8">
-        <f>E3+1</f>
-        <v>45709</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="E4" s="33"/>
-      <c r="H4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>0.4375</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>0.45833333333333398</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>0.53125</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>0.54166666666666696</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>0.5625</v>
-      </c>
-      <c r="D15" s="36"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-    </row>
-    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-    </row>
-    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-    </row>
-    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-    </row>
-    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-    </row>
-    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-    </row>
-    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-    </row>
-    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-    </row>
-    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B4 F5:F14 B15:B25 D9:D13 D15">
-    <cfRule type="expression" dxfId="133" priority="10">
+  <conditionalFormatting sqref="E6:E25">
+    <cfRule type="expression" dxfId="133" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="132" priority="27">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="131" priority="26">
-      <formula>B3 = TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="130" priority="25">
-      <formula>NOT(ISBLANK(B28))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="129" priority="6">
+  <conditionalFormatting sqref="F5:F14 B5:B25">
+    <cfRule type="expression" dxfId="132" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="128" priority="7">
+  <conditionalFormatting sqref="F16:F25">
+    <cfRule type="expression" dxfId="131" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="127" priority="22">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="126" priority="28">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="130" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11724,47 +11669,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="125" priority="23">
+    <cfRule type="expression" dxfId="120" priority="23">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="124" priority="22">
+    <cfRule type="expression" dxfId="119" priority="22">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="123" priority="21">
+    <cfRule type="expression" dxfId="118" priority="21">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="122" priority="2">
+    <cfRule type="expression" dxfId="117" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="121" priority="24">
+    <cfRule type="expression" dxfId="116" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="120" priority="1">
+    <cfRule type="expression" dxfId="115" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="119" priority="4">
+    <cfRule type="expression" dxfId="114" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B5:B25">
-    <cfRule type="expression" dxfId="118" priority="14">
+    <cfRule type="expression" dxfId="113" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="117" priority="18">
+    <cfRule type="expression" dxfId="112" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12155,52 +12100,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="116" priority="9">
+    <cfRule type="expression" dxfId="111" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="115" priority="18">
+    <cfRule type="expression" dxfId="110" priority="18">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="114" priority="17">
+    <cfRule type="expression" dxfId="109" priority="17">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="113" priority="16">
+    <cfRule type="expression" dxfId="108" priority="16">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="112" priority="3">
+    <cfRule type="expression" dxfId="107" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="111" priority="2">
+  <conditionalFormatting sqref="D9:D15">
+    <cfRule type="expression" dxfId="106" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="110" priority="4">
+    <cfRule type="expression" dxfId="105" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="109" priority="13">
+    <cfRule type="expression" dxfId="104" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="108" priority="19">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="103" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12590,47 +12530,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="107" priority="23">
+    <cfRule type="expression" dxfId="102" priority="23">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="106" priority="22">
+    <cfRule type="expression" dxfId="101" priority="22">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="105" priority="21">
+    <cfRule type="expression" dxfId="100" priority="21">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="104" priority="1">
+    <cfRule type="expression" dxfId="99" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="103" priority="24">
+    <cfRule type="expression" dxfId="98" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="102" priority="17">
+    <cfRule type="expression" dxfId="97" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="101" priority="3">
+    <cfRule type="expression" dxfId="96" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B5:B25">
-    <cfRule type="expression" dxfId="100" priority="14">
+    <cfRule type="expression" dxfId="95" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="99" priority="18">
+    <cfRule type="expression" dxfId="94" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13019,52 +12959,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="98" priority="7">
+    <cfRule type="expression" dxfId="93" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="97" priority="18">
+    <cfRule type="expression" dxfId="92" priority="18">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="96" priority="17">
+    <cfRule type="expression" dxfId="91" priority="17">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="95" priority="16">
+    <cfRule type="expression" dxfId="90" priority="16">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="94" priority="2">
+    <cfRule type="expression" dxfId="89" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="93" priority="19">
+    <cfRule type="expression" dxfId="88" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="92" priority="12">
+  <conditionalFormatting sqref="D9:D14">
+    <cfRule type="expression" dxfId="87" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="91" priority="3">
+    <cfRule type="expression" dxfId="86" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="90" priority="13">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="85" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13454,47 +13389,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="89" priority="21">
+    <cfRule type="expression" dxfId="84" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="88" priority="20">
+    <cfRule type="expression" dxfId="83" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="87" priority="19">
+    <cfRule type="expression" dxfId="82" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="86" priority="1">
+    <cfRule type="expression" dxfId="81" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="85" priority="22">
+    <cfRule type="expression" dxfId="80" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="84" priority="15">
+    <cfRule type="expression" dxfId="79" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="83" priority="3">
+    <cfRule type="expression" dxfId="78" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B5:B25">
-    <cfRule type="expression" dxfId="82" priority="13">
+    <cfRule type="expression" dxfId="77" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="81" priority="16">
+    <cfRule type="expression" dxfId="76" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13890,32 +13825,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F6 E7:F25 B15:D25">
-    <cfRule type="expression" dxfId="80" priority="4">
+    <cfRule type="expression" dxfId="75" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="79" priority="18">
+    <cfRule type="expression" dxfId="74" priority="18">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="78" priority="17">
+    <cfRule type="expression" dxfId="73" priority="17">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="77" priority="16">
+    <cfRule type="expression" dxfId="72" priority="16">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="76" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="75" priority="13">
+    <cfRule type="expression" dxfId="70" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14319,30 +14254,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="286" priority="3">
+    <cfRule type="expression" dxfId="281" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="285" priority="14">
+    <cfRule type="expression" dxfId="280" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="284" priority="15">
+    <cfRule type="expression" dxfId="279" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="283" priority="7">
+    <cfRule type="expression" dxfId="278" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="282" priority="9">
+    <cfRule type="expression" dxfId="277" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="281" priority="12">
+    <cfRule type="expression" dxfId="276" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14757,22 +14692,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D6 F5:F6 E6:E7 B7:F25">
-    <cfRule type="expression" dxfId="74" priority="1">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="73" priority="16">
+    <cfRule type="expression" dxfId="68" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="72" priority="15">
+    <cfRule type="expression" dxfId="67" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="71" priority="14">
+    <cfRule type="expression" dxfId="66" priority="14">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15185,22 +15120,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="70" priority="21">
+    <cfRule type="expression" dxfId="65" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="69" priority="20">
+    <cfRule type="expression" dxfId="64" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="68" priority="6">
+    <cfRule type="expression" dxfId="63" priority="6">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 B4:C13 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15586,37 +15521,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="66" priority="2">
+    <cfRule type="expression" dxfId="61" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="65" priority="24">
+    <cfRule type="expression" dxfId="60" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="64" priority="23">
+    <cfRule type="expression" dxfId="59" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="63" priority="22">
+    <cfRule type="expression" dxfId="58" priority="22">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="62" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="60" priority="7">
+    <cfRule type="expression" dxfId="55" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15978,38 +15913,33 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D8 B14:D25 B9:C13">
-    <cfRule type="expression" dxfId="59" priority="2">
+  <conditionalFormatting sqref="B4:D25">
+    <cfRule type="expression" dxfId="54" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="58" priority="29">
+    <cfRule type="expression" dxfId="53" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="57" priority="28">
+    <cfRule type="expression" dxfId="52" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="56" priority="27">
+    <cfRule type="expression" dxfId="51" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="55" priority="7">
+    <cfRule type="expression" dxfId="50" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="54" priority="4">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="49" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16414,32 +16344,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="53" priority="24">
+    <cfRule type="expression" dxfId="48" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="52" priority="31">
+    <cfRule type="expression" dxfId="47" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="51" priority="30">
+    <cfRule type="expression" dxfId="46" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="50" priority="29">
+    <cfRule type="expression" dxfId="45" priority="29">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="49" priority="1">
+    <cfRule type="expression" dxfId="44" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="48" priority="23">
+    <cfRule type="expression" dxfId="43" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16843,42 +16773,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="47" priority="27">
+    <cfRule type="expression" dxfId="42" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="46" priority="34">
+    <cfRule type="expression" dxfId="41" priority="34">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="45" priority="33">
+    <cfRule type="expression" dxfId="40" priority="33">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="44" priority="32">
+    <cfRule type="expression" dxfId="39" priority="32">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 C14:D14 C9:C13">
-    <cfRule type="expression" dxfId="43" priority="2">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="42" priority="4">
+    <cfRule type="expression" dxfId="37" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="41" priority="26">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="36" priority="26">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17285,37 +17210,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="40" priority="15">
+    <cfRule type="expression" dxfId="35" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="39" priority="14">
+    <cfRule type="expression" dxfId="34" priority="14">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="38" priority="13">
+    <cfRule type="expression" dxfId="33" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="37" priority="1">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="36" priority="4">
+    <cfRule type="expression" dxfId="31" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B5:B14 B15:D25">
-    <cfRule type="expression" dxfId="35" priority="11">
+    <cfRule type="expression" dxfId="30" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="34" priority="10">
+    <cfRule type="expression" dxfId="29" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17725,32 +17650,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="33" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="32" priority="16">
+    <cfRule type="expression" dxfId="27" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="31" priority="15">
+    <cfRule type="expression" dxfId="26" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="30" priority="14">
+    <cfRule type="expression" dxfId="25" priority="14">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="29" priority="5">
+    <cfRule type="expression" dxfId="24" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="28" priority="11">
+    <cfRule type="expression" dxfId="23" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18156,32 +18081,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="26" priority="16">
+    <cfRule type="expression" dxfId="21" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="25" priority="15">
+    <cfRule type="expression" dxfId="20" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="24" priority="14">
+    <cfRule type="expression" dxfId="19" priority="14">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="23" priority="5">
+    <cfRule type="expression" dxfId="18" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="22" priority="11">
+    <cfRule type="expression" dxfId="17" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18597,32 +18522,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="20" priority="16">
+    <cfRule type="expression" dxfId="15" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="19" priority="15">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="18" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="17" priority="5">
+    <cfRule type="expression" dxfId="12" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="16" priority="11">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19047,22 +18972,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="280" priority="10">
+    <cfRule type="expression" dxfId="275" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="279" priority="9">
+    <cfRule type="expression" dxfId="274" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="278" priority="1">
+    <cfRule type="expression" dxfId="273" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="277" priority="7">
+    <cfRule type="expression" dxfId="272" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19479,32 +19404,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="9" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="8" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="12" priority="14">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="5" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19916,27 +19841,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="8" priority="16">
+    <cfRule type="expression" dxfId="3" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="7" priority="15">
+    <cfRule type="expression" dxfId="2" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="6" priority="14">
+    <cfRule type="expression" dxfId="1" priority="14">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20381,42 +20306,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="276" priority="15">
+    <cfRule type="expression" dxfId="271" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="275" priority="13">
+    <cfRule type="expression" dxfId="270" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="274" priority="30">
+    <cfRule type="expression" dxfId="269" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="273" priority="29">
+    <cfRule type="expression" dxfId="268" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="272" priority="7">
+    <cfRule type="expression" dxfId="267" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="271" priority="24">
+    <cfRule type="expression" dxfId="266" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="270" priority="20">
+    <cfRule type="expression" dxfId="265" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="269" priority="25">
+    <cfRule type="expression" dxfId="264" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20817,32 +20742,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="268" priority="8">
+    <cfRule type="expression" dxfId="263" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="267" priority="13">
+    <cfRule type="expression" dxfId="262" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="266" priority="12">
+    <cfRule type="expression" dxfId="261" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="265" priority="1">
+    <cfRule type="expression" dxfId="260" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="264" priority="4">
+    <cfRule type="expression" dxfId="259" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="263" priority="7">
+    <cfRule type="expression" dxfId="258" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21226,52 +21151,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="262" priority="22">
+    <cfRule type="expression" dxfId="257" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="261" priority="23">
+    <cfRule type="expression" dxfId="256" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="260" priority="45">
+    <cfRule type="expression" dxfId="255" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="259" priority="44">
+    <cfRule type="expression" dxfId="254" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="258" priority="1">
+    <cfRule type="expression" dxfId="253" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="257" priority="35">
+    <cfRule type="expression" dxfId="252" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="256" priority="36">
+    <cfRule type="expression" dxfId="251" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="255" priority="16">
+    <cfRule type="expression" dxfId="250" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="254" priority="34">
+    <cfRule type="expression" dxfId="249" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="253" priority="5">
+    <cfRule type="expression" dxfId="248" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21684,47 +21609,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="252" priority="16">
+    <cfRule type="expression" dxfId="247" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="251" priority="19">
+    <cfRule type="expression" dxfId="246" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="250" priority="18">
+    <cfRule type="expression" dxfId="245" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="249" priority="1">
+    <cfRule type="expression" dxfId="244" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="248" priority="15">
+    <cfRule type="expression" dxfId="243" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="247" priority="12">
+    <cfRule type="expression" dxfId="242" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="246" priority="11">
+    <cfRule type="expression" dxfId="241" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="245" priority="14">
+    <cfRule type="expression" dxfId="240" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="244" priority="5">
+    <cfRule type="expression" dxfId="239" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22147,32 +22072,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="243" priority="2">
+    <cfRule type="expression" dxfId="238" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="242" priority="4">
+    <cfRule type="expression" dxfId="237" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="241" priority="16">
+    <cfRule type="expression" dxfId="236" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="240" priority="15">
+    <cfRule type="expression" dxfId="235" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="239" priority="1">
+    <cfRule type="expression" dxfId="234" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="238" priority="7">
+    <cfRule type="expression" dxfId="233" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20F817A-035B-4939-8602-0BD953CB0032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A309E3-7CBA-455E-BF47-86B6C72096E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -34,8 +34,8 @@
     <sheet name="Week 18" sheetId="22" r:id="rId19"/>
     <sheet name="Week 19" sheetId="23" r:id="rId20"/>
     <sheet name="Week 20" sheetId="24" r:id="rId21"/>
-    <sheet name="Week 22" sheetId="26" r:id="rId22"/>
-    <sheet name="Week 21" sheetId="25" r:id="rId23"/>
+    <sheet name="Week 21" sheetId="25" r:id="rId22"/>
+    <sheet name="Week 22" sheetId="26" r:id="rId23"/>
     <sheet name="Week 23" sheetId="27" r:id="rId24"/>
     <sheet name="Week 24" sheetId="28" r:id="rId25"/>
     <sheet name="Week 25" sheetId="29" r:id="rId26"/>
@@ -2659,6 +2659,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2733,46 +2743,36 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -10410,6 +10410,446 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5250EE95-0BED-45B5-9E71-085C4126A053}">
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="6" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4">
+        <v>21</v>
+      </c>
+      <c r="D1" s="18">
+        <f>C1/Data!B2</f>
+        <v>0.52500000000000002</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8">
+        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
+        <v>45698</v>
+      </c>
+      <c r="C3" s="8">
+        <f>B3+1</f>
+        <v>45699</v>
+      </c>
+      <c r="D3" s="8">
+        <f>C3+1</f>
+        <v>45700</v>
+      </c>
+      <c r="E3" s="8">
+        <f>D3+1</f>
+        <v>45701</v>
+      </c>
+      <c r="F3" s="8">
+        <f>E3+1</f>
+        <v>45702</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="E7" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="5"/>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="D14" s="35"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D15" s="36"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="F29" s="17"/>
+    </row>
+    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+    </row>
+    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+    </row>
+    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+    </row>
+    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+    </row>
+    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+    </row>
+    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+    </row>
+    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="129" priority="28">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
+    <cfRule type="expression" dxfId="128" priority="27">
+      <formula>B3 = TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="127" priority="26">
+      <formula>NOT(ISBLANK(B28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C25">
+    <cfRule type="expression" dxfId="126" priority="6">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D15">
+    <cfRule type="expression" dxfId="125" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E25">
+    <cfRule type="expression" dxfId="124" priority="8">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F14 B5:B25">
+    <cfRule type="expression" dxfId="123" priority="14">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:F25">
+    <cfRule type="expression" dxfId="122" priority="23">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H19 J17:J21">
+    <cfRule type="expression" dxfId="121" priority="29">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1003C9-1B1D-4C87-A4F1-C57BF5E9D303}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10793,487 +11233,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="129" priority="10">
+    <cfRule type="expression" dxfId="138" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="128" priority="27">
+    <cfRule type="expression" dxfId="137" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="127" priority="26">
+    <cfRule type="expression" dxfId="136" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="126" priority="25">
+    <cfRule type="expression" dxfId="135" priority="25">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="125" priority="6">
+    <cfRule type="expression" dxfId="134" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="124" priority="1">
+    <cfRule type="expression" dxfId="133" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="123" priority="7">
+    <cfRule type="expression" dxfId="132" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="122" priority="22">
+    <cfRule type="expression" dxfId="131" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="121" priority="28">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5250EE95-0BED-45B5-9E71-085C4126A053}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="6" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4">
-        <v>21</v>
-      </c>
-      <c r="D1" s="18">
-        <f>C1/Data!B2</f>
-        <v>0.52500000000000002</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="8">
-        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
-        <v>45698</v>
-      </c>
-      <c r="C3" s="8">
-        <f>B3+1</f>
-        <v>45699</v>
-      </c>
-      <c r="D3" s="8">
-        <f>C3+1</f>
-        <v>45700</v>
-      </c>
-      <c r="E3" s="8">
-        <f>D3+1</f>
-        <v>45701</v>
-      </c>
-      <c r="F3" s="8">
-        <f>E3+1</f>
-        <v>45702</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>0.4375</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="5"/>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>0.45833333333333398</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>0.53125</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="D14" s="35"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>0.5625</v>
-      </c>
-      <c r="D15" s="36"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="F29" s="17"/>
-    </row>
-    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-    </row>
-    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-    </row>
-    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-    </row>
-    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-    </row>
-    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-    </row>
-    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-    </row>
-    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="138" priority="28">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="137" priority="27">
-      <formula>B3 = TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="136" priority="26">
-      <formula>NOT(ISBLANK(B28))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="135" priority="6">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D15">
-    <cfRule type="expression" dxfId="134" priority="1">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="133" priority="8">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 B5:B25">
-    <cfRule type="expression" dxfId="132" priority="14">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="131" priority="23">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="130" priority="29">
+    <cfRule type="expression" dxfId="130" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A309E3-7CBA-455E-BF47-86B6C72096E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76FF003-5A5F-495F-BC86-410AEE1528AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="368">
   <si>
     <t>Week</t>
   </si>
@@ -1184,6 +1184,21 @@
   </si>
   <si>
     <t>Inhaalmoment presentaties</t>
+  </si>
+  <si>
+    <t>Ter beken (Ham)</t>
+  </si>
+  <si>
+    <t>Lokaal C114</t>
+  </si>
+  <si>
+    <t>CM: Bookmaking</t>
+  </si>
+  <si>
+    <t>CM: Illu-foto (basis)</t>
+  </si>
+  <si>
+    <t>Lokaal D303</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1387,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1493,6 +1508,9 @@
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="8" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="5" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="20% - Accent2" xfId="3" builtinId="34"/>
@@ -1505,7 +1523,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="286">
+  <dxfs count="343">
     <dxf>
       <font>
         <color theme="1"/>
@@ -1517,6 +1535,436 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1571,6 +2019,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1625,6 +2083,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1679,6 +2147,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1733,6 +2211,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1807,6 +2295,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1861,6 +2359,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -1915,6 +2423,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2077,6 +2595,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2101,6 +2629,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2249,6 +2787,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2417,6 +2965,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2585,6 +3143,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2659,6 +3227,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2669,6 +3261,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2677,6 +3279,73 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
       </font>
@@ -2689,90 +3358,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4837,47 +5422,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="232" priority="17">
+    <cfRule type="expression" dxfId="289" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="231" priority="25">
+    <cfRule type="expression" dxfId="288" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="230" priority="24">
+    <cfRule type="expression" dxfId="287" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="229" priority="5">
+    <cfRule type="expression" dxfId="286" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="228" priority="9">
+    <cfRule type="expression" dxfId="285" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="227" priority="8">
+    <cfRule type="expression" dxfId="284" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="226" priority="11">
+    <cfRule type="expression" dxfId="283" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="225" priority="15">
+    <cfRule type="expression" dxfId="282" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="224" priority="2">
+    <cfRule type="expression" dxfId="281" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5336,42 +5921,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="223" priority="15">
+    <cfRule type="expression" dxfId="280" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="222" priority="10">
+    <cfRule type="expression" dxfId="279" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="221" priority="24">
+    <cfRule type="expression" dxfId="278" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="220" priority="23">
+    <cfRule type="expression" dxfId="277" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="219" priority="1">
+    <cfRule type="expression" dxfId="276" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="218" priority="7">
+    <cfRule type="expression" dxfId="275" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="217" priority="3">
+    <cfRule type="expression" dxfId="274" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="216" priority="14">
+    <cfRule type="expression" dxfId="273" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5810,47 +6395,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="215" priority="10">
+    <cfRule type="expression" dxfId="272" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="214" priority="1">
+    <cfRule type="expression" dxfId="271" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="213" priority="25">
+    <cfRule type="expression" dxfId="270" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="212" priority="24">
+    <cfRule type="expression" dxfId="269" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="211" priority="4">
+    <cfRule type="expression" dxfId="268" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="210" priority="3">
+    <cfRule type="expression" dxfId="267" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="209" priority="6">
+    <cfRule type="expression" dxfId="266" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="208" priority="9">
+    <cfRule type="expression" dxfId="265" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="207" priority="11">
+    <cfRule type="expression" dxfId="264" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6313,57 +6898,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="206" priority="36">
+    <cfRule type="expression" dxfId="263" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="205" priority="51">
+    <cfRule type="expression" dxfId="262" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="204" priority="50">
+    <cfRule type="expression" dxfId="261" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="203" priority="9">
+    <cfRule type="expression" dxfId="260" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="202" priority="28">
+    <cfRule type="expression" dxfId="259" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="201" priority="11">
+    <cfRule type="expression" dxfId="258" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="200" priority="24">
+    <cfRule type="expression" dxfId="257" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="199" priority="31">
+    <cfRule type="expression" dxfId="256" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="198" priority="7">
+    <cfRule type="expression" dxfId="255" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="197" priority="35">
+    <cfRule type="expression" dxfId="254" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="196" priority="1">
+    <cfRule type="expression" dxfId="253" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6795,59 +7380,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="195" priority="35">
+    <cfRule type="expression" dxfId="252" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="194" priority="42">
+    <cfRule type="expression" dxfId="251" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="193" priority="54">
+    <cfRule type="expression" dxfId="250" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="192" priority="53">
+    <cfRule type="expression" dxfId="249" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="191" priority="5">
+    <cfRule type="expression" dxfId="248" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="190" priority="30">
+    <cfRule type="expression" dxfId="247" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="189" priority="33">
+    <cfRule type="expression" dxfId="246" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="188" priority="37">
+    <cfRule type="expression" dxfId="245" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="187" priority="41">
+    <cfRule type="expression" dxfId="244" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="186" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="184" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="183" priority="1">
+    <cfRule type="expression" dxfId="240" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7313,57 +7898,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="182" priority="1">
+    <cfRule type="expression" dxfId="239" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="181" priority="18">
+    <cfRule type="expression" dxfId="238" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="180" priority="41">
+    <cfRule type="expression" dxfId="237" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="179" priority="40">
+    <cfRule type="expression" dxfId="236" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="178" priority="13">
+    <cfRule type="expression" dxfId="235" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="177" priority="3">
+    <cfRule type="expression" dxfId="234" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="176" priority="5">
+    <cfRule type="expression" dxfId="233" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="175" priority="19">
+    <cfRule type="expression" dxfId="232" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="174" priority="7">
+    <cfRule type="expression" dxfId="231" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="173" priority="27">
+    <cfRule type="expression" dxfId="230" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="172" priority="8">
+    <cfRule type="expression" dxfId="229" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7823,32 +8408,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="171" priority="21">
+    <cfRule type="expression" dxfId="228" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="170" priority="43">
+    <cfRule type="expression" dxfId="227" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="169" priority="42">
+    <cfRule type="expression" dxfId="226" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="168" priority="1">
+    <cfRule type="expression" dxfId="225" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="167" priority="16">
+    <cfRule type="expression" dxfId="224" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="166" priority="24">
+    <cfRule type="expression" dxfId="223" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8264,32 +8849,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="165" priority="30">
+    <cfRule type="expression" dxfId="222" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="164" priority="29">
+    <cfRule type="expression" dxfId="221" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="163" priority="16">
+    <cfRule type="expression" dxfId="220" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="1">
+    <cfRule type="expression" dxfId="219" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="161" priority="4">
+    <cfRule type="expression" dxfId="218" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="160" priority="5">
+    <cfRule type="expression" dxfId="217" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8699,32 +9284,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="159" priority="39">
+    <cfRule type="expression" dxfId="216" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="158" priority="38">
+    <cfRule type="expression" dxfId="215" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="157" priority="20">
+    <cfRule type="expression" dxfId="214" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="156" priority="1">
+    <cfRule type="expression" dxfId="213" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="155" priority="3">
+    <cfRule type="expression" dxfId="212" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="154" priority="2">
+    <cfRule type="expression" dxfId="211" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9144,37 +9729,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="153" priority="18">
+    <cfRule type="expression" dxfId="210" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="152" priority="2">
+    <cfRule type="expression" dxfId="209" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="151" priority="32">
+    <cfRule type="expression" dxfId="208" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="150" priority="31">
+    <cfRule type="expression" dxfId="207" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="149" priority="5">
+    <cfRule type="expression" dxfId="206" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="148" priority="1">
+    <cfRule type="expression" dxfId="205" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="147" priority="3">
+    <cfRule type="expression" dxfId="204" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9590,22 +10175,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="285" priority="14">
+    <cfRule type="expression" dxfId="342" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="284" priority="6">
+    <cfRule type="expression" dxfId="341" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="283" priority="15">
+    <cfRule type="expression" dxfId="340" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="282" priority="1">
+    <cfRule type="expression" dxfId="339" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9937,9 +10522,7 @@
       <c r="C30" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>347</v>
-      </c>
+      <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>
@@ -10005,22 +10588,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="146" priority="32">
+    <cfRule type="expression" dxfId="203" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="145" priority="31">
+    <cfRule type="expression" dxfId="202" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="144" priority="12">
+    <cfRule type="expression" dxfId="201" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="143" priority="1">
+    <cfRule type="expression" dxfId="200" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10386,22 +10969,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="142" priority="17">
+    <cfRule type="expression" dxfId="199" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="141" priority="16">
+    <cfRule type="expression" dxfId="198" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="140" priority="2">
+    <cfRule type="expression" dxfId="197" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="139" priority="1">
+    <cfRule type="expression" dxfId="196" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10483,8 +11066,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10494,6 +11080,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -10506,8 +11095,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -10520,6 +11110,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -10534,6 +11125,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -10548,6 +11140,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -10556,6 +11151,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -10564,6 +11162,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -10572,6 +11171,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -10580,6 +11180,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -10735,7 +11336,9 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="16" t="s">
+        <v>347</v>
+      </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17" t="s">
@@ -10801,47 +11404,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="129" priority="28">
+    <cfRule type="expression" dxfId="195" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="128" priority="27">
+    <cfRule type="expression" dxfId="194" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="127" priority="26">
+  <conditionalFormatting sqref="B28:F28 B30:F36 C29:F29">
+    <cfRule type="expression" dxfId="193" priority="28">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="126" priority="6">
+    <cfRule type="expression" dxfId="192" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D15">
-    <cfRule type="expression" dxfId="125" priority="1">
+  <conditionalFormatting sqref="D14:D15">
+    <cfRule type="expression" dxfId="191" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="124" priority="8">
+    <cfRule type="expression" dxfId="190" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B5:B25">
-    <cfRule type="expression" dxfId="123" priority="14">
+    <cfRule type="expression" dxfId="189" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="122" priority="23">
+    <cfRule type="expression" dxfId="188" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="121" priority="29">
+    <cfRule type="expression" dxfId="187" priority="31">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="expression" dxfId="186" priority="2">
+      <formula>NOT(ISBLANK(B29))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="185" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10923,15 +11536,21 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -10944,6 +11563,7 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -10952,6 +11572,7 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="C7" s="28"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -10962,6 +11583,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="C8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -10974,6 +11596,9 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
       </c>
@@ -10984,6 +11609,9 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>357</v>
       </c>
@@ -10994,6 +11622,7 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
         <v>358</v>
       </c>
@@ -11004,6 +11633,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="C12" s="28"/>
       <c r="D12" s="5"/>
       <c r="E12" s="36"/>
       <c r="F12" s="5"/>
@@ -11012,6 +11642,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="C13" s="28"/>
       <c r="D13" s="5"/>
       <c r="E13" s="36"/>
       <c r="F13" s="5"/>
@@ -11233,47 +11864,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="138" priority="10">
+    <cfRule type="expression" dxfId="184" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="137" priority="27">
+    <cfRule type="expression" dxfId="183" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="136" priority="26">
+    <cfRule type="expression" dxfId="182" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="135" priority="25">
+    <cfRule type="expression" dxfId="181" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="134" priority="6">
+  <conditionalFormatting sqref="C14:C25">
+    <cfRule type="expression" dxfId="180" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="133" priority="1">
+    <cfRule type="expression" dxfId="179" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="132" priority="7">
+    <cfRule type="expression" dxfId="178" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="131" priority="22">
+    <cfRule type="expression" dxfId="177" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="130" priority="28">
+    <cfRule type="expression" dxfId="176" priority="30">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="41" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="40" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11355,8 +11996,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11366,6 +12010,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -11378,8 +12025,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -11392,6 +12040,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -11406,6 +12055,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="33"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
@@ -11421,6 +12071,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="D9" s="34"/>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -11430,6 +12083,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -11438,6 +12094,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -11446,6 +12103,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -11454,6 +12112,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="35"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
@@ -11669,47 +12328,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="120" priority="23">
+    <cfRule type="expression" dxfId="175" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="119" priority="22">
+    <cfRule type="expression" dxfId="174" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="118" priority="21">
+    <cfRule type="expression" dxfId="173" priority="24">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="117" priority="2">
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" dxfId="172" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="116" priority="24">
+    <cfRule type="expression" dxfId="171" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="115" priority="1">
+    <cfRule type="expression" dxfId="170" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="114" priority="4">
+    <cfRule type="expression" dxfId="169" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F13 B5:B25">
-    <cfRule type="expression" dxfId="113" priority="14">
+  <conditionalFormatting sqref="F5:F13 B5 B7:B25">
+    <cfRule type="expression" dxfId="168" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="112" priority="18">
+    <cfRule type="expression" dxfId="167" priority="21">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="166" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="37" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11791,15 +12465,21 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -11812,6 +12492,7 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -11820,6 +12501,7 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="C7" s="28"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -11830,6 +12512,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="C8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -11842,6 +12525,9 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
       </c>
@@ -11852,6 +12538,9 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>357</v>
       </c>
@@ -11862,6 +12551,7 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
         <v>359</v>
       </c>
@@ -11872,6 +12562,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="C12" s="28"/>
       <c r="D12" s="5"/>
       <c r="E12" s="36"/>
       <c r="F12" s="5"/>
@@ -11880,6 +12571,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="C13" s="28"/>
       <c r="D13" s="5"/>
       <c r="E13" s="36"/>
       <c r="F13" s="5"/>
@@ -12100,47 +12792,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="111" priority="9">
+    <cfRule type="expression" dxfId="165" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="110" priority="18">
+    <cfRule type="expression" dxfId="164" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="109" priority="17">
+    <cfRule type="expression" dxfId="163" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="108" priority="16">
+    <cfRule type="expression" dxfId="162" priority="18">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="107" priority="3">
+  <conditionalFormatting sqref="C14:C25">
+    <cfRule type="expression" dxfId="161" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="106" priority="1">
+    <cfRule type="expression" dxfId="160" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="105" priority="4">
+    <cfRule type="expression" dxfId="159" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="104" priority="13">
+    <cfRule type="expression" dxfId="158" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="103" priority="19">
+    <cfRule type="expression" dxfId="157" priority="21">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="39" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="38" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12222,8 +12924,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -12233,6 +12938,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -12245,8 +12953,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -12259,6 +12968,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -12273,6 +12983,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -12287,6 +12998,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -12295,6 +13009,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -12303,6 +13020,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -12311,6 +13029,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -12319,6 +13038,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -12530,47 +13250,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="102" priority="23">
+    <cfRule type="expression" dxfId="156" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="155" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="100" priority="21">
+    <cfRule type="expression" dxfId="154" priority="24">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="99" priority="1">
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" dxfId="153" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="98" priority="24">
+    <cfRule type="expression" dxfId="152" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="97" priority="17">
+    <cfRule type="expression" dxfId="151" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="96" priority="3">
+    <cfRule type="expression" dxfId="150" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 B5:B25">
-    <cfRule type="expression" dxfId="95" priority="14">
+  <conditionalFormatting sqref="F5:F14 B5 B7:B25">
+    <cfRule type="expression" dxfId="149" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="94" priority="18">
+    <cfRule type="expression" dxfId="148" priority="21">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="147" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="35" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12652,15 +13387,21 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -12673,6 +13414,7 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -12681,6 +13423,7 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="C7" s="28"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -12691,6 +13434,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="C8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -12703,6 +13447,9 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
       </c>
@@ -12713,6 +13460,9 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>357</v>
       </c>
@@ -12723,6 +13473,7 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
         <v>360</v>
       </c>
@@ -12733,6 +13484,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="C12" s="28"/>
       <c r="D12" s="5"/>
       <c r="E12" s="36"/>
       <c r="F12" s="5"/>
@@ -12741,6 +13493,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="C13" s="28"/>
       <c r="D13" s="5"/>
       <c r="E13" s="36"/>
       <c r="F13" s="5"/>
@@ -12959,47 +13712,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="93" priority="7">
+    <cfRule type="expression" dxfId="146" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="92" priority="18">
+    <cfRule type="expression" dxfId="145" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="91" priority="17">
+    <cfRule type="expression" dxfId="144" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="90" priority="16">
+    <cfRule type="expression" dxfId="143" priority="18">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="89" priority="2">
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" dxfId="142" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="88" priority="19">
+    <cfRule type="expression" dxfId="141" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="87" priority="1">
+    <cfRule type="expression" dxfId="140" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="86" priority="3">
+    <cfRule type="expression" dxfId="139" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="85" priority="13">
+    <cfRule type="expression" dxfId="138" priority="15">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="33" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="32" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13081,8 +13844,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -13092,6 +13858,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -13104,8 +13873,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -13118,6 +13888,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -13132,6 +13903,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -13146,6 +13918,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -13154,6 +13929,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -13162,6 +13940,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -13170,6 +13949,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -13178,6 +13958,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -13389,47 +14170,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="84" priority="21">
+    <cfRule type="expression" dxfId="137" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="83" priority="20">
+    <cfRule type="expression" dxfId="136" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="82" priority="19">
+    <cfRule type="expression" dxfId="135" priority="22">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="81" priority="1">
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" dxfId="134" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="80" priority="22">
+    <cfRule type="expression" dxfId="133" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="79" priority="15">
+    <cfRule type="expression" dxfId="132" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="78" priority="3">
+    <cfRule type="expression" dxfId="131" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F13 B5:B25">
-    <cfRule type="expression" dxfId="77" priority="13">
+  <conditionalFormatting sqref="F5:F13 B5 B7:B25">
+    <cfRule type="expression" dxfId="130" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="76" priority="16">
+    <cfRule type="expression" dxfId="129" priority="19">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="128" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="31" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13511,14 +14307,20 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -13530,6 +14332,7 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -13541,6 +14344,7 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -13554,6 +14358,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -13567,6 +14372,9 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -13574,6 +14382,9 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -13581,6 +14392,7 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -13588,6 +14400,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -13595,6 +14408,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -13825,32 +14639,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F6 E7:F25 B15:D25">
-    <cfRule type="expression" dxfId="75" priority="4">
+    <cfRule type="expression" dxfId="127" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="74" priority="18">
+    <cfRule type="expression" dxfId="126" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="73" priority="17">
+    <cfRule type="expression" dxfId="125" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="72" priority="16">
+    <cfRule type="expression" dxfId="124" priority="18">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D8 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="71" priority="1">
+  <conditionalFormatting sqref="D4:D8 C14:D14">
+    <cfRule type="expression" dxfId="123" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="70" priority="13">
+    <cfRule type="expression" dxfId="122" priority="15">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="29" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14254,30 +15078,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="281" priority="3">
+    <cfRule type="expression" dxfId="338" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="280" priority="14">
+    <cfRule type="expression" dxfId="337" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="279" priority="15">
+    <cfRule type="expression" dxfId="336" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="278" priority="7">
+    <cfRule type="expression" dxfId="335" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="277" priority="9">
+    <cfRule type="expression" dxfId="334" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="276" priority="12">
+    <cfRule type="expression" dxfId="333" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14361,8 +15185,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="B4" s="11"/>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -14372,6 +15199,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -14384,8 +15214,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -14398,6 +15229,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -14412,6 +15244,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -14426,6 +15259,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -14434,6 +15270,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -14442,6 +15281,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -14450,6 +15290,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -14458,6 +15299,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -14691,24 +15533,39 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D6 F5:F6 E6:E7 B7:F25">
-    <cfRule type="expression" dxfId="69" priority="1">
+  <conditionalFormatting sqref="B4:B5 F5:F6 E6:E7 B14:F25 B7:B13 D7:F13 D4:D6">
+    <cfRule type="expression" dxfId="121" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="68" priority="16">
+    <cfRule type="expression" dxfId="120" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="67" priority="15">
+    <cfRule type="expression" dxfId="119" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="66" priority="14">
+    <cfRule type="expression" dxfId="118" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="117" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="27" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="26" priority="1">
+      <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14789,8 +15646,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -14800,6 +15660,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -14812,8 +15675,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -14826,6 +15690,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -14840,6 +15705,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -14854,6 +15720,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -14862,6 +15731,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -14870,6 +15742,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -14878,6 +15751,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -14886,6 +15760,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -15120,22 +15995,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="65" priority="21">
+    <cfRule type="expression" dxfId="116" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="64" priority="20">
+    <cfRule type="expression" dxfId="115" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="63" priority="6">
+    <cfRule type="expression" dxfId="114" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D6 B4:C13 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="62" priority="1">
+  <conditionalFormatting sqref="D4:D6 B4:B5 F5:F6 E6:E7 B14:F25 B7:B13 D7:F13">
+    <cfRule type="expression" dxfId="113" priority="4">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="112" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="23" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15217,14 +16107,20 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -15236,6 +16132,7 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -15247,6 +16144,7 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -15260,6 +16158,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -15273,6 +16172,9 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -15280,6 +16182,9 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -15287,6 +16192,7 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -15294,6 +16200,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -15301,6 +16208,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -15520,38 +16428,48 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="61" priority="2">
+  <conditionalFormatting sqref="B4:B13">
+    <cfRule type="expression" dxfId="111" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="60" priority="24">
+    <cfRule type="expression" dxfId="110" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="59" priority="23">
+    <cfRule type="expression" dxfId="109" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="58" priority="22">
+    <cfRule type="expression" dxfId="108" priority="24">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="57" priority="3">
+    <cfRule type="expression" dxfId="107" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="106" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="55" priority="7">
+    <cfRule type="expression" dxfId="105" priority="9">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="21" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15633,14 +16551,20 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -15652,6 +16576,7 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -15660,6 +16585,7 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="C7" s="28"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -15670,6 +16596,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="C8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -15682,6 +16609,9 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
       </c>
@@ -15691,6 +16621,9 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>357</v>
       </c>
@@ -15700,6 +16633,7 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
         <v>361</v>
       </c>
@@ -15709,6 +16643,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="C12" s="28"/>
       <c r="D12" s="5"/>
       <c r="F12" s="5"/>
     </row>
@@ -15716,6 +16651,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="C13" s="28"/>
       <c r="D13" s="5"/>
       <c r="F13" s="5"/>
     </row>
@@ -15913,33 +16849,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="54" priority="1">
+  <conditionalFormatting sqref="B14:D25 B4:B13 D4:D13">
+    <cfRule type="expression" dxfId="104" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="53" priority="29">
+    <cfRule type="expression" dxfId="103" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="52" priority="28">
+    <cfRule type="expression" dxfId="102" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="51" priority="27">
+    <cfRule type="expression" dxfId="101" priority="29">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="50" priority="7">
+    <cfRule type="expression" dxfId="100" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="49" priority="4">
+    <cfRule type="expression" dxfId="99" priority="6">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16021,8 +16967,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -16032,6 +16981,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -16044,8 +16996,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -16058,6 +17011,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -16072,6 +17026,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -16086,6 +17041,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -16094,6 +17052,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -16102,6 +17063,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -16110,6 +17072,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -16118,6 +17081,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -16343,33 +17307,48 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B14 F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="48" priority="24">
+  <conditionalFormatting sqref="B5 F5:F14 E6:E26 B15:D25 B7:B14">
+    <cfRule type="expression" dxfId="98" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="47" priority="31">
+    <cfRule type="expression" dxfId="97" priority="34">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="46" priority="30">
+    <cfRule type="expression" dxfId="96" priority="33">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="45" priority="29">
+    <cfRule type="expression" dxfId="95" priority="32">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="44" priority="1">
+  <conditionalFormatting sqref="C14:D14 D4:D13">
+    <cfRule type="expression" dxfId="94" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="43" priority="23">
+    <cfRule type="expression" dxfId="93" priority="26">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="92" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="17" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16451,9 +17430,12 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -16463,6 +17445,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -16476,8 +17461,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -16489,6 +17475,7 @@
       <c r="B7" s="9" t="s">
         <v>99</v>
       </c>
+      <c r="C7" s="28"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -16500,6 +17487,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -16513,6 +17501,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
       </c>
@@ -16524,18 +17515,22 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="D10" s="5" t="s">
         <v>357</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="68" t="s">
         <v>362</v>
       </c>
       <c r="E11" s="36"/>
@@ -16546,6 +17541,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="5"/>
       <c r="E12" s="36"/>
       <c r="F12" s="5"/>
@@ -16555,6 +17551,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="5"/>
       <c r="E13" s="36"/>
       <c r="F13" s="5"/>
@@ -16772,38 +17769,53 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B14 F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="42" priority="27">
+  <conditionalFormatting sqref="B5 F5:F14 B15:D25 B7:B14">
+    <cfRule type="expression" dxfId="91" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="41" priority="34">
+    <cfRule type="expression" dxfId="90" priority="37">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="40" priority="33">
+    <cfRule type="expression" dxfId="89" priority="36">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="39" priority="32">
+    <cfRule type="expression" dxfId="88" priority="35">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="38" priority="1">
+  <conditionalFormatting sqref="C14:D14 D4:D13">
+    <cfRule type="expression" dxfId="87" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="37" priority="4">
+    <cfRule type="expression" dxfId="86" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="36" priority="26">
+    <cfRule type="expression" dxfId="85" priority="29">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="84" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16885,8 +17897,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -16896,6 +17911,9 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -16908,8 +17926,9 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -16922,6 +17941,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -16936,6 +17956,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -16950,6 +17971,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -16958,6 +17982,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -16966,6 +17993,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -16974,6 +18002,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -16982,6 +18011,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -17210,37 +18240,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="35" priority="15">
+    <cfRule type="expression" dxfId="83" priority="18">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="34" priority="14">
+    <cfRule type="expression" dxfId="82" priority="17">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="33" priority="13">
+    <cfRule type="expression" dxfId="81" priority="16">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="32" priority="1">
+  <conditionalFormatting sqref="C14:D14 D4:D13">
+    <cfRule type="expression" dxfId="80" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="31" priority="4">
+    <cfRule type="expression" dxfId="79" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F13 B5:B14 B15:D25">
-    <cfRule type="expression" dxfId="30" priority="11">
+  <conditionalFormatting sqref="F5:F13 B5 B15:D25 B7:B14">
+    <cfRule type="expression" dxfId="78" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="29" priority="10">
+    <cfRule type="expression" dxfId="77" priority="13">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="76" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17322,19 +18367,22 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -17347,7 +18395,10 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -17360,6 +18411,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -17374,6 +18426,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -17388,6 +18441,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -17396,6 +18452,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -17404,6 +18463,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -17412,6 +18472,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -17420,6 +18481,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -17649,33 +18711,48 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="28" priority="1">
+  <conditionalFormatting sqref="B5 B15:D25 C14:D14 B7:B14 D4:D13">
+    <cfRule type="expression" dxfId="75" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="27" priority="16">
+    <cfRule type="expression" dxfId="74" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="26" priority="15">
+    <cfRule type="expression" dxfId="73" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="25" priority="14">
+    <cfRule type="expression" dxfId="72" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="24" priority="5">
+    <cfRule type="expression" dxfId="71" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="23" priority="11">
+    <cfRule type="expression" dxfId="70" priority="14">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="69" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="11" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17757,19 +18834,22 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -17782,7 +18862,10 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -17795,6 +18878,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -17809,6 +18893,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -17823,6 +18908,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -17831,6 +18919,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -17839,6 +18930,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -17847,6 +18939,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -17855,6 +18948,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -18080,33 +19174,48 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="22" priority="1">
+  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
+    <cfRule type="expression" dxfId="68" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="21" priority="16">
+    <cfRule type="expression" dxfId="67" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="20" priority="15">
+    <cfRule type="expression" dxfId="66" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="19" priority="14">
+    <cfRule type="expression" dxfId="65" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="18" priority="5">
+    <cfRule type="expression" dxfId="64" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="17" priority="11">
+    <cfRule type="expression" dxfId="63" priority="14">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="62" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18188,19 +19297,22 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -18213,7 +19325,10 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -18226,6 +19341,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -18240,6 +19356,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -18254,6 +19371,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -18262,6 +19382,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -18270,6 +19393,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -18278,6 +19402,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -18286,6 +19411,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -18521,33 +19647,48 @@
       <c r="F36" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="16" priority="1">
+  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
+    <cfRule type="expression" dxfId="61" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="60" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="59" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="58" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="12" priority="5">
+    <cfRule type="expression" dxfId="57" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="56" priority="14">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="55" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18972,22 +20113,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="275" priority="10">
+    <cfRule type="expression" dxfId="332" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="274" priority="9">
+    <cfRule type="expression" dxfId="331" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="273" priority="1">
+    <cfRule type="expression" dxfId="330" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="272" priority="7">
+    <cfRule type="expression" dxfId="329" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19070,19 +20211,22 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -19095,7 +20239,10 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -19108,6 +20255,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -19122,6 +20270,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -19136,6 +20285,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -19144,6 +20296,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -19152,6 +20307,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -19160,6 +20316,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -19168,6 +20325,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -19403,33 +20561,48 @@
       <c r="F36" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="10" priority="1">
+  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
+    <cfRule type="expression" dxfId="54" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="9" priority="16">
+    <cfRule type="expression" dxfId="53" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="8" priority="15">
+    <cfRule type="expression" dxfId="52" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="51" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="50" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="5" priority="11">
+    <cfRule type="expression" dxfId="49" priority="14">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="48" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19511,19 +20684,22 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
+      <c r="C4" s="29" t="s">
+        <v>366</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>10</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>7</v>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>367</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -19536,7 +20712,10 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7"/>
+      <c r="B6" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -19549,6 +20728,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
+      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -19563,6 +20743,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
+      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -19577,6 +20758,9 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="B9" s="7"/>
+      <c r="C9" s="29" t="s">
+        <v>365</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -19585,6 +20769,9 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="B10" s="7"/>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -19593,6 +20780,7 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B11" s="7"/>
+      <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -19601,6 +20789,7 @@
         <v>0.5</v>
       </c>
       <c r="B12" s="7"/>
+      <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -19609,6 +20798,7 @@
         <v>0.53125</v>
       </c>
       <c r="B13" s="7"/>
+      <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -19840,28 +21030,43 @@
       <c r="F36" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="4" priority="1">
+  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
+    <cfRule type="expression" dxfId="47" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="3" priority="16">
+    <cfRule type="expression" dxfId="46" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="2" priority="15">
+    <cfRule type="expression" dxfId="45" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="1" priority="14">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="43" priority="8">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="expression" dxfId="42" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20306,42 +21511,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="271" priority="15">
+    <cfRule type="expression" dxfId="328" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="270" priority="13">
+    <cfRule type="expression" dxfId="327" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="269" priority="30">
+    <cfRule type="expression" dxfId="326" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="268" priority="29">
+    <cfRule type="expression" dxfId="325" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="267" priority="7">
+    <cfRule type="expression" dxfId="324" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="266" priority="24">
+    <cfRule type="expression" dxfId="323" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="265" priority="20">
+    <cfRule type="expression" dxfId="322" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="264" priority="25">
+    <cfRule type="expression" dxfId="321" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20742,32 +21947,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="263" priority="8">
+    <cfRule type="expression" dxfId="320" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="262" priority="13">
+    <cfRule type="expression" dxfId="319" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="261" priority="12">
+    <cfRule type="expression" dxfId="318" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="260" priority="1">
+    <cfRule type="expression" dxfId="317" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="259" priority="4">
+    <cfRule type="expression" dxfId="316" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="258" priority="7">
+    <cfRule type="expression" dxfId="315" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21151,52 +22356,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="257" priority="22">
+    <cfRule type="expression" dxfId="314" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="256" priority="23">
+    <cfRule type="expression" dxfId="313" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="255" priority="45">
+    <cfRule type="expression" dxfId="312" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="254" priority="44">
+    <cfRule type="expression" dxfId="311" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="253" priority="1">
+    <cfRule type="expression" dxfId="310" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="252" priority="35">
+    <cfRule type="expression" dxfId="309" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="251" priority="36">
+    <cfRule type="expression" dxfId="308" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="250" priority="16">
+    <cfRule type="expression" dxfId="307" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="249" priority="34">
+    <cfRule type="expression" dxfId="306" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="248" priority="5">
+    <cfRule type="expression" dxfId="305" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21609,47 +22814,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="247" priority="16">
+    <cfRule type="expression" dxfId="304" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="246" priority="19">
+    <cfRule type="expression" dxfId="303" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="245" priority="18">
+    <cfRule type="expression" dxfId="302" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="244" priority="1">
+    <cfRule type="expression" dxfId="301" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="243" priority="15">
+    <cfRule type="expression" dxfId="300" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="242" priority="12">
+    <cfRule type="expression" dxfId="299" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="241" priority="11">
+    <cfRule type="expression" dxfId="298" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="240" priority="14">
+    <cfRule type="expression" dxfId="297" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="239" priority="5">
+    <cfRule type="expression" dxfId="296" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22072,32 +23277,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="238" priority="2">
+    <cfRule type="expression" dxfId="295" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="237" priority="4">
+    <cfRule type="expression" dxfId="294" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="236" priority="16">
+    <cfRule type="expression" dxfId="293" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="235" priority="15">
+    <cfRule type="expression" dxfId="292" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="234" priority="1">
+    <cfRule type="expression" dxfId="291" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="233" priority="7">
+    <cfRule type="expression" dxfId="290" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76FF003-5A5F-495F-BC86-410AEE1528AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDCDC35-2A13-4798-9BB7-F04954FCBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="375">
   <si>
     <t>Week</t>
   </si>
@@ -1199,6 +1199,27 @@
   </si>
   <si>
     <t>Lokaal D303</t>
+  </si>
+  <si>
+    <t>Eerste les + briefing in lokaal 309</t>
+  </si>
+  <si>
+    <t>Potlood, krijt, grafiet</t>
+  </si>
+  <si>
+    <t>Snelstudies model</t>
+  </si>
+  <si>
+    <t>Lavis, nat in nat</t>
+  </si>
+  <si>
+    <t>Bister, inkt meedoen voor tekenen</t>
+  </si>
+  <si>
+    <t>Plooien, draperie, kleding</t>
+  </si>
+  <si>
+    <t>Houtskool, kneedgom, grafiet, papier met korrel</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1408,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1511,6 +1532,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="5" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="6" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="20% - Accent2" xfId="3" builtinId="34"/>
@@ -1523,7 +1547,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="343">
+  <dxfs count="305">
     <dxf>
       <font>
         <color theme="1"/>
@@ -1545,6 +1569,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1595,6 +1643,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1645,6 +1717,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1695,6 +1791,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1745,6 +1865,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1805,6 +1949,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1855,6 +2023,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1895,6 +2087,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -1925,6 +2141,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2009,6 +2249,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2157,6 +2421,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2221,6 +2515,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2305,6 +2619,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2369,6 +2693,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2433,6 +2777,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2487,6 +2861,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2517,763 +2921,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5422,47 +5069,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="289" priority="17">
+    <cfRule type="expression" dxfId="251" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="288" priority="25">
+    <cfRule type="expression" dxfId="250" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="287" priority="24">
+    <cfRule type="expression" dxfId="249" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="286" priority="5">
+    <cfRule type="expression" dxfId="248" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="285" priority="9">
+    <cfRule type="expression" dxfId="247" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="284" priority="8">
+    <cfRule type="expression" dxfId="246" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="283" priority="11">
+    <cfRule type="expression" dxfId="245" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="282" priority="15">
+    <cfRule type="expression" dxfId="244" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="281" priority="2">
+    <cfRule type="expression" dxfId="243" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5921,42 +5568,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="280" priority="15">
+    <cfRule type="expression" dxfId="242" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="279" priority="10">
+    <cfRule type="expression" dxfId="241" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="278" priority="24">
+    <cfRule type="expression" dxfId="240" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="277" priority="23">
+    <cfRule type="expression" dxfId="239" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="276" priority="1">
+    <cfRule type="expression" dxfId="238" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="275" priority="7">
+    <cfRule type="expression" dxfId="237" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="274" priority="3">
+    <cfRule type="expression" dxfId="236" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="273" priority="14">
+    <cfRule type="expression" dxfId="235" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6395,47 +6042,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="272" priority="10">
+    <cfRule type="expression" dxfId="234" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="271" priority="1">
+    <cfRule type="expression" dxfId="233" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="270" priority="25">
+    <cfRule type="expression" dxfId="232" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="269" priority="24">
+    <cfRule type="expression" dxfId="231" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="268" priority="4">
+    <cfRule type="expression" dxfId="230" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="267" priority="3">
+    <cfRule type="expression" dxfId="229" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="266" priority="6">
+    <cfRule type="expression" dxfId="228" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="265" priority="9">
+    <cfRule type="expression" dxfId="227" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="264" priority="11">
+    <cfRule type="expression" dxfId="226" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6898,57 +6545,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="263" priority="36">
+    <cfRule type="expression" dxfId="225" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="262" priority="51">
+    <cfRule type="expression" dxfId="224" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="261" priority="50">
+    <cfRule type="expression" dxfId="223" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="260" priority="9">
+    <cfRule type="expression" dxfId="222" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="259" priority="28">
+    <cfRule type="expression" dxfId="221" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="258" priority="11">
+    <cfRule type="expression" dxfId="220" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="257" priority="24">
+    <cfRule type="expression" dxfId="219" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="256" priority="31">
+    <cfRule type="expression" dxfId="218" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="255" priority="7">
+    <cfRule type="expression" dxfId="217" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="254" priority="35">
+    <cfRule type="expression" dxfId="216" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="253" priority="1">
+    <cfRule type="expression" dxfId="215" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7380,59 +7027,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="252" priority="35">
+    <cfRule type="expression" dxfId="214" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="251" priority="42">
+    <cfRule type="expression" dxfId="213" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="250" priority="54">
+    <cfRule type="expression" dxfId="212" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="249" priority="53">
+    <cfRule type="expression" dxfId="211" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="248" priority="5">
+    <cfRule type="expression" dxfId="210" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="247" priority="30">
+    <cfRule type="expression" dxfId="209" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="246" priority="33">
+    <cfRule type="expression" dxfId="208" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="245" priority="37">
+    <cfRule type="expression" dxfId="207" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="244" priority="41">
+    <cfRule type="expression" dxfId="206" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="243" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="241" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="240" priority="1">
+    <cfRule type="expression" dxfId="202" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7898,57 +7545,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="239" priority="1">
+    <cfRule type="expression" dxfId="201" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="238" priority="18">
+    <cfRule type="expression" dxfId="200" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="237" priority="41">
+    <cfRule type="expression" dxfId="199" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="236" priority="40">
+    <cfRule type="expression" dxfId="198" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="235" priority="13">
+    <cfRule type="expression" dxfId="197" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="234" priority="3">
+    <cfRule type="expression" dxfId="196" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="233" priority="5">
+    <cfRule type="expression" dxfId="195" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="232" priority="19">
+    <cfRule type="expression" dxfId="194" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="231" priority="7">
+    <cfRule type="expression" dxfId="193" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="230" priority="27">
+    <cfRule type="expression" dxfId="192" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="229" priority="8">
+    <cfRule type="expression" dxfId="191" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8408,32 +8055,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="228" priority="21">
+    <cfRule type="expression" dxfId="190" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="227" priority="43">
+    <cfRule type="expression" dxfId="189" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="226" priority="42">
+    <cfRule type="expression" dxfId="188" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="225" priority="1">
+    <cfRule type="expression" dxfId="187" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="224" priority="16">
+    <cfRule type="expression" dxfId="186" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="223" priority="24">
+    <cfRule type="expression" dxfId="185" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8849,32 +8496,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="222" priority="30">
+    <cfRule type="expression" dxfId="184" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="221" priority="29">
+    <cfRule type="expression" dxfId="183" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="220" priority="16">
+    <cfRule type="expression" dxfId="182" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="219" priority="1">
+    <cfRule type="expression" dxfId="181" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="218" priority="4">
+    <cfRule type="expression" dxfId="180" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="217" priority="5">
+    <cfRule type="expression" dxfId="179" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9284,32 +8931,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="216" priority="39">
+    <cfRule type="expression" dxfId="178" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="215" priority="38">
+    <cfRule type="expression" dxfId="177" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="214" priority="20">
+    <cfRule type="expression" dxfId="176" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="213" priority="1">
+    <cfRule type="expression" dxfId="175" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="212" priority="3">
+    <cfRule type="expression" dxfId="174" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="211" priority="2">
+    <cfRule type="expression" dxfId="173" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9729,37 +9376,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="210" priority="18">
+    <cfRule type="expression" dxfId="172" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="209" priority="2">
+    <cfRule type="expression" dxfId="171" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="208" priority="32">
+    <cfRule type="expression" dxfId="170" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="207" priority="31">
+    <cfRule type="expression" dxfId="169" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="206" priority="5">
+    <cfRule type="expression" dxfId="168" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="205" priority="1">
+    <cfRule type="expression" dxfId="167" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="204" priority="3">
+    <cfRule type="expression" dxfId="166" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10175,22 +9822,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="342" priority="14">
+    <cfRule type="expression" dxfId="304" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="341" priority="6">
+    <cfRule type="expression" dxfId="303" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="340" priority="15">
+    <cfRule type="expression" dxfId="302" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="339" priority="1">
+    <cfRule type="expression" dxfId="301" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10588,22 +10235,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="203" priority="32">
+    <cfRule type="expression" dxfId="165" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="202" priority="31">
+    <cfRule type="expression" dxfId="164" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="201" priority="12">
+    <cfRule type="expression" dxfId="163" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="200" priority="1">
+    <cfRule type="expression" dxfId="162" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10969,22 +10616,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="199" priority="17">
+    <cfRule type="expression" dxfId="161" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="198" priority="16">
+    <cfRule type="expression" dxfId="160" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="197" priority="2">
+    <cfRule type="expression" dxfId="159" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="196" priority="1">
+    <cfRule type="expression" dxfId="158" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11077,9 +10724,6 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="C5" s="28" t="s">
         <v>367</v>
       </c>
@@ -11094,8 +10738,8 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>364</v>
+      <c r="B6" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -11109,7 +10753,9 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>364</v>
+      </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -11124,7 +10770,9 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
-      <c r="B8" s="7"/>
+      <c r="B8" s="7" t="s">
+        <v>370</v>
+      </c>
       <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
@@ -11195,6 +10843,7 @@
       <c r="A15" s="3">
         <v>0.5625</v>
       </c>
+      <c r="B15" s="7"/>
       <c r="D15" s="36"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -11219,7 +10868,7 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>13</v>
+        <v>357</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>27</v>
@@ -11325,7 +10974,9 @@
       <c r="B28" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>368</v>
+      </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16" t="s">
         <v>297</v>
@@ -11348,7 +10999,9 @@
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="19" t="s">
+        <v>369</v>
+      </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -11404,57 +11057,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="195" priority="30">
+    <cfRule type="expression" dxfId="157" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="194" priority="29">
+    <cfRule type="expression" dxfId="156" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F28 B30:F36 C29:F29">
-    <cfRule type="expression" dxfId="193" priority="28">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="155" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="192" priority="8">
+  <conditionalFormatting sqref="C4:C25 B6:B25">
+    <cfRule type="expression" dxfId="154" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="191" priority="3">
+    <cfRule type="expression" dxfId="153" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="190" priority="10">
+    <cfRule type="expression" dxfId="152" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 B5:B25">
-    <cfRule type="expression" dxfId="189" priority="16">
+  <conditionalFormatting sqref="F5:F14">
+    <cfRule type="expression" dxfId="151" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="188" priority="25">
+    <cfRule type="expression" dxfId="150" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="187" priority="31">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="expression" dxfId="186" priority="2">
-      <formula>NOT(ISBLANK(B29))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="185" priority="1">
+    <cfRule type="expression" dxfId="149" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11864,57 +11507,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="184" priority="12">
+    <cfRule type="expression" dxfId="148" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="183" priority="29">
+    <cfRule type="expression" dxfId="147" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="182" priority="28">
+    <cfRule type="expression" dxfId="146" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="181" priority="27">
+    <cfRule type="expression" dxfId="145" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:C25">
-    <cfRule type="expression" dxfId="180" priority="8">
+  <conditionalFormatting sqref="C4:C25">
+    <cfRule type="expression" dxfId="144" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="179" priority="3">
+    <cfRule type="expression" dxfId="143" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="178" priority="9">
+    <cfRule type="expression" dxfId="142" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="177" priority="24">
+    <cfRule type="expression" dxfId="141" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="176" priority="30">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="41" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="140" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12039,7 +11672,9 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>371</v>
+      </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -12254,7 +11889,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>372</v>
+      </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
         <v>36</v>
@@ -12327,63 +11964,53 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5:B25">
+    <cfRule type="expression" dxfId="139" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="175" priority="26">
+    <cfRule type="expression" dxfId="138" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="174" priority="25">
+    <cfRule type="expression" dxfId="137" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="173" priority="24">
+    <cfRule type="expression" dxfId="136" priority="24">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="172" priority="5">
+  <conditionalFormatting sqref="C4:C14">
+    <cfRule type="expression" dxfId="135" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="171" priority="27">
+    <cfRule type="expression" dxfId="134" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="170" priority="4">
+    <cfRule type="expression" dxfId="133" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="169" priority="7">
+    <cfRule type="expression" dxfId="132" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F13 B5 B7:B25">
-    <cfRule type="expression" dxfId="168" priority="17">
+  <conditionalFormatting sqref="F5:F13">
+    <cfRule type="expression" dxfId="131" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="167" priority="21">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="166" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="37" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="130" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12792,57 +12419,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="165" priority="11">
+    <cfRule type="expression" dxfId="129" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="164" priority="20">
+    <cfRule type="expression" dxfId="128" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="163" priority="19">
+    <cfRule type="expression" dxfId="127" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="18">
+    <cfRule type="expression" dxfId="126" priority="18">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:C25">
-    <cfRule type="expression" dxfId="161" priority="5">
+  <conditionalFormatting sqref="C4:C25">
+    <cfRule type="expression" dxfId="125" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="160" priority="3">
+    <cfRule type="expression" dxfId="124" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="159" priority="6">
+    <cfRule type="expression" dxfId="123" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="158" priority="15">
+    <cfRule type="expression" dxfId="122" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="157" priority="21">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="39" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="38" priority="1">
+    <cfRule type="expression" dxfId="121" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12963,11 +12580,13 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="69" t="s">
+        <v>373</v>
+      </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -13178,7 +12797,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>374</v>
+      </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -13249,63 +12870,53 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5:B25">
+    <cfRule type="expression" dxfId="120" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="156" priority="26">
+    <cfRule type="expression" dxfId="119" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="155" priority="25">
+    <cfRule type="expression" dxfId="118" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="154" priority="24">
+    <cfRule type="expression" dxfId="117" priority="24">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="153" priority="4">
+  <conditionalFormatting sqref="C4:C14">
+    <cfRule type="expression" dxfId="116" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="152" priority="27">
+    <cfRule type="expression" dxfId="115" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="151" priority="20">
+    <cfRule type="expression" dxfId="114" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="150" priority="6">
+    <cfRule type="expression" dxfId="113" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 B5 B7:B25">
-    <cfRule type="expression" dxfId="149" priority="17">
+  <conditionalFormatting sqref="F5:F14">
+    <cfRule type="expression" dxfId="112" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="148" priority="21">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="147" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="35" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="111" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13712,57 +13323,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="146" priority="9">
+    <cfRule type="expression" dxfId="110" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="145" priority="20">
+    <cfRule type="expression" dxfId="109" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="144" priority="19">
+    <cfRule type="expression" dxfId="108" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="143" priority="18">
+    <cfRule type="expression" dxfId="107" priority="18">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="142" priority="4">
+  <conditionalFormatting sqref="C4:C14">
+    <cfRule type="expression" dxfId="106" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="141" priority="21">
+    <cfRule type="expression" dxfId="105" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="140" priority="3">
+    <cfRule type="expression" dxfId="104" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="139" priority="5">
+    <cfRule type="expression" dxfId="103" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="138" priority="15">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="33" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="32" priority="1">
+    <cfRule type="expression" dxfId="102" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14169,63 +13770,53 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5:B25">
+    <cfRule type="expression" dxfId="101" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="137" priority="24">
+    <cfRule type="expression" dxfId="100" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="136" priority="23">
+    <cfRule type="expression" dxfId="99" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="135" priority="22">
+    <cfRule type="expression" dxfId="98" priority="22">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="134" priority="4">
+  <conditionalFormatting sqref="C4:C14">
+    <cfRule type="expression" dxfId="97" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="133" priority="25">
+    <cfRule type="expression" dxfId="96" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="132" priority="18">
+    <cfRule type="expression" dxfId="95" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="131" priority="6">
+    <cfRule type="expression" dxfId="94" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F13 B5 B7:B25">
-    <cfRule type="expression" dxfId="130" priority="16">
+  <conditionalFormatting sqref="F5:F13">
+    <cfRule type="expression" dxfId="93" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="129" priority="19">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="128" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="31" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="92" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14639,42 +14230,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F6 E7:F25 B15:D25">
-    <cfRule type="expression" dxfId="127" priority="6">
+    <cfRule type="expression" dxfId="91" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="126" priority="20">
+    <cfRule type="expression" dxfId="90" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="125" priority="19">
+    <cfRule type="expression" dxfId="89" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="124" priority="18">
+    <cfRule type="expression" dxfId="88" priority="18">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C13">
+    <cfRule type="expression" dxfId="87" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8 C14:D14">
-    <cfRule type="expression" dxfId="123" priority="3">
+    <cfRule type="expression" dxfId="86" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="122" priority="15">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="29" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="85" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15078,30 +14664,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="338" priority="3">
+    <cfRule type="expression" dxfId="300" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="337" priority="14">
+    <cfRule type="expression" dxfId="299" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="336" priority="15">
+    <cfRule type="expression" dxfId="298" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="335" priority="7">
+    <cfRule type="expression" dxfId="297" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="334" priority="9">
+    <cfRule type="expression" dxfId="296" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="333" priority="12">
+    <cfRule type="expression" dxfId="295" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15533,38 +15119,28 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:B5 F5:F6 E6:E7 B14:F25 B7:B13 D7:F13 D4:D6">
-    <cfRule type="expression" dxfId="121" priority="4">
+  <conditionalFormatting sqref="B4:C13">
+    <cfRule type="expression" dxfId="84" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="120" priority="19">
+    <cfRule type="expression" dxfId="83" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="119" priority="18">
+    <cfRule type="expression" dxfId="82" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="118" priority="17">
+    <cfRule type="expression" dxfId="81" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="117" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="27" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="26" priority="1">
+  <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
+    <cfRule type="expression" dxfId="80" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15994,38 +15570,28 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B4:C13">
+    <cfRule type="expression" dxfId="79" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="116" priority="24">
+    <cfRule type="expression" dxfId="78" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="115" priority="23">
+    <cfRule type="expression" dxfId="77" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="114" priority="9">
+    <cfRule type="expression" dxfId="76" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D6 B4:B5 F5:F6 E6:E7 B14:F25 B7:B13 D7:F13">
-    <cfRule type="expression" dxfId="113" priority="4">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="112" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="23" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="22" priority="1">
+  <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
+    <cfRule type="expression" dxfId="75" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16428,48 +15994,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:B13">
-    <cfRule type="expression" dxfId="111" priority="4">
+  <conditionalFormatting sqref="B4:C13">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="110" priority="26">
+    <cfRule type="expression" dxfId="73" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="109" priority="25">
+    <cfRule type="expression" dxfId="72" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="108" priority="24">
+    <cfRule type="expression" dxfId="71" priority="24">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="107" priority="5">
+    <cfRule type="expression" dxfId="70" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="106" priority="3">
+    <cfRule type="expression" dxfId="69" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="105" priority="9">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="21" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="20" priority="1">
+    <cfRule type="expression" dxfId="68" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16849,43 +16405,33 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B14:D25 B4:B13 D4:D13">
-    <cfRule type="expression" dxfId="104" priority="3">
+  <conditionalFormatting sqref="B4:D25">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="103" priority="31">
+    <cfRule type="expression" dxfId="66" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="102" priority="30">
+    <cfRule type="expression" dxfId="65" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="101" priority="29">
+    <cfRule type="expression" dxfId="64" priority="29">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="100" priority="9">
+    <cfRule type="expression" dxfId="63" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="99" priority="6">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="19" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="62" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17307,48 +16853,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5 F5:F14 E6:E26 B15:D25 B7:B14">
-    <cfRule type="expression" dxfId="98" priority="27">
+  <conditionalFormatting sqref="B5:B14">
+    <cfRule type="expression" dxfId="61" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="97" priority="34">
+    <cfRule type="expression" dxfId="60" priority="34">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="96" priority="33">
+    <cfRule type="expression" dxfId="59" priority="33">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="95" priority="32">
+    <cfRule type="expression" dxfId="58" priority="32">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:D14 D4:D13">
-    <cfRule type="expression" dxfId="94" priority="4">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="57" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
+    <cfRule type="expression" dxfId="56" priority="27">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="93" priority="26">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="92" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="17" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="55" priority="26">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17769,53 +17305,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5 F5:F14 B15:D25 B7:B14">
-    <cfRule type="expression" dxfId="91" priority="30">
+  <conditionalFormatting sqref="B5:B14">
+    <cfRule type="expression" dxfId="54" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="90" priority="37">
+    <cfRule type="expression" dxfId="53" priority="37">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="89" priority="36">
+    <cfRule type="expression" dxfId="52" priority="36">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="88" priority="35">
+    <cfRule type="expression" dxfId="51" priority="35">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:D14 D4:D13">
-    <cfRule type="expression" dxfId="87" priority="4">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="50" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="86" priority="7">
+    <cfRule type="expression" dxfId="49" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F14 B15:D25">
+    <cfRule type="expression" dxfId="48" priority="30">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="85" priority="29">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="84" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="15" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="47" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18239,53 +17765,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5:B14">
+    <cfRule type="expression" dxfId="46" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="83" priority="18">
+    <cfRule type="expression" dxfId="45" priority="18">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="82" priority="17">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="81" priority="16">
+    <cfRule type="expression" dxfId="43" priority="16">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:D14 D4:D13">
-    <cfRule type="expression" dxfId="80" priority="4">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="79" priority="7">
+    <cfRule type="expression" dxfId="41" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F13 B5 B15:D25 B7:B14">
-    <cfRule type="expression" dxfId="78" priority="14">
+  <conditionalFormatting sqref="F5:F13 B15:D25">
+    <cfRule type="expression" dxfId="40" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="77" priority="13">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="76" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="13" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="39" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18711,48 +18227,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5 B15:D25 C14:D14 B7:B14 D4:D13">
-    <cfRule type="expression" dxfId="75" priority="4">
+  <conditionalFormatting sqref="B5:B14">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B15:D25">
+    <cfRule type="expression" dxfId="37" priority="4">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="74" priority="19">
+    <cfRule type="expression" dxfId="36" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="73" priority="18">
+    <cfRule type="expression" dxfId="35" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="72" priority="17">
+    <cfRule type="expression" dxfId="34" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="33" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="71" priority="8">
+    <cfRule type="expression" dxfId="32" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="70" priority="14">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="69" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="11" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="31" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19174,48 +18685,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
-    <cfRule type="expression" dxfId="68" priority="4">
+  <conditionalFormatting sqref="B5:B13">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B14:D25">
+    <cfRule type="expression" dxfId="29" priority="4">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="67" priority="19">
+    <cfRule type="expression" dxfId="28" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="66" priority="18">
+    <cfRule type="expression" dxfId="27" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="65" priority="17">
+    <cfRule type="expression" dxfId="26" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="25" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="64" priority="8">
+    <cfRule type="expression" dxfId="24" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="63" priority="14">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="62" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="9" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="23" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19647,48 +19153,43 @@
       <c r="F36" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
-    <cfRule type="expression" dxfId="61" priority="4">
+  <conditionalFormatting sqref="B5:B13">
+    <cfRule type="expression" dxfId="22" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B14:D25">
+    <cfRule type="expression" dxfId="21" priority="4">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="60" priority="19">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="59" priority="18">
+    <cfRule type="expression" dxfId="19" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="58" priority="17">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="57" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="56" priority="14">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="55" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="15" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20113,22 +19614,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="332" priority="10">
+    <cfRule type="expression" dxfId="294" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="331" priority="9">
+    <cfRule type="expression" dxfId="293" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="330" priority="1">
+    <cfRule type="expression" dxfId="292" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="329" priority="7">
+    <cfRule type="expression" dxfId="291" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20561,48 +20062,43 @@
       <c r="F36" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
-    <cfRule type="expression" dxfId="54" priority="4">
+  <conditionalFormatting sqref="B5:B13">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B14:D25">
+    <cfRule type="expression" dxfId="13" priority="4">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="53" priority="19">
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="52" priority="18">
+    <cfRule type="expression" dxfId="11" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="51" priority="17">
+    <cfRule type="expression" dxfId="10" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="50" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="49" priority="14">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="48" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21030,43 +20526,38 @@
       <c r="F36" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5 B14:D25 D4:D13 B7:B13">
-    <cfRule type="expression" dxfId="47" priority="4">
+  <conditionalFormatting sqref="B5:B13">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B14:D25">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="46" priority="19">
+    <cfRule type="expression" dxfId="4" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="45" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="44" priority="17">
+    <cfRule type="expression" dxfId="2" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="43" priority="8">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" dxfId="42" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21511,42 +21002,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="328" priority="15">
+    <cfRule type="expression" dxfId="290" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="327" priority="13">
+    <cfRule type="expression" dxfId="289" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="326" priority="30">
+    <cfRule type="expression" dxfId="288" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="325" priority="29">
+    <cfRule type="expression" dxfId="287" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="324" priority="7">
+    <cfRule type="expression" dxfId="286" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="323" priority="24">
+    <cfRule type="expression" dxfId="285" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="322" priority="20">
+    <cfRule type="expression" dxfId="284" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="321" priority="25">
+    <cfRule type="expression" dxfId="283" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21947,32 +21438,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="320" priority="8">
+    <cfRule type="expression" dxfId="282" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="319" priority="13">
+    <cfRule type="expression" dxfId="281" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="318" priority="12">
+    <cfRule type="expression" dxfId="280" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="317" priority="1">
+    <cfRule type="expression" dxfId="279" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="316" priority="4">
+    <cfRule type="expression" dxfId="278" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="315" priority="7">
+    <cfRule type="expression" dxfId="277" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22356,52 +21847,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="314" priority="22">
+    <cfRule type="expression" dxfId="276" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="313" priority="23">
+    <cfRule type="expression" dxfId="275" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="312" priority="45">
+    <cfRule type="expression" dxfId="274" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="311" priority="44">
+    <cfRule type="expression" dxfId="273" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="310" priority="1">
+    <cfRule type="expression" dxfId="272" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="309" priority="35">
+    <cfRule type="expression" dxfId="271" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="308" priority="36">
+    <cfRule type="expression" dxfId="270" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="307" priority="16">
+    <cfRule type="expression" dxfId="269" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="306" priority="34">
+    <cfRule type="expression" dxfId="268" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="305" priority="5">
+    <cfRule type="expression" dxfId="267" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22814,47 +22305,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="304" priority="16">
+    <cfRule type="expression" dxfId="266" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="303" priority="19">
+    <cfRule type="expression" dxfId="265" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="302" priority="18">
+    <cfRule type="expression" dxfId="264" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="301" priority="1">
+    <cfRule type="expression" dxfId="263" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="300" priority="15">
+    <cfRule type="expression" dxfId="262" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="299" priority="12">
+    <cfRule type="expression" dxfId="261" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="298" priority="11">
+    <cfRule type="expression" dxfId="260" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="297" priority="14">
+    <cfRule type="expression" dxfId="259" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="296" priority="5">
+    <cfRule type="expression" dxfId="258" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23277,32 +22768,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="295" priority="2">
+    <cfRule type="expression" dxfId="257" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="294" priority="4">
+    <cfRule type="expression" dxfId="256" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="293" priority="16">
+    <cfRule type="expression" dxfId="255" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="292" priority="15">
+    <cfRule type="expression" dxfId="254" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="291" priority="1">
+    <cfRule type="expression" dxfId="253" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="290" priority="7">
+    <cfRule type="expression" dxfId="252" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDCDC35-2A13-4798-9BB7-F04954FCBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AB5D2F-ED4E-4427-9795-70B015538898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="377">
   <si>
     <t>Week</t>
   </si>
@@ -1220,6 +1220,12 @@
   </si>
   <si>
     <t>Houtskool, kneedgom, grafiet, papier met korrel</t>
+  </si>
+  <si>
+    <t>Experiment</t>
+  </si>
+  <si>
+    <t>Lokaal C15</t>
   </si>
 </sst>
 </file>
@@ -10727,6 +10733,9 @@
       <c r="C5" s="28" t="s">
         <v>367</v>
       </c>
+      <c r="E5" s="29" t="s">
+        <v>375</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -10742,8 +10751,8 @@
         <v>11</v>
       </c>
       <c r="C6" s="28"/>
-      <c r="E6" s="29" t="s">
-        <v>108</v>
+      <c r="E6" s="32" t="s">
+        <v>376</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -10757,9 +10766,7 @@
         <v>364</v>
       </c>
       <c r="C7" s="28"/>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
+      <c r="E7" s="32"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -11081,7 +11088,7 @@
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E25">
+  <conditionalFormatting sqref="E5:E25">
     <cfRule type="expression" dxfId="152" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AB5D2F-ED4E-4427-9795-70B015538898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA0A438-60E6-4D21-B5DB-C825178A79BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="378">
   <si>
     <t>Week</t>
   </si>
@@ -1226,6 +1226,9 @@
   </si>
   <si>
     <t>Lokaal C15</t>
+  </si>
+  <si>
+    <t>Nog meer experiment? Checken agenda ofzo</t>
   </si>
 </sst>
 </file>
@@ -11011,7 +11014,9 @@
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="E30" s="19" t="s">
+        <v>377</v>
+      </c>
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA0A438-60E6-4D21-B5DB-C825178A79BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82600BC-20C9-4F3B-807D-66F120396827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="379">
   <si>
     <t>Week</t>
   </si>
@@ -1229,6 +1229,9 @@
   </si>
   <si>
     <t>Nog meer experiment? Checken agenda ofzo</t>
+  </si>
+  <si>
+    <t>Video ding maken enzo</t>
   </si>
 </sst>
 </file>
@@ -10987,7 +10990,9 @@
       <c r="C28" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="D28" s="16"/>
+      <c r="D28" s="16" t="s">
+        <v>378</v>
+      </c>
       <c r="E28" s="16" t="s">
         <v>297</v>
       </c>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCCF341-A4EA-441D-97B4-C0A964B62CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2D3149-6694-4954-97FE-C502C2EAB7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="385">
   <si>
     <t>Week</t>
   </si>
@@ -1232,6 +1232,24 @@
   </si>
   <si>
     <t>Video ding maken enzo</t>
+  </si>
+  <si>
+    <t>Geen video meer, wel nog les experiment ofzo?</t>
+  </si>
+  <si>
+    <t>Feedback mogelijk in de ochtend</t>
+  </si>
+  <si>
+    <t>Feedback AZ animation</t>
+  </si>
+  <si>
+    <t>Finalize week begint</t>
+  </si>
+  <si>
+    <t>Feedback + indienen AZ animation tegen 14U!</t>
+  </si>
+  <si>
+    <t>In google doc AZ animatie feedback vragen en whatsapp</t>
   </si>
 </sst>
 </file>
@@ -10984,17 +11002,17 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="22" t="s">
         <v>368</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>297</v>
+      <c r="E28" s="19" t="s">
+        <v>377</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>352</v>
@@ -11002,33 +11020,37 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11"/>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="23" t="s">
         <v>369</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="F29" s="17"/>
+      <c r="E29" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="19" t="s">
-        <v>377</v>
-      </c>
+      <c r="D30" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
+      <c r="D31" s="17" t="s">
+        <v>384</v>
+      </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
     </row>
@@ -11074,51 +11096,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="157" priority="30">
+    <cfRule type="expression" dxfId="157" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="156" priority="29">
+    <cfRule type="expression" dxfId="156" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="155" priority="2">
+    <cfRule type="expression" dxfId="155" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="154" priority="1">
+    <cfRule type="expression" dxfId="154" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="153" priority="3">
+    <cfRule type="expression" dxfId="153" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="152" priority="10">
+    <cfRule type="expression" dxfId="152" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="151" priority="16">
+    <cfRule type="expression" dxfId="151" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="150" priority="25">
+    <cfRule type="expression" dxfId="150" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="149" priority="31">
+    <cfRule type="expression" dxfId="149" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11456,11 +11479,15 @@
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="F28" s="16" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>382</v>
+      </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -11913,7 +11940,9 @@
       <c r="D28" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="16"/>
+      <c r="E28" s="16" t="s">
+        <v>297</v>
+      </c>
       <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
@@ -11921,7 +11950,9 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="E29" s="17" t="s">
+        <v>355</v>
+      </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
@@ -11982,52 +12013,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="139" priority="3">
+    <cfRule type="expression" dxfId="139" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="138" priority="26">
+    <cfRule type="expression" dxfId="138" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="137" priority="25">
+    <cfRule type="expression" dxfId="137" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="136" priority="24">
+    <cfRule type="expression" dxfId="136" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="135" priority="1">
+    <cfRule type="expression" dxfId="135" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="134" priority="27">
+    <cfRule type="expression" dxfId="134" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="133" priority="4">
+    <cfRule type="expression" dxfId="133" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="132" priority="7">
+    <cfRule type="expression" dxfId="132" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="131" priority="17">
+    <cfRule type="expression" dxfId="131" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="130" priority="21">
+    <cfRule type="expression" dxfId="130" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C9EA31-5B2B-4D0F-9DF3-B8F90DE54E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE6DE4B-42F3-4C28-96B5-9106A9A5A46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="388">
   <si>
     <t>Week</t>
   </si>
@@ -1231,9 +1231,6 @@
     <t>Video ding maken enzo</t>
   </si>
   <si>
-    <t>Feedback mogelijk in de ochtend</t>
-  </si>
-  <si>
     <t>Feedback AZ animation</t>
   </si>
   <si>
@@ -1253,6 +1250,15 @@
   </si>
   <si>
     <t>nieuwe proces doc?</t>
+  </si>
+  <si>
+    <t>Crossmedia: mee gaan naar graphius? Moet beslist zijn tegen vandaag</t>
+  </si>
+  <si>
+    <t>Bookmaking: materiaal aankopen</t>
+  </si>
+  <si>
+    <t>veel werken voor A-Z animatie ding</t>
   </si>
 </sst>
 </file>
@@ -11027,39 +11033,39 @@
         <v>369</v>
       </c>
       <c r="C29" s="17"/>
-      <c r="D29" s="16" t="s">
-        <v>347</v>
+      <c r="D29" s="19" t="s">
+        <v>381</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="19" t="s">
-        <v>378</v>
-      </c>
+      <c r="D30" s="17"/>
       <c r="E30" s="19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
@@ -11483,19 +11489,23 @@
       <c r="B28" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>385</v>
+      </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="C29" s="17"/>
+        <v>379</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>386</v>
+      </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955A4E1E-719F-4413-994D-DE3DB68AB5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877C8CEF-A53F-4CC4-8916-8C278525C679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="19" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -1273,7 +1273,7 @@
     <t>Design geschiedenis: boek voorstellen (speciale waarde, waarom dit boek, …) moet gelinked zijn aan het vak en vormgeving</t>
   </si>
   <si>
-    <t>Design geschiedenis gaat niet door, wel savonds komen</t>
+    <t>Design geschiedenis: boek voorstellen (speciale waarde, waarom dit boek, …) moet gelinked zijn aan het vak en vormgeving + inschrijven via link</t>
   </si>
 </sst>
 </file>
@@ -11061,7 +11061,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="23" t="s">
         <v>382</v>
       </c>
       <c r="F30" s="19" t="s">
@@ -11073,7 +11073,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="23" t="s">
         <v>387</v>
       </c>
       <c r="F31" s="16" t="s">
@@ -11085,7 +11085,7 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="23" t="s">
         <v>381</v>
       </c>
       <c r="F32" s="17"/>
@@ -11508,7 +11508,7 @@
         <v>385</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
@@ -12434,7 +12434,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -12505,17 +12505,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="129" priority="12">
+    <cfRule type="expression" dxfId="129" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="128" priority="21">
+    <cfRule type="expression" dxfId="128" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="127" priority="20">
+    <cfRule type="expression" dxfId="127" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12525,27 +12525,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="125" priority="2">
+    <cfRule type="expression" dxfId="125" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="124" priority="4">
+    <cfRule type="expression" dxfId="124" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="123" priority="7">
+    <cfRule type="expression" dxfId="123" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="122" priority="16">
+    <cfRule type="expression" dxfId="122" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="121" priority="22">
+    <cfRule type="expression" dxfId="121" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -12959,17 +12959,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="120" priority="4">
+    <cfRule type="expression" dxfId="120" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="119" priority="27">
+    <cfRule type="expression" dxfId="119" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="118" priority="26">
+    <cfRule type="expression" dxfId="118" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12979,32 +12979,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="116" priority="2">
+    <cfRule type="expression" dxfId="116" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="115" priority="28">
+    <cfRule type="expression" dxfId="115" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="114" priority="21">
+    <cfRule type="expression" dxfId="114" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="113" priority="7">
+    <cfRule type="expression" dxfId="113" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="112" priority="18">
+    <cfRule type="expression" dxfId="112" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="111" priority="22">
+    <cfRule type="expression" dxfId="111" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13342,7 +13342,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -13413,17 +13413,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="110" priority="10">
+    <cfRule type="expression" dxfId="110" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="109" priority="21">
+    <cfRule type="expression" dxfId="109" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="108" priority="20">
+    <cfRule type="expression" dxfId="108" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13433,27 +13433,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="106" priority="2">
+    <cfRule type="expression" dxfId="106" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="105" priority="22">
+    <cfRule type="expression" dxfId="105" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="104" priority="4">
+    <cfRule type="expression" dxfId="104" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="103" priority="6">
+    <cfRule type="expression" dxfId="103" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="102" priority="16">
+    <cfRule type="expression" dxfId="102" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13792,7 +13792,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -13863,17 +13863,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="101" priority="4">
+    <cfRule type="expression" dxfId="101" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="100" priority="25">
+    <cfRule type="expression" dxfId="100" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="99" priority="24">
+    <cfRule type="expression" dxfId="99" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13883,32 +13883,32 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="97" priority="2">
+    <cfRule type="expression" dxfId="97" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="96" priority="26">
+    <cfRule type="expression" dxfId="96" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="95" priority="19">
+    <cfRule type="expression" dxfId="95" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="94" priority="7">
+    <cfRule type="expression" dxfId="94" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="93" priority="17">
+    <cfRule type="expression" dxfId="93" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="92" priority="20">
+    <cfRule type="expression" dxfId="92" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14251,7 +14251,7 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>261</v>
@@ -14324,17 +14324,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F6 E7:F25 B15:D25">
-    <cfRule type="expression" dxfId="91" priority="7">
+    <cfRule type="expression" dxfId="91" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="90" priority="21">
+    <cfRule type="expression" dxfId="90" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="89" priority="20">
+    <cfRule type="expression" dxfId="89" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14344,17 +14344,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="87" priority="2">
+    <cfRule type="expression" dxfId="87" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8 C14:D14">
-    <cfRule type="expression" dxfId="86" priority="4">
+    <cfRule type="expression" dxfId="86" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="85" priority="16">
+    <cfRule type="expression" dxfId="85" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16028,7 +16028,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16091,17 +16091,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="74" priority="2">
+    <cfRule type="expression" dxfId="74" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="73" priority="27">
+    <cfRule type="expression" dxfId="73" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="72" priority="26">
+    <cfRule type="expression" dxfId="72" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16111,17 +16111,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="70" priority="6">
+    <cfRule type="expression" dxfId="70" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="69" priority="4">
+    <cfRule type="expression" dxfId="69" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="68" priority="10">
+    <cfRule type="expression" dxfId="68" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16431,7 +16431,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>40</v>
@@ -16504,17 +16504,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="67" priority="2">
+    <cfRule type="expression" dxfId="67" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="66" priority="32">
+    <cfRule type="expression" dxfId="66" priority="33">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="65" priority="31">
+    <cfRule type="expression" dxfId="65" priority="32">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16524,12 +16524,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="63" priority="10">
+    <cfRule type="expression" dxfId="63" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="62" priority="7">
+    <cfRule type="expression" dxfId="62" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16893,7 +16893,7 @@
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="16" t="s">
         <v>392</v>
       </c>
       <c r="E30" s="17"/>
@@ -16949,17 +16949,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="61" priority="4">
+    <cfRule type="expression" dxfId="61" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="60" priority="35">
+    <cfRule type="expression" dxfId="60" priority="36">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="59" priority="34">
+    <cfRule type="expression" dxfId="59" priority="35">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16969,17 +16969,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="57" priority="2">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="56" priority="28">
+    <cfRule type="expression" dxfId="56" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="55" priority="27">
+    <cfRule type="expression" dxfId="55" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877C8CEF-A53F-4CC4-8916-8C278525C679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC290A20-2A64-422A-8608-1670ACE90A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="15" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="391">
   <si>
     <t>Week</t>
   </si>
@@ -1153,9 +1153,6 @@
     <t>NAAR AZZA ZUIDPARK GAAN AN EXAMEN!</t>
   </si>
   <si>
-    <t>Valentijn</t>
-  </si>
-  <si>
     <t>deadline crossmedia</t>
   </si>
   <si>
@@ -1247,9 +1244,6 @@
   </si>
   <si>
     <t>Geen video meer, thuisblijven</t>
-  </si>
-  <si>
-    <t>nieuwe proces doc?</t>
   </si>
   <si>
     <t>Crossmedia: mee gaan naar graphius? Moet beslist zijn tegen vandaag</t>
@@ -1599,7 +1593,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="305">
     <dxf>
@@ -8506,7 +8500,7 @@
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>321</v>
@@ -9387,7 +9381,7 @@
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>313</v>
@@ -10212,7 +10206,7 @@
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="47" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -10768,10 +10762,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -10779,7 +10773,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E5" s="29" t="s">
         <v>108</v>
@@ -10800,7 +10794,7 @@
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="32" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -10811,7 +10805,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32"/>
@@ -10826,7 +10820,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C8" s="28"/>
       <c r="E8" s="28"/>
@@ -10844,7 +10838,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -10923,7 +10917,7 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>27</v>
@@ -11030,30 +11024,30 @@
         <v>35</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D28" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="F28" s="19" t="s">
         <v>377</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>378</v>
+        <v>382</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -11062,11 +11056,9 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>384</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -11074,11 +11066,9 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>347</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="F31" s="17"/>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
@@ -11086,7 +11076,7 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F32" s="17"/>
     </row>
@@ -11248,11 +11238,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11260,7 +11250,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -11308,7 +11298,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -11324,7 +11314,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -11335,7 +11325,7 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -11505,23 +11495,23 @@
         <v>319</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -11708,10 +11698,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11722,7 +11712,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -11736,7 +11726,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -11751,7 +11741,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
@@ -11785,7 +11775,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="30"/>
@@ -11968,7 +11958,7 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
@@ -11984,10 +11974,10 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F29" s="17"/>
     </row>
@@ -12177,11 +12167,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -12189,7 +12179,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -12237,7 +12227,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -12253,7 +12243,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -12264,7 +12254,7 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -12434,7 +12424,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -12628,10 +12618,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -12642,7 +12632,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -12656,7 +12646,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -12671,7 +12661,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
@@ -12704,7 +12694,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -12884,11 +12874,11 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -13087,11 +13077,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -13099,7 +13089,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -13147,7 +13137,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -13163,7 +13153,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -13174,7 +13164,7 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -13342,7 +13332,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -13536,10 +13526,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -13550,7 +13540,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -13564,7 +13554,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -13610,7 +13600,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -13792,7 +13782,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -13991,10 +13981,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -14002,7 +13992,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -14056,7 +14046,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -14251,7 +14241,7 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>261</v>
@@ -14866,10 +14856,10 @@
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -14880,7 +14870,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -14894,7 +14884,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -14940,7 +14930,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15317,10 +15307,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -15331,7 +15321,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -15345,7 +15335,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -15391,7 +15381,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15768,10 +15758,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -15779,7 +15769,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -15833,7 +15823,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16028,7 +16018,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16204,10 +16194,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -16215,7 +16205,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -16262,7 +16252,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -16277,7 +16267,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F10" s="5"/>
     </row>
@@ -16287,7 +16277,7 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F11" s="5"/>
     </row>
@@ -16431,7 +16421,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>40</v>
@@ -16612,10 +16602,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -16626,7 +16616,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -16640,7 +16630,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -16686,7 +16676,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16874,7 +16864,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -16884,7 +16874,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16894,7 +16884,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17062,11 +17052,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -17077,7 +17067,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -17092,7 +17082,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
@@ -17133,7 +17123,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -17150,7 +17140,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -17162,7 +17152,7 @@
       <c r="B11" s="7"/>
       <c r="C11" s="28"/>
       <c r="D11" s="68" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -17332,7 +17322,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -17342,7 +17332,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -17523,10 +17513,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -17537,7 +17527,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -17551,7 +17541,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -17597,7 +17587,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -17983,10 +17973,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -17997,7 +17987,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -18011,7 +18001,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -18057,7 +18047,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18445,10 +18435,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -18459,7 +18449,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -18473,7 +18463,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -18519,7 +18509,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18903,10 +18893,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -18917,7 +18907,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -18931,7 +18921,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -18977,7 +18967,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19812,10 +19802,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -19826,7 +19816,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -19840,7 +19830,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -19886,7 +19876,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -20280,10 +20270,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -20294,7 +20284,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -20308,7 +20298,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
@@ -20354,7 +20344,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC290A20-2A64-422A-8608-1670ACE90A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E28E15-9971-4BF8-9F91-BE052B6B85AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" firstSheet="15" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24090" yWindow="2190" windowWidth="21600" windowHeight="11300" firstSheet="15" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="394">
   <si>
     <t>Week</t>
   </si>
@@ -1268,6 +1268,15 @@
   </si>
   <si>
     <t>Design geschiedenis: boek voorstellen (speciale waarde, waarom dit boek, …) moet gelinked zijn aan het vak en vormgeving + inschrijven via link</t>
+  </si>
+  <si>
+    <t>SD: new briefing with special request</t>
+  </si>
+  <si>
+    <t>9-18u normal feedback mixed with jury feedback (lists and organisation follow)</t>
+  </si>
+  <si>
+    <t>IETS MEEDOEN NAAR DE KLAS (take something that you don't use everyday, but think is cool looking!) something that speaks to you from a vibe/esthetic point of view. Iets "brandingbaar"</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1602,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="305">
     <dxf>
@@ -11515,12 +11524,16 @@
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="F29" s="17" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="C30" s="19" t="s">
+        <v>391</v>
+      </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -11528,7 +11541,9 @@
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="C31" s="16" t="s">
+        <v>393</v>
+      </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E28E15-9971-4BF8-9F91-BE052B6B85AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A89F08-EBED-45BF-8C5E-86DDE124CF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24090" yWindow="2190" windowWidth="21600" windowHeight="11300" firstSheet="15" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -11041,7 +11041,7 @@
       <c r="E28" s="23" t="s">
         <v>375</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="23" t="s">
         <v>377</v>
       </c>
     </row>
@@ -11516,45 +11516,45 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="19" t="s">
         <v>378</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17" t="s">
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="19"/>
       <c r="C30" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="19"/>
       <c r="C31" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A89F08-EBED-45BF-8C5E-86DDE124CF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22050052-AA56-40B1-8557-9BF1EB948521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -28,14 +28,14 @@
     <sheet name="Week 12" sheetId="16" r:id="rId13"/>
     <sheet name="Week 13" sheetId="17" r:id="rId14"/>
     <sheet name="Week 14" sheetId="18" r:id="rId15"/>
-    <sheet name="Week 15" sheetId="19" r:id="rId16"/>
-    <sheet name="Week 16" sheetId="20" r:id="rId17"/>
-    <sheet name="Week 17" sheetId="21" r:id="rId18"/>
-    <sheet name="Week 18" sheetId="22" r:id="rId19"/>
-    <sheet name="Week 19" sheetId="23" r:id="rId20"/>
-    <sheet name="Week 20" sheetId="24" r:id="rId21"/>
-    <sheet name="Week 21" sheetId="25" r:id="rId22"/>
-    <sheet name="Week 22" sheetId="26" r:id="rId23"/>
+    <sheet name="Week 22" sheetId="26" r:id="rId16"/>
+    <sheet name="Week 15" sheetId="19" r:id="rId17"/>
+    <sheet name="Week 16" sheetId="20" r:id="rId18"/>
+    <sheet name="Week 17" sheetId="21" r:id="rId19"/>
+    <sheet name="Week 18" sheetId="22" r:id="rId20"/>
+    <sheet name="Week 19" sheetId="23" r:id="rId21"/>
+    <sheet name="Week 20" sheetId="24" r:id="rId22"/>
+    <sheet name="Week 21" sheetId="25" r:id="rId23"/>
     <sheet name="Week 23" sheetId="27" r:id="rId24"/>
     <sheet name="Week 24" sheetId="28" r:id="rId25"/>
     <sheet name="Week 25" sheetId="29" r:id="rId26"/>
@@ -7661,6 +7661,472 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1003C9-1B1D-4C87-A4F1-C57BF5E9D303}">
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="6" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4">
+        <v>22</v>
+      </c>
+      <c r="D1" s="18">
+        <f>C1/Data!B2</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8">
+        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
+        <v>45705</v>
+      </c>
+      <c r="C3" s="8">
+        <f>B3+1</f>
+        <v>45706</v>
+      </c>
+      <c r="D3" s="8">
+        <f>C3+1</f>
+        <v>45707</v>
+      </c>
+      <c r="E3" s="8">
+        <f>D3+1</f>
+        <v>45708</v>
+      </c>
+      <c r="F3" s="8">
+        <f>E3+1</f>
+        <v>45709</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="H4" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="F7" s="5"/>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="F8" s="5"/>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>0.54166666666666696</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D15" s="36"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="33"/>
+      <c r="F16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+    </row>
+    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+    </row>
+    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+    </row>
+    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+    </row>
+    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+    </row>
+    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+    </row>
+    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4 F5:F14 B15:B25">
+    <cfRule type="expression" dxfId="148" priority="12">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="147" priority="29">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
+    <cfRule type="expression" dxfId="146" priority="28">
+      <formula>B3 = TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="145" priority="27">
+      <formula>NOT(ISBLANK(B28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C25">
+    <cfRule type="expression" dxfId="144" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:D15">
+    <cfRule type="expression" dxfId="143" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E25">
+    <cfRule type="expression" dxfId="142" priority="9">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:F25">
+    <cfRule type="expression" dxfId="141" priority="24">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H19 J17:J21">
+    <cfRule type="expression" dxfId="140" priority="30">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FEC417-0927-464E-94D2-92EC928AAF8C}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8145,7 +8611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE344092-AF2F-4CC8-8CEA-BA4A03843B53}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8587,7 +9053,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79B1A04-F46B-4F28-AC40-C23EF67608FF}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9015,456 +9481,6 @@
   <conditionalFormatting sqref="F14">
     <cfRule type="expression" dxfId="173" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2541638-04C8-411C-9550-9517F44E2AF8}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="6" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4">
-        <v>18</v>
-      </c>
-      <c r="D1" s="18">
-        <f>C1/Data!B2</f>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="8">
-        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
-        <v>45677</v>
-      </c>
-      <c r="C3" s="8">
-        <f>B3+1</f>
-        <v>45678</v>
-      </c>
-      <c r="D3" s="8">
-        <f>C3+1</f>
-        <v>45679</v>
-      </c>
-      <c r="E3" s="8">
-        <f>D3+1</f>
-        <v>45680</v>
-      </c>
-      <c r="F3" s="8">
-        <f>E3+1</f>
-        <v>45681</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="F4" s="37"/>
-      <c r="H4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="F5" s="38"/>
-      <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="D6" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="38"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="F7" s="38"/>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>0.4375</v>
-      </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="38"/>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="38"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>0.45833333333333398</v>
-      </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="38"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="38"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="38"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>0.53125</v>
-      </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="38"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>0.5625</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="37"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="38"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="38"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="38"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="38"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>0.6875</v>
-      </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="38"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="38"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="38"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="38"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="C25" s="38"/>
-      <c r="F25" s="38"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-    </row>
-    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-    </row>
-    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-    </row>
-    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="172" priority="18">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="171" priority="2">
-      <formula>NOT(ISBLANK(B31))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="170" priority="32">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="169" priority="31">
-      <formula>B3 = TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="168" priority="5">
-      <formula>NOT(ISBLANK(B28))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="167" priority="1">
-      <formula>NOT(ISBLANK(B33))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="166" priority="3">
-      <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9904,6 +9920,456 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2541638-04C8-411C-9550-9517F44E2AF8}">
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="6" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4">
+        <v>18</v>
+      </c>
+      <c r="D1" s="18">
+        <f>C1/Data!B2</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8">
+        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
+        <v>45677</v>
+      </c>
+      <c r="C3" s="8">
+        <f>B3+1</f>
+        <v>45678</v>
+      </c>
+      <c r="D3" s="8">
+        <f>C3+1</f>
+        <v>45679</v>
+      </c>
+      <c r="E3" s="8">
+        <f>D3+1</f>
+        <v>45680</v>
+      </c>
+      <c r="F3" s="8">
+        <f>E3+1</f>
+        <v>45681</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="F4" s="37"/>
+      <c r="H4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="38"/>
+      <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="38"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="38"/>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D8" s="52"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="38"/>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="38"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="38"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="D11" s="52"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="38"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="52"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="38"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="D13" s="52"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="38"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="37"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="C17" s="38"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="38"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C18" s="38"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="38"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="38"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="C20" s="38"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="38"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="38"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="C22" s="38"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="38"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="C23" s="38"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="C24" s="38"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="38"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C25" s="38"/>
+      <c r="F25" s="38"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+    </row>
+    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+    </row>
+    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+    </row>
+    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4:C4 F4 B5:F25">
+    <cfRule type="expression" dxfId="172" priority="18">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:E32">
+    <cfRule type="expression" dxfId="171" priority="2">
+      <formula>NOT(ISBLANK(B31))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="170" priority="32">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
+    <cfRule type="expression" dxfId="169" priority="31">
+      <formula>B3 = TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:F30">
+    <cfRule type="expression" dxfId="168" priority="5">
+      <formula>NOT(ISBLANK(B28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:F36">
+    <cfRule type="expression" dxfId="167" priority="1">
+      <formula>NOT(ISBLANK(B33))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F32">
+    <cfRule type="expression" dxfId="166" priority="3">
+      <formula>NOT(ISBLANK(F30))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21C3BF1-5D0C-4522-B17E-2E9DEAE2158F}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10316,7 +10782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A7CBCC-4A7F-411E-AE6E-73D8D99D1A8E}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10696,7 +11162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5250EE95-0BED-45B5-9E71-085C4126A053}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11169,472 +11635,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1003C9-1B1D-4C87-A4F1-C57BF5E9D303}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="6" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4">
-        <v>22</v>
-      </c>
-      <c r="D1" s="18">
-        <f>C1/Data!B2</f>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="8">
-        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
-        <v>45705</v>
-      </c>
-      <c r="C3" s="8">
-        <f>B3+1</f>
-        <v>45706</v>
-      </c>
-      <c r="D3" s="8">
-        <f>C3+1</f>
-        <v>45707</v>
-      </c>
-      <c r="E3" s="8">
-        <f>D3+1</f>
-        <v>45708</v>
-      </c>
-      <c r="F3" s="8">
-        <f>E3+1</f>
-        <v>45709</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
-      <c r="E4" s="33"/>
-      <c r="H4" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="F7" s="5"/>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>0.4375</v>
-      </c>
-      <c r="C8" s="28"/>
-      <c r="F8" s="5"/>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>0.45833333333333398</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>0.53125</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>0.54166666666666696</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>0.5625</v>
-      </c>
-      <c r="D15" s="36"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>390</v>
-      </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-    </row>
-    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-    </row>
-    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-    </row>
-    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-    </row>
-    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-    </row>
-    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-    </row>
-    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="148" priority="12">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="147" priority="29">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="146" priority="28">
-      <formula>B3 = TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="145" priority="27">
-      <formula>NOT(ISBLANK(B28))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="144" priority="1">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="143" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="142" priority="9">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="141" priority="24">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="140" priority="30">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22050052-AA56-40B1-8557-9BF1EB948521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C06628-A079-49BF-A188-FE667981E70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21820" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="395">
   <si>
     <t>Week</t>
   </si>
@@ -1277,6 +1277,9 @@
   </si>
   <si>
     <t>IETS MEEDOEN NAAR DE KLAS (take something that you don't use everyday, but think is cool looking!) something that speaks to you from a vibe/esthetic point of view. Iets "brandingbaar"</t>
+  </si>
+  <si>
+    <t>bookmaking crossmedia: materiaal aankopen</t>
   </si>
 </sst>
 </file>
@@ -2948,6 +2951,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2972,6 +2985,13 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2983,6 +3003,30 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -2993,6 +3037,68 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -3002,6 +3108,27 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -3013,6 +3140,44 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -3023,6 +3188,23 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -3066,13 +3248,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -3084,30 +3259,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -3118,68 +3269,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -3189,98 +3278,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8039,7 +8042,9 @@
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
+      <c r="C32" s="19" t="s">
+        <v>394</v>
+      </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
@@ -8078,47 +8083,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="148" priority="12">
+    <cfRule type="expression" dxfId="190" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="147" priority="29">
+    <cfRule type="expression" dxfId="189" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="146" priority="28">
+    <cfRule type="expression" dxfId="188" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="145" priority="27">
+    <cfRule type="expression" dxfId="187" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="144" priority="1">
+    <cfRule type="expression" dxfId="186" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="143" priority="3">
+    <cfRule type="expression" dxfId="185" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="142" priority="9">
+    <cfRule type="expression" dxfId="184" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="141" priority="24">
+    <cfRule type="expression" dxfId="183" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="140" priority="30">
+    <cfRule type="expression" dxfId="182" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8578,32 +8583,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="190" priority="21">
+    <cfRule type="expression" dxfId="181" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="189" priority="43">
+    <cfRule type="expression" dxfId="180" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="188" priority="42">
+    <cfRule type="expression" dxfId="179" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="187" priority="1">
+    <cfRule type="expression" dxfId="178" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="186" priority="16">
+    <cfRule type="expression" dxfId="177" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="185" priority="24">
+    <cfRule type="expression" dxfId="176" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9019,32 +9024,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="184" priority="30">
+    <cfRule type="expression" dxfId="175" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="183" priority="29">
+    <cfRule type="expression" dxfId="174" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="182" priority="16">
+    <cfRule type="expression" dxfId="173" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="181" priority="1">
+    <cfRule type="expression" dxfId="172" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="180" priority="4">
+    <cfRule type="expression" dxfId="171" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="179" priority="5">
+    <cfRule type="expression" dxfId="170" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9454,32 +9459,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="178" priority="39">
+    <cfRule type="expression" dxfId="169" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="177" priority="38">
+    <cfRule type="expression" dxfId="168" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="176" priority="20">
+    <cfRule type="expression" dxfId="167" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="175" priority="1">
+    <cfRule type="expression" dxfId="166" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="174" priority="3">
+    <cfRule type="expression" dxfId="165" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="173" priority="2">
+    <cfRule type="expression" dxfId="164" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10331,37 +10336,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="172" priority="18">
+    <cfRule type="expression" dxfId="163" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="171" priority="2">
+    <cfRule type="expression" dxfId="162" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="170" priority="32">
+    <cfRule type="expression" dxfId="161" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="169" priority="31">
+    <cfRule type="expression" dxfId="160" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="168" priority="5">
+    <cfRule type="expression" dxfId="159" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="167" priority="1">
+    <cfRule type="expression" dxfId="158" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="166" priority="3">
+    <cfRule type="expression" dxfId="157" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10758,22 +10763,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="165" priority="32">
+    <cfRule type="expression" dxfId="156" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="164" priority="31">
+    <cfRule type="expression" dxfId="155" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="163" priority="12">
+    <cfRule type="expression" dxfId="154" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="1">
+    <cfRule type="expression" dxfId="153" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11139,22 +11144,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="17">
+    <cfRule type="expression" dxfId="152" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="16">
+    <cfRule type="expression" dxfId="151" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="159" priority="2">
+    <cfRule type="expression" dxfId="150" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="158" priority="1">
+    <cfRule type="expression" dxfId="149" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11589,47 +11594,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="157" priority="32">
+    <cfRule type="expression" dxfId="148" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="156" priority="31">
+    <cfRule type="expression" dxfId="147" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="155" priority="1">
+    <cfRule type="expression" dxfId="146" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="154" priority="3">
+    <cfRule type="expression" dxfId="145" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="153" priority="5">
+    <cfRule type="expression" dxfId="144" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="152" priority="12">
+    <cfRule type="expression" dxfId="143" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="151" priority="18">
+    <cfRule type="expression" dxfId="142" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="150" priority="27">
+    <cfRule type="expression" dxfId="141" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="149" priority="33">
+    <cfRule type="expression" dxfId="140" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C06628-A079-49BF-A188-FE667981E70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2E5497-396F-4BD3-864F-837EA1180BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21820" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="18" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -28,14 +28,14 @@
     <sheet name="Week 12" sheetId="16" r:id="rId13"/>
     <sheet name="Week 13" sheetId="17" r:id="rId14"/>
     <sheet name="Week 14" sheetId="18" r:id="rId15"/>
-    <sheet name="Week 22" sheetId="26" r:id="rId16"/>
-    <sheet name="Week 15" sheetId="19" r:id="rId17"/>
-    <sheet name="Week 16" sheetId="20" r:id="rId18"/>
-    <sheet name="Week 17" sheetId="21" r:id="rId19"/>
-    <sheet name="Week 18" sheetId="22" r:id="rId20"/>
-    <sheet name="Week 19" sheetId="23" r:id="rId21"/>
-    <sheet name="Week 20" sheetId="24" r:id="rId22"/>
-    <sheet name="Week 21" sheetId="25" r:id="rId23"/>
+    <sheet name="Week 15" sheetId="19" r:id="rId16"/>
+    <sheet name="Week 16" sheetId="20" r:id="rId17"/>
+    <sheet name="Week 17" sheetId="21" r:id="rId18"/>
+    <sheet name="Week 18" sheetId="22" r:id="rId19"/>
+    <sheet name="Week 19" sheetId="23" r:id="rId20"/>
+    <sheet name="Week 20" sheetId="24" r:id="rId21"/>
+    <sheet name="Week 21" sheetId="25" r:id="rId22"/>
+    <sheet name="Week 22" sheetId="26" r:id="rId23"/>
     <sheet name="Week 23" sheetId="27" r:id="rId24"/>
     <sheet name="Week 24" sheetId="28" r:id="rId25"/>
     <sheet name="Week 25" sheetId="29" r:id="rId26"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1664" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="394">
   <si>
     <t>Week</t>
   </si>
@@ -1247,9 +1247,6 @@
   </si>
   <si>
     <t>Crossmedia: mee gaan naar graphius? Moet beslist zijn tegen vandaag</t>
-  </si>
-  <si>
-    <t>Bookmaking: materiaal aankopen</t>
   </si>
   <si>
     <t>veel werken voor A-Z animatie ding</t>
@@ -1468,7 +1465,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1594,6 +1591,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="6" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -7664,474 +7664,6 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1003C9-1B1D-4C87-A4F1-C57BF5E9D303}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="6" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4">
-        <v>22</v>
-      </c>
-      <c r="D1" s="18">
-        <f>C1/Data!B2</f>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="8">
-        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
-        <v>45705</v>
-      </c>
-      <c r="C3" s="8">
-        <f>B3+1</f>
-        <v>45706</v>
-      </c>
-      <c r="D3" s="8">
-        <f>C3+1</f>
-        <v>45707</v>
-      </c>
-      <c r="E3" s="8">
-        <f>D3+1</f>
-        <v>45708</v>
-      </c>
-      <c r="F3" s="8">
-        <f>E3+1</f>
-        <v>45709</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
-      <c r="E4" s="33"/>
-      <c r="H4" s="7" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="F7" s="5"/>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>0.4375</v>
-      </c>
-      <c r="C8" s="28"/>
-      <c r="F8" s="5"/>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>0.45833333333333398</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>0.53125</v>
-      </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>0.54166666666666696</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>0.5625</v>
-      </c>
-      <c r="D15" s="36"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F21" s="5"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="F23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>390</v>
-      </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19" t="s">
-        <v>391</v>
-      </c>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-    </row>
-    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-    </row>
-    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19" t="s">
-        <v>394</v>
-      </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-    </row>
-    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-    </row>
-    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-    </row>
-    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-    </row>
-    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="190" priority="12">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="189" priority="29">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="188" priority="28">
-      <formula>B3 = TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="187" priority="27">
-      <formula>NOT(ISBLANK(B28))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="186" priority="1">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="185" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="184" priority="9">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="183" priority="24">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="182" priority="30">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FEC417-0927-464E-94D2-92EC928AAF8C}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8616,7 +8148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE344092-AF2F-4CC8-8CEA-BA4A03843B53}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9058,7 +8590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79B1A04-F46B-4F28-AC40-C23EF67608FF}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9486,6 +9018,456 @@
   <conditionalFormatting sqref="F14">
     <cfRule type="expression" dxfId="164" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2541638-04C8-411C-9550-9517F44E2AF8}">
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="6" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4">
+        <v>18</v>
+      </c>
+      <c r="D1" s="18">
+        <f>C1/Data!B2</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8">
+        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
+        <v>45677</v>
+      </c>
+      <c r="C3" s="8">
+        <f>B3+1</f>
+        <v>45678</v>
+      </c>
+      <c r="D3" s="8">
+        <f>C3+1</f>
+        <v>45679</v>
+      </c>
+      <c r="E3" s="8">
+        <f>D3+1</f>
+        <v>45680</v>
+      </c>
+      <c r="F3" s="8">
+        <f>E3+1</f>
+        <v>45681</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C4" s="33"/>
+      <c r="F4" s="37"/>
+      <c r="H4" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="F5" s="38"/>
+      <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="38"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="38"/>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="D8" s="52"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="38"/>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="38"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="38"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="D11" s="52"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="38"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="52"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="38"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="D13" s="52"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="38"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="37"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="C17" s="38"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="38"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="C18" s="38"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="38"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="C19" s="38"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="38"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="C20" s="38"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="38"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>0.6875</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="38"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="C22" s="38"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="38"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="C23" s="38"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="C24" s="38"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="38"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C25" s="38"/>
+      <c r="F25" s="38"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>313</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+    </row>
+    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+    </row>
+    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+    </row>
+    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4:C4 F4 B5:F25">
+    <cfRule type="expression" dxfId="163" priority="18">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31:E32">
+    <cfRule type="expression" dxfId="162" priority="2">
+      <formula>NOT(ISBLANK(B31))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="161" priority="32">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
+    <cfRule type="expression" dxfId="160" priority="31">
+      <formula>B3 = TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:F30">
+    <cfRule type="expression" dxfId="159" priority="5">
+      <formula>NOT(ISBLANK(B28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B33:F36">
+    <cfRule type="expression" dxfId="158" priority="1">
+      <formula>NOT(ISBLANK(B33))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F32">
+    <cfRule type="expression" dxfId="157" priority="3">
+      <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9925,456 +9907,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2541638-04C8-411C-9550-9517F44E2AF8}">
-  <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="6" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4">
-        <v>18</v>
-      </c>
-      <c r="D1" s="18">
-        <f>C1/Data!B2</f>
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="8">
-        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
-        <v>45677</v>
-      </c>
-      <c r="C3" s="8">
-        <f>B3+1</f>
-        <v>45678</v>
-      </c>
-      <c r="D3" s="8">
-        <f>C3+1</f>
-        <v>45679</v>
-      </c>
-      <c r="E3" s="8">
-        <f>D3+1</f>
-        <v>45680</v>
-      </c>
-      <c r="F3" s="8">
-        <f>E3+1</f>
-        <v>45681</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="F4" s="37"/>
-      <c r="H4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>0.375</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="F5" s="38"/>
-      <c r="H5" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>0.39583333333333298</v>
-      </c>
-      <c r="D6" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="38"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>0.41666666666666702</v>
-      </c>
-      <c r="D7" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="E7" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="F7" s="38"/>
-      <c r="H7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>0.4375</v>
-      </c>
-      <c r="D8" s="52"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="38"/>
-      <c r="H8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>0.44791666666666669</v>
-      </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="38"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>0.45833333333333398</v>
-      </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="38"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>0.47916666666666702</v>
-      </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="56"/>
-      <c r="F11" s="38"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="52"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="38"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>0.53125</v>
-      </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="38"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>0.5625</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>0.58333333333333304</v>
-      </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="37"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>0.60416666666666696</v>
-      </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="38"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>0.625</v>
-      </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="38"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>0.64583333333333304</v>
-      </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="38"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>0.66666666666666696</v>
-      </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="38"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>0.6875</v>
-      </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="38"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="38"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>0.72916666666666696</v>
-      </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="38"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="51"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="38"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="C25" s="38"/>
-      <c r="F25" s="38"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11"/>
-      <c r="B31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="E31" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-    </row>
-    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-    </row>
-    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-    </row>
-    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="163" priority="18">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="162" priority="2">
-      <formula>NOT(ISBLANK(B31))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="32">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="31">
-      <formula>B3 = TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="159" priority="5">
-      <formula>NOT(ISBLANK(B28))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="158" priority="1">
-      <formula>NOT(ISBLANK(B33))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="157" priority="3">
-      <formula>NOT(ISBLANK(F30))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21C3BF1-5D0C-4522-B17E-2E9DEAE2158F}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10787,7 +10319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A7CBCC-4A7F-411E-AE6E-73D8D99D1A8E}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11167,7 +10699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5250EE95-0BED-45B5-9E71-085C4126A053}">
   <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11546,7 +11078,7 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F31" s="17"/>
     </row>
@@ -11640,6 +11172,473 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1003C9-1B1D-4C87-A4F1-C57BF5E9D303}">
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="6" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="64.5" x14ac:dyDescent="0.95">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4">
+        <v>22</v>
+      </c>
+      <c r="D1" s="18">
+        <f>C1/Data!B2</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="8">
+        <f>DATE(2024,9,23) + ((C1-1)*7)</f>
+        <v>45705</v>
+      </c>
+      <c r="C3" s="8">
+        <f>B3+1</f>
+        <v>45706</v>
+      </c>
+      <c r="D3" s="8">
+        <f>C3+1</f>
+        <v>45707</v>
+      </c>
+      <c r="E3" s="8">
+        <f>D3+1</f>
+        <v>45708</v>
+      </c>
+      <c r="F3" s="8">
+        <f>E3+1</f>
+        <v>45709</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="H4" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>0.39583333333333298</v>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="F7" s="5"/>
+      <c r="H7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>0.4375</v>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="F8" s="5"/>
+      <c r="H8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="10">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="35"/>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>0.45833333333333398</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>0.47916666666666702</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>0.53125</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>0.54166666666666696</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>0.5625</v>
+      </c>
+      <c r="D15" s="36"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="33"/>
+      <c r="F16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>0.60416666666666696</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>0.64583333333333304</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>0.72916666666666696</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
+      <c r="B28" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11"/>
+      <c r="B29" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="C29" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="70" t="s">
+        <v>390</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+    </row>
+    <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+    </row>
+    <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+    </row>
+    <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+    </row>
+    <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+    </row>
+    <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+    </row>
+    <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B4 F5:F14 B15:B25">
+    <cfRule type="expression" dxfId="190" priority="12">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="189" priority="29">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
+    <cfRule type="expression" dxfId="188" priority="28">
+      <formula>B3 = TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="187" priority="27">
+      <formula>NOT(ISBLANK(B28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C25">
+    <cfRule type="expression" dxfId="186" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:D15">
+    <cfRule type="expression" dxfId="185" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E25">
+    <cfRule type="expression" dxfId="184" priority="9">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:F25">
+    <cfRule type="expression" dxfId="183" priority="24">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15:H19 J17:J21">
+    <cfRule type="expression" dxfId="182" priority="30">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11994,7 +11993,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>354</v>
@@ -12444,7 +12443,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -12898,7 +12897,7 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -13352,7 +13351,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -13802,7 +13801,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -14261,7 +14260,7 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>261</v>
@@ -16038,7 +16037,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16441,7 +16440,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>40</v>
@@ -16884,7 +16883,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -16894,7 +16893,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16904,7 +16903,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="16" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17342,7 +17341,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -17352,7 +17351,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="16" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2E5497-396F-4BD3-864F-837EA1180BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F9D5A0-152F-4627-BB09-FD4BE57F8495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="18" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1663" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="401">
   <si>
     <t>Week</t>
   </si>
@@ -1277,6 +1277,27 @@
   </si>
   <si>
     <t>bookmaking crossmedia: materiaal aankopen</t>
+  </si>
+  <si>
+    <t>Studiereis Parijs</t>
+  </si>
+  <si>
+    <t>Feedback 3 mooboards/lighting Tut</t>
+  </si>
+  <si>
+    <t>Feedback styleframe</t>
+  </si>
+  <si>
+    <t>Feedback + tech support</t>
+  </si>
+  <si>
+    <t>Feedback</t>
+  </si>
+  <si>
+    <t>Deadline opdracht "in the right direction"</t>
+  </si>
+  <si>
+    <t>Alles op google doc updaten</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1486,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1592,9 +1613,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="6" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="20% - Accent2" xfId="3" builtinId="34"/>
@@ -2951,6 +2969,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2961,6 +3003,66 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -3200,90 +3302,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8115,32 +8133,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="181" priority="21">
+    <cfRule type="expression" dxfId="190" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="180" priority="43">
+    <cfRule type="expression" dxfId="189" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="179" priority="42">
+    <cfRule type="expression" dxfId="188" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="178" priority="1">
+    <cfRule type="expression" dxfId="187" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="177" priority="16">
+    <cfRule type="expression" dxfId="186" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="176" priority="24">
+    <cfRule type="expression" dxfId="185" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8556,32 +8574,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="175" priority="30">
+    <cfRule type="expression" dxfId="184" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="174" priority="29">
+    <cfRule type="expression" dxfId="183" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="173" priority="16">
+    <cfRule type="expression" dxfId="182" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="172" priority="1">
+    <cfRule type="expression" dxfId="181" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="171" priority="4">
+    <cfRule type="expression" dxfId="180" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="170" priority="5">
+    <cfRule type="expression" dxfId="179" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8991,32 +9009,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="169" priority="39">
+    <cfRule type="expression" dxfId="178" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="168" priority="38">
+    <cfRule type="expression" dxfId="177" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="167" priority="20">
+    <cfRule type="expression" dxfId="176" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="166" priority="1">
+    <cfRule type="expression" dxfId="175" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="165" priority="3">
+    <cfRule type="expression" dxfId="174" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="164" priority="2">
+    <cfRule type="expression" dxfId="173" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9436,37 +9454,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="163" priority="18">
+    <cfRule type="expression" dxfId="172" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="162" priority="2">
+    <cfRule type="expression" dxfId="171" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="32">
+    <cfRule type="expression" dxfId="170" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="31">
+    <cfRule type="expression" dxfId="169" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="159" priority="5">
+    <cfRule type="expression" dxfId="168" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="158" priority="1">
+    <cfRule type="expression" dxfId="167" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="157" priority="3">
+    <cfRule type="expression" dxfId="166" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10295,22 +10313,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="156" priority="32">
+    <cfRule type="expression" dxfId="165" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="155" priority="31">
+    <cfRule type="expression" dxfId="164" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="154" priority="12">
+    <cfRule type="expression" dxfId="163" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="153" priority="1">
+    <cfRule type="expression" dxfId="162" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10676,22 +10694,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="152" priority="17">
+    <cfRule type="expression" dxfId="161" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="151" priority="16">
+    <cfRule type="expression" dxfId="160" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="150" priority="2">
+    <cfRule type="expression" dxfId="159" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="149" priority="1">
+    <cfRule type="expression" dxfId="158" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11126,47 +11144,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="148" priority="32">
+    <cfRule type="expression" dxfId="157" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="147" priority="31">
+    <cfRule type="expression" dxfId="156" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="146" priority="1">
+    <cfRule type="expression" dxfId="155" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="145" priority="3">
+    <cfRule type="expression" dxfId="154" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="144" priority="5">
+    <cfRule type="expression" dxfId="153" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="143" priority="12">
+    <cfRule type="expression" dxfId="152" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="142" priority="18">
+    <cfRule type="expression" dxfId="151" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="141" priority="27">
+    <cfRule type="expression" dxfId="150" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="140" priority="33">
+    <cfRule type="expression" dxfId="149" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11506,12 +11524,10 @@
       <c r="B28" s="22" t="s">
         <v>319</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="22" t="s">
         <v>383</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>389</v>
-      </c>
+      <c r="D28" s="19"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
         <v>379</v>
@@ -11522,7 +11538,7 @@
       <c r="B29" s="23" t="s">
         <v>378</v>
       </c>
-      <c r="C29" s="70" t="s">
+      <c r="C29" s="23" t="s">
         <v>393</v>
       </c>
       <c r="D29" s="19"/>
@@ -11534,12 +11550,14 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="19"/>
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="23" t="s">
         <v>390</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="F30" s="19" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -11549,7 +11567,9 @@
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
+      <c r="F31" s="19" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
@@ -11593,47 +11613,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="190" priority="12">
+    <cfRule type="expression" dxfId="148" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="189" priority="29">
+    <cfRule type="expression" dxfId="147" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="188" priority="28">
+    <cfRule type="expression" dxfId="146" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="187" priority="27">
+    <cfRule type="expression" dxfId="145" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="186" priority="1">
+    <cfRule type="expression" dxfId="144" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="185" priority="3">
+    <cfRule type="expression" dxfId="143" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="184" priority="9">
+    <cfRule type="expression" dxfId="142" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="183" priority="24">
+    <cfRule type="expression" dxfId="141" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="182" priority="30">
+    <cfRule type="expression" dxfId="140" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11979,14 +11999,18 @@
       <c r="B28" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>396</v>
+      </c>
       <c r="D28" s="16" t="s">
         <v>36</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="F28" s="16"/>
+      <c r="F28" s="16" t="s">
+        <v>397</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
@@ -12441,12 +12465,16 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>398</v>
+      </c>
       <c r="D28" s="16" t="s">
         <v>389</v>
       </c>
       <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="F28" s="16" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
@@ -12895,7 +12923,9 @@
       <c r="B28" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>399</v>
+      </c>
       <c r="D28" s="16" t="s">
         <v>389</v>
       </c>
@@ -16035,18 +16065,26 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="C29" s="17" t="s">
+        <v>394</v>
+      </c>
       <c r="D29" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="E29" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
+      <c r="D30" s="17" t="s">
+        <v>394</v>
+      </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F9D5A0-152F-4627-BB09-FD4BE57F8495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54062ACF-9825-408D-A909-3C9F65510413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="402">
   <si>
     <t>Week</t>
   </si>
@@ -1298,6 +1298,9 @@
   </si>
   <si>
     <t>Alles op google doc updaten</t>
+  </si>
+  <si>
+    <t>Trein boeken!</t>
   </si>
 </sst>
 </file>
@@ -11577,7 +11580,9 @@
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
+      <c r="F32" s="19" t="s">
+        <v>401</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0DA649-F5FD-42AF-A24F-37961F7488D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79394737-0EEB-4208-806D-B10F42EEA629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="22" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="20" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="16"/>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="22" t="s">
         <v>379</v>
       </c>
     </row>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="23" t="s">
         <v>391</v>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="23" t="s">
         <v>395</v>
       </c>
     </row>
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="23" t="s">
         <v>400</v>
       </c>
     </row>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8135A9E2-CAF0-4ABD-BCDE-7A380C6A37AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A5B82F-22F7-4639-B918-AF8ECC52B01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -1634,21 +1634,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="307">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="305">
     <dxf>
       <font>
         <color theme="1"/>
@@ -5170,47 +5156,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="253" priority="17">
+    <cfRule type="expression" dxfId="251" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="252" priority="25">
+    <cfRule type="expression" dxfId="250" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="251" priority="24">
+    <cfRule type="expression" dxfId="249" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="250" priority="5">
+    <cfRule type="expression" dxfId="248" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="249" priority="9">
+    <cfRule type="expression" dxfId="247" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="248" priority="8">
+    <cfRule type="expression" dxfId="246" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="247" priority="11">
+    <cfRule type="expression" dxfId="245" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="246" priority="15">
+    <cfRule type="expression" dxfId="244" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="245" priority="2">
+    <cfRule type="expression" dxfId="243" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5669,42 +5655,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="244" priority="15">
+    <cfRule type="expression" dxfId="242" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="243" priority="10">
+    <cfRule type="expression" dxfId="241" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="242" priority="24">
+    <cfRule type="expression" dxfId="240" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="241" priority="23">
+    <cfRule type="expression" dxfId="239" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="240" priority="1">
+    <cfRule type="expression" dxfId="238" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="239" priority="7">
+    <cfRule type="expression" dxfId="237" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="238" priority="3">
+    <cfRule type="expression" dxfId="236" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="237" priority="14">
+    <cfRule type="expression" dxfId="235" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6143,47 +6129,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="236" priority="10">
+    <cfRule type="expression" dxfId="234" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="235" priority="1">
+    <cfRule type="expression" dxfId="233" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="234" priority="25">
+    <cfRule type="expression" dxfId="232" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="233" priority="24">
+    <cfRule type="expression" dxfId="231" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="232" priority="4">
+    <cfRule type="expression" dxfId="230" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="231" priority="3">
+    <cfRule type="expression" dxfId="229" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="230" priority="6">
+    <cfRule type="expression" dxfId="228" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="229" priority="9">
+    <cfRule type="expression" dxfId="227" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="228" priority="11">
+    <cfRule type="expression" dxfId="226" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6646,57 +6632,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="227" priority="36">
+    <cfRule type="expression" dxfId="225" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="226" priority="51">
+    <cfRule type="expression" dxfId="224" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="225" priority="50">
+    <cfRule type="expression" dxfId="223" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="224" priority="9">
+    <cfRule type="expression" dxfId="222" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="223" priority="28">
+    <cfRule type="expression" dxfId="221" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="222" priority="11">
+    <cfRule type="expression" dxfId="220" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="221" priority="24">
+    <cfRule type="expression" dxfId="219" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="220" priority="31">
+    <cfRule type="expression" dxfId="218" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="219" priority="7">
+    <cfRule type="expression" dxfId="217" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="218" priority="35">
+    <cfRule type="expression" dxfId="216" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="217" priority="1">
+    <cfRule type="expression" dxfId="215" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7128,59 +7114,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="216" priority="35">
+    <cfRule type="expression" dxfId="214" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="215" priority="42">
+    <cfRule type="expression" dxfId="213" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="214" priority="54">
+    <cfRule type="expression" dxfId="212" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="213" priority="53">
+    <cfRule type="expression" dxfId="211" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="212" priority="5">
+    <cfRule type="expression" dxfId="210" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="211" priority="30">
+    <cfRule type="expression" dxfId="209" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="210" priority="33">
+    <cfRule type="expression" dxfId="208" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="209" priority="37">
+    <cfRule type="expression" dxfId="207" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="208" priority="41">
+    <cfRule type="expression" dxfId="206" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="207" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="205" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="204" priority="1">
+    <cfRule type="expression" dxfId="202" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7646,57 +7632,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="203" priority="1">
+    <cfRule type="expression" dxfId="201" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="202" priority="18">
+    <cfRule type="expression" dxfId="200" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="201" priority="41">
+    <cfRule type="expression" dxfId="199" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="200" priority="40">
+    <cfRule type="expression" dxfId="198" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="199" priority="13">
+    <cfRule type="expression" dxfId="197" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="198" priority="3">
+    <cfRule type="expression" dxfId="196" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="197" priority="5">
+    <cfRule type="expression" dxfId="195" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="196" priority="19">
+    <cfRule type="expression" dxfId="194" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="195" priority="7">
+    <cfRule type="expression" dxfId="193" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="194" priority="27">
+    <cfRule type="expression" dxfId="192" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="193" priority="8">
+    <cfRule type="expression" dxfId="191" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8156,32 +8142,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="192" priority="21">
+    <cfRule type="expression" dxfId="190" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="191" priority="43">
+    <cfRule type="expression" dxfId="189" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="190" priority="42">
+    <cfRule type="expression" dxfId="188" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="189" priority="1">
+    <cfRule type="expression" dxfId="187" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="188" priority="16">
+    <cfRule type="expression" dxfId="186" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="187" priority="24">
+    <cfRule type="expression" dxfId="185" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8597,32 +8583,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="186" priority="30">
+    <cfRule type="expression" dxfId="184" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="185" priority="29">
+    <cfRule type="expression" dxfId="183" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="184" priority="16">
+    <cfRule type="expression" dxfId="182" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="183" priority="1">
+    <cfRule type="expression" dxfId="181" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="182" priority="4">
+    <cfRule type="expression" dxfId="180" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="181" priority="5">
+    <cfRule type="expression" dxfId="179" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9032,32 +9018,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="180" priority="39">
+    <cfRule type="expression" dxfId="178" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="179" priority="38">
+    <cfRule type="expression" dxfId="177" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="178" priority="20">
+    <cfRule type="expression" dxfId="176" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="177" priority="1">
+    <cfRule type="expression" dxfId="175" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="176" priority="3">
+    <cfRule type="expression" dxfId="174" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="175" priority="2">
+    <cfRule type="expression" dxfId="173" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9477,37 +9463,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="174" priority="18">
+    <cfRule type="expression" dxfId="172" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="173" priority="2">
+    <cfRule type="expression" dxfId="171" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="172" priority="32">
+    <cfRule type="expression" dxfId="170" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="171" priority="31">
+    <cfRule type="expression" dxfId="169" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="170" priority="5">
+    <cfRule type="expression" dxfId="168" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="169" priority="1">
+    <cfRule type="expression" dxfId="167" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="168" priority="3">
+    <cfRule type="expression" dxfId="166" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9923,22 +9909,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="306" priority="14">
+    <cfRule type="expression" dxfId="304" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="305" priority="6">
+    <cfRule type="expression" dxfId="303" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="304" priority="15">
+    <cfRule type="expression" dxfId="302" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="303" priority="1">
+    <cfRule type="expression" dxfId="301" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10336,22 +10322,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="167" priority="32">
+    <cfRule type="expression" dxfId="165" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="166" priority="31">
+    <cfRule type="expression" dxfId="164" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="165" priority="12">
+    <cfRule type="expression" dxfId="163" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="164" priority="1">
+    <cfRule type="expression" dxfId="162" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10717,22 +10703,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="163" priority="17">
+    <cfRule type="expression" dxfId="161" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="162" priority="16">
+    <cfRule type="expression" dxfId="160" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="161" priority="2">
+    <cfRule type="expression" dxfId="159" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="160" priority="1">
+    <cfRule type="expression" dxfId="158" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11167,47 +11153,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="159" priority="32">
+    <cfRule type="expression" dxfId="157" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="158" priority="31">
+    <cfRule type="expression" dxfId="156" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="157" priority="1">
+    <cfRule type="expression" dxfId="155" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="156" priority="3">
+    <cfRule type="expression" dxfId="154" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="155" priority="5">
+    <cfRule type="expression" dxfId="153" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="154" priority="12">
+    <cfRule type="expression" dxfId="152" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="153" priority="18">
+    <cfRule type="expression" dxfId="151" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="152" priority="27">
+    <cfRule type="expression" dxfId="150" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="151" priority="33">
+    <cfRule type="expression" dxfId="149" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11638,47 +11624,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="150" priority="12">
+    <cfRule type="expression" dxfId="148" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="149" priority="29">
+    <cfRule type="expression" dxfId="147" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="148" priority="28">
+    <cfRule type="expression" dxfId="146" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="147" priority="27">
+    <cfRule type="expression" dxfId="145" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="146" priority="1">
+    <cfRule type="expression" dxfId="144" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="145" priority="3">
+    <cfRule type="expression" dxfId="143" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="144" priority="9">
+    <cfRule type="expression" dxfId="142" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="143" priority="24">
+    <cfRule type="expression" dxfId="141" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="142" priority="30">
+    <cfRule type="expression" dxfId="140" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12109,52 +12095,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="141" priority="4">
+    <cfRule type="expression" dxfId="139" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="140" priority="27">
+    <cfRule type="expression" dxfId="138" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="139" priority="26">
+    <cfRule type="expression" dxfId="137" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="138" priority="1">
+    <cfRule type="expression" dxfId="136" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="137" priority="2">
+    <cfRule type="expression" dxfId="135" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="136" priority="28">
+    <cfRule type="expression" dxfId="134" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="135" priority="5">
+    <cfRule type="expression" dxfId="133" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="134" priority="8">
+    <cfRule type="expression" dxfId="132" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="133" priority="18">
+    <cfRule type="expression" dxfId="131" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="132" priority="22">
+    <cfRule type="expression" dxfId="130" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12569,47 +12555,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="131" priority="13">
+    <cfRule type="expression" dxfId="129" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="130" priority="22">
+    <cfRule type="expression" dxfId="128" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="129" priority="21">
+    <cfRule type="expression" dxfId="127" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="128" priority="1">
+    <cfRule type="expression" dxfId="126" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="127" priority="3">
+    <cfRule type="expression" dxfId="125" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="126" priority="5">
+    <cfRule type="expression" dxfId="124" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="125" priority="8">
+    <cfRule type="expression" dxfId="123" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="124" priority="17">
+    <cfRule type="expression" dxfId="122" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="123" priority="23">
+    <cfRule type="expression" dxfId="121" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13025,52 +13011,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="122" priority="5">
+    <cfRule type="expression" dxfId="120" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="121" priority="28">
+    <cfRule type="expression" dxfId="119" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="120" priority="27">
+    <cfRule type="expression" dxfId="118" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="119" priority="1">
+    <cfRule type="expression" dxfId="117" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="118" priority="3">
+    <cfRule type="expression" dxfId="116" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="117" priority="29">
+    <cfRule type="expression" dxfId="115" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="116" priority="22">
+    <cfRule type="expression" dxfId="114" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="115" priority="8">
+    <cfRule type="expression" dxfId="113" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="114" priority="19">
+    <cfRule type="expression" dxfId="112" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="113" priority="23">
+    <cfRule type="expression" dxfId="111" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13479,47 +13465,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="112" priority="11">
+    <cfRule type="expression" dxfId="110" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="111" priority="22">
+    <cfRule type="expression" dxfId="109" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="110" priority="21">
+    <cfRule type="expression" dxfId="108" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="109" priority="1">
+    <cfRule type="expression" dxfId="107" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="108" priority="3">
+    <cfRule type="expression" dxfId="106" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="107" priority="23">
+    <cfRule type="expression" dxfId="105" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="106" priority="5">
+    <cfRule type="expression" dxfId="104" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="105" priority="7">
+    <cfRule type="expression" dxfId="103" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="104" priority="17">
+    <cfRule type="expression" dxfId="102" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13929,52 +13915,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="103" priority="5">
+    <cfRule type="expression" dxfId="101" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="102" priority="26">
+    <cfRule type="expression" dxfId="100" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="101" priority="25">
+    <cfRule type="expression" dxfId="99" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="100" priority="1">
+    <cfRule type="expression" dxfId="98" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="99" priority="3">
+    <cfRule type="expression" dxfId="97" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="98" priority="27">
+    <cfRule type="expression" dxfId="96" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="97" priority="20">
+    <cfRule type="expression" dxfId="95" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="96" priority="8">
+    <cfRule type="expression" dxfId="94" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="95" priority="18">
+    <cfRule type="expression" dxfId="93" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="94" priority="21">
+    <cfRule type="expression" dxfId="92" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14390,37 +14376,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F6 E7:F25 B15:D25">
-    <cfRule type="expression" dxfId="93" priority="8">
+    <cfRule type="expression" dxfId="91" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="92" priority="22">
+    <cfRule type="expression" dxfId="90" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="91" priority="21">
+    <cfRule type="expression" dxfId="89" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="90" priority="1">
+    <cfRule type="expression" dxfId="88" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="89" priority="3">
+    <cfRule type="expression" dxfId="87" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8 C14:D14">
-    <cfRule type="expression" dxfId="88" priority="5">
+    <cfRule type="expression" dxfId="86" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="87" priority="17">
+    <cfRule type="expression" dxfId="85" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14824,30 +14810,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="302" priority="3">
+    <cfRule type="expression" dxfId="300" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="301" priority="14">
+    <cfRule type="expression" dxfId="299" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="300" priority="15">
+    <cfRule type="expression" dxfId="298" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="299" priority="7">
+    <cfRule type="expression" dxfId="297" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="298" priority="9">
+    <cfRule type="expression" dxfId="296" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="297" priority="12">
+    <cfRule type="expression" dxfId="295" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15280,27 +15266,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="86" priority="1">
+    <cfRule type="expression" dxfId="84" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="85" priority="19">
+    <cfRule type="expression" dxfId="83" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="84" priority="18">
+    <cfRule type="expression" dxfId="82" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="83" priority="17">
+    <cfRule type="expression" dxfId="81" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="82" priority="4">
+    <cfRule type="expression" dxfId="80" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15733,33 +15719,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="81" priority="2">
+    <cfRule type="expression" dxfId="79" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="80" priority="25">
+    <cfRule type="expression" dxfId="78" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="79" priority="24">
+    <cfRule type="expression" dxfId="77" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F28 B30:F36 B29:E29">
-    <cfRule type="expression" dxfId="78" priority="10">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="77" priority="5">
+    <cfRule type="expression" dxfId="75" priority="5">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F29">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16174,43 +16155,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="76" priority="4">
+    <cfRule type="expression" dxfId="74" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="75" priority="29">
+    <cfRule type="expression" dxfId="73" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="74" priority="28">
+    <cfRule type="expression" dxfId="72" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F28 B30:F36 C29:F29">
-    <cfRule type="expression" dxfId="73" priority="2">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="72" priority="8">
+    <cfRule type="expression" dxfId="70" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="71" priority="6">
+    <cfRule type="expression" dxfId="69" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="70" priority="12">
+    <cfRule type="expression" dxfId="68" priority="12">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>NOT(ISBLANK(B29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16592,32 +16568,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="69" priority="3">
+    <cfRule type="expression" dxfId="67" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="68" priority="33">
+    <cfRule type="expression" dxfId="66" priority="33">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="67" priority="32">
+    <cfRule type="expression" dxfId="65" priority="32">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="66" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="65" priority="11">
+    <cfRule type="expression" dxfId="63" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="64" priority="8">
+    <cfRule type="expression" dxfId="62" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17037,37 +17013,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="63" priority="5">
+    <cfRule type="expression" dxfId="61" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="62" priority="36">
+    <cfRule type="expression" dxfId="60" priority="36">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="61" priority="35">
+    <cfRule type="expression" dxfId="59" priority="35">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="60" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="59" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="58" priority="29">
+    <cfRule type="expression" dxfId="56" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="57" priority="28">
+    <cfRule type="expression" dxfId="55" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17493,42 +17469,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="56" priority="4">
+    <cfRule type="expression" dxfId="54" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="55" priority="38">
+    <cfRule type="expression" dxfId="53" priority="38">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="54" priority="37">
+    <cfRule type="expression" dxfId="52" priority="37">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="53" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="52" priority="2">
+    <cfRule type="expression" dxfId="50" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="51" priority="8">
+    <cfRule type="expression" dxfId="49" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="50" priority="31">
+    <cfRule type="expression" dxfId="48" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="49" priority="30">
+    <cfRule type="expression" dxfId="47" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17953,42 +17929,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="48" priority="3">
+    <cfRule type="expression" dxfId="46" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="47" priority="18">
+    <cfRule type="expression" dxfId="45" priority="18">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="46" priority="17">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="45" priority="16">
+    <cfRule type="expression" dxfId="43" priority="16">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="44" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="43" priority="7">
+    <cfRule type="expression" dxfId="41" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B15:D25">
-    <cfRule type="expression" dxfId="42" priority="14">
+    <cfRule type="expression" dxfId="40" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="41" priority="13">
+    <cfRule type="expression" dxfId="39" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18415,42 +18391,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="40" priority="3">
+    <cfRule type="expression" dxfId="38" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D25">
-    <cfRule type="expression" dxfId="39" priority="4">
+    <cfRule type="expression" dxfId="37" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="38" priority="19">
+    <cfRule type="expression" dxfId="36" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="37" priority="18">
+    <cfRule type="expression" dxfId="35" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="36" priority="17">
+    <cfRule type="expression" dxfId="34" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="35" priority="1">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="34" priority="8">
+    <cfRule type="expression" dxfId="32" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="33" priority="14">
+    <cfRule type="expression" dxfId="31" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18873,42 +18849,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="32" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="31" priority="4">
+    <cfRule type="expression" dxfId="29" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="30" priority="19">
+    <cfRule type="expression" dxfId="28" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="29" priority="18">
+    <cfRule type="expression" dxfId="27" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="28" priority="17">
+    <cfRule type="expression" dxfId="26" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="27" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="26" priority="8">
+    <cfRule type="expression" dxfId="24" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="25" priority="14">
+    <cfRule type="expression" dxfId="23" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19341,42 +19317,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="24" priority="3">
+    <cfRule type="expression" dxfId="22" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="23" priority="4">
+    <cfRule type="expression" dxfId="21" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="22" priority="19">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="21" priority="18">
+    <cfRule type="expression" dxfId="19" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="20" priority="17">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="18" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="17" priority="14">
+    <cfRule type="expression" dxfId="15" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19801,22 +19777,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="296" priority="10">
+    <cfRule type="expression" dxfId="294" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="295" priority="9">
+    <cfRule type="expression" dxfId="293" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="294" priority="1">
+    <cfRule type="expression" dxfId="292" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="293" priority="7">
+    <cfRule type="expression" dxfId="291" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20250,42 +20226,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="15" priority="4">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="14" priority="19">
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="13" priority="18">
+    <cfRule type="expression" dxfId="11" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="12" priority="17">
+    <cfRule type="expression" dxfId="10" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="10" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20714,37 +20690,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="7" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="6" priority="19">
+    <cfRule type="expression" dxfId="4" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="5" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="4" priority="17">
+    <cfRule type="expression" dxfId="2" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="2" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21189,42 +21165,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="292" priority="15">
+    <cfRule type="expression" dxfId="290" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="291" priority="13">
+    <cfRule type="expression" dxfId="289" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="290" priority="30">
+    <cfRule type="expression" dxfId="288" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="289" priority="29">
+    <cfRule type="expression" dxfId="287" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="288" priority="7">
+    <cfRule type="expression" dxfId="286" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="287" priority="24">
+    <cfRule type="expression" dxfId="285" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="286" priority="20">
+    <cfRule type="expression" dxfId="284" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="285" priority="25">
+    <cfRule type="expression" dxfId="283" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21625,32 +21601,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="284" priority="8">
+    <cfRule type="expression" dxfId="282" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="283" priority="13">
+    <cfRule type="expression" dxfId="281" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="282" priority="12">
+    <cfRule type="expression" dxfId="280" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="281" priority="1">
+    <cfRule type="expression" dxfId="279" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="280" priority="4">
+    <cfRule type="expression" dxfId="278" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="279" priority="7">
+    <cfRule type="expression" dxfId="277" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22034,52 +22010,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="278" priority="22">
+    <cfRule type="expression" dxfId="276" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="277" priority="23">
+    <cfRule type="expression" dxfId="275" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="276" priority="45">
+    <cfRule type="expression" dxfId="274" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="275" priority="44">
+    <cfRule type="expression" dxfId="273" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="274" priority="1">
+    <cfRule type="expression" dxfId="272" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="273" priority="35">
+    <cfRule type="expression" dxfId="271" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="272" priority="36">
+    <cfRule type="expression" dxfId="270" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="271" priority="16">
+    <cfRule type="expression" dxfId="269" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="270" priority="34">
+    <cfRule type="expression" dxfId="268" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="269" priority="5">
+    <cfRule type="expression" dxfId="267" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22492,47 +22468,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="268" priority="16">
+    <cfRule type="expression" dxfId="266" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="267" priority="19">
+    <cfRule type="expression" dxfId="265" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="266" priority="18">
+    <cfRule type="expression" dxfId="264" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="265" priority="1">
+    <cfRule type="expression" dxfId="263" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="264" priority="15">
+    <cfRule type="expression" dxfId="262" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="263" priority="12">
+    <cfRule type="expression" dxfId="261" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="262" priority="11">
+    <cfRule type="expression" dxfId="260" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="261" priority="14">
+    <cfRule type="expression" dxfId="259" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="260" priority="5">
+    <cfRule type="expression" dxfId="258" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22955,32 +22931,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="259" priority="2">
+    <cfRule type="expression" dxfId="257" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="258" priority="4">
+    <cfRule type="expression" dxfId="256" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="257" priority="16">
+    <cfRule type="expression" dxfId="255" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="256" priority="15">
+    <cfRule type="expression" dxfId="254" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="255" priority="1">
+    <cfRule type="expression" dxfId="253" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="254" priority="7">
+    <cfRule type="expression" dxfId="252" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A5B82F-22F7-4639-B918-AF8ECC52B01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A9E4A5-04A4-48AA-B7CB-F35DC4EB11A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="405">
   <si>
     <t>Week</t>
   </si>
@@ -1307,6 +1307,9 @@
   </si>
   <si>
     <t>Studiereis tickets zouden moeten doorgemaild worden van de trein + afprinten</t>
+  </si>
+  <si>
+    <t>Common terre korte presentatie</t>
   </si>
 </sst>
 </file>
@@ -12493,7 +12496,9 @@
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="D29" s="17" t="s">
+        <v>404</v>
+      </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
     </row>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A9E4A5-04A4-48AA-B7CB-F35DC4EB11A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19937F7-3FB3-4D00-BD0B-1CA9ED089432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BB7234-AD7F-40DA-8B51-5CAAF87F7438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CDECDC-8600-4A99-9D72-40863CD4F2D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" firstSheet="20" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -12050,7 +12050,7 @@
       <c r="E29" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="22" t="s">
         <v>405</v>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="47" t="s">
         <v>408</v>
       </c>
       <c r="F30" s="16" t="s">

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD43733-9C5E-41C9-B244-55C9550F19C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA7C6F5-B26C-4025-916F-10A18AC3D88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="411">
   <si>
     <t>Week</t>
   </si>
@@ -1319,6 +1319,15 @@
   </si>
   <si>
     <t>harde schijf teruggeven!!!</t>
+  </si>
+  <si>
+    <t>dad bday</t>
+  </si>
+  <si>
+    <t>dad bday iets kopen</t>
+  </si>
+  <si>
+    <t>sasha bday iets kopen</t>
   </si>
 </sst>
 </file>
@@ -12493,7 +12502,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>409</v>
+      </c>
       <c r="C28" s="16" t="s">
         <v>398</v>
       </c>
@@ -12507,8 +12518,10 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17" t="s">
+      <c r="B29" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>406</v>
       </c>
       <c r="D29" s="17" t="s">
@@ -12520,7 +12533,9 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="C30" s="17" t="s">
+        <v>408</v>
+      </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA7C6F5-B26C-4025-916F-10A18AC3D88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EB70C1-8842-4F95-BA0E-1422AED99178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1684" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="415">
   <si>
     <t>Week</t>
   </si>
@@ -1328,6 +1328,18 @@
   </si>
   <si>
     <t>sasha bday iets kopen</t>
+  </si>
+  <si>
+    <t>High-fidelity wireframes (designs)</t>
+  </si>
+  <si>
+    <t>Op 17/03 om 17u kiezen we per pagina één definitieve versie</t>
+  </si>
+  <si>
+    <t>Interactieve prototype in Figma/XD</t>
+  </si>
+  <si>
+    <t>Website live + eindpresentatie</t>
   </si>
 </sst>
 </file>
@@ -12518,9 +12530,7 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="16" t="s">
-        <v>410</v>
-      </c>
+      <c r="B29" s="17"/>
       <c r="C29" s="16" t="s">
         <v>406</v>
       </c>
@@ -12543,7 +12553,9 @@
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="C31" s="16" t="s">
+        <v>410</v>
+      </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -13426,7 +13438,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>411</v>
+      </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
         <v>389</v>
@@ -13436,7 +13450,9 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="16" t="s">
+        <v>412</v>
+      </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -13545,6 +13561,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14347,7 +14364,9 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="16" t="s">
+        <v>413</v>
+      </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
@@ -16970,7 +16989,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>414</v>
+      </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
         <v>387</v>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C390FC3-4373-4127-90AD-0F6D2CA325FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767A0795-C0A4-48D2-8C23-31DFD7FEBF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="16200" windowHeight="9307" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -12543,7 +12543,7 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="22" t="s">
         <v>408</v>
       </c>
       <c r="D30" s="17"/>
@@ -12647,6 +12647,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767A0795-C0A4-48D2-8C23-31DFD7FEBF32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CE5A87-189A-4A3B-9D22-C3BEB51A89FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="16200" windowHeight="9307" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="417">
   <si>
     <t>Week</t>
   </si>
@@ -1309,9 +1309,6 @@
     <t>Studiereis tickets zouden moeten doorgemaild worden van de trein + afprinten</t>
   </si>
   <si>
-    <t>Common terre korte presentatie</t>
-  </si>
-  <si>
     <t>inschrijven feedback</t>
   </si>
   <si>
@@ -1340,6 +1337,15 @@
   </si>
   <si>
     <t>Website live + eindpresentatie</t>
+  </si>
+  <si>
+    <t>Sasha bday</t>
+  </si>
+  <si>
+    <t>SASHA TRUI MEEDOEN</t>
+  </si>
+  <si>
+    <t>veel werken atelier morgen</t>
   </si>
 </sst>
 </file>
@@ -12069,7 +12075,7 @@
         <v>354</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
@@ -12078,7 +12084,7 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="47" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F30" s="17"/>
     </row>
@@ -12515,15 +12521,15 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>409</v>
-      </c>
-      <c r="C28" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="C28" s="22" t="s">
         <v>398</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="E28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="16" t="s">
+        <v>416</v>
+      </c>
       <c r="F28" s="16" t="s">
         <v>398</v>
       </c>
@@ -12531,30 +12537,32 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
-      <c r="C29" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>404</v>
-      </c>
+      <c r="C29" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="D29" s="17"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="F29" s="16" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="16" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="16" t="s">
-        <v>410</v>
+      <c r="C31" s="22" t="s">
+        <v>409</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -13440,7 +13448,7 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">
@@ -13452,7 +13460,7 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11"/>
       <c r="B29" s="16" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -14366,7 +14374,7 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11"/>
       <c r="B29" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -16991,7 +16999,7 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16" t="s">

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A175F486-42CD-48B1-B072-2D903E5C00F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B7C368-66F3-403E-B81E-6AD60891BE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="420">
   <si>
     <t>Week</t>
   </si>
@@ -1349,6 +1349,12 @@
   </si>
   <si>
     <t>laptop resolutie terugzetten</t>
+  </si>
+  <si>
+    <t>common terre wireframes website maken</t>
+  </si>
+  <si>
+    <t>naar theo ding sasha bday</t>
   </si>
 </sst>
 </file>
@@ -12530,7 +12536,7 @@
         <v>398</v>
       </c>
       <c r="D28" s="17"/>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="22" t="s">
         <v>416</v>
       </c>
       <c r="F28" s="16" t="s">
@@ -12544,9 +12550,7 @@
         <v>405</v>
       </c>
       <c r="D29" s="17"/>
-      <c r="E29" s="16" t="s">
-        <v>417</v>
-      </c>
+      <c r="E29" s="17"/>
       <c r="F29" s="16" t="s">
         <v>414</v>
       </c>
@@ -12571,7 +12575,9 @@
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="F31" s="16" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
@@ -12579,7 +12585,9 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="F32" s="16" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
@@ -13474,7 +13482,9 @@
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>418</v>
+      </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AB8C76-99EC-4C77-81D8-4FD1C6D8EE66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6D7F24-3F7B-4804-9C4F-8BC40D85DEAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13003,7 +13003,7 @@
       <c r="B28" s="22" t="s">
         <v>373</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="22" t="s">
         <v>399</v>
       </c>
       <c r="D28" s="16" t="s">

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7330739B-945B-4FD2-947F-F4DC9F31A69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33296890-FEF9-495E-96C9-0F913BCDF5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" firstSheet="22" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="431">
   <si>
     <t>Week</t>
   </si>
@@ -1382,6 +1382,12 @@
   </si>
   <si>
     <t>Resolutie terug zetten laptop</t>
+  </si>
+  <si>
+    <t>korte essayfilm ding maken</t>
+  </si>
+  <si>
+    <t>common terre ding?</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1713,7 @@
     <cellStyle name="Bad" xfId="7" builtinId="27"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="305">
     <dxf>
@@ -13034,7 +13040,7 @@
         <v>399</v>
       </c>
       <c r="D28" s="17"/>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="22" t="s">
         <v>426</v>
       </c>
       <c r="F28" s="16" t="s">
@@ -13046,10 +13052,10 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="17"/>
+      <c r="F29" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
@@ -13057,7 +13063,9 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="16" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -13959,7 +13967,9 @@
       <c r="D28" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="E28" s="16"/>
+      <c r="E28" s="16" t="s">
+        <v>429</v>
+      </c>
       <c r="F28" s="16" t="s">
         <v>397</v>
       </c>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8771C2C8-86AD-48A2-8344-A54670511FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5083B91-2C89-4B80-A211-67BE564DAF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="433">
   <si>
     <t>Week</t>
   </si>
@@ -13503,7 +13503,7 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="22" t="s">
         <v>410</v>
       </c>
       <c r="C28" s="16" t="s">
@@ -13533,7 +13533,7 @@
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="47" t="s">
         <v>418</v>
       </c>
       <c r="C30" s="17" t="s">
@@ -13545,7 +13545,9 @@
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="16" t="s">
+        <v>304</v>
+      </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5083B91-2C89-4B80-A211-67BE564DAF4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0B8A1A-FD41-47E3-A176-BF7DB5220C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="436">
   <si>
     <t>Week</t>
   </si>
@@ -1394,6 +1394,15 @@
   </si>
   <si>
     <t>Leerkracht vragen CALAN ding</t>
+  </si>
+  <si>
+    <t>Marketing ding opschrijven enzo</t>
+  </si>
+  <si>
+    <t>Ardennen huisje zoeken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laatste keer design thinking maar id ochtend door want daarna les portfolio ofzoiets tijdens magneetweek (ochtend is 9.00u of 9u30) </t>
   </si>
 </sst>
 </file>
@@ -13536,7 +13545,7 @@
       <c r="B30" s="47" t="s">
         <v>418</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="16" t="s">
         <v>432</v>
       </c>
       <c r="D30" s="17"/>
@@ -13548,7 +13557,9 @@
       <c r="B31" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="C31" s="17"/>
+      <c r="C31" s="16" t="s">
+        <v>433</v>
+      </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -13556,7 +13567,9 @@
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
+      <c r="C32" s="16" t="s">
+        <v>434</v>
+      </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
@@ -14190,6 +14203,9 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="28" t="s">
         <v>366</v>
       </c>
@@ -14204,6 +14220,9 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
@@ -14212,9 +14231,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>63</v>
       </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
@@ -14230,6 +14252,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
@@ -14244,6 +14267,7 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="B9" s="5"/>
       <c r="C9" s="29" t="s">
         <v>364</v>
       </c>
@@ -14254,6 +14278,7 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="B10" s="5"/>
       <c r="C10" s="28" t="s">
         <v>13</v>
       </c>
@@ -14264,6 +14289,7 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="B11" s="5"/>
       <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
@@ -14272,6 +14298,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="B12" s="5"/>
       <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
@@ -14280,6 +14307,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="B13" s="5"/>
       <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
@@ -14288,6 +14316,7 @@
       <c r="A14" s="3">
         <v>0.54166666666666696</v>
       </c>
+      <c r="B14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -14298,9 +14327,6 @@
       <c r="A16" s="3">
         <v>0.58333333333333304</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
@@ -14318,9 +14344,6 @@
       <c r="A17" s="3">
         <v>0.60416666666666696</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
@@ -14334,12 +14357,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>0.625</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>63</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -14350,7 +14370,6 @@
       <c r="A19" s="3">
         <v>0.64583333333333304</v>
       </c>
-      <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="31"/>
@@ -14360,7 +14379,6 @@
       <c r="A20" s="3">
         <v>0.66666666666666696</v>
       </c>
-      <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="31"/>
@@ -14370,7 +14388,6 @@
       <c r="A21" s="3">
         <v>0.67708333333333337</v>
       </c>
-      <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -14382,7 +14399,6 @@
       <c r="A22" s="3">
         <v>0.70833333333333304</v>
       </c>
-      <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5" t="s">
         <v>27</v>
@@ -14394,7 +14410,6 @@
       <c r="A23" s="3">
         <v>0.72916666666666696</v>
       </c>
-      <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="28"/>
@@ -14404,7 +14419,6 @@
       <c r="A24" s="3">
         <v>0.75</v>
       </c>
-      <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="28"/>
@@ -14414,7 +14428,6 @@
       <c r="A25" s="3">
         <v>0.76041666666666663</v>
       </c>
-      <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="28"/>
@@ -14463,7 +14476,9 @@
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>435</v>
+      </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -14518,7 +14533,7 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4 F5:F6 E7:F25 B15:D25">
+  <conditionalFormatting sqref="F5:F6 E7:F25 B15:D15 C16:D25 B4:B14">
     <cfRule type="expression" dxfId="91" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C2AC26-9D95-4DAE-A92A-B4C3F8F0C829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08210E6-F1C9-405A-B782-8EE429371A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="24" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="444">
   <si>
     <t>Week</t>
   </si>
@@ -1424,6 +1424,9 @@
   </si>
   <si>
     <t>DEADLINE C&amp;O 25 MEI</t>
+  </si>
+  <si>
+    <t>werken studio digi</t>
   </si>
 </sst>
 </file>
@@ -1751,14 +1754,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="306">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="305">
     <dxf>
       <font>
         <color theme="1"/>
@@ -5280,47 +5276,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="252" priority="17">
+    <cfRule type="expression" dxfId="251" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="251" priority="25">
+    <cfRule type="expression" dxfId="250" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="250" priority="24">
+    <cfRule type="expression" dxfId="249" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="249" priority="5">
+    <cfRule type="expression" dxfId="248" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="248" priority="9">
+    <cfRule type="expression" dxfId="247" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="247" priority="8">
+    <cfRule type="expression" dxfId="246" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="246" priority="11">
+    <cfRule type="expression" dxfId="245" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="245" priority="15">
+    <cfRule type="expression" dxfId="244" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="244" priority="2">
+    <cfRule type="expression" dxfId="243" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5779,42 +5775,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="243" priority="15">
+    <cfRule type="expression" dxfId="242" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="242" priority="10">
+    <cfRule type="expression" dxfId="241" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="241" priority="24">
+    <cfRule type="expression" dxfId="240" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="240" priority="23">
+    <cfRule type="expression" dxfId="239" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="239" priority="1">
+    <cfRule type="expression" dxfId="238" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="238" priority="7">
+    <cfRule type="expression" dxfId="237" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="237" priority="3">
+    <cfRule type="expression" dxfId="236" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="236" priority="14">
+    <cfRule type="expression" dxfId="235" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6253,47 +6249,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="235" priority="10">
+    <cfRule type="expression" dxfId="234" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="234" priority="1">
+    <cfRule type="expression" dxfId="233" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="233" priority="25">
+    <cfRule type="expression" dxfId="232" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="232" priority="24">
+    <cfRule type="expression" dxfId="231" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="231" priority="4">
+    <cfRule type="expression" dxfId="230" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="230" priority="3">
+    <cfRule type="expression" dxfId="229" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="229" priority="6">
+    <cfRule type="expression" dxfId="228" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="228" priority="9">
+    <cfRule type="expression" dxfId="227" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="227" priority="11">
+    <cfRule type="expression" dxfId="226" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6756,57 +6752,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="226" priority="36">
+    <cfRule type="expression" dxfId="225" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="225" priority="51">
+    <cfRule type="expression" dxfId="224" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="224" priority="50">
+    <cfRule type="expression" dxfId="223" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="223" priority="9">
+    <cfRule type="expression" dxfId="222" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="222" priority="28">
+    <cfRule type="expression" dxfId="221" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="221" priority="11">
+    <cfRule type="expression" dxfId="220" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="220" priority="24">
+    <cfRule type="expression" dxfId="219" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="219" priority="31">
+    <cfRule type="expression" dxfId="218" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="218" priority="7">
+    <cfRule type="expression" dxfId="217" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="217" priority="35">
+    <cfRule type="expression" dxfId="216" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="216" priority="1">
+    <cfRule type="expression" dxfId="215" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7238,59 +7234,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="215" priority="35">
+    <cfRule type="expression" dxfId="214" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="214" priority="42">
+    <cfRule type="expression" dxfId="213" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="213" priority="54">
+    <cfRule type="expression" dxfId="212" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="212" priority="53">
+    <cfRule type="expression" dxfId="211" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="211" priority="5">
+    <cfRule type="expression" dxfId="210" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="210" priority="30">
+    <cfRule type="expression" dxfId="209" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="209" priority="33">
+    <cfRule type="expression" dxfId="208" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="208" priority="37">
+    <cfRule type="expression" dxfId="207" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="207" priority="41">
+    <cfRule type="expression" dxfId="206" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="206" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="204" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="203" priority="1">
+    <cfRule type="expression" dxfId="202" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7756,57 +7752,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="202" priority="1">
+    <cfRule type="expression" dxfId="201" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="201" priority="18">
+    <cfRule type="expression" dxfId="200" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="200" priority="41">
+    <cfRule type="expression" dxfId="199" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="199" priority="40">
+    <cfRule type="expression" dxfId="198" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="198" priority="13">
+    <cfRule type="expression" dxfId="197" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="197" priority="3">
+    <cfRule type="expression" dxfId="196" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="196" priority="5">
+    <cfRule type="expression" dxfId="195" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="195" priority="19">
+    <cfRule type="expression" dxfId="194" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="194" priority="7">
+    <cfRule type="expression" dxfId="193" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="193" priority="27">
+    <cfRule type="expression" dxfId="192" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="192" priority="8">
+    <cfRule type="expression" dxfId="191" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8266,32 +8262,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="191" priority="21">
+    <cfRule type="expression" dxfId="190" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="190" priority="43">
+    <cfRule type="expression" dxfId="189" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="189" priority="42">
+    <cfRule type="expression" dxfId="188" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="188" priority="1">
+    <cfRule type="expression" dxfId="187" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="187" priority="16">
+    <cfRule type="expression" dxfId="186" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="186" priority="24">
+    <cfRule type="expression" dxfId="185" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8707,32 +8703,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="185" priority="30">
+    <cfRule type="expression" dxfId="184" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="184" priority="29">
+    <cfRule type="expression" dxfId="183" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="183" priority="16">
+    <cfRule type="expression" dxfId="182" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="182" priority="1">
+    <cfRule type="expression" dxfId="181" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="181" priority="4">
+    <cfRule type="expression" dxfId="180" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="180" priority="5">
+    <cfRule type="expression" dxfId="179" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9142,32 +9138,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="179" priority="39">
+    <cfRule type="expression" dxfId="178" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="178" priority="38">
+    <cfRule type="expression" dxfId="177" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="177" priority="20">
+    <cfRule type="expression" dxfId="176" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="176" priority="1">
+    <cfRule type="expression" dxfId="175" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="175" priority="3">
+    <cfRule type="expression" dxfId="174" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="174" priority="2">
+    <cfRule type="expression" dxfId="173" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9587,37 +9583,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="173" priority="18">
+    <cfRule type="expression" dxfId="172" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="172" priority="2">
+    <cfRule type="expression" dxfId="171" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="171" priority="32">
+    <cfRule type="expression" dxfId="170" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="170" priority="31">
+    <cfRule type="expression" dxfId="169" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="169" priority="5">
+    <cfRule type="expression" dxfId="168" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="168" priority="1">
+    <cfRule type="expression" dxfId="167" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="167" priority="3">
+    <cfRule type="expression" dxfId="166" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10033,22 +10029,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="305" priority="14">
+    <cfRule type="expression" dxfId="304" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="304" priority="6">
+    <cfRule type="expression" dxfId="303" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="303" priority="15">
+    <cfRule type="expression" dxfId="302" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="302" priority="1">
+    <cfRule type="expression" dxfId="301" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10446,22 +10442,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="166" priority="32">
+    <cfRule type="expression" dxfId="165" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="165" priority="31">
+    <cfRule type="expression" dxfId="164" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="164" priority="12">
+    <cfRule type="expression" dxfId="163" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="163" priority="1">
+    <cfRule type="expression" dxfId="162" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10827,22 +10823,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="162" priority="17">
+    <cfRule type="expression" dxfId="161" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="161" priority="16">
+    <cfRule type="expression" dxfId="160" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="160" priority="2">
+    <cfRule type="expression" dxfId="159" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="159" priority="1">
+    <cfRule type="expression" dxfId="158" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11277,47 +11273,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="158" priority="32">
+    <cfRule type="expression" dxfId="157" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="157" priority="31">
+    <cfRule type="expression" dxfId="156" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="156" priority="1">
+    <cfRule type="expression" dxfId="155" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="155" priority="3">
+    <cfRule type="expression" dxfId="154" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="154" priority="5">
+    <cfRule type="expression" dxfId="153" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="153" priority="12">
+    <cfRule type="expression" dxfId="152" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="152" priority="18">
+    <cfRule type="expression" dxfId="151" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="151" priority="27">
+    <cfRule type="expression" dxfId="150" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="150" priority="33">
+    <cfRule type="expression" dxfId="149" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11748,47 +11744,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="149" priority="12">
+    <cfRule type="expression" dxfId="148" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="148" priority="29">
+    <cfRule type="expression" dxfId="147" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="147" priority="28">
+    <cfRule type="expression" dxfId="146" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="146" priority="27">
+    <cfRule type="expression" dxfId="145" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="145" priority="1">
+    <cfRule type="expression" dxfId="144" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="144" priority="3">
+    <cfRule type="expression" dxfId="143" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="143" priority="9">
+    <cfRule type="expression" dxfId="142" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="142" priority="24">
+    <cfRule type="expression" dxfId="141" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="141" priority="30">
+    <cfRule type="expression" dxfId="140" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12223,52 +12219,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="140" priority="4">
+    <cfRule type="expression" dxfId="139" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="139" priority="27">
+    <cfRule type="expression" dxfId="138" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="138" priority="26">
+    <cfRule type="expression" dxfId="137" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="137" priority="1">
+    <cfRule type="expression" dxfId="136" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="136" priority="2">
+    <cfRule type="expression" dxfId="135" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="135" priority="28">
+    <cfRule type="expression" dxfId="134" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="134" priority="5">
+    <cfRule type="expression" dxfId="133" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="133" priority="8">
+    <cfRule type="expression" dxfId="132" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="132" priority="18">
+    <cfRule type="expression" dxfId="131" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="131" priority="22">
+    <cfRule type="expression" dxfId="130" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12697,47 +12693,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="130" priority="13">
+    <cfRule type="expression" dxfId="129" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="129" priority="22">
+    <cfRule type="expression" dxfId="128" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="128" priority="21">
+    <cfRule type="expression" dxfId="127" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="127" priority="1">
+    <cfRule type="expression" dxfId="126" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="126" priority="3">
+    <cfRule type="expression" dxfId="125" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="125" priority="5">
+    <cfRule type="expression" dxfId="124" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="124" priority="8">
+    <cfRule type="expression" dxfId="123" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="123" priority="17">
+    <cfRule type="expression" dxfId="122" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="122" priority="23">
+    <cfRule type="expression" dxfId="121" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13160,52 +13156,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="121" priority="5">
+    <cfRule type="expression" dxfId="120" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="120" priority="28">
+    <cfRule type="expression" dxfId="119" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="119" priority="27">
+    <cfRule type="expression" dxfId="118" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="118" priority="1">
+    <cfRule type="expression" dxfId="117" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="117" priority="3">
+    <cfRule type="expression" dxfId="116" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="116" priority="29">
+    <cfRule type="expression" dxfId="115" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="115" priority="22">
+    <cfRule type="expression" dxfId="114" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="114" priority="8">
+    <cfRule type="expression" dxfId="113" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="113" priority="19">
+    <cfRule type="expression" dxfId="112" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="112" priority="23">
+    <cfRule type="expression" dxfId="111" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13543,11 +13539,11 @@
       <c r="B28" s="22" t="s">
         <v>410</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="22" t="s">
         <v>421</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>389</v>
+        <v>443</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>427</v>
@@ -13561,7 +13557,7 @@
       <c r="B29" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="22" t="s">
         <v>431</v>
       </c>
       <c r="D29" s="17"/>
@@ -13573,7 +13569,7 @@
       <c r="B30" s="47" t="s">
         <v>418</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="22" t="s">
         <v>432</v>
       </c>
       <c r="D30" s="17"/>
@@ -13634,47 +13630,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="111" priority="11">
+    <cfRule type="expression" dxfId="110" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="110" priority="22">
+    <cfRule type="expression" dxfId="109" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="109" priority="21">
+    <cfRule type="expression" dxfId="108" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="108" priority="1">
+    <cfRule type="expression" dxfId="107" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="107" priority="3">
+    <cfRule type="expression" dxfId="106" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="106" priority="23">
+    <cfRule type="expression" dxfId="105" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="105" priority="5">
+    <cfRule type="expression" dxfId="104" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="104" priority="7">
+    <cfRule type="expression" dxfId="103" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="103" priority="17">
+    <cfRule type="expression" dxfId="102" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14093,52 +14089,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="102" priority="5">
+    <cfRule type="expression" dxfId="101" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="101" priority="26">
+    <cfRule type="expression" dxfId="100" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="100" priority="25">
+    <cfRule type="expression" dxfId="99" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="99" priority="1">
+    <cfRule type="expression" dxfId="98" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="98" priority="3">
+    <cfRule type="expression" dxfId="97" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="97" priority="27">
+    <cfRule type="expression" dxfId="96" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="96" priority="20">
+    <cfRule type="expression" dxfId="95" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="95" priority="8">
+    <cfRule type="expression" dxfId="94" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="94" priority="18">
+    <cfRule type="expression" dxfId="93" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="93" priority="21">
+    <cfRule type="expression" dxfId="92" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14566,37 +14562,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B14 F5:F6 E7:F25 B15:D15 C16:D25">
-    <cfRule type="expression" dxfId="92" priority="8">
+    <cfRule type="expression" dxfId="91" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="91" priority="22">
+    <cfRule type="expression" dxfId="90" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="90" priority="21">
+    <cfRule type="expression" dxfId="89" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="89" priority="1">
+    <cfRule type="expression" dxfId="88" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="88" priority="3">
+    <cfRule type="expression" dxfId="87" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8 C14:D14">
-    <cfRule type="expression" dxfId="87" priority="5">
+    <cfRule type="expression" dxfId="86" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="86" priority="17">
+    <cfRule type="expression" dxfId="85" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15000,30 +14996,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="301" priority="3">
+    <cfRule type="expression" dxfId="300" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="300" priority="14">
+    <cfRule type="expression" dxfId="299" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="299" priority="15">
+    <cfRule type="expression" dxfId="298" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="298" priority="7">
+    <cfRule type="expression" dxfId="297" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="297" priority="9">
+    <cfRule type="expression" dxfId="296" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="296" priority="12">
+    <cfRule type="expression" dxfId="295" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15456,27 +15452,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="85" priority="1">
+    <cfRule type="expression" dxfId="84" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="84" priority="19">
+    <cfRule type="expression" dxfId="83" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="83" priority="18">
+    <cfRule type="expression" dxfId="82" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="82" priority="17">
+    <cfRule type="expression" dxfId="81" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="81" priority="4">
+    <cfRule type="expression" dxfId="80" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15909,27 +15905,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="80" priority="2">
+    <cfRule type="expression" dxfId="79" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="79" priority="25">
+    <cfRule type="expression" dxfId="78" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="78" priority="24">
+    <cfRule type="expression" dxfId="77" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="77" priority="1">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="76" priority="5">
+    <cfRule type="expression" dxfId="75" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16345,37 +16341,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="75" priority="4">
+    <cfRule type="expression" dxfId="74" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="74" priority="29">
+    <cfRule type="expression" dxfId="73" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="73" priority="28">
+    <cfRule type="expression" dxfId="72" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="72" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="71" priority="8">
+    <cfRule type="expression" dxfId="70" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="70" priority="6">
+    <cfRule type="expression" dxfId="69" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="69" priority="12">
+    <cfRule type="expression" dxfId="68" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16762,32 +16758,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="68" priority="3">
+    <cfRule type="expression" dxfId="67" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="67" priority="33">
+    <cfRule type="expression" dxfId="66" priority="33">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="66" priority="32">
+    <cfRule type="expression" dxfId="65" priority="32">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="65" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="64" priority="11">
+    <cfRule type="expression" dxfId="63" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="63" priority="8">
+    <cfRule type="expression" dxfId="62" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17215,37 +17211,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="62" priority="5">
+    <cfRule type="expression" dxfId="61" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="61" priority="36">
+    <cfRule type="expression" dxfId="60" priority="36">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="60" priority="35">
+    <cfRule type="expression" dxfId="59" priority="35">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="58" priority="3">
+    <cfRule type="expression" dxfId="57" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="57" priority="29">
+    <cfRule type="expression" dxfId="56" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="56" priority="28">
+    <cfRule type="expression" dxfId="55" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17671,42 +17667,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="55" priority="4">
+    <cfRule type="expression" dxfId="54" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="54" priority="38">
+    <cfRule type="expression" dxfId="53" priority="38">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="53" priority="37">
+    <cfRule type="expression" dxfId="52" priority="37">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="52" priority="1">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="51" priority="2">
+    <cfRule type="expression" dxfId="50" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="50" priority="8">
+    <cfRule type="expression" dxfId="49" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="49" priority="31">
+    <cfRule type="expression" dxfId="48" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="48" priority="30">
+    <cfRule type="expression" dxfId="47" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18135,42 +18131,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="47" priority="3">
+    <cfRule type="expression" dxfId="46" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="46" priority="18">
+    <cfRule type="expression" dxfId="45" priority="18">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="45" priority="17">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="44" priority="16">
+    <cfRule type="expression" dxfId="43" priority="16">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="42" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="42" priority="7">
+    <cfRule type="expression" dxfId="41" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B15:D25">
-    <cfRule type="expression" dxfId="41" priority="14">
+    <cfRule type="expression" dxfId="40" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="40" priority="13">
+    <cfRule type="expression" dxfId="39" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18601,48 +18597,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="39" priority="4">
+    <cfRule type="expression" dxfId="38" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D25">
-    <cfRule type="expression" dxfId="38" priority="5">
+    <cfRule type="expression" dxfId="37" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="37" priority="20">
+    <cfRule type="expression" dxfId="36" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="36" priority="19">
+    <cfRule type="expression" dxfId="35" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F29 B31:F36 C30:F30">
-    <cfRule type="expression" dxfId="35" priority="18">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="34" priority="2">
+    <cfRule type="expression" dxfId="33" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="33" priority="9">
+    <cfRule type="expression" dxfId="32" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="32" priority="15">
+    <cfRule type="expression" dxfId="31" priority="15">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19064,42 +19055,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="31" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="30" priority="4">
+    <cfRule type="expression" dxfId="29" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="29" priority="19">
+    <cfRule type="expression" dxfId="28" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="28" priority="18">
+    <cfRule type="expression" dxfId="27" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="27" priority="17">
+    <cfRule type="expression" dxfId="26" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="25" priority="8">
+    <cfRule type="expression" dxfId="24" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="24" priority="14">
+    <cfRule type="expression" dxfId="23" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19532,42 +19523,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="23" priority="3">
+    <cfRule type="expression" dxfId="22" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="22" priority="4">
+    <cfRule type="expression" dxfId="21" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="21" priority="19">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="20" priority="18">
+    <cfRule type="expression" dxfId="19" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="19" priority="17">
+    <cfRule type="expression" dxfId="18" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="17" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="15" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19992,22 +19983,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="295" priority="10">
+    <cfRule type="expression" dxfId="294" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="294" priority="9">
+    <cfRule type="expression" dxfId="293" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="293" priority="1">
+    <cfRule type="expression" dxfId="292" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="292" priority="7">
+    <cfRule type="expression" dxfId="291" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20441,42 +20432,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="14" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="13" priority="19">
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="12" priority="18">
+    <cfRule type="expression" dxfId="11" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="11" priority="17">
+    <cfRule type="expression" dxfId="10" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="8" priority="14">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20905,37 +20896,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="6" priority="4">
+    <cfRule type="expression" dxfId="5" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="5" priority="19">
+    <cfRule type="expression" dxfId="4" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="4" priority="18">
+    <cfRule type="expression" dxfId="3" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="3" priority="17">
+    <cfRule type="expression" dxfId="2" priority="17">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="1" priority="8">
+    <cfRule type="expression" dxfId="0" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21380,42 +21371,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="291" priority="15">
+    <cfRule type="expression" dxfId="290" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="290" priority="13">
+    <cfRule type="expression" dxfId="289" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="289" priority="30">
+    <cfRule type="expression" dxfId="288" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="288" priority="29">
+    <cfRule type="expression" dxfId="287" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="287" priority="7">
+    <cfRule type="expression" dxfId="286" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="286" priority="24">
+    <cfRule type="expression" dxfId="285" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="285" priority="20">
+    <cfRule type="expression" dxfId="284" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="284" priority="25">
+    <cfRule type="expression" dxfId="283" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21816,32 +21807,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="283" priority="8">
+    <cfRule type="expression" dxfId="282" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="282" priority="13">
+    <cfRule type="expression" dxfId="281" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="281" priority="12">
+    <cfRule type="expression" dxfId="280" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="280" priority="1">
+    <cfRule type="expression" dxfId="279" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="279" priority="4">
+    <cfRule type="expression" dxfId="278" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="278" priority="7">
+    <cfRule type="expression" dxfId="277" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22225,52 +22216,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="277" priority="22">
+    <cfRule type="expression" dxfId="276" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="276" priority="23">
+    <cfRule type="expression" dxfId="275" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="275" priority="45">
+    <cfRule type="expression" dxfId="274" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="274" priority="44">
+    <cfRule type="expression" dxfId="273" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="273" priority="1">
+    <cfRule type="expression" dxfId="272" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="272" priority="35">
+    <cfRule type="expression" dxfId="271" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="271" priority="36">
+    <cfRule type="expression" dxfId="270" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="270" priority="16">
+    <cfRule type="expression" dxfId="269" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="269" priority="34">
+    <cfRule type="expression" dxfId="268" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="268" priority="5">
+    <cfRule type="expression" dxfId="267" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22683,47 +22674,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="267" priority="16">
+    <cfRule type="expression" dxfId="266" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="266" priority="19">
+    <cfRule type="expression" dxfId="265" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="265" priority="18">
+    <cfRule type="expression" dxfId="264" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="264" priority="1">
+    <cfRule type="expression" dxfId="263" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="263" priority="15">
+    <cfRule type="expression" dxfId="262" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="262" priority="12">
+    <cfRule type="expression" dxfId="261" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="261" priority="11">
+    <cfRule type="expression" dxfId="260" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="260" priority="14">
+    <cfRule type="expression" dxfId="259" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="259" priority="5">
+    <cfRule type="expression" dxfId="258" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23146,32 +23137,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="258" priority="2">
+    <cfRule type="expression" dxfId="257" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="257" priority="4">
+    <cfRule type="expression" dxfId="256" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="256" priority="16">
+    <cfRule type="expression" dxfId="255" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="255" priority="15">
+    <cfRule type="expression" dxfId="254" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="254" priority="1">
+    <cfRule type="expression" dxfId="253" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="253" priority="7">
+    <cfRule type="expression" dxfId="252" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08210E6-F1C9-405A-B782-8EE429371A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1959430D-9FDE-4CEA-BC15-42A70CD2E95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="24" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="24" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="446">
   <si>
     <t>Week</t>
   </si>
@@ -1427,6 +1427,12 @@
   </si>
   <si>
     <t>werken studio digi</t>
+  </si>
+  <si>
+    <t>Communicatie deadline: structuurblad</t>
+  </si>
+  <si>
+    <t>Communicatie: eigen presentatie + kijken naar de andere</t>
   </si>
 </sst>
 </file>
@@ -14009,7 +14015,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>444</v>
+      </c>
       <c r="C28" s="16" t="s">
         <v>423</v>
       </c>
@@ -14027,7 +14035,9 @@
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="D29" s="17" t="s">
+        <v>445</v>
+      </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
     </row>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{568F801A-4679-495B-9785-A28FBB072DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C470EF6-4F8B-4D0D-914D-EB1B1B543591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="453">
   <si>
     <t>Week</t>
   </si>
@@ -1442,6 +1442,18 @@
   </si>
   <si>
     <t>TERUG NAAR BELGIE</t>
+  </si>
+  <si>
+    <t>Blijkbaar examen deze dag?</t>
+  </si>
+  <si>
+    <t>Blijkbaar examen 2 deze dag?</t>
+  </si>
+  <si>
+    <t>Presentatie geven communicatie!</t>
+  </si>
+  <si>
+    <t>DEADLINE crossmedia?</t>
   </si>
 </sst>
 </file>
@@ -1769,7 +1781,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="305">
+  <dxfs count="306">
     <dxf>
       <font>
         <color theme="1"/>
@@ -2535,6 +2547,16 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5291,47 +5313,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="251" priority="17">
+    <cfRule type="expression" dxfId="252" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="250" priority="25">
+    <cfRule type="expression" dxfId="251" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="249" priority="24">
+    <cfRule type="expression" dxfId="250" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="248" priority="5">
+    <cfRule type="expression" dxfId="249" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="247" priority="9">
+    <cfRule type="expression" dxfId="248" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="246" priority="8">
+    <cfRule type="expression" dxfId="247" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="245" priority="11">
+    <cfRule type="expression" dxfId="246" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="244" priority="15">
+    <cfRule type="expression" dxfId="245" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="243" priority="2">
+    <cfRule type="expression" dxfId="244" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5790,42 +5812,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="242" priority="15">
+    <cfRule type="expression" dxfId="243" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="241" priority="10">
+    <cfRule type="expression" dxfId="242" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="240" priority="24">
+    <cfRule type="expression" dxfId="241" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="239" priority="23">
+    <cfRule type="expression" dxfId="240" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="238" priority="1">
+    <cfRule type="expression" dxfId="239" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="237" priority="7">
+    <cfRule type="expression" dxfId="238" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="236" priority="3">
+    <cfRule type="expression" dxfId="237" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="235" priority="14">
+    <cfRule type="expression" dxfId="236" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6264,47 +6286,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="234" priority="10">
+    <cfRule type="expression" dxfId="235" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="233" priority="1">
+    <cfRule type="expression" dxfId="234" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="232" priority="25">
+    <cfRule type="expression" dxfId="233" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="231" priority="24">
+    <cfRule type="expression" dxfId="232" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="230" priority="4">
+    <cfRule type="expression" dxfId="231" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="229" priority="3">
+    <cfRule type="expression" dxfId="230" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="228" priority="6">
+    <cfRule type="expression" dxfId="229" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="227" priority="9">
+    <cfRule type="expression" dxfId="228" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="226" priority="11">
+    <cfRule type="expression" dxfId="227" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6767,57 +6789,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="225" priority="36">
+    <cfRule type="expression" dxfId="226" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="224" priority="51">
+    <cfRule type="expression" dxfId="225" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="223" priority="50">
+    <cfRule type="expression" dxfId="224" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="222" priority="9">
+    <cfRule type="expression" dxfId="223" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="221" priority="28">
+    <cfRule type="expression" dxfId="222" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="220" priority="11">
+    <cfRule type="expression" dxfId="221" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="219" priority="24">
+    <cfRule type="expression" dxfId="220" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="218" priority="31">
+    <cfRule type="expression" dxfId="219" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="217" priority="7">
+    <cfRule type="expression" dxfId="218" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="216" priority="35">
+    <cfRule type="expression" dxfId="217" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="215" priority="1">
+    <cfRule type="expression" dxfId="216" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7249,59 +7271,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="214" priority="35">
+    <cfRule type="expression" dxfId="215" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="213" priority="42">
+    <cfRule type="expression" dxfId="214" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="212" priority="54">
+    <cfRule type="expression" dxfId="213" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="211" priority="53">
+    <cfRule type="expression" dxfId="212" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="210" priority="5">
+    <cfRule type="expression" dxfId="211" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="209" priority="30">
+    <cfRule type="expression" dxfId="210" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="208" priority="33">
+    <cfRule type="expression" dxfId="209" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="207" priority="37">
+    <cfRule type="expression" dxfId="208" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="206" priority="41">
+    <cfRule type="expression" dxfId="207" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="205" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="203" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="202" priority="1">
+    <cfRule type="expression" dxfId="203" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7767,57 +7789,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="201" priority="1">
+    <cfRule type="expression" dxfId="202" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="200" priority="18">
+    <cfRule type="expression" dxfId="201" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="199" priority="41">
+    <cfRule type="expression" dxfId="200" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="198" priority="40">
+    <cfRule type="expression" dxfId="199" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="197" priority="13">
+    <cfRule type="expression" dxfId="198" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="196" priority="3">
+    <cfRule type="expression" dxfId="197" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="195" priority="5">
+    <cfRule type="expression" dxfId="196" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="194" priority="19">
+    <cfRule type="expression" dxfId="195" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="193" priority="7">
+    <cfRule type="expression" dxfId="194" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="192" priority="27">
+    <cfRule type="expression" dxfId="193" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="191" priority="8">
+    <cfRule type="expression" dxfId="192" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8277,32 +8299,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="190" priority="21">
+    <cfRule type="expression" dxfId="191" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="189" priority="43">
+    <cfRule type="expression" dxfId="190" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="188" priority="42">
+    <cfRule type="expression" dxfId="189" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="187" priority="1">
+    <cfRule type="expression" dxfId="188" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="186" priority="16">
+    <cfRule type="expression" dxfId="187" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="185" priority="24">
+    <cfRule type="expression" dxfId="186" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8718,32 +8740,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="184" priority="30">
+    <cfRule type="expression" dxfId="185" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="183" priority="29">
+    <cfRule type="expression" dxfId="184" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="182" priority="16">
+    <cfRule type="expression" dxfId="183" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="181" priority="1">
+    <cfRule type="expression" dxfId="182" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="180" priority="4">
+    <cfRule type="expression" dxfId="181" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="179" priority="5">
+    <cfRule type="expression" dxfId="180" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9153,32 +9175,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="178" priority="39">
+    <cfRule type="expression" dxfId="179" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="177" priority="38">
+    <cfRule type="expression" dxfId="178" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="176" priority="20">
+    <cfRule type="expression" dxfId="177" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="175" priority="1">
+    <cfRule type="expression" dxfId="176" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="174" priority="3">
+    <cfRule type="expression" dxfId="175" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="173" priority="2">
+    <cfRule type="expression" dxfId="174" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9598,37 +9620,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="172" priority="18">
+    <cfRule type="expression" dxfId="173" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="171" priority="2">
+    <cfRule type="expression" dxfId="172" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="170" priority="32">
+    <cfRule type="expression" dxfId="171" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="169" priority="31">
+    <cfRule type="expression" dxfId="170" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="168" priority="5">
+    <cfRule type="expression" dxfId="169" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="167" priority="1">
+    <cfRule type="expression" dxfId="168" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="166" priority="3">
+    <cfRule type="expression" dxfId="167" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10044,22 +10066,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="304" priority="14">
+    <cfRule type="expression" dxfId="305" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="303" priority="6">
+    <cfRule type="expression" dxfId="304" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="302" priority="15">
+    <cfRule type="expression" dxfId="303" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="301" priority="1">
+    <cfRule type="expression" dxfId="302" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10457,22 +10479,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="165" priority="32">
+    <cfRule type="expression" dxfId="166" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="164" priority="31">
+    <cfRule type="expression" dxfId="165" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="163" priority="12">
+    <cfRule type="expression" dxfId="164" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="1">
+    <cfRule type="expression" dxfId="163" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10838,22 +10860,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="17">
+    <cfRule type="expression" dxfId="162" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="16">
+    <cfRule type="expression" dxfId="161" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="159" priority="2">
+    <cfRule type="expression" dxfId="160" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="158" priority="1">
+    <cfRule type="expression" dxfId="159" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11288,47 +11310,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="157" priority="32">
+    <cfRule type="expression" dxfId="158" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="156" priority="31">
+    <cfRule type="expression" dxfId="157" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="155" priority="1">
+    <cfRule type="expression" dxfId="156" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="154" priority="3">
+    <cfRule type="expression" dxfId="155" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="153" priority="5">
+    <cfRule type="expression" dxfId="154" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="152" priority="12">
+    <cfRule type="expression" dxfId="153" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="151" priority="18">
+    <cfRule type="expression" dxfId="152" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="150" priority="27">
+    <cfRule type="expression" dxfId="151" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="149" priority="33">
+    <cfRule type="expression" dxfId="150" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11759,47 +11781,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="148" priority="12">
+    <cfRule type="expression" dxfId="149" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="147" priority="29">
+    <cfRule type="expression" dxfId="148" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="146" priority="28">
+    <cfRule type="expression" dxfId="147" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="145" priority="27">
+    <cfRule type="expression" dxfId="146" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="144" priority="1">
+    <cfRule type="expression" dxfId="145" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="143" priority="3">
+    <cfRule type="expression" dxfId="144" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="142" priority="9">
+    <cfRule type="expression" dxfId="143" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="141" priority="24">
+    <cfRule type="expression" dxfId="142" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="140" priority="30">
+    <cfRule type="expression" dxfId="141" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12234,52 +12256,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="139" priority="4">
+    <cfRule type="expression" dxfId="140" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="138" priority="27">
+    <cfRule type="expression" dxfId="139" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="137" priority="26">
+    <cfRule type="expression" dxfId="138" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="136" priority="1">
+    <cfRule type="expression" dxfId="137" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="135" priority="2">
+    <cfRule type="expression" dxfId="136" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="134" priority="28">
+    <cfRule type="expression" dxfId="135" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="133" priority="5">
+    <cfRule type="expression" dxfId="134" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="132" priority="8">
+    <cfRule type="expression" dxfId="133" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="131" priority="18">
+    <cfRule type="expression" dxfId="132" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="130" priority="22">
+    <cfRule type="expression" dxfId="131" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12708,47 +12730,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="129" priority="13">
+    <cfRule type="expression" dxfId="130" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="128" priority="22">
+    <cfRule type="expression" dxfId="129" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="127" priority="21">
+    <cfRule type="expression" dxfId="128" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="126" priority="1">
+    <cfRule type="expression" dxfId="127" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="125" priority="3">
+    <cfRule type="expression" dxfId="126" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="124" priority="5">
+    <cfRule type="expression" dxfId="125" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="123" priority="8">
+    <cfRule type="expression" dxfId="124" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="122" priority="17">
+    <cfRule type="expression" dxfId="123" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="121" priority="23">
+    <cfRule type="expression" dxfId="122" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13171,52 +13193,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="120" priority="5">
+    <cfRule type="expression" dxfId="121" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="119" priority="28">
+    <cfRule type="expression" dxfId="120" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="118" priority="27">
+    <cfRule type="expression" dxfId="119" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="117" priority="1">
+    <cfRule type="expression" dxfId="118" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="116" priority="3">
+    <cfRule type="expression" dxfId="117" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="115" priority="29">
+    <cfRule type="expression" dxfId="116" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="114" priority="22">
+    <cfRule type="expression" dxfId="115" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="113" priority="8">
+    <cfRule type="expression" dxfId="114" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="112" priority="19">
+    <cfRule type="expression" dxfId="113" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="111" priority="23">
+    <cfRule type="expression" dxfId="112" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13557,9 +13579,7 @@
       <c r="C28" s="22" t="s">
         <v>421</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>443</v>
-      </c>
+      <c r="D28" s="17"/>
       <c r="E28" s="16" t="s">
         <v>427</v>
       </c>
@@ -13569,14 +13589,16 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="22" t="s">
         <v>411</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>431</v>
       </c>
       <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="E29" s="22" t="s">
+        <v>443</v>
+      </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13593,7 +13615,7 @@
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="22" t="s">
         <v>304</v>
       </c>
       <c r="C31" s="22" t="s">
@@ -13645,47 +13667,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="110" priority="11">
+    <cfRule type="expression" dxfId="111" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="109" priority="22">
+    <cfRule type="expression" dxfId="110" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="108" priority="21">
+    <cfRule type="expression" dxfId="109" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="107" priority="1">
+    <cfRule type="expression" dxfId="108" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="106" priority="3">
+    <cfRule type="expression" dxfId="107" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="105" priority="23">
+    <cfRule type="expression" dxfId="106" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="104" priority="5">
+    <cfRule type="expression" dxfId="105" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="103" priority="7">
+    <cfRule type="expression" dxfId="104" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="102" priority="17">
+    <cfRule type="expression" dxfId="103" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14108,52 +14130,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="101" priority="5">
+    <cfRule type="expression" dxfId="102" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="100" priority="26">
+    <cfRule type="expression" dxfId="101" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="99" priority="25">
+    <cfRule type="expression" dxfId="100" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="98" priority="1">
+    <cfRule type="expression" dxfId="99" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="97" priority="3">
+    <cfRule type="expression" dxfId="98" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="96" priority="27">
+    <cfRule type="expression" dxfId="97" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="95" priority="20">
+    <cfRule type="expression" dxfId="96" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="94" priority="8">
+    <cfRule type="expression" dxfId="95" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="93" priority="18">
+    <cfRule type="expression" dxfId="94" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="92" priority="21">
+    <cfRule type="expression" dxfId="93" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14314,6 +14336,9 @@
       <c r="C9" s="29" t="s">
         <v>364</v>
       </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -14325,6 +14350,9 @@
       <c r="C10" s="28" t="s">
         <v>13</v>
       </c>
+      <c r="D10" s="5" t="s">
+        <v>356</v>
+      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -14334,6 +14362,9 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="28"/>
+      <c r="D11" s="5" t="s">
+        <v>359</v>
+      </c>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -14343,6 +14374,7 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="28"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -14352,6 +14384,7 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="28"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -14519,14 +14552,18 @@
       <c r="E29" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="F29" s="17"/>
+      <c r="F29" s="17" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="C30" s="17"/>
+      <c r="C30" s="17" t="s">
+        <v>452</v>
+      </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -14581,37 +14618,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B14 F5:F6 E7:F25 B15:D15 C16:D25">
-    <cfRule type="expression" dxfId="91" priority="8">
+    <cfRule type="expression" dxfId="92" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="91" priority="23">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
     <cfRule type="expression" dxfId="90" priority="22">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="89" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="88" priority="1">
+    <cfRule type="expression" dxfId="89" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="87" priority="3">
+    <cfRule type="expression" dxfId="88" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8 C14:D14">
-    <cfRule type="expression" dxfId="86" priority="5">
+    <cfRule type="expression" dxfId="87" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="85" priority="17">
+    <cfRule type="expression" dxfId="86" priority="18">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:D13">
+    <cfRule type="expression" dxfId="85" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15015,30 +15057,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="300" priority="3">
+    <cfRule type="expression" dxfId="301" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="299" priority="14">
+    <cfRule type="expression" dxfId="300" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="298" priority="15">
+    <cfRule type="expression" dxfId="299" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="297" priority="7">
+    <cfRule type="expression" dxfId="298" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="296" priority="9">
+    <cfRule type="expression" dxfId="297" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="295" priority="12">
+    <cfRule type="expression" dxfId="296" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16715,7 +16757,9 @@
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="D29" s="17" t="s">
+        <v>451</v>
+      </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
     </row>
@@ -19489,8 +19533,12 @@
       <c r="B29" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
+      <c r="C29" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>450</v>
+      </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
     </row>
@@ -20012,22 +20060,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="294" priority="10">
+    <cfRule type="expression" dxfId="295" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="293" priority="9">
+    <cfRule type="expression" dxfId="294" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="292" priority="1">
+    <cfRule type="expression" dxfId="293" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="291" priority="7">
+    <cfRule type="expression" dxfId="292" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21400,42 +21448,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="290" priority="15">
+    <cfRule type="expression" dxfId="291" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="289" priority="13">
+    <cfRule type="expression" dxfId="290" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="288" priority="30">
+    <cfRule type="expression" dxfId="289" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="287" priority="29">
+    <cfRule type="expression" dxfId="288" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="286" priority="7">
+    <cfRule type="expression" dxfId="287" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="285" priority="24">
+    <cfRule type="expression" dxfId="286" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="284" priority="20">
+    <cfRule type="expression" dxfId="285" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="283" priority="25">
+    <cfRule type="expression" dxfId="284" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21836,32 +21884,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="282" priority="8">
+    <cfRule type="expression" dxfId="283" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="281" priority="13">
+    <cfRule type="expression" dxfId="282" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="280" priority="12">
+    <cfRule type="expression" dxfId="281" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="279" priority="1">
+    <cfRule type="expression" dxfId="280" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="278" priority="4">
+    <cfRule type="expression" dxfId="279" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="277" priority="7">
+    <cfRule type="expression" dxfId="278" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22245,52 +22293,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="276" priority="22">
+    <cfRule type="expression" dxfId="277" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="275" priority="23">
+    <cfRule type="expression" dxfId="276" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="274" priority="45">
+    <cfRule type="expression" dxfId="275" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="273" priority="44">
+    <cfRule type="expression" dxfId="274" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="272" priority="1">
+    <cfRule type="expression" dxfId="273" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="271" priority="35">
+    <cfRule type="expression" dxfId="272" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="270" priority="36">
+    <cfRule type="expression" dxfId="271" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="269" priority="16">
+    <cfRule type="expression" dxfId="270" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="268" priority="34">
+    <cfRule type="expression" dxfId="269" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="267" priority="5">
+    <cfRule type="expression" dxfId="268" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22703,47 +22751,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="266" priority="16">
+    <cfRule type="expression" dxfId="267" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="265" priority="19">
+    <cfRule type="expression" dxfId="266" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="264" priority="18">
+    <cfRule type="expression" dxfId="265" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="263" priority="1">
+    <cfRule type="expression" dxfId="264" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="262" priority="15">
+    <cfRule type="expression" dxfId="263" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="261" priority="12">
+    <cfRule type="expression" dxfId="262" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="260" priority="11">
+    <cfRule type="expression" dxfId="261" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="259" priority="14">
+    <cfRule type="expression" dxfId="260" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="258" priority="5">
+    <cfRule type="expression" dxfId="259" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23166,32 +23214,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="257" priority="2">
+    <cfRule type="expression" dxfId="258" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="256" priority="4">
+    <cfRule type="expression" dxfId="257" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="255" priority="16">
+    <cfRule type="expression" dxfId="256" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="254" priority="15">
+    <cfRule type="expression" dxfId="255" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="253" priority="1">
+    <cfRule type="expression" dxfId="254" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="252" priority="7">
+    <cfRule type="expression" dxfId="253" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C470EF6-4F8B-4D0D-914D-EB1B1B543591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E90BEDE-C9C3-4183-BDA1-2F58E5C0BB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="452">
   <si>
     <t>Week</t>
   </si>
@@ -1430,9 +1430,6 @@
   </si>
   <si>
     <t>Communicatie deadline: structuurblad</t>
-  </si>
-  <si>
-    <t>Communicatie: eigen presentatie + kijken naar de andere</t>
   </si>
   <si>
     <t>CALAN</t>
@@ -1781,7 +1778,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="306">
+  <dxfs count="304">
     <dxf>
       <font>
         <color theme="1"/>
@@ -2547,26 +2544,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5313,47 +5290,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="252" priority="17">
+    <cfRule type="expression" dxfId="250" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="251" priority="25">
+    <cfRule type="expression" dxfId="249" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="250" priority="24">
+    <cfRule type="expression" dxfId="248" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="249" priority="5">
+    <cfRule type="expression" dxfId="247" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="248" priority="9">
+    <cfRule type="expression" dxfId="246" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="247" priority="8">
+    <cfRule type="expression" dxfId="245" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="246" priority="11">
+    <cfRule type="expression" dxfId="244" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="245" priority="15">
+    <cfRule type="expression" dxfId="243" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="244" priority="2">
+    <cfRule type="expression" dxfId="242" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5812,42 +5789,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="243" priority="15">
+    <cfRule type="expression" dxfId="241" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="242" priority="10">
+    <cfRule type="expression" dxfId="240" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="241" priority="24">
+    <cfRule type="expression" dxfId="239" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="240" priority="23">
+    <cfRule type="expression" dxfId="238" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="239" priority="1">
+    <cfRule type="expression" dxfId="237" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="238" priority="7">
+    <cfRule type="expression" dxfId="236" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="237" priority="3">
+    <cfRule type="expression" dxfId="235" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="236" priority="14">
+    <cfRule type="expression" dxfId="234" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6286,47 +6263,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="235" priority="10">
+    <cfRule type="expression" dxfId="233" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="234" priority="1">
+    <cfRule type="expression" dxfId="232" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="233" priority="25">
+    <cfRule type="expression" dxfId="231" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="232" priority="24">
+    <cfRule type="expression" dxfId="230" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="231" priority="4">
+    <cfRule type="expression" dxfId="229" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="230" priority="3">
+    <cfRule type="expression" dxfId="228" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="229" priority="6">
+    <cfRule type="expression" dxfId="227" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="228" priority="9">
+    <cfRule type="expression" dxfId="226" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="227" priority="11">
+    <cfRule type="expression" dxfId="225" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6789,57 +6766,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="226" priority="36">
+    <cfRule type="expression" dxfId="224" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="225" priority="51">
+    <cfRule type="expression" dxfId="223" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="224" priority="50">
+    <cfRule type="expression" dxfId="222" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="223" priority="9">
+    <cfRule type="expression" dxfId="221" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="222" priority="28">
+    <cfRule type="expression" dxfId="220" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="221" priority="11">
+    <cfRule type="expression" dxfId="219" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="220" priority="24">
+    <cfRule type="expression" dxfId="218" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="219" priority="31">
+    <cfRule type="expression" dxfId="217" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="218" priority="7">
+    <cfRule type="expression" dxfId="216" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="217" priority="35">
+    <cfRule type="expression" dxfId="215" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="216" priority="1">
+    <cfRule type="expression" dxfId="214" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7271,59 +7248,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="215" priority="35">
+    <cfRule type="expression" dxfId="213" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="214" priority="42">
+    <cfRule type="expression" dxfId="212" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="213" priority="54">
+    <cfRule type="expression" dxfId="211" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="212" priority="53">
+    <cfRule type="expression" dxfId="210" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="211" priority="5">
+    <cfRule type="expression" dxfId="209" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="210" priority="30">
+    <cfRule type="expression" dxfId="208" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="209" priority="33">
+    <cfRule type="expression" dxfId="207" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="208" priority="37">
+    <cfRule type="expression" dxfId="206" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="207" priority="41">
+    <cfRule type="expression" dxfId="205" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="206" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="204" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="203" priority="1">
+    <cfRule type="expression" dxfId="201" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7789,57 +7766,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="202" priority="1">
+    <cfRule type="expression" dxfId="200" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="201" priority="18">
+    <cfRule type="expression" dxfId="199" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="200" priority="41">
+    <cfRule type="expression" dxfId="198" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="199" priority="40">
+    <cfRule type="expression" dxfId="197" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="198" priority="13">
+    <cfRule type="expression" dxfId="196" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="197" priority="3">
+    <cfRule type="expression" dxfId="195" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="196" priority="5">
+    <cfRule type="expression" dxfId="194" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="195" priority="19">
+    <cfRule type="expression" dxfId="193" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="194" priority="7">
+    <cfRule type="expression" dxfId="192" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="193" priority="27">
+    <cfRule type="expression" dxfId="191" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="192" priority="8">
+    <cfRule type="expression" dxfId="190" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8299,32 +8276,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="191" priority="21">
+    <cfRule type="expression" dxfId="189" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="190" priority="43">
+    <cfRule type="expression" dxfId="188" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="189" priority="42">
+    <cfRule type="expression" dxfId="187" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="188" priority="1">
+    <cfRule type="expression" dxfId="186" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="187" priority="16">
+    <cfRule type="expression" dxfId="185" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="186" priority="24">
+    <cfRule type="expression" dxfId="184" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8740,32 +8717,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="185" priority="30">
+    <cfRule type="expression" dxfId="183" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="184" priority="29">
+    <cfRule type="expression" dxfId="182" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="183" priority="16">
+    <cfRule type="expression" dxfId="181" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="182" priority="1">
+    <cfRule type="expression" dxfId="180" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="181" priority="4">
+    <cfRule type="expression" dxfId="179" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="180" priority="5">
+    <cfRule type="expression" dxfId="178" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9175,32 +9152,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="179" priority="39">
+    <cfRule type="expression" dxfId="177" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="178" priority="38">
+    <cfRule type="expression" dxfId="176" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="177" priority="20">
+    <cfRule type="expression" dxfId="175" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="176" priority="1">
+    <cfRule type="expression" dxfId="174" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="175" priority="3">
+    <cfRule type="expression" dxfId="173" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="174" priority="2">
+    <cfRule type="expression" dxfId="172" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9620,37 +9597,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="173" priority="18">
+    <cfRule type="expression" dxfId="171" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="172" priority="2">
+    <cfRule type="expression" dxfId="170" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="171" priority="32">
+    <cfRule type="expression" dxfId="169" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="170" priority="31">
+    <cfRule type="expression" dxfId="168" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="169" priority="5">
+    <cfRule type="expression" dxfId="167" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="168" priority="1">
+    <cfRule type="expression" dxfId="166" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="167" priority="3">
+    <cfRule type="expression" dxfId="165" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10066,22 +10043,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="305" priority="14">
+    <cfRule type="expression" dxfId="303" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="304" priority="6">
+    <cfRule type="expression" dxfId="302" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="303" priority="15">
+    <cfRule type="expression" dxfId="301" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="302" priority="1">
+    <cfRule type="expression" dxfId="300" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10479,22 +10456,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="166" priority="32">
+    <cfRule type="expression" dxfId="164" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="165" priority="31">
+    <cfRule type="expression" dxfId="163" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="164" priority="12">
+    <cfRule type="expression" dxfId="162" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="163" priority="1">
+    <cfRule type="expression" dxfId="161" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10860,22 +10837,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="162" priority="17">
+    <cfRule type="expression" dxfId="160" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="161" priority="16">
+    <cfRule type="expression" dxfId="159" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="160" priority="2">
+    <cfRule type="expression" dxfId="158" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="159" priority="1">
+    <cfRule type="expression" dxfId="157" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11310,47 +11287,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="158" priority="32">
+    <cfRule type="expression" dxfId="156" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="157" priority="31">
+    <cfRule type="expression" dxfId="155" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="156" priority="1">
+    <cfRule type="expression" dxfId="154" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="155" priority="3">
+    <cfRule type="expression" dxfId="153" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="154" priority="5">
+    <cfRule type="expression" dxfId="152" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="153" priority="12">
+    <cfRule type="expression" dxfId="151" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="152" priority="18">
+    <cfRule type="expression" dxfId="150" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="151" priority="27">
+    <cfRule type="expression" dxfId="149" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="150" priority="33">
+    <cfRule type="expression" dxfId="148" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11781,47 +11758,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="149" priority="12">
+    <cfRule type="expression" dxfId="147" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="148" priority="29">
+    <cfRule type="expression" dxfId="146" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="147" priority="28">
+    <cfRule type="expression" dxfId="145" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="146" priority="27">
+    <cfRule type="expression" dxfId="144" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="145" priority="1">
+    <cfRule type="expression" dxfId="143" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="144" priority="3">
+    <cfRule type="expression" dxfId="142" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="143" priority="9">
+    <cfRule type="expression" dxfId="141" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="142" priority="24">
+    <cfRule type="expression" dxfId="140" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="141" priority="30">
+    <cfRule type="expression" dxfId="139" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12256,52 +12233,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="140" priority="4">
+    <cfRule type="expression" dxfId="138" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="139" priority="27">
+    <cfRule type="expression" dxfId="137" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="138" priority="26">
+    <cfRule type="expression" dxfId="136" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="137" priority="1">
+    <cfRule type="expression" dxfId="135" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="136" priority="2">
+    <cfRule type="expression" dxfId="134" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="135" priority="28">
+    <cfRule type="expression" dxfId="133" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="134" priority="5">
+    <cfRule type="expression" dxfId="132" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="133" priority="8">
+    <cfRule type="expression" dxfId="131" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="132" priority="18">
+    <cfRule type="expression" dxfId="130" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="131" priority="22">
+    <cfRule type="expression" dxfId="129" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12730,47 +12707,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="130" priority="13">
+    <cfRule type="expression" dxfId="128" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="129" priority="22">
+    <cfRule type="expression" dxfId="127" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="128" priority="21">
+    <cfRule type="expression" dxfId="126" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="127" priority="1">
+    <cfRule type="expression" dxfId="125" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="126" priority="3">
+    <cfRule type="expression" dxfId="124" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="125" priority="5">
+    <cfRule type="expression" dxfId="123" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="124" priority="8">
+    <cfRule type="expression" dxfId="122" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="123" priority="17">
+    <cfRule type="expression" dxfId="121" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="122" priority="23">
+    <cfRule type="expression" dxfId="120" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13193,52 +13170,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="121" priority="5">
+    <cfRule type="expression" dxfId="119" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="120" priority="28">
+    <cfRule type="expression" dxfId="118" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="119" priority="27">
+    <cfRule type="expression" dxfId="117" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="118" priority="1">
+    <cfRule type="expression" dxfId="116" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="117" priority="3">
+    <cfRule type="expression" dxfId="115" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="116" priority="29">
+    <cfRule type="expression" dxfId="114" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="115" priority="22">
+    <cfRule type="expression" dxfId="113" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="114" priority="8">
+    <cfRule type="expression" dxfId="112" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="113" priority="19">
+    <cfRule type="expression" dxfId="111" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="112" priority="23">
+    <cfRule type="expression" dxfId="110" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13580,10 +13557,10 @@
         <v>421</v>
       </c>
       <c r="D28" s="17"/>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="22" t="s">
         <v>427</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="22" t="s">
         <v>422</v>
       </c>
     </row>
@@ -13667,47 +13644,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="111" priority="11">
+    <cfRule type="expression" dxfId="109" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="110" priority="22">
+    <cfRule type="expression" dxfId="108" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="109" priority="21">
+    <cfRule type="expression" dxfId="107" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="108" priority="1">
+    <cfRule type="expression" dxfId="106" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="107" priority="3">
+    <cfRule type="expression" dxfId="105" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="106" priority="23">
+    <cfRule type="expression" dxfId="104" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="105" priority="5">
+    <cfRule type="expression" dxfId="103" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="104" priority="7">
+    <cfRule type="expression" dxfId="102" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="103" priority="17">
+    <cfRule type="expression" dxfId="101" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14066,9 +14043,7 @@
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="17" t="s">
-        <v>445</v>
-      </c>
+      <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
     </row>
@@ -14130,52 +14105,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="102" priority="5">
+    <cfRule type="expression" dxfId="100" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="101" priority="26">
+    <cfRule type="expression" dxfId="99" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="100" priority="25">
+    <cfRule type="expression" dxfId="98" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="99" priority="1">
+    <cfRule type="expression" dxfId="97" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="98" priority="3">
+    <cfRule type="expression" dxfId="96" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="97" priority="27">
+    <cfRule type="expression" dxfId="95" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="96" priority="20">
+    <cfRule type="expression" dxfId="94" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="95" priority="8">
+    <cfRule type="expression" dxfId="93" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="94" priority="18">
+    <cfRule type="expression" dxfId="92" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="93" priority="21">
+    <cfRule type="expression" dxfId="91" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14553,7 +14528,7 @@
         <v>440</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14562,7 +14537,7 @@
         <v>434</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -14617,34 +14592,24 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:B14 F5:F6 E7:F25 B15:D15 C16:D25">
-    <cfRule type="expression" dxfId="92" priority="9">
+  <conditionalFormatting sqref="B4:D15">
+    <cfRule type="expression" dxfId="90" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="91" priority="23">
+    <cfRule type="expression" dxfId="89" priority="23">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="90" priority="22">
+    <cfRule type="expression" dxfId="88" priority="22">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="89" priority="2">
+    <cfRule type="expression" dxfId="87" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="88" priority="4">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D8 C14:D14">
-    <cfRule type="expression" dxfId="87" priority="6">
-      <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
@@ -14652,8 +14617,8 @@
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="85" priority="1">
+  <conditionalFormatting sqref="F5:F6 E7:F25 C16:D25">
+    <cfRule type="expression" dxfId="85" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15057,30 +15022,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="301" priority="3">
+    <cfRule type="expression" dxfId="299" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="300" priority="14">
+    <cfRule type="expression" dxfId="298" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="299" priority="15">
+    <cfRule type="expression" dxfId="297" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="298" priority="7">
+    <cfRule type="expression" dxfId="296" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="297" priority="9">
+    <cfRule type="expression" dxfId="295" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="296" priority="12">
+    <cfRule type="expression" dxfId="294" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16758,7 +16723,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -17656,16 +17621,16 @@
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>386</v>
       </c>
       <c r="E28" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="F28" s="16" t="s">
         <v>446</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -17683,7 +17648,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -18147,7 +18112,7 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -19534,10 +19499,10 @@
         <v>43</v>
       </c>
       <c r="C29" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="D29" s="19" t="s">
         <v>449</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>450</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
@@ -20060,22 +20025,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="295" priority="10">
+    <cfRule type="expression" dxfId="293" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="294" priority="9">
+    <cfRule type="expression" dxfId="292" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="293" priority="1">
+    <cfRule type="expression" dxfId="291" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="292" priority="7">
+    <cfRule type="expression" dxfId="290" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21448,42 +21413,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="291" priority="15">
+    <cfRule type="expression" dxfId="289" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="290" priority="13">
+    <cfRule type="expression" dxfId="288" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="289" priority="30">
+    <cfRule type="expression" dxfId="287" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="288" priority="29">
+    <cfRule type="expression" dxfId="286" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="287" priority="7">
+    <cfRule type="expression" dxfId="285" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="286" priority="24">
+    <cfRule type="expression" dxfId="284" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="285" priority="20">
+    <cfRule type="expression" dxfId="283" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="284" priority="25">
+    <cfRule type="expression" dxfId="282" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21884,32 +21849,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="283" priority="8">
+    <cfRule type="expression" dxfId="281" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="282" priority="13">
+    <cfRule type="expression" dxfId="280" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="281" priority="12">
+    <cfRule type="expression" dxfId="279" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="280" priority="1">
+    <cfRule type="expression" dxfId="278" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="279" priority="4">
+    <cfRule type="expression" dxfId="277" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="278" priority="7">
+    <cfRule type="expression" dxfId="276" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22293,52 +22258,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="277" priority="22">
+    <cfRule type="expression" dxfId="275" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="276" priority="23">
+    <cfRule type="expression" dxfId="274" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="275" priority="45">
+    <cfRule type="expression" dxfId="273" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="274" priority="44">
+    <cfRule type="expression" dxfId="272" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="273" priority="1">
+    <cfRule type="expression" dxfId="271" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="272" priority="35">
+    <cfRule type="expression" dxfId="270" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="271" priority="36">
+    <cfRule type="expression" dxfId="269" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="270" priority="16">
+    <cfRule type="expression" dxfId="268" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="269" priority="34">
+    <cfRule type="expression" dxfId="267" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="268" priority="5">
+    <cfRule type="expression" dxfId="266" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22751,47 +22716,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="267" priority="16">
+    <cfRule type="expression" dxfId="265" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="266" priority="19">
+    <cfRule type="expression" dxfId="264" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="265" priority="18">
+    <cfRule type="expression" dxfId="263" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="264" priority="1">
+    <cfRule type="expression" dxfId="262" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="263" priority="15">
+    <cfRule type="expression" dxfId="261" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="262" priority="12">
+    <cfRule type="expression" dxfId="260" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="261" priority="11">
+    <cfRule type="expression" dxfId="259" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="260" priority="14">
+    <cfRule type="expression" dxfId="258" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="259" priority="5">
+    <cfRule type="expression" dxfId="257" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23214,32 +23179,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="258" priority="2">
+    <cfRule type="expression" dxfId="256" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="257" priority="4">
+    <cfRule type="expression" dxfId="255" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="256" priority="16">
+    <cfRule type="expression" dxfId="254" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="255" priority="15">
+    <cfRule type="expression" dxfId="253" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="254" priority="1">
+    <cfRule type="expression" dxfId="252" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="253" priority="7">
+    <cfRule type="expression" dxfId="251" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E90BEDE-C9C3-4183-BDA1-2F58E5C0BB1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E938C334-72C4-4537-B933-4D7B6C757CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="460">
   <si>
     <t>Week</t>
   </si>
@@ -1451,6 +1451,30 @@
   </si>
   <si>
     <t>DEADLINE crossmedia?</t>
+  </si>
+  <si>
+    <t>VERHOOR</t>
+  </si>
+  <si>
+    <t>CM: Bookmaking 2</t>
+  </si>
+  <si>
+    <t>Crossmedia bookmaking book moet gemaakt zijn</t>
+  </si>
+  <si>
+    <t>Boek maken bookmaking</t>
+  </si>
+  <si>
+    <t>Crossmedia's indienen</t>
+  </si>
+  <si>
+    <t>Werken studio digitaal!</t>
+  </si>
+  <si>
+    <t>Fimen video donderdag</t>
+  </si>
+  <si>
+    <t>Video donderdag moet af zijn!</t>
   </si>
 </sst>
 </file>
@@ -1778,7 +1802,257 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="304">
+  <dxfs count="329">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -5290,47 +5564,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="250" priority="17">
+    <cfRule type="expression" dxfId="275" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="249" priority="25">
+    <cfRule type="expression" dxfId="274" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="248" priority="24">
+    <cfRule type="expression" dxfId="273" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="247" priority="5">
+    <cfRule type="expression" dxfId="272" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="246" priority="9">
+    <cfRule type="expression" dxfId="271" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="245" priority="8">
+    <cfRule type="expression" dxfId="270" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="244" priority="11">
+    <cfRule type="expression" dxfId="269" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="243" priority="15">
+    <cfRule type="expression" dxfId="268" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="242" priority="2">
+    <cfRule type="expression" dxfId="267" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5789,42 +6063,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="241" priority="15">
+    <cfRule type="expression" dxfId="266" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="240" priority="10">
+    <cfRule type="expression" dxfId="265" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="239" priority="24">
+    <cfRule type="expression" dxfId="264" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="238" priority="23">
+    <cfRule type="expression" dxfId="263" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="237" priority="1">
+    <cfRule type="expression" dxfId="262" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="236" priority="7">
+    <cfRule type="expression" dxfId="261" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="235" priority="3">
+    <cfRule type="expression" dxfId="260" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="234" priority="14">
+    <cfRule type="expression" dxfId="259" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6263,47 +6537,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="233" priority="10">
+    <cfRule type="expression" dxfId="258" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="232" priority="1">
+    <cfRule type="expression" dxfId="257" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="231" priority="25">
+    <cfRule type="expression" dxfId="256" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="230" priority="24">
+    <cfRule type="expression" dxfId="255" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="229" priority="4">
+    <cfRule type="expression" dxfId="254" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="228" priority="3">
+    <cfRule type="expression" dxfId="253" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="227" priority="6">
+    <cfRule type="expression" dxfId="252" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="226" priority="9">
+    <cfRule type="expression" dxfId="251" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="225" priority="11">
+    <cfRule type="expression" dxfId="250" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6766,57 +7040,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="224" priority="36">
+    <cfRule type="expression" dxfId="249" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="223" priority="51">
+    <cfRule type="expression" dxfId="248" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="222" priority="50">
+    <cfRule type="expression" dxfId="247" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="221" priority="9">
+    <cfRule type="expression" dxfId="246" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="220" priority="28">
+    <cfRule type="expression" dxfId="245" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="219" priority="11">
+    <cfRule type="expression" dxfId="244" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="218" priority="24">
+    <cfRule type="expression" dxfId="243" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="217" priority="31">
+    <cfRule type="expression" dxfId="242" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="216" priority="7">
+    <cfRule type="expression" dxfId="241" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="215" priority="35">
+    <cfRule type="expression" dxfId="240" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="214" priority="1">
+    <cfRule type="expression" dxfId="239" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7248,59 +7522,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="213" priority="35">
+    <cfRule type="expression" dxfId="238" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="212" priority="42">
+    <cfRule type="expression" dxfId="237" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="211" priority="54">
+    <cfRule type="expression" dxfId="236" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="210" priority="53">
+    <cfRule type="expression" dxfId="235" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="209" priority="5">
+    <cfRule type="expression" dxfId="234" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="208" priority="30">
+    <cfRule type="expression" dxfId="233" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="207" priority="33">
+    <cfRule type="expression" dxfId="232" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="206" priority="37">
+    <cfRule type="expression" dxfId="231" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="205" priority="41">
+    <cfRule type="expression" dxfId="230" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="204" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="202" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="201" priority="1">
+    <cfRule type="expression" dxfId="226" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7766,57 +8040,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="200" priority="1">
+    <cfRule type="expression" dxfId="225" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="199" priority="18">
+    <cfRule type="expression" dxfId="224" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="198" priority="41">
+    <cfRule type="expression" dxfId="223" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="197" priority="40">
+    <cfRule type="expression" dxfId="222" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="196" priority="13">
+    <cfRule type="expression" dxfId="221" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="195" priority="3">
+    <cfRule type="expression" dxfId="220" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="194" priority="5">
+    <cfRule type="expression" dxfId="219" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="193" priority="19">
+    <cfRule type="expression" dxfId="218" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="192" priority="7">
+    <cfRule type="expression" dxfId="217" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="191" priority="27">
+    <cfRule type="expression" dxfId="216" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="190" priority="8">
+    <cfRule type="expression" dxfId="215" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8276,32 +8550,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="189" priority="21">
+    <cfRule type="expression" dxfId="214" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="188" priority="43">
+    <cfRule type="expression" dxfId="213" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="187" priority="42">
+    <cfRule type="expression" dxfId="212" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="186" priority="1">
+    <cfRule type="expression" dxfId="211" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="185" priority="16">
+    <cfRule type="expression" dxfId="210" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="184" priority="24">
+    <cfRule type="expression" dxfId="209" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8717,32 +8991,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="183" priority="30">
+    <cfRule type="expression" dxfId="208" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="182" priority="29">
+    <cfRule type="expression" dxfId="207" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="181" priority="16">
+    <cfRule type="expression" dxfId="206" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="180" priority="1">
+    <cfRule type="expression" dxfId="205" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="179" priority="4">
+    <cfRule type="expression" dxfId="204" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="178" priority="5">
+    <cfRule type="expression" dxfId="203" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9152,32 +9426,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="177" priority="39">
+    <cfRule type="expression" dxfId="202" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="176" priority="38">
+    <cfRule type="expression" dxfId="201" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="175" priority="20">
+    <cfRule type="expression" dxfId="200" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="174" priority="1">
+    <cfRule type="expression" dxfId="199" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="173" priority="3">
+    <cfRule type="expression" dxfId="198" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="172" priority="2">
+    <cfRule type="expression" dxfId="197" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9597,37 +9871,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="171" priority="18">
+    <cfRule type="expression" dxfId="196" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="170" priority="2">
+    <cfRule type="expression" dxfId="195" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="169" priority="32">
+    <cfRule type="expression" dxfId="194" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="168" priority="31">
+    <cfRule type="expression" dxfId="193" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="167" priority="5">
+    <cfRule type="expression" dxfId="192" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="166" priority="1">
+    <cfRule type="expression" dxfId="191" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="165" priority="3">
+    <cfRule type="expression" dxfId="190" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10043,22 +10317,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="303" priority="14">
+    <cfRule type="expression" dxfId="328" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="302" priority="6">
+    <cfRule type="expression" dxfId="327" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="301" priority="15">
+    <cfRule type="expression" dxfId="326" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="300" priority="1">
+    <cfRule type="expression" dxfId="325" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10456,22 +10730,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="164" priority="32">
+    <cfRule type="expression" dxfId="189" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="163" priority="31">
+    <cfRule type="expression" dxfId="188" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="162" priority="12">
+    <cfRule type="expression" dxfId="187" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="161" priority="1">
+    <cfRule type="expression" dxfId="186" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10837,22 +11111,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="160" priority="17">
+    <cfRule type="expression" dxfId="185" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="159" priority="16">
+    <cfRule type="expression" dxfId="184" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="158" priority="2">
+    <cfRule type="expression" dxfId="183" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="157" priority="1">
+    <cfRule type="expression" dxfId="182" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11287,47 +11561,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="156" priority="32">
+    <cfRule type="expression" dxfId="181" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="155" priority="31">
+    <cfRule type="expression" dxfId="180" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="154" priority="1">
+    <cfRule type="expression" dxfId="179" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="153" priority="3">
+    <cfRule type="expression" dxfId="178" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="152" priority="5">
+    <cfRule type="expression" dxfId="177" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="151" priority="12">
+    <cfRule type="expression" dxfId="176" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="150" priority="18">
+    <cfRule type="expression" dxfId="175" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="149" priority="27">
+    <cfRule type="expression" dxfId="174" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="148" priority="33">
+    <cfRule type="expression" dxfId="173" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11758,47 +12032,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="147" priority="12">
+    <cfRule type="expression" dxfId="172" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="146" priority="29">
+    <cfRule type="expression" dxfId="171" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="145" priority="28">
+    <cfRule type="expression" dxfId="170" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="144" priority="27">
+    <cfRule type="expression" dxfId="169" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="143" priority="1">
+    <cfRule type="expression" dxfId="168" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="142" priority="3">
+    <cfRule type="expression" dxfId="167" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="141" priority="9">
+    <cfRule type="expression" dxfId="166" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="140" priority="24">
+    <cfRule type="expression" dxfId="165" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="139" priority="30">
+    <cfRule type="expression" dxfId="164" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12233,52 +12507,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="138" priority="4">
+    <cfRule type="expression" dxfId="163" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="137" priority="27">
+    <cfRule type="expression" dxfId="162" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="136" priority="26">
+    <cfRule type="expression" dxfId="161" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="135" priority="1">
+    <cfRule type="expression" dxfId="160" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="134" priority="2">
+    <cfRule type="expression" dxfId="159" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="133" priority="28">
+    <cfRule type="expression" dxfId="158" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="132" priority="5">
+    <cfRule type="expression" dxfId="157" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="131" priority="8">
+    <cfRule type="expression" dxfId="156" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="130" priority="18">
+    <cfRule type="expression" dxfId="155" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="129" priority="22">
+    <cfRule type="expression" dxfId="154" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12707,47 +12981,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="128" priority="13">
+    <cfRule type="expression" dxfId="153" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="127" priority="22">
+    <cfRule type="expression" dxfId="152" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="126" priority="21">
+    <cfRule type="expression" dxfId="151" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="125" priority="1">
+    <cfRule type="expression" dxfId="150" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="124" priority="3">
+    <cfRule type="expression" dxfId="149" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="123" priority="5">
+    <cfRule type="expression" dxfId="148" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="122" priority="8">
+    <cfRule type="expression" dxfId="147" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="121" priority="17">
+    <cfRule type="expression" dxfId="146" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="120" priority="23">
+    <cfRule type="expression" dxfId="145" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13170,52 +13444,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="119" priority="5">
+    <cfRule type="expression" dxfId="144" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="118" priority="28">
+    <cfRule type="expression" dxfId="143" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="117" priority="27">
+    <cfRule type="expression" dxfId="142" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="116" priority="1">
+    <cfRule type="expression" dxfId="141" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="115" priority="3">
+    <cfRule type="expression" dxfId="140" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="114" priority="29">
+    <cfRule type="expression" dxfId="139" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="113" priority="22">
+    <cfRule type="expression" dxfId="138" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="112" priority="8">
+    <cfRule type="expression" dxfId="137" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="111" priority="19">
+    <cfRule type="expression" dxfId="136" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="110" priority="23">
+    <cfRule type="expression" dxfId="135" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13644,47 +13918,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="109" priority="11">
+    <cfRule type="expression" dxfId="134" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="108" priority="22">
+    <cfRule type="expression" dxfId="133" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="107" priority="21">
+    <cfRule type="expression" dxfId="132" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="106" priority="1">
+    <cfRule type="expression" dxfId="131" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="105" priority="3">
+    <cfRule type="expression" dxfId="130" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="104" priority="23">
+    <cfRule type="expression" dxfId="129" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="103" priority="5">
+    <cfRule type="expression" dxfId="128" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="102" priority="7">
+    <cfRule type="expression" dxfId="127" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="101" priority="17">
+    <cfRule type="expression" dxfId="126" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13767,9 +14041,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -13781,9 +14052,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -13798,7 +14066,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -13813,7 +14080,6 @@
       <c r="B7" s="69" t="s">
         <v>435</v>
       </c>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -13828,7 +14094,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -13844,7 +14109,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -14023,7 +14288,7 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="22" t="s">
         <v>444</v>
       </c>
       <c r="C28" s="16" t="s">
@@ -14041,23 +14306,39 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="B29" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>454</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>452</v>
+      </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="B30" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>458</v>
+      </c>
       <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="E30" s="17" t="s">
+        <v>456</v>
+      </c>
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="16" t="s">
+        <v>458</v>
+      </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -14105,56 +14386,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="100" priority="5">
+    <cfRule type="expression" dxfId="125" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="99" priority="26">
+    <cfRule type="expression" dxfId="124" priority="26">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="98" priority="25">
+    <cfRule type="expression" dxfId="123" priority="25">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="97" priority="1">
+    <cfRule type="expression" dxfId="122" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="96" priority="3">
+  <conditionalFormatting sqref="C9:C14">
+    <cfRule type="expression" dxfId="121" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="95" priority="27">
+    <cfRule type="expression" dxfId="120" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="94" priority="20">
+    <cfRule type="expression" dxfId="119" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="93" priority="8">
+    <cfRule type="expression" dxfId="118" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="92" priority="18">
+    <cfRule type="expression" dxfId="117" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="91" priority="21">
+    <cfRule type="expression" dxfId="116" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14232,9 +14514,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -14246,9 +14525,6 @@
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -14263,7 +14539,6 @@
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -14278,7 +14553,6 @@
       <c r="B7" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -14293,7 +14567,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -14309,7 +14582,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -14592,33 +14865,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="90" priority="1">
+  <conditionalFormatting sqref="B4:D8 B10:D15 B9 D9">
+    <cfRule type="expression" dxfId="115" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="89" priority="23">
+    <cfRule type="expression" dxfId="114" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="88" priority="22">
+    <cfRule type="expression" dxfId="113" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="87" priority="2">
+    <cfRule type="expression" dxfId="112" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="86" priority="18">
+    <cfRule type="expression" dxfId="111" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E7:F25 C16:D25">
-    <cfRule type="expression" dxfId="85" priority="9">
+    <cfRule type="expression" dxfId="110" priority="10">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15022,30 +15300,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="299" priority="3">
+    <cfRule type="expression" dxfId="324" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="298" priority="14">
+    <cfRule type="expression" dxfId="323" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="297" priority="15">
+    <cfRule type="expression" dxfId="322" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="296" priority="7">
+    <cfRule type="expression" dxfId="321" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="295" priority="9">
+    <cfRule type="expression" dxfId="320" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="294" priority="12">
+    <cfRule type="expression" dxfId="319" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15129,9 +15407,6 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="B4" s="11"/>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -15143,9 +15418,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -15160,7 +15432,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -15173,7 +15444,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -15188,7 +15458,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -15204,7 +15473,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15477,28 +15746,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="84" priority="1">
+  <conditionalFormatting sqref="B10:C13 B4:B9">
+    <cfRule type="expression" dxfId="109" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="83" priority="19">
+    <cfRule type="expression" dxfId="108" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="82" priority="18">
+    <cfRule type="expression" dxfId="107" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="81" priority="17">
+    <cfRule type="expression" dxfId="106" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="80" priority="4">
+    <cfRule type="expression" dxfId="105" priority="6">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="24" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15580,9 +15859,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -15594,9 +15870,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -15611,7 +15884,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -15624,7 +15896,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -15639,7 +15910,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -15655,7 +15925,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15930,28 +16200,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="79" priority="2">
+  <conditionalFormatting sqref="B10:C13 B4:B9">
+    <cfRule type="expression" dxfId="104" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="78" priority="25">
+    <cfRule type="expression" dxfId="103" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="77" priority="24">
+    <cfRule type="expression" dxfId="102" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="76" priority="1">
+    <cfRule type="expression" dxfId="101" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="75" priority="5">
+    <cfRule type="expression" dxfId="100" priority="7">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="23" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16033,9 +16313,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -16044,9 +16321,6 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -16058,7 +16332,6 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -16070,7 +16343,6 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -16084,7 +16356,6 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -16099,7 +16370,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16366,38 +16637,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="74" priority="4">
+  <conditionalFormatting sqref="B4:C8 B10:C13 B9">
+    <cfRule type="expression" dxfId="99" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="73" priority="29">
+    <cfRule type="expression" dxfId="98" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="72" priority="28">
+    <cfRule type="expression" dxfId="97" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="96" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="70" priority="8">
+    <cfRule type="expression" dxfId="95" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="69" priority="6">
+    <cfRule type="expression" dxfId="94" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="68" priority="12">
+    <cfRule type="expression" dxfId="93" priority="13">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16479,9 +16755,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -16490,9 +16763,6 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -16504,7 +16774,6 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -16513,7 +16782,6 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="C7" s="28"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -16524,7 +16792,6 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
-      <c r="C8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -16538,7 +16805,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -16785,33 +17052,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="67" priority="3">
+  <conditionalFormatting sqref="B10:D25 B4:B9 D4:D9">
+    <cfRule type="expression" dxfId="92" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="66" priority="33">
+    <cfRule type="expression" dxfId="91" priority="35">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="65" priority="32">
+    <cfRule type="expression" dxfId="90" priority="34">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="89" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="63" priority="11">
+    <cfRule type="expression" dxfId="88" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="62" priority="8">
+    <cfRule type="expression" dxfId="87" priority="10">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16893,9 +17170,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -16907,9 +17181,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -16924,7 +17195,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -16937,7 +17207,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -16952,7 +17221,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -16968,7 +17236,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -17239,37 +17507,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="61" priority="5">
+    <cfRule type="expression" dxfId="86" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="60" priority="36">
+    <cfRule type="expression" dxfId="85" priority="38">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="59" priority="35">
+    <cfRule type="expression" dxfId="84" priority="37">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="83" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="57" priority="3">
+  <conditionalFormatting sqref="C10:D14 D4:D9">
+    <cfRule type="expression" dxfId="82" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="56" priority="29">
+    <cfRule type="expression" dxfId="81" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="55" priority="28">
+    <cfRule type="expression" dxfId="80" priority="30">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="21" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17351,9 +17629,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
         <v>362</v>
@@ -17366,9 +17641,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -17384,7 +17656,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -17396,7 +17667,6 @@
       <c r="B7" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="28"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -17408,7 +17678,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -17423,7 +17692,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -17703,42 +17972,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="54" priority="4">
+    <cfRule type="expression" dxfId="79" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="53" priority="38">
+    <cfRule type="expression" dxfId="78" priority="40">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="52" priority="37">
+    <cfRule type="expression" dxfId="77" priority="39">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="76" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="50" priority="2">
+  <conditionalFormatting sqref="C10:D14 D4:D9">
+    <cfRule type="expression" dxfId="75" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="49" priority="8">
+    <cfRule type="expression" dxfId="74" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="48" priority="31">
+    <cfRule type="expression" dxfId="73" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="47" priority="30">
+    <cfRule type="expression" dxfId="72" priority="32">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="20" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17820,9 +18099,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -17834,9 +18110,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -17851,7 +18124,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -17864,7 +18136,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -17879,7 +18150,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -17895,7 +18165,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18169,42 +18439,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="46" priority="3">
+    <cfRule type="expression" dxfId="71" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="45" priority="18">
+    <cfRule type="expression" dxfId="70" priority="20">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="44" priority="17">
+    <cfRule type="expression" dxfId="69" priority="19">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="43" priority="16">
+    <cfRule type="expression" dxfId="68" priority="18">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="42" priority="1">
+  <conditionalFormatting sqref="C10:D14 D4:D9">
+    <cfRule type="expression" dxfId="67" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="41" priority="7">
+    <cfRule type="expression" dxfId="66" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B15:D25">
-    <cfRule type="expression" dxfId="40" priority="14">
+    <cfRule type="expression" dxfId="65" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="39" priority="13">
+    <cfRule type="expression" dxfId="64" priority="15">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18286,9 +18566,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -18300,9 +18577,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -18317,7 +18591,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -18330,7 +18603,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -18345,7 +18617,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -18361,7 +18632,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18635,42 +18906,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="38" priority="4">
+    <cfRule type="expression" dxfId="63" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D25">
-    <cfRule type="expression" dxfId="37" priority="5">
+    <cfRule type="expression" dxfId="62" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="36" priority="20">
+    <cfRule type="expression" dxfId="61" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="35" priority="19">
+    <cfRule type="expression" dxfId="60" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="59" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="33" priority="2">
+  <conditionalFormatting sqref="C10:D14 D4:D9">
+    <cfRule type="expression" dxfId="58" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="32" priority="9">
+    <cfRule type="expression" dxfId="57" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="31" priority="15">
+    <cfRule type="expression" dxfId="56" priority="17">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="18" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18752,9 +19033,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -18766,9 +19044,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -18783,7 +19058,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -18796,7 +19070,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -18811,7 +19084,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -18827,7 +19099,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19093,42 +19365,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="30" priority="3">
+    <cfRule type="expression" dxfId="55" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="29" priority="4">
+    <cfRule type="expression" dxfId="54" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="28" priority="19">
+    <cfRule type="expression" dxfId="53" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="27" priority="18">
+    <cfRule type="expression" dxfId="52" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="26" priority="17">
+    <cfRule type="expression" dxfId="51" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="25" priority="1">
+  <conditionalFormatting sqref="C10:D13 D4:D9">
+    <cfRule type="expression" dxfId="50" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="24" priority="8">
+    <cfRule type="expression" dxfId="49" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="23" priority="14">
+    <cfRule type="expression" dxfId="48" priority="16">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="17" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19210,9 +19492,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -19224,9 +19503,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -19241,7 +19517,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -19254,7 +19529,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -19269,7 +19543,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -19285,7 +19558,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19565,42 +19838,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="22" priority="3">
+    <cfRule type="expression" dxfId="47" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="21" priority="4">
+    <cfRule type="expression" dxfId="46" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="20" priority="19">
+    <cfRule type="expression" dxfId="45" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="19" priority="18">
+    <cfRule type="expression" dxfId="44" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="18" priority="17">
+    <cfRule type="expression" dxfId="43" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="17" priority="1">
+  <conditionalFormatting sqref="C10:D13 D4:D9">
+    <cfRule type="expression" dxfId="42" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="41" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="15" priority="14">
+    <cfRule type="expression" dxfId="40" priority="16">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20025,22 +20308,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="293" priority="10">
+    <cfRule type="expression" dxfId="318" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="292" priority="9">
+    <cfRule type="expression" dxfId="317" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="291" priority="1">
+    <cfRule type="expression" dxfId="316" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="290" priority="7">
+    <cfRule type="expression" dxfId="315" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20123,9 +20406,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -20137,9 +20417,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -20154,7 +20431,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -20167,7 +20443,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -20182,7 +20457,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -20198,7 +20472,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -20474,42 +20748,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="39" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="13" priority="4">
+    <cfRule type="expression" dxfId="38" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="12" priority="19">
+    <cfRule type="expression" dxfId="37" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="11" priority="18">
+    <cfRule type="expression" dxfId="36" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="35" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="9" priority="1">
+  <conditionalFormatting sqref="C10:D13 D4:D9">
+    <cfRule type="expression" dxfId="34" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="33" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="32" priority="16">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="15" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20591,9 +20875,6 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
-      <c r="C4" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="H4" s="7" t="s">
         <v>362</v>
       </c>
@@ -20605,9 +20886,6 @@
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>366</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -20622,7 +20900,6 @@
       <c r="B6" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
         <v>108</v>
       </c>
@@ -20635,7 +20912,6 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -20650,7 +20926,6 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -20666,7 +20941,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -20938,37 +21213,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="31" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="30" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="4" priority="19">
+    <cfRule type="expression" dxfId="29" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="3" priority="18">
+    <cfRule type="expression" dxfId="28" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="2" priority="17">
+    <cfRule type="expression" dxfId="27" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="C10:D13 D4:D9">
+    <cfRule type="expression" dxfId="26" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="25" priority="10">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:C8">
+    <cfRule type="expression" dxfId="14" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21413,42 +21698,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="289" priority="15">
+    <cfRule type="expression" dxfId="314" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="288" priority="13">
+    <cfRule type="expression" dxfId="313" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="287" priority="30">
+    <cfRule type="expression" dxfId="312" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="286" priority="29">
+    <cfRule type="expression" dxfId="311" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="285" priority="7">
+    <cfRule type="expression" dxfId="310" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="284" priority="24">
+    <cfRule type="expression" dxfId="309" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="283" priority="20">
+    <cfRule type="expression" dxfId="308" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="282" priority="25">
+    <cfRule type="expression" dxfId="307" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21849,32 +22134,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="281" priority="8">
+    <cfRule type="expression" dxfId="306" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="280" priority="13">
+    <cfRule type="expression" dxfId="305" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="279" priority="12">
+    <cfRule type="expression" dxfId="304" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="278" priority="1">
+    <cfRule type="expression" dxfId="303" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="277" priority="4">
+    <cfRule type="expression" dxfId="302" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="276" priority="7">
+    <cfRule type="expression" dxfId="301" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22258,52 +22543,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="275" priority="22">
+    <cfRule type="expression" dxfId="300" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="274" priority="23">
+    <cfRule type="expression" dxfId="299" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="273" priority="45">
+    <cfRule type="expression" dxfId="298" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="272" priority="44">
+    <cfRule type="expression" dxfId="297" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="271" priority="1">
+    <cfRule type="expression" dxfId="296" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="270" priority="35">
+    <cfRule type="expression" dxfId="295" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="269" priority="36">
+    <cfRule type="expression" dxfId="294" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="268" priority="16">
+    <cfRule type="expression" dxfId="293" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="267" priority="34">
+    <cfRule type="expression" dxfId="292" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="266" priority="5">
+    <cfRule type="expression" dxfId="291" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22716,47 +23001,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="265" priority="16">
+    <cfRule type="expression" dxfId="290" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="264" priority="19">
+    <cfRule type="expression" dxfId="289" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="263" priority="18">
+    <cfRule type="expression" dxfId="288" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="262" priority="1">
+    <cfRule type="expression" dxfId="287" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="261" priority="15">
+    <cfRule type="expression" dxfId="286" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="260" priority="12">
+    <cfRule type="expression" dxfId="285" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="259" priority="11">
+    <cfRule type="expression" dxfId="284" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="258" priority="14">
+    <cfRule type="expression" dxfId="283" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="257" priority="5">
+    <cfRule type="expression" dxfId="282" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23179,32 +23464,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="256" priority="2">
+    <cfRule type="expression" dxfId="281" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="255" priority="4">
+    <cfRule type="expression" dxfId="280" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="254" priority="16">
+    <cfRule type="expression" dxfId="279" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="253" priority="15">
+    <cfRule type="expression" dxfId="278" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="252" priority="1">
+    <cfRule type="expression" dxfId="277" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="276" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E938C334-72C4-4537-B933-4D7B6C757CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0299195B-3360-4FCA-8D4E-8FDE8951EBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="461">
   <si>
     <t>Week</t>
   </si>
@@ -1475,6 +1475,9 @@
   </si>
   <si>
     <t>Video donderdag moet af zijn!</t>
+  </si>
+  <si>
+    <t>Materiaal meedoen boekmaking</t>
   </si>
 </sst>
 </file>
@@ -1802,254 +1805,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="329">
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
+  <dxfs count="314">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5564,47 +5387,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="275" priority="17">
+    <cfRule type="expression" dxfId="260" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="274" priority="25">
+    <cfRule type="expression" dxfId="259" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="273" priority="24">
+    <cfRule type="expression" dxfId="258" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="272" priority="5">
+    <cfRule type="expression" dxfId="257" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="271" priority="9">
+    <cfRule type="expression" dxfId="256" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="270" priority="8">
+    <cfRule type="expression" dxfId="255" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="269" priority="11">
+    <cfRule type="expression" dxfId="254" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="268" priority="15">
+    <cfRule type="expression" dxfId="253" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="267" priority="2">
+    <cfRule type="expression" dxfId="252" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6063,42 +5886,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="266" priority="15">
+    <cfRule type="expression" dxfId="251" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="265" priority="10">
+    <cfRule type="expression" dxfId="250" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="264" priority="24">
+    <cfRule type="expression" dxfId="249" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="263" priority="23">
+    <cfRule type="expression" dxfId="248" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="262" priority="1">
+    <cfRule type="expression" dxfId="247" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="261" priority="7">
+    <cfRule type="expression" dxfId="246" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="260" priority="3">
+    <cfRule type="expression" dxfId="245" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="259" priority="14">
+    <cfRule type="expression" dxfId="244" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6537,47 +6360,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="258" priority="10">
+    <cfRule type="expression" dxfId="243" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="257" priority="1">
+    <cfRule type="expression" dxfId="242" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="256" priority="25">
+    <cfRule type="expression" dxfId="241" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="255" priority="24">
+    <cfRule type="expression" dxfId="240" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="254" priority="4">
+    <cfRule type="expression" dxfId="239" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="253" priority="3">
+    <cfRule type="expression" dxfId="238" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="252" priority="6">
+    <cfRule type="expression" dxfId="237" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="251" priority="9">
+    <cfRule type="expression" dxfId="236" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="250" priority="11">
+    <cfRule type="expression" dxfId="235" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7040,57 +6863,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="249" priority="36">
+    <cfRule type="expression" dxfId="234" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="248" priority="51">
+    <cfRule type="expression" dxfId="233" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="247" priority="50">
+    <cfRule type="expression" dxfId="232" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="246" priority="9">
+    <cfRule type="expression" dxfId="231" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="245" priority="28">
+    <cfRule type="expression" dxfId="230" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="244" priority="11">
+    <cfRule type="expression" dxfId="229" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="243" priority="24">
+    <cfRule type="expression" dxfId="228" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="242" priority="31">
+    <cfRule type="expression" dxfId="227" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="241" priority="7">
+    <cfRule type="expression" dxfId="226" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="240" priority="35">
+    <cfRule type="expression" dxfId="225" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="239" priority="1">
+    <cfRule type="expression" dxfId="224" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7522,59 +7345,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="238" priority="35">
+    <cfRule type="expression" dxfId="223" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="237" priority="42">
+    <cfRule type="expression" dxfId="222" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="236" priority="54">
+    <cfRule type="expression" dxfId="221" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="235" priority="53">
+    <cfRule type="expression" dxfId="220" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="234" priority="5">
+    <cfRule type="expression" dxfId="219" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="233" priority="30">
+    <cfRule type="expression" dxfId="218" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="232" priority="33">
+    <cfRule type="expression" dxfId="217" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="231" priority="37">
+    <cfRule type="expression" dxfId="216" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="230" priority="41">
+    <cfRule type="expression" dxfId="215" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="229" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="227" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="226" priority="1">
+    <cfRule type="expression" dxfId="211" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8040,57 +7863,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="225" priority="1">
+    <cfRule type="expression" dxfId="210" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="224" priority="18">
+    <cfRule type="expression" dxfId="209" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="223" priority="41">
+    <cfRule type="expression" dxfId="208" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="222" priority="40">
+    <cfRule type="expression" dxfId="207" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="221" priority="13">
+    <cfRule type="expression" dxfId="206" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="220" priority="3">
+    <cfRule type="expression" dxfId="205" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="219" priority="5">
+    <cfRule type="expression" dxfId="204" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="218" priority="19">
+    <cfRule type="expression" dxfId="203" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="217" priority="7">
+    <cfRule type="expression" dxfId="202" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="216" priority="27">
+    <cfRule type="expression" dxfId="201" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="215" priority="8">
+    <cfRule type="expression" dxfId="200" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8550,32 +8373,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="214" priority="21">
+    <cfRule type="expression" dxfId="199" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="213" priority="43">
+    <cfRule type="expression" dxfId="198" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="212" priority="42">
+    <cfRule type="expression" dxfId="197" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="211" priority="1">
+    <cfRule type="expression" dxfId="196" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="210" priority="16">
+    <cfRule type="expression" dxfId="195" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="209" priority="24">
+    <cfRule type="expression" dxfId="194" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8991,32 +8814,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="208" priority="30">
+    <cfRule type="expression" dxfId="193" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="207" priority="29">
+    <cfRule type="expression" dxfId="192" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="206" priority="16">
+    <cfRule type="expression" dxfId="191" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="205" priority="1">
+    <cfRule type="expression" dxfId="190" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="204" priority="4">
+    <cfRule type="expression" dxfId="189" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="203" priority="5">
+    <cfRule type="expression" dxfId="188" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9426,32 +9249,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="202" priority="39">
+    <cfRule type="expression" dxfId="187" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="201" priority="38">
+    <cfRule type="expression" dxfId="186" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="200" priority="20">
+    <cfRule type="expression" dxfId="185" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="199" priority="1">
+    <cfRule type="expression" dxfId="184" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="198" priority="3">
+    <cfRule type="expression" dxfId="183" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="197" priority="2">
+    <cfRule type="expression" dxfId="182" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9871,37 +9694,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="196" priority="18">
+    <cfRule type="expression" dxfId="181" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="195" priority="2">
+    <cfRule type="expression" dxfId="180" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="194" priority="32">
+    <cfRule type="expression" dxfId="179" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="193" priority="31">
+    <cfRule type="expression" dxfId="178" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="192" priority="5">
+    <cfRule type="expression" dxfId="177" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="191" priority="1">
+    <cfRule type="expression" dxfId="176" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="190" priority="3">
+    <cfRule type="expression" dxfId="175" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10317,22 +10140,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="328" priority="14">
+    <cfRule type="expression" dxfId="313" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="327" priority="6">
+    <cfRule type="expression" dxfId="312" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="326" priority="15">
+    <cfRule type="expression" dxfId="311" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="325" priority="1">
+    <cfRule type="expression" dxfId="310" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10730,22 +10553,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="189" priority="32">
+    <cfRule type="expression" dxfId="174" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="188" priority="31">
+    <cfRule type="expression" dxfId="173" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="187" priority="12">
+    <cfRule type="expression" dxfId="172" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="186" priority="1">
+    <cfRule type="expression" dxfId="171" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11111,22 +10934,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="185" priority="17">
+    <cfRule type="expression" dxfId="170" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="184" priority="16">
+    <cfRule type="expression" dxfId="169" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="183" priority="2">
+    <cfRule type="expression" dxfId="168" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="182" priority="1">
+    <cfRule type="expression" dxfId="167" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11561,47 +11384,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="181" priority="32">
+    <cfRule type="expression" dxfId="166" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="180" priority="31">
+    <cfRule type="expression" dxfId="165" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="179" priority="1">
+    <cfRule type="expression" dxfId="164" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="178" priority="3">
+    <cfRule type="expression" dxfId="163" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="177" priority="5">
+    <cfRule type="expression" dxfId="162" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="176" priority="12">
+    <cfRule type="expression" dxfId="161" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="175" priority="18">
+    <cfRule type="expression" dxfId="160" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="174" priority="27">
+    <cfRule type="expression" dxfId="159" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="173" priority="33">
+    <cfRule type="expression" dxfId="158" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12032,47 +11855,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="172" priority="12">
+    <cfRule type="expression" dxfId="157" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="171" priority="29">
+    <cfRule type="expression" dxfId="156" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="170" priority="28">
+    <cfRule type="expression" dxfId="155" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="169" priority="27">
+    <cfRule type="expression" dxfId="154" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="168" priority="1">
+    <cfRule type="expression" dxfId="153" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="167" priority="3">
+    <cfRule type="expression" dxfId="152" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="166" priority="9">
+    <cfRule type="expression" dxfId="151" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="165" priority="24">
+    <cfRule type="expression" dxfId="150" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="164" priority="30">
+    <cfRule type="expression" dxfId="149" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12507,52 +12330,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="163" priority="4">
+    <cfRule type="expression" dxfId="148" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="162" priority="27">
+    <cfRule type="expression" dxfId="147" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="161" priority="26">
+    <cfRule type="expression" dxfId="146" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="160" priority="1">
+    <cfRule type="expression" dxfId="145" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="159" priority="2">
+    <cfRule type="expression" dxfId="144" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="158" priority="28">
+    <cfRule type="expression" dxfId="143" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="157" priority="5">
+    <cfRule type="expression" dxfId="142" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="156" priority="8">
+    <cfRule type="expression" dxfId="141" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="155" priority="18">
+    <cfRule type="expression" dxfId="140" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="154" priority="22">
+    <cfRule type="expression" dxfId="139" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12981,47 +12804,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="153" priority="13">
+    <cfRule type="expression" dxfId="138" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="152" priority="22">
+    <cfRule type="expression" dxfId="137" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="151" priority="21">
+    <cfRule type="expression" dxfId="136" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="150" priority="1">
+    <cfRule type="expression" dxfId="135" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="149" priority="3">
+    <cfRule type="expression" dxfId="134" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="148" priority="5">
+    <cfRule type="expression" dxfId="133" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="147" priority="8">
+    <cfRule type="expression" dxfId="132" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="146" priority="17">
+    <cfRule type="expression" dxfId="131" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="145" priority="23">
+    <cfRule type="expression" dxfId="130" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13444,52 +13267,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="144" priority="5">
+    <cfRule type="expression" dxfId="129" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="143" priority="28">
+    <cfRule type="expression" dxfId="128" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="142" priority="27">
+    <cfRule type="expression" dxfId="127" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="141" priority="1">
+    <cfRule type="expression" dxfId="126" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="140" priority="3">
+    <cfRule type="expression" dxfId="125" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="139" priority="29">
+    <cfRule type="expression" dxfId="124" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="138" priority="22">
+    <cfRule type="expression" dxfId="123" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="137" priority="8">
+    <cfRule type="expression" dxfId="122" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="136" priority="19">
+    <cfRule type="expression" dxfId="121" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="135" priority="23">
+    <cfRule type="expression" dxfId="120" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13918,47 +13741,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="134" priority="11">
+    <cfRule type="expression" dxfId="119" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="133" priority="22">
+    <cfRule type="expression" dxfId="118" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="132" priority="21">
+    <cfRule type="expression" dxfId="117" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="131" priority="1">
+    <cfRule type="expression" dxfId="116" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="130" priority="3">
+    <cfRule type="expression" dxfId="115" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="129" priority="23">
+    <cfRule type="expression" dxfId="114" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="128" priority="5">
+    <cfRule type="expression" dxfId="113" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="127" priority="7">
+    <cfRule type="expression" dxfId="112" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="126" priority="17">
+    <cfRule type="expression" dxfId="111" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14306,10 +14129,10 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="22" t="s">
         <v>455</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="47" t="s">
         <v>454</v>
       </c>
       <c r="D29" s="17" t="s">
@@ -14336,10 +14159,12 @@
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="22" t="s">
         <v>458</v>
       </c>
-      <c r="C31" s="17"/>
+      <c r="C31" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -14386,53 +14211,58 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="125" priority="5">
+    <cfRule type="expression" dxfId="110" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="124" priority="26">
+    <cfRule type="expression" dxfId="109" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="123" priority="25">
+    <cfRule type="expression" dxfId="108" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="122" priority="1">
+  <conditionalFormatting sqref="B28:F30 B32:F36 B31 D31:F31">
+    <cfRule type="expression" dxfId="107" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="121" priority="3">
+    <cfRule type="expression" dxfId="106" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="120" priority="27">
+    <cfRule type="expression" dxfId="105" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="119" priority="20">
+    <cfRule type="expression" dxfId="104" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="118" priority="8">
+    <cfRule type="expression" dxfId="103" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="117" priority="18">
+    <cfRule type="expression" dxfId="102" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="116" priority="21">
+    <cfRule type="expression" dxfId="101" priority="22">
       <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14819,7 +14649,9 @@
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="C31" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -14865,38 +14697,33 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D8 B10:D15 B9 D9">
-    <cfRule type="expression" dxfId="115" priority="2">
+  <conditionalFormatting sqref="B4:D15">
+    <cfRule type="expression" dxfId="100" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="114" priority="24">
+    <cfRule type="expression" dxfId="99" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="113" priority="23">
+    <cfRule type="expression" dxfId="98" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="112" priority="3">
+    <cfRule type="expression" dxfId="97" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="111" priority="19">
+    <cfRule type="expression" dxfId="96" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E7:F25 C16:D25">
-    <cfRule type="expression" dxfId="110" priority="10">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="95" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15300,30 +15127,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="324" priority="3">
+    <cfRule type="expression" dxfId="309" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="323" priority="14">
+    <cfRule type="expression" dxfId="308" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="322" priority="15">
+    <cfRule type="expression" dxfId="307" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="321" priority="7">
+    <cfRule type="expression" dxfId="306" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="320" priority="9">
+    <cfRule type="expression" dxfId="305" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="319" priority="12">
+    <cfRule type="expression" dxfId="304" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15746,38 +15573,28 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B10:C13 B4:B9">
-    <cfRule type="expression" dxfId="109" priority="3">
+  <conditionalFormatting sqref="B4:C13">
+    <cfRule type="expression" dxfId="94" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="108" priority="21">
+    <cfRule type="expression" dxfId="93" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="107" priority="20">
+    <cfRule type="expression" dxfId="92" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="106" priority="19">
+    <cfRule type="expression" dxfId="91" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="105" priority="6">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="24" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="90" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16200,38 +16017,28 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B10:C13 B4:B9">
-    <cfRule type="expression" dxfId="104" priority="4">
+  <conditionalFormatting sqref="B4:C13">
+    <cfRule type="expression" dxfId="89" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="103" priority="27">
+    <cfRule type="expression" dxfId="88" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="102" priority="26">
+    <cfRule type="expression" dxfId="87" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="101" priority="3">
+    <cfRule type="expression" dxfId="86" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="100" priority="7">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="23" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="85" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16581,7 +16388,9 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="C30" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D30" s="17" t="s">
         <v>394</v>
       </c>
@@ -16637,44 +16446,44 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:C8 B10:C13 B9">
-    <cfRule type="expression" dxfId="99" priority="5">
+  <conditionalFormatting sqref="B4:C13">
+    <cfRule type="expression" dxfId="84" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="98" priority="30">
+    <cfRule type="expression" dxfId="83" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="97" priority="29">
+    <cfRule type="expression" dxfId="82" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="96" priority="2">
+  <conditionalFormatting sqref="B28:F29 B31:F36 B30 D30:F30">
+    <cfRule type="expression" dxfId="81" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="95" priority="9">
+    <cfRule type="expression" dxfId="80" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="94" priority="7">
+    <cfRule type="expression" dxfId="79" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="93" priority="13">
+    <cfRule type="expression" dxfId="78" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="10" priority="1">
-      <formula>$I$8 = TRUE</formula>
+  <conditionalFormatting sqref="C30">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16988,7 +16797,9 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="C29" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D29" s="17" t="s">
         <v>450</v>
       </c>
@@ -17052,44 +16863,39 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B10:D25 B4:B9 D4:D9">
-    <cfRule type="expression" dxfId="92" priority="5">
+  <conditionalFormatting sqref="B4:D25">
+    <cfRule type="expression" dxfId="77" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="91" priority="35">
+    <cfRule type="expression" dxfId="76" priority="36">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="90" priority="34">
+    <cfRule type="expression" dxfId="75" priority="35">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="89" priority="3">
+  <conditionalFormatting sqref="B28:F28 B30:F36 B29 D29:F29">
+    <cfRule type="expression" dxfId="74" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="88" priority="13">
+    <cfRule type="expression" dxfId="73" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="87" priority="10">
+    <cfRule type="expression" dxfId="72" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="22" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="9" priority="1">
-      <formula>$I$8 = TRUE</formula>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>NOT(ISBLANK(C29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17438,7 +17244,9 @@
       <c r="B29" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="C29" s="17"/>
+      <c r="C29" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D29" s="16" t="s">
         <v>388</v>
       </c>
@@ -17507,48 +17315,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="86" priority="7">
+    <cfRule type="expression" dxfId="71" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="85" priority="38">
+    <cfRule type="expression" dxfId="70" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="84" priority="37">
+    <cfRule type="expression" dxfId="69" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="83" priority="3">
+  <conditionalFormatting sqref="B28:F28 B30:F36 B29 D29:F29">
+    <cfRule type="expression" dxfId="68" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D14 D4:D9">
-    <cfRule type="expression" dxfId="82" priority="5">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="67" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="81" priority="31">
+    <cfRule type="expression" dxfId="66" priority="32">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="80" priority="30">
+    <cfRule type="expression" dxfId="65" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="21" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>$I$8 = TRUE</formula>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>NOT(ISBLANK(C29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17905,7 +17708,9 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="C29" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D29" s="16" t="s">
         <v>388</v>
       </c>
@@ -17972,53 +17777,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="79" priority="6">
+    <cfRule type="expression" dxfId="64" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="78" priority="40">
+    <cfRule type="expression" dxfId="63" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="77" priority="39">
+    <cfRule type="expression" dxfId="62" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="76" priority="3">
+  <conditionalFormatting sqref="B28:F28 B30:F36 B29 D29:F29">
+    <cfRule type="expression" dxfId="61" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D14 D4:D9">
-    <cfRule type="expression" dxfId="75" priority="4">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="60" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="74" priority="10">
+    <cfRule type="expression" dxfId="59" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="73" priority="33">
+    <cfRule type="expression" dxfId="58" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="72" priority="32">
+    <cfRule type="expression" dxfId="57" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="20" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="7" priority="1">
-      <formula>$I$8 = TRUE</formula>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>NOT(ISBLANK(C29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18360,7 +18160,9 @@
       <c r="B28" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
@@ -18439,53 +18241,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="71" priority="5">
+    <cfRule type="expression" dxfId="56" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="70" priority="20">
+    <cfRule type="expression" dxfId="55" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="69" priority="19">
+    <cfRule type="expression" dxfId="54" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="68" priority="18">
+  <conditionalFormatting sqref="B29:F36 B28 D28:F28">
+    <cfRule type="expression" dxfId="53" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D14 D4:D9">
-    <cfRule type="expression" dxfId="67" priority="3">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="52" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="66" priority="9">
+    <cfRule type="expression" dxfId="51" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B15:D25">
-    <cfRule type="expression" dxfId="65" priority="16">
+    <cfRule type="expression" dxfId="50" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="64" priority="15">
+    <cfRule type="expression" dxfId="49" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="19" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>$I$8 = TRUE</formula>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18827,7 +18624,9 @@
       <c r="B28" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16" t="s">
         <v>42</v>
@@ -18906,53 +18705,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="63" priority="6">
+    <cfRule type="expression" dxfId="48" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D25">
-    <cfRule type="expression" dxfId="62" priority="7">
+    <cfRule type="expression" dxfId="47" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="61" priority="22">
+    <cfRule type="expression" dxfId="46" priority="23">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="60" priority="21">
+    <cfRule type="expression" dxfId="45" priority="22">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="59" priority="3">
+  <conditionalFormatting sqref="B29:F36 B28 D28:F28">
+    <cfRule type="expression" dxfId="44" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D14 D4:D9">
-    <cfRule type="expression" dxfId="58" priority="4">
+  <conditionalFormatting sqref="C4:D14">
+    <cfRule type="expression" dxfId="43" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="57" priority="11">
+    <cfRule type="expression" dxfId="42" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="56" priority="17">
+    <cfRule type="expression" dxfId="41" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="18" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>$I$8 = TRUE</formula>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19294,7 +19088,9 @@
       <c r="B28" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="16"/>
+      <c r="C28" s="16" t="s">
+        <v>460</v>
+      </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
@@ -19365,53 +19161,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="55" priority="5">
+    <cfRule type="expression" dxfId="40" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="39" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="53" priority="21">
+    <cfRule type="expression" dxfId="38" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="52" priority="20">
+    <cfRule type="expression" dxfId="37" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="51" priority="19">
+  <conditionalFormatting sqref="B29:F36 B28 D28:F28">
+    <cfRule type="expression" dxfId="36" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D13 D4:D9">
-    <cfRule type="expression" dxfId="50" priority="3">
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="49" priority="10">
+    <cfRule type="expression" dxfId="34" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="48" priority="16">
+    <cfRule type="expression" dxfId="33" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="17" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$I$8 = TRUE</formula>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19838,52 +19629,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="47" priority="5">
+    <cfRule type="expression" dxfId="32" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="46" priority="6">
+    <cfRule type="expression" dxfId="31" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="45" priority="21">
+    <cfRule type="expression" dxfId="30" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="44" priority="20">
+    <cfRule type="expression" dxfId="29" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="43" priority="19">
+    <cfRule type="expression" dxfId="28" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D13 D4:D9">
-    <cfRule type="expression" dxfId="42" priority="3">
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="27" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="41" priority="10">
+    <cfRule type="expression" dxfId="26" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="40" priority="16">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="16" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="25" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20308,22 +20089,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="318" priority="10">
+    <cfRule type="expression" dxfId="303" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="317" priority="9">
+    <cfRule type="expression" dxfId="302" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="316" priority="1">
+    <cfRule type="expression" dxfId="301" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="315" priority="7">
+    <cfRule type="expression" dxfId="300" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20748,52 +20529,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="39" priority="5">
+    <cfRule type="expression" dxfId="24" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="38" priority="6">
+    <cfRule type="expression" dxfId="23" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="37" priority="21">
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="36" priority="20">
+    <cfRule type="expression" dxfId="21" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="35" priority="19">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D13 D4:D9">
-    <cfRule type="expression" dxfId="34" priority="3">
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="33" priority="10">
+    <cfRule type="expression" dxfId="18" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="32" priority="16">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="15" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="17" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21213,47 +20984,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="31" priority="5">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="30" priority="6">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="29" priority="21">
+    <cfRule type="expression" dxfId="14" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="28" priority="20">
+    <cfRule type="expression" dxfId="13" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="27" priority="19">
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D13 D4:D9">
-    <cfRule type="expression" dxfId="26" priority="3">
+  <conditionalFormatting sqref="C4:D13">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="25" priority="10">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C8">
-    <cfRule type="expression" dxfId="14" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21698,42 +21459,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="314" priority="15">
+    <cfRule type="expression" dxfId="299" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="313" priority="13">
+    <cfRule type="expression" dxfId="298" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="312" priority="30">
+    <cfRule type="expression" dxfId="297" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="311" priority="29">
+    <cfRule type="expression" dxfId="296" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="310" priority="7">
+    <cfRule type="expression" dxfId="295" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="309" priority="24">
+    <cfRule type="expression" dxfId="294" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="308" priority="20">
+    <cfRule type="expression" dxfId="293" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="307" priority="25">
+    <cfRule type="expression" dxfId="292" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22134,32 +21895,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="306" priority="8">
+    <cfRule type="expression" dxfId="291" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="305" priority="13">
+    <cfRule type="expression" dxfId="290" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="304" priority="12">
+    <cfRule type="expression" dxfId="289" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="303" priority="1">
+    <cfRule type="expression" dxfId="288" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="302" priority="4">
+    <cfRule type="expression" dxfId="287" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="301" priority="7">
+    <cfRule type="expression" dxfId="286" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22543,52 +22304,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="300" priority="22">
+    <cfRule type="expression" dxfId="285" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="299" priority="23">
+    <cfRule type="expression" dxfId="284" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="298" priority="45">
+    <cfRule type="expression" dxfId="283" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="297" priority="44">
+    <cfRule type="expression" dxfId="282" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="296" priority="1">
+    <cfRule type="expression" dxfId="281" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="295" priority="35">
+    <cfRule type="expression" dxfId="280" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="294" priority="36">
+    <cfRule type="expression" dxfId="279" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="293" priority="16">
+    <cfRule type="expression" dxfId="278" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="292" priority="34">
+    <cfRule type="expression" dxfId="277" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="291" priority="5">
+    <cfRule type="expression" dxfId="276" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23001,47 +22762,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="290" priority="16">
+    <cfRule type="expression" dxfId="275" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="289" priority="19">
+    <cfRule type="expression" dxfId="274" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="288" priority="18">
+    <cfRule type="expression" dxfId="273" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="287" priority="1">
+    <cfRule type="expression" dxfId="272" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="286" priority="15">
+    <cfRule type="expression" dxfId="271" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="285" priority="12">
+    <cfRule type="expression" dxfId="270" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="284" priority="11">
+    <cfRule type="expression" dxfId="269" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="283" priority="14">
+    <cfRule type="expression" dxfId="268" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="282" priority="5">
+    <cfRule type="expression" dxfId="267" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23464,32 +23225,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="281" priority="2">
+    <cfRule type="expression" dxfId="266" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="280" priority="4">
+    <cfRule type="expression" dxfId="265" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="279" priority="16">
+    <cfRule type="expression" dxfId="264" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="278" priority="15">
+    <cfRule type="expression" dxfId="263" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="277" priority="1">
+    <cfRule type="expression" dxfId="262" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="276" priority="7">
+    <cfRule type="expression" dxfId="261" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0299195B-3360-4FCA-8D4E-8FDE8951EBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C07FF84-912D-4473-8B3C-DCE7B4FAFA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="459">
   <si>
     <t>Week</t>
   </si>
@@ -1366,9 +1366,6 @@
     <t>PITCHEN IN GROEP + first concepts</t>
   </si>
   <si>
-    <t>Storyboard / animatics feedback</t>
-  </si>
-  <si>
     <t>OVERLAP WEEK! (mogelijkheid tot afwerken en laatste feedback)</t>
   </si>
   <si>
@@ -1466,9 +1463,6 @@
   </si>
   <si>
     <t>Crossmedia's indienen</t>
-  </si>
-  <si>
-    <t>Werken studio digitaal!</t>
   </si>
   <si>
     <t>Fimen video donderdag</t>
@@ -1805,77 +1799,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="314">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="304">
     <dxf>
       <font>
         <color theme="1"/>
@@ -5387,47 +5311,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="260" priority="17">
+    <cfRule type="expression" dxfId="250" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="259" priority="25">
+    <cfRule type="expression" dxfId="249" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="258" priority="24">
+    <cfRule type="expression" dxfId="248" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="257" priority="5">
+    <cfRule type="expression" dxfId="247" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="256" priority="9">
+    <cfRule type="expression" dxfId="246" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="255" priority="8">
+    <cfRule type="expression" dxfId="245" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="254" priority="11">
+    <cfRule type="expression" dxfId="244" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="253" priority="15">
+    <cfRule type="expression" dxfId="243" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="252" priority="2">
+    <cfRule type="expression" dxfId="242" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5886,42 +5810,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="251" priority="15">
+    <cfRule type="expression" dxfId="241" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="250" priority="10">
+    <cfRule type="expression" dxfId="240" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="249" priority="24">
+    <cfRule type="expression" dxfId="239" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="248" priority="23">
+    <cfRule type="expression" dxfId="238" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="247" priority="1">
+    <cfRule type="expression" dxfId="237" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="246" priority="7">
+    <cfRule type="expression" dxfId="236" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="245" priority="3">
+    <cfRule type="expression" dxfId="235" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="244" priority="14">
+    <cfRule type="expression" dxfId="234" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6360,47 +6284,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="243" priority="10">
+    <cfRule type="expression" dxfId="233" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="242" priority="1">
+    <cfRule type="expression" dxfId="232" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="241" priority="25">
+    <cfRule type="expression" dxfId="231" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="240" priority="24">
+    <cfRule type="expression" dxfId="230" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="239" priority="4">
+    <cfRule type="expression" dxfId="229" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="238" priority="3">
+    <cfRule type="expression" dxfId="228" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="237" priority="6">
+    <cfRule type="expression" dxfId="227" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="236" priority="9">
+    <cfRule type="expression" dxfId="226" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="235" priority="11">
+    <cfRule type="expression" dxfId="225" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6863,57 +6787,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="234" priority="36">
+    <cfRule type="expression" dxfId="224" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="233" priority="51">
+    <cfRule type="expression" dxfId="223" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="232" priority="50">
+    <cfRule type="expression" dxfId="222" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="231" priority="9">
+    <cfRule type="expression" dxfId="221" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="230" priority="28">
+    <cfRule type="expression" dxfId="220" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="229" priority="11">
+    <cfRule type="expression" dxfId="219" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="228" priority="24">
+    <cfRule type="expression" dxfId="218" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="227" priority="31">
+    <cfRule type="expression" dxfId="217" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="226" priority="7">
+    <cfRule type="expression" dxfId="216" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="225" priority="35">
+    <cfRule type="expression" dxfId="215" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="224" priority="1">
+    <cfRule type="expression" dxfId="214" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7345,59 +7269,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="223" priority="35">
+    <cfRule type="expression" dxfId="213" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="222" priority="42">
+    <cfRule type="expression" dxfId="212" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="221" priority="54">
+    <cfRule type="expression" dxfId="211" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="220" priority="53">
+    <cfRule type="expression" dxfId="210" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="219" priority="5">
+    <cfRule type="expression" dxfId="209" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="218" priority="30">
+    <cfRule type="expression" dxfId="208" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="217" priority="33">
+    <cfRule type="expression" dxfId="207" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="216" priority="37">
+    <cfRule type="expression" dxfId="206" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="215" priority="41">
+    <cfRule type="expression" dxfId="205" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="214" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="212" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="211" priority="1">
+    <cfRule type="expression" dxfId="201" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7863,57 +7787,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="210" priority="1">
+    <cfRule type="expression" dxfId="200" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="209" priority="18">
+    <cfRule type="expression" dxfId="199" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="208" priority="41">
+    <cfRule type="expression" dxfId="198" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="207" priority="40">
+    <cfRule type="expression" dxfId="197" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="206" priority="13">
+    <cfRule type="expression" dxfId="196" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="205" priority="3">
+    <cfRule type="expression" dxfId="195" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="204" priority="5">
+    <cfRule type="expression" dxfId="194" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="203" priority="19">
+    <cfRule type="expression" dxfId="193" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="202" priority="7">
+    <cfRule type="expression" dxfId="192" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="201" priority="27">
+    <cfRule type="expression" dxfId="191" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="200" priority="8">
+    <cfRule type="expression" dxfId="190" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8373,32 +8297,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="199" priority="21">
+    <cfRule type="expression" dxfId="189" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="198" priority="43">
+    <cfRule type="expression" dxfId="188" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="197" priority="42">
+    <cfRule type="expression" dxfId="187" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="196" priority="1">
+    <cfRule type="expression" dxfId="186" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="195" priority="16">
+    <cfRule type="expression" dxfId="185" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="194" priority="24">
+    <cfRule type="expression" dxfId="184" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8814,32 +8738,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="193" priority="30">
+    <cfRule type="expression" dxfId="183" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="192" priority="29">
+    <cfRule type="expression" dxfId="182" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="191" priority="16">
+    <cfRule type="expression" dxfId="181" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="190" priority="1">
+    <cfRule type="expression" dxfId="180" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="189" priority="4">
+    <cfRule type="expression" dxfId="179" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="188" priority="5">
+    <cfRule type="expression" dxfId="178" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9249,32 +9173,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="187" priority="39">
+    <cfRule type="expression" dxfId="177" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="186" priority="38">
+    <cfRule type="expression" dxfId="176" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="185" priority="20">
+    <cfRule type="expression" dxfId="175" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="184" priority="1">
+    <cfRule type="expression" dxfId="174" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="183" priority="3">
+    <cfRule type="expression" dxfId="173" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="182" priority="2">
+    <cfRule type="expression" dxfId="172" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9694,37 +9618,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="181" priority="18">
+    <cfRule type="expression" dxfId="171" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="180" priority="2">
+    <cfRule type="expression" dxfId="170" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="179" priority="32">
+    <cfRule type="expression" dxfId="169" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="178" priority="31">
+    <cfRule type="expression" dxfId="168" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="177" priority="5">
+    <cfRule type="expression" dxfId="167" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="176" priority="1">
+    <cfRule type="expression" dxfId="166" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="175" priority="3">
+    <cfRule type="expression" dxfId="165" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10140,22 +10064,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="313" priority="14">
+    <cfRule type="expression" dxfId="303" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="312" priority="6">
+    <cfRule type="expression" dxfId="302" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="311" priority="15">
+    <cfRule type="expression" dxfId="301" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="310" priority="1">
+    <cfRule type="expression" dxfId="300" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10553,22 +10477,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="174" priority="32">
+    <cfRule type="expression" dxfId="164" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="173" priority="31">
+    <cfRule type="expression" dxfId="163" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="172" priority="12">
+    <cfRule type="expression" dxfId="162" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="171" priority="1">
+    <cfRule type="expression" dxfId="161" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10934,22 +10858,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="170" priority="17">
+    <cfRule type="expression" dxfId="160" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="169" priority="16">
+    <cfRule type="expression" dxfId="159" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="168" priority="2">
+    <cfRule type="expression" dxfId="158" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="167" priority="1">
+    <cfRule type="expression" dxfId="157" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11384,47 +11308,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="166" priority="32">
+    <cfRule type="expression" dxfId="156" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="165" priority="31">
+    <cfRule type="expression" dxfId="155" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="164" priority="1">
+    <cfRule type="expression" dxfId="154" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="163" priority="3">
+    <cfRule type="expression" dxfId="153" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="162" priority="5">
+    <cfRule type="expression" dxfId="152" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="161" priority="12">
+    <cfRule type="expression" dxfId="151" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="160" priority="18">
+    <cfRule type="expression" dxfId="150" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="159" priority="27">
+    <cfRule type="expression" dxfId="149" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="158" priority="33">
+    <cfRule type="expression" dxfId="148" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11855,47 +11779,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="157" priority="12">
+    <cfRule type="expression" dxfId="147" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="156" priority="29">
+    <cfRule type="expression" dxfId="146" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="155" priority="28">
+    <cfRule type="expression" dxfId="145" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="154" priority="27">
+    <cfRule type="expression" dxfId="144" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="153" priority="1">
+    <cfRule type="expression" dxfId="143" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="152" priority="3">
+    <cfRule type="expression" dxfId="142" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="151" priority="9">
+    <cfRule type="expression" dxfId="141" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="150" priority="24">
+    <cfRule type="expression" dxfId="140" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="149" priority="30">
+    <cfRule type="expression" dxfId="139" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12330,52 +12254,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="148" priority="4">
+    <cfRule type="expression" dxfId="138" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="147" priority="27">
+    <cfRule type="expression" dxfId="137" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="146" priority="26">
+    <cfRule type="expression" dxfId="136" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="145" priority="1">
+    <cfRule type="expression" dxfId="135" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="144" priority="2">
+    <cfRule type="expression" dxfId="134" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="143" priority="28">
+    <cfRule type="expression" dxfId="133" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="142" priority="5">
+    <cfRule type="expression" dxfId="132" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="141" priority="8">
+    <cfRule type="expression" dxfId="131" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="140" priority="18">
+    <cfRule type="expression" dxfId="130" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="139" priority="22">
+    <cfRule type="expression" dxfId="129" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12804,47 +12728,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="138" priority="13">
+    <cfRule type="expression" dxfId="128" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="137" priority="22">
+    <cfRule type="expression" dxfId="127" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="136" priority="21">
+    <cfRule type="expression" dxfId="126" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="135" priority="1">
+    <cfRule type="expression" dxfId="125" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="134" priority="3">
+    <cfRule type="expression" dxfId="124" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="133" priority="5">
+    <cfRule type="expression" dxfId="123" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="132" priority="8">
+    <cfRule type="expression" dxfId="122" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="131" priority="17">
+    <cfRule type="expression" dxfId="121" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="130" priority="23">
+    <cfRule type="expression" dxfId="120" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13191,7 +13115,7 @@
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>420</v>
@@ -13204,7 +13128,7 @@
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="47" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13214,7 +13138,7 @@
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13267,52 +13191,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="129" priority="5">
+    <cfRule type="expression" dxfId="119" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="128" priority="28">
+    <cfRule type="expression" dxfId="118" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="127" priority="27">
+    <cfRule type="expression" dxfId="117" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="126" priority="1">
+    <cfRule type="expression" dxfId="116" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="125" priority="3">
+    <cfRule type="expression" dxfId="115" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="124" priority="29">
+    <cfRule type="expression" dxfId="114" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="123" priority="22">
+    <cfRule type="expression" dxfId="113" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="122" priority="8">
+    <cfRule type="expression" dxfId="112" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="121" priority="19">
+    <cfRule type="expression" dxfId="111" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="120" priority="23">
+    <cfRule type="expression" dxfId="110" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13655,7 +13579,7 @@
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>422</v>
@@ -13667,11 +13591,11 @@
         <v>411</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="22" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F29" s="17"/>
     </row>
@@ -13681,7 +13605,7 @@
         <v>418</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -13693,7 +13617,7 @@
         <v>304</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -13741,47 +13665,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="119" priority="11">
+    <cfRule type="expression" dxfId="109" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="118" priority="22">
+    <cfRule type="expression" dxfId="108" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="117" priority="21">
+    <cfRule type="expression" dxfId="107" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="116" priority="1">
+    <cfRule type="expression" dxfId="106" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="115" priority="3">
+    <cfRule type="expression" dxfId="105" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="114" priority="23">
+    <cfRule type="expression" dxfId="104" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="113" priority="5">
+    <cfRule type="expression" dxfId="103" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="112" priority="7">
+    <cfRule type="expression" dxfId="102" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="111" priority="17">
+    <cfRule type="expression" dxfId="101" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13901,7 +13825,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -13932,7 +13856,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -14112,16 +14036,16 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>444</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>423</v>
+        <v>443</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>453</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>389</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F28" s="16" t="s">
         <v>397</v>
@@ -14130,41 +14054,37 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="C30" s="17" t="s">
+      <c r="B30" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="C30" s="22" t="s">
         <v>458</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="22" t="s">
-        <v>458</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>460</v>
-      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -14211,58 +14131,53 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="110" priority="6">
+    <cfRule type="expression" dxfId="100" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="109" priority="27">
+    <cfRule type="expression" dxfId="99" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="108" priority="26">
+    <cfRule type="expression" dxfId="98" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F30 B32:F36 B31 D31:F31">
-    <cfRule type="expression" dxfId="107" priority="2">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="97" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="106" priority="4">
+    <cfRule type="expression" dxfId="96" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="105" priority="28">
+    <cfRule type="expression" dxfId="95" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="104" priority="21">
+    <cfRule type="expression" dxfId="94" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="103" priority="9">
+    <cfRule type="expression" dxfId="93" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="102" priority="19">
+    <cfRule type="expression" dxfId="92" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="101" priority="22">
+    <cfRule type="expression" dxfId="91" priority="22">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C31">
-    <cfRule type="expression" dxfId="9" priority="1">
-      <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14412,7 +14327,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -14624,23 +14539,23 @@
         <v>412</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="19" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -14650,7 +14565,7 @@
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -14698,32 +14613,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="100" priority="1">
+    <cfRule type="expression" dxfId="90" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="99" priority="24">
+    <cfRule type="expression" dxfId="89" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="98" priority="23">
+    <cfRule type="expression" dxfId="88" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="97" priority="3">
+    <cfRule type="expression" dxfId="87" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="96" priority="19">
+    <cfRule type="expression" dxfId="86" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E7:F25 C16:D25">
-    <cfRule type="expression" dxfId="95" priority="10">
+    <cfRule type="expression" dxfId="85" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15127,30 +15042,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="309" priority="3">
+    <cfRule type="expression" dxfId="299" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="308" priority="14">
+    <cfRule type="expression" dxfId="298" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="307" priority="15">
+    <cfRule type="expression" dxfId="297" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="306" priority="7">
+    <cfRule type="expression" dxfId="296" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="305" priority="9">
+    <cfRule type="expression" dxfId="295" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="304" priority="12">
+    <cfRule type="expression" dxfId="294" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15300,7 +15215,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15574,27 +15489,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="94" priority="1">
+    <cfRule type="expression" dxfId="84" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="93" priority="21">
+    <cfRule type="expression" dxfId="83" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="92" priority="20">
+    <cfRule type="expression" dxfId="82" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="91" priority="19">
+    <cfRule type="expression" dxfId="81" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="90" priority="6">
+    <cfRule type="expression" dxfId="80" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15742,7 +15657,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16018,27 +15933,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="89" priority="1">
+    <cfRule type="expression" dxfId="79" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="88" priority="27">
+    <cfRule type="expression" dxfId="78" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="87" priority="26">
+    <cfRule type="expression" dxfId="77" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="86" priority="3">
+    <cfRule type="expression" dxfId="76" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="85" priority="7">
+    <cfRule type="expression" dxfId="75" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16177,7 +16092,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16389,7 +16304,7 @@
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>394</v>
@@ -16447,43 +16362,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="84" priority="2">
+    <cfRule type="expression" dxfId="74" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="83" priority="31">
+    <cfRule type="expression" dxfId="73" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="82" priority="30">
+    <cfRule type="expression" dxfId="72" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F29 B31:F36 B30 D30:F30">
-    <cfRule type="expression" dxfId="81" priority="3">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="80" priority="10">
+    <cfRule type="expression" dxfId="70" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="79" priority="8">
+    <cfRule type="expression" dxfId="69" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="78" priority="14">
+    <cfRule type="expression" dxfId="68" priority="14">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C30">
-    <cfRule type="expression" dxfId="7" priority="1">
-      <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16614,7 +16524,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -16782,7 +16692,7 @@
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>389</v>
@@ -16791,17 +16701,17 @@
         <v>40</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16864,38 +16774,33 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="77" priority="2">
+    <cfRule type="expression" dxfId="67" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="76" priority="36">
+    <cfRule type="expression" dxfId="66" priority="36">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="75" priority="35">
+    <cfRule type="expression" dxfId="65" priority="35">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F28 B30:F36 B29 D29:F29">
-    <cfRule type="expression" dxfId="74" priority="4">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="73" priority="14">
+    <cfRule type="expression" dxfId="63" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="72" priority="11">
+    <cfRule type="expression" dxfId="62" priority="11">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>NOT(ISBLANK(C29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17042,7 +16947,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -17231,7 +17136,7 @@
         <v>413</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>387</v>
@@ -17242,10 +17147,10 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>388</v>
@@ -17256,7 +17161,7 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="16" t="s">
@@ -17315,43 +17220,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="71" priority="8">
+    <cfRule type="expression" dxfId="61" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="70" priority="39">
+    <cfRule type="expression" dxfId="60" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="69" priority="38">
+    <cfRule type="expression" dxfId="59" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F28 B30:F36 B29 D29:F29">
-    <cfRule type="expression" dxfId="68" priority="4">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="58" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="67" priority="2">
+    <cfRule type="expression" dxfId="57" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="66" priority="32">
+    <cfRule type="expression" dxfId="56" priority="32">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="65" priority="31">
+    <cfRule type="expression" dxfId="55" priority="31">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>NOT(ISBLANK(C29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17495,7 +17395,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -17693,23 +17593,23 @@
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>386</v>
       </c>
       <c r="E28" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="F28" s="16" t="s">
         <v>445</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>388</v>
@@ -17722,7 +17622,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17777,48 +17677,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="64" priority="7">
+    <cfRule type="expression" dxfId="54" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="63" priority="41">
+    <cfRule type="expression" dxfId="53" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="62" priority="40">
+    <cfRule type="expression" dxfId="52" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F28 B30:F36 B29 D29:F29">
-    <cfRule type="expression" dxfId="61" priority="4">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="51" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="60" priority="2">
+    <cfRule type="expression" dxfId="50" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="59" priority="11">
+    <cfRule type="expression" dxfId="49" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="58" priority="34">
+    <cfRule type="expression" dxfId="48" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="57" priority="33">
+    <cfRule type="expression" dxfId="47" priority="33">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C29">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>NOT(ISBLANK(C29))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17965,7 +17860,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18161,12 +18056,12 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -18178,13 +18073,13 @@
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="16" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -18241,48 +18136,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="56" priority="6">
+    <cfRule type="expression" dxfId="46" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="55" priority="21">
+    <cfRule type="expression" dxfId="45" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="54" priority="20">
+    <cfRule type="expression" dxfId="44" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:F36 B28 D28:F28">
-    <cfRule type="expression" dxfId="53" priority="19">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="43" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="52" priority="2">
+    <cfRule type="expression" dxfId="42" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="51" priority="10">
+    <cfRule type="expression" dxfId="41" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B15:D25">
-    <cfRule type="expression" dxfId="50" priority="17">
+    <cfRule type="expression" dxfId="40" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="49" priority="16">
+    <cfRule type="expression" dxfId="39" priority="16">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18429,7 +18319,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18625,7 +18515,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16" t="s">
@@ -18638,7 +18528,7 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -18648,7 +18538,7 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -18705,48 +18595,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="48" priority="7">
+    <cfRule type="expression" dxfId="38" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D25">
-    <cfRule type="expression" dxfId="47" priority="8">
+    <cfRule type="expression" dxfId="37" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="46" priority="23">
+    <cfRule type="expression" dxfId="36" priority="23">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="45" priority="22">
+    <cfRule type="expression" dxfId="35" priority="22">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:F36 B28 D28:F28">
-    <cfRule type="expression" dxfId="44" priority="4">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="34" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="43" priority="2">
+    <cfRule type="expression" dxfId="33" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="42" priority="12">
+    <cfRule type="expression" dxfId="32" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="41" priority="18">
+    <cfRule type="expression" dxfId="31" priority="18">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18893,7 +18778,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19089,7 +18974,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -19161,48 +19046,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="40" priority="6">
+    <cfRule type="expression" dxfId="30" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="39" priority="7">
+    <cfRule type="expression" dxfId="29" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="38" priority="22">
+    <cfRule type="expression" dxfId="28" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="37" priority="21">
+    <cfRule type="expression" dxfId="27" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:F36 B28 D28:F28">
-    <cfRule type="expression" dxfId="36" priority="20">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="35" priority="2">
+    <cfRule type="expression" dxfId="25" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="34" priority="11">
+    <cfRule type="expression" dxfId="24" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="33" priority="17">
+    <cfRule type="expression" dxfId="23" priority="17">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19349,7 +19229,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19563,10 +19443,10 @@
         <v>43</v>
       </c>
       <c r="C29" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="D29" s="19" t="s">
         <v>448</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>449</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
@@ -19629,42 +19509,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="32" priority="6">
+    <cfRule type="expression" dxfId="22" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="31" priority="7">
+    <cfRule type="expression" dxfId="21" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="30" priority="22">
+    <cfRule type="expression" dxfId="20" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="29" priority="21">
+    <cfRule type="expression" dxfId="19" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="28" priority="20">
+    <cfRule type="expression" dxfId="18" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="27" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="26" priority="11">
+    <cfRule type="expression" dxfId="16" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="25" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20089,22 +19969,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="303" priority="10">
+    <cfRule type="expression" dxfId="293" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="302" priority="9">
+    <cfRule type="expression" dxfId="292" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="301" priority="1">
+    <cfRule type="expression" dxfId="291" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="300" priority="7">
+    <cfRule type="expression" dxfId="290" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20253,7 +20133,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -20529,42 +20409,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="24" priority="5">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="23" priority="6">
+    <cfRule type="expression" dxfId="13" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="22" priority="21">
+    <cfRule type="expression" dxfId="12" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="21" priority="20">
+    <cfRule type="expression" dxfId="11" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="20" priority="19">
+    <cfRule type="expression" dxfId="10" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="18" priority="10">
+    <cfRule type="expression" dxfId="8" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="17" priority="16">
+    <cfRule type="expression" dxfId="7" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20712,7 +20592,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -20984,37 +20864,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="16" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="15" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="14" priority="21">
+    <cfRule type="expression" dxfId="4" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="13" priority="20">
+    <cfRule type="expression" dxfId="3" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="12" priority="19">
+    <cfRule type="expression" dxfId="2" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="10" priority="10">
+    <cfRule type="expression" dxfId="0" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21459,42 +21339,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="299" priority="15">
+    <cfRule type="expression" dxfId="289" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="298" priority="13">
+    <cfRule type="expression" dxfId="288" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="297" priority="30">
+    <cfRule type="expression" dxfId="287" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="296" priority="29">
+    <cfRule type="expression" dxfId="286" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="295" priority="7">
+    <cfRule type="expression" dxfId="285" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="294" priority="24">
+    <cfRule type="expression" dxfId="284" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="293" priority="20">
+    <cfRule type="expression" dxfId="283" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="292" priority="25">
+    <cfRule type="expression" dxfId="282" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21895,32 +21775,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="291" priority="8">
+    <cfRule type="expression" dxfId="281" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="290" priority="13">
+    <cfRule type="expression" dxfId="280" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="289" priority="12">
+    <cfRule type="expression" dxfId="279" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="288" priority="1">
+    <cfRule type="expression" dxfId="278" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="287" priority="4">
+    <cfRule type="expression" dxfId="277" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="286" priority="7">
+    <cfRule type="expression" dxfId="276" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22304,52 +22184,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="285" priority="22">
+    <cfRule type="expression" dxfId="275" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="284" priority="23">
+    <cfRule type="expression" dxfId="274" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="283" priority="45">
+    <cfRule type="expression" dxfId="273" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="282" priority="44">
+    <cfRule type="expression" dxfId="272" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="281" priority="1">
+    <cfRule type="expression" dxfId="271" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="280" priority="35">
+    <cfRule type="expression" dxfId="270" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="279" priority="36">
+    <cfRule type="expression" dxfId="269" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="278" priority="16">
+    <cfRule type="expression" dxfId="268" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="277" priority="34">
+    <cfRule type="expression" dxfId="267" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="276" priority="5">
+    <cfRule type="expression" dxfId="266" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22762,47 +22642,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="275" priority="16">
+    <cfRule type="expression" dxfId="265" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="274" priority="19">
+    <cfRule type="expression" dxfId="264" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="273" priority="18">
+    <cfRule type="expression" dxfId="263" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="272" priority="1">
+    <cfRule type="expression" dxfId="262" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="271" priority="15">
+    <cfRule type="expression" dxfId="261" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="270" priority="12">
+    <cfRule type="expression" dxfId="260" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="269" priority="11">
+    <cfRule type="expression" dxfId="259" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="268" priority="14">
+    <cfRule type="expression" dxfId="258" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="267" priority="5">
+    <cfRule type="expression" dxfId="257" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23225,32 +23105,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="266" priority="2">
+    <cfRule type="expression" dxfId="256" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="265" priority="4">
+    <cfRule type="expression" dxfId="255" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="264" priority="16">
+    <cfRule type="expression" dxfId="254" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="263" priority="15">
+    <cfRule type="expression" dxfId="253" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="262" priority="1">
+    <cfRule type="expression" dxfId="252" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="261" priority="7">
+    <cfRule type="expression" dxfId="251" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C07FF84-912D-4473-8B3C-DCE7B4FAFA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754F85D7-4343-48DC-BDFA-30C5D1190AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="468">
   <si>
     <t>Week</t>
   </si>
@@ -1472,6 +1472,33 @@
   </si>
   <si>
     <t>Materiaal meedoen boekmaking</t>
+  </si>
+  <si>
+    <t>MORGEN MC MOVIE</t>
+  </si>
+  <si>
+    <t>9u30 - 11u30: Screening essayfilms en filmgedichten.</t>
+  </si>
+  <si>
+    <t>14u - ...: Facultatieve feedback.</t>
+  </si>
+  <si>
+    <t>Facultatieve feedback op alle eindwerken in Luca Gent.</t>
+  </si>
+  <si>
+    <t>25 april Facultatieve feedback op alle eindwerken online .</t>
+  </si>
+  <si>
+    <t>Screening van de moodpieces voor finale klassikale feedback.</t>
+  </si>
+  <si>
+    <t>Screening van de video eindopdrachten voor finale klassikale feedback.</t>
+  </si>
+  <si>
+    <t>BOEK TOCH MEEDOEN LAATSTE LES DENKIK</t>
+  </si>
+  <si>
+    <t>BOEK TOCH MEEDOEN</t>
   </si>
 </sst>
 </file>
@@ -14075,7 +14102,9 @@
       <c r="C30" s="22" t="s">
         <v>458</v>
       </c>
-      <c r="D30" s="17"/>
+      <c r="D30" s="17" t="s">
+        <v>467</v>
+      </c>
       <c r="E30" s="17" t="s">
         <v>455</v>
       </c>
@@ -14086,7 +14115,9 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="E31" s="17" t="s">
+        <v>460</v>
+      </c>
       <c r="F31" s="17"/>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14094,7 +14125,9 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
+      <c r="E32" s="17" t="s">
+        <v>461</v>
+      </c>
       <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14541,7 +14574,9 @@
       <c r="C29" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="D29" s="17"/>
+      <c r="D29" s="17" t="s">
+        <v>466</v>
+      </c>
       <c r="E29" s="19" t="s">
         <v>439</v>
       </c>
@@ -14559,7 +14594,9 @@
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="16" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -16309,8 +16346,12 @@
       <c r="D30" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="E30" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -17141,7 +17182,9 @@
       <c r="D28" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="E28" s="16"/>
+      <c r="E28" s="16" t="s">
+        <v>464</v>
+      </c>
       <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -17153,9 +17196,11 @@
         <v>458</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="E29" s="17"/>
+        <v>389</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>465</v>
+      </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -17164,9 +17209,7 @@
         <v>436</v>
       </c>
       <c r="C30" s="17"/>
-      <c r="D30" s="16" t="s">
-        <v>389</v>
-      </c>
+      <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{754F85D7-4343-48DC-BDFA-30C5D1190AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFC03CD-BDCC-4A30-BFFC-884416893D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="22" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="20" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="469">
   <si>
     <t>Week</t>
   </si>
@@ -1499,6 +1499,9 @@
   </si>
   <si>
     <t>BOEK TOCH MEEDOEN</t>
+  </si>
+  <si>
+    <t>WERKENDE SITE DINGEN HEBBEN</t>
   </si>
 </sst>
 </file>
@@ -14068,10 +14071,10 @@
       <c r="C28" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="E28" s="16" t="s">
+      <c r="D28" s="47" t="s">
+        <v>457</v>
+      </c>
+      <c r="E28" s="22" t="s">
         <v>428</v>
       </c>
       <c r="F28" s="16" t="s">
@@ -14086,13 +14089,15 @@
       <c r="C29" s="47" t="s">
         <v>456</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="E29" s="16" t="s">
+      <c r="D29" s="47" t="s">
+        <v>467</v>
+      </c>
+      <c r="E29" s="22" t="s">
         <v>451</v>
       </c>
-      <c r="F29" s="17"/>
+      <c r="F29" s="19" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
@@ -14102,11 +14107,9 @@
       <c r="C30" s="22" t="s">
         <v>458</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>467</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>455</v>
+      <c r="D30" s="17"/>
+      <c r="E30" s="22" t="s">
+        <v>460</v>
       </c>
       <c r="F30" s="17"/>
     </row>
@@ -14115,8 +14118,8 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="17" t="s">
-        <v>460</v>
+      <c r="E31" s="22" t="s">
+        <v>461</v>
       </c>
       <c r="F31" s="17"/>
     </row>
@@ -14125,9 +14128,7 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="17" t="s">
-        <v>461</v>
-      </c>
+      <c r="E32" s="17"/>
       <c r="F32" s="17"/>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14600,7 +14601,9 @@
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="16" t="s">
+        <v>468</v>
+      </c>
       <c r="C31" s="16" t="s">
         <v>458</v>
       </c>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F454A65C-FE22-461F-B120-C798436B1745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82CAA52-9F1C-430E-8626-3390C3C054F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="25" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="474">
   <si>
     <t>Week</t>
   </si>
@@ -271,9 +271,6 @@
   </si>
   <si>
     <t>C&amp;D: opleverdatum</t>
-  </si>
-  <si>
-    <t>A&amp;B: Opleverdatum</t>
   </si>
   <si>
     <t>ABCD: Meeting project owner</t>
@@ -385,9 +382,6 @@
     <t>Design thinking waarschijnlijk in voormiddag</t>
   </si>
   <si>
-    <t>Uurrooster ontbreekt op toledo?</t>
-  </si>
-  <si>
     <t>Feedback verdieping</t>
   </si>
   <si>
@@ -1333,9 +1327,6 @@
     <t>Op 17/03 om 17u kiezen we per pagina één definitieve versie</t>
   </si>
   <si>
-    <t>Interactieve prototype in Figma/XD</t>
-  </si>
-  <si>
     <t>Website live + eindpresentatie</t>
   </si>
   <si>
@@ -1492,9 +1483,6 @@
     <t>Screening van de video eindopdrachten voor finale klassikale feedback.</t>
   </si>
   <si>
-    <t>BOEK TOCH MEEDOEN LAATSTE LES DENKIK</t>
-  </si>
-  <si>
     <t>BOEK TOCH MEEDOEN</t>
   </si>
   <si>
@@ -1502,6 +1490,33 @@
   </si>
   <si>
     <t>Crossmedia's indienen + THEO FOTOS GEVEN CROSSMEDIA BOOKMAKING</t>
+  </si>
+  <si>
+    <t>Portfolio deadlines opschrijven ofzo</t>
+  </si>
+  <si>
+    <t>DESIGN THINKING MOET AF ZIJN!</t>
+  </si>
+  <si>
+    <t>DESIGNS MOETEN AF ZIJN VAN COMMON TERRE!</t>
+  </si>
+  <si>
+    <t>14:00u PLANNING PARIJS!</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t>Lokaal 303</t>
+  </si>
+  <si>
+    <t>Is er nog communicatie?</t>
+  </si>
+  <si>
+    <t>Creatief &amp; Ondernemend</t>
+  </si>
+  <si>
+    <t>Checken crossmedia's punten</t>
   </si>
 </sst>
 </file>
@@ -1829,7 +1844,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="305">
+  <dxfs count="313">
     <dxf>
       <font>
         <color theme="1"/>
@@ -2305,6 +2320,46 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2369,6 +2424,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2423,6 +2488,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2609,9 +2684,32 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4885,10 +4983,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="26" t="s">
         <v>83</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -4901,18 +4999,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="24" t="s">
         <v>85</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4995,7 +5093,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33"/>
@@ -5008,7 +5106,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
@@ -5057,7 +5155,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="35"/>
@@ -5068,7 +5166,7 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
@@ -5153,7 +5251,7 @@
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="42" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E18" s="36"/>
       <c r="F18" s="49"/>
@@ -5243,75 +5341,75 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D29" s="47" t="s">
+        <v>221</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>225</v>
-      </c>
       <c r="F29" s="23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="47" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="23" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="23" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="17"/>
       <c r="C32" s="47" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="23" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5348,47 +5446,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="251" priority="17">
+    <cfRule type="expression" dxfId="259" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="250" priority="25">
+    <cfRule type="expression" dxfId="258" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="249" priority="24">
+    <cfRule type="expression" dxfId="257" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="248" priority="5">
+    <cfRule type="expression" dxfId="256" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="247" priority="9">
+    <cfRule type="expression" dxfId="255" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="246" priority="8">
+    <cfRule type="expression" dxfId="254" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="245" priority="11">
+    <cfRule type="expression" dxfId="253" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="244" priority="15">
+    <cfRule type="expression" dxfId="252" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="243" priority="2">
+    <cfRule type="expression" dxfId="251" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5472,7 +5570,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
@@ -5486,7 +5584,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>24</v>
@@ -5510,7 +5608,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -5523,7 +5621,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="28"/>
       <c r="D7" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -5556,7 +5654,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="30"/>
@@ -5568,7 +5666,7 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="31"/>
@@ -5623,7 +5721,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -5738,75 +5836,75 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D29" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="E29" s="22" t="s">
-        <v>241</v>
-      </c>
       <c r="F29" s="22" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="22" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E30" s="16"/>
       <c r="F30" s="22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
       <c r="F31" s="22" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="22" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="22" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5816,7 +5914,7 @@
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
       <c r="F33" s="22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5826,7 +5924,7 @@
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
       <c r="F34" s="22" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -5847,42 +5945,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="242" priority="15">
+    <cfRule type="expression" dxfId="250" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="241" priority="10">
+    <cfRule type="expression" dxfId="249" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="240" priority="24">
+    <cfRule type="expression" dxfId="248" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="239" priority="23">
+    <cfRule type="expression" dxfId="247" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="238" priority="1">
+    <cfRule type="expression" dxfId="246" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="237" priority="7">
+    <cfRule type="expression" dxfId="245" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="236" priority="3">
+    <cfRule type="expression" dxfId="244" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="235" priority="14">
+    <cfRule type="expression" dxfId="243" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5966,7 +6064,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D4" s="33"/>
       <c r="E4" s="33"/>
@@ -5979,7 +6077,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
@@ -6028,7 +6126,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D9" s="35"/>
       <c r="E9" s="35"/>
@@ -6039,7 +6137,7 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
@@ -6212,76 +6310,76 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>211</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="23" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="23" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="23" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F31" s="19"/>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
@@ -6321,47 +6419,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="234" priority="10">
+    <cfRule type="expression" dxfId="242" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="233" priority="1">
+    <cfRule type="expression" dxfId="241" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="232" priority="25">
+    <cfRule type="expression" dxfId="240" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="231" priority="24">
+    <cfRule type="expression" dxfId="239" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="230" priority="4">
+    <cfRule type="expression" dxfId="238" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="229" priority="3">
+    <cfRule type="expression" dxfId="237" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="228" priority="6">
+    <cfRule type="expression" dxfId="236" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="227" priority="9">
+    <cfRule type="expression" dxfId="235" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="226" priority="11">
+    <cfRule type="expression" dxfId="234" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6477,7 +6575,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -6489,7 +6587,7 @@
       </c>
       <c r="B7" s="7"/>
       <c r="D7" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -6555,7 +6653,7 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="16" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
@@ -6582,7 +6680,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -6697,102 +6795,102 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="22" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="22" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="22" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="22" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="22" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F33" s="16"/>
     </row>
@@ -6800,7 +6898,7 @@
       <c r="A34" s="11"/>
       <c r="B34" s="16"/>
       <c r="C34" s="22" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
@@ -6824,57 +6922,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="225" priority="36">
+    <cfRule type="expression" dxfId="233" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="224" priority="51">
+    <cfRule type="expression" dxfId="232" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="223" priority="50">
+    <cfRule type="expression" dxfId="231" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="222" priority="9">
+    <cfRule type="expression" dxfId="230" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="221" priority="28">
+    <cfRule type="expression" dxfId="229" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="220" priority="11">
+    <cfRule type="expression" dxfId="228" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="219" priority="24">
+    <cfRule type="expression" dxfId="227" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="218" priority="31">
+    <cfRule type="expression" dxfId="226" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="217" priority="7">
+    <cfRule type="expression" dxfId="225" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="216" priority="35">
+    <cfRule type="expression" dxfId="224" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="215" priority="1">
+    <cfRule type="expression" dxfId="223" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7186,81 +7284,81 @@
     <row r="28" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G28" s="61"/>
     </row>
     <row r="29" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="22" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G29" s="61"/>
     </row>
     <row r="30" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="22" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="22" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G30" s="61"/>
     </row>
     <row r="31" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
       <c r="E31" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G31" s="61"/>
     </row>
     <row r="32" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
       <c r="F32" s="22" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G32" s="61"/>
     </row>
@@ -7271,7 +7369,7 @@
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
       <c r="F33" s="22" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G33" s="61"/>
     </row>
@@ -7282,7 +7380,7 @@
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
       <c r="F34" s="22" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G34" s="61"/>
     </row>
@@ -7293,7 +7391,7 @@
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
       <c r="F35" s="65" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -7306,59 +7404,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="214" priority="35">
+    <cfRule type="expression" dxfId="222" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="213" priority="42">
+    <cfRule type="expression" dxfId="221" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="212" priority="54">
+    <cfRule type="expression" dxfId="220" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="211" priority="53">
+    <cfRule type="expression" dxfId="219" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="210" priority="5">
+    <cfRule type="expression" dxfId="218" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="209" priority="30">
+    <cfRule type="expression" dxfId="217" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="208" priority="33">
+    <cfRule type="expression" dxfId="216" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="207" priority="37">
+    <cfRule type="expression" dxfId="215" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="206" priority="41">
+    <cfRule type="expression" dxfId="214" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="205" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="203" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="202" priority="1">
+    <cfRule type="expression" dxfId="210" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7469,7 +7567,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -7569,7 +7667,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -7713,91 +7811,91 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="17" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="17" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="17" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -7807,7 +7905,7 @@
     <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="16" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -7824,57 +7922,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="201" priority="1">
+    <cfRule type="expression" dxfId="209" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="200" priority="18">
+    <cfRule type="expression" dxfId="208" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="199" priority="41">
+    <cfRule type="expression" dxfId="207" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="198" priority="40">
+    <cfRule type="expression" dxfId="206" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="197" priority="13">
+    <cfRule type="expression" dxfId="205" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="196" priority="3">
+    <cfRule type="expression" dxfId="204" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="195" priority="5">
+    <cfRule type="expression" dxfId="203" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="194" priority="19">
+    <cfRule type="expression" dxfId="202" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="193" priority="7">
+    <cfRule type="expression" dxfId="201" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="192" priority="27">
+    <cfRule type="expression" dxfId="200" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="191" priority="8">
+    <cfRule type="expression" dxfId="199" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7989,7 +8087,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -8001,7 +8099,7 @@
       </c>
       <c r="B7" s="7"/>
       <c r="D7" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -8093,7 +8191,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -8237,55 +8335,55 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -8295,7 +8393,7 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -8305,7 +8403,7 @@
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -8334,32 +8432,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="190" priority="21">
+    <cfRule type="expression" dxfId="198" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="189" priority="43">
+    <cfRule type="expression" dxfId="197" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="188" priority="42">
+    <cfRule type="expression" dxfId="196" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="187" priority="1">
+    <cfRule type="expression" dxfId="195" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="186" priority="16">
+    <cfRule type="expression" dxfId="194" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="185" priority="24">
+    <cfRule type="expression" dxfId="193" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8555,17 +8653,17 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="B17" s="50" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D17" s="62" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="67" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -8573,7 +8671,7 @@
         <v>0.625</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C18" s="38"/>
       <c r="D18" s="40"/>
@@ -8585,7 +8683,7 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C19" s="38"/>
       <c r="D19" s="40"/>
@@ -8672,81 +8770,81 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="23" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="19" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C33" s="19"/>
       <c r="D33" s="16"/>
       <c r="E33" s="19"/>
       <c r="F33" s="19" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -8775,32 +8873,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="184" priority="30">
+    <cfRule type="expression" dxfId="192" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="183" priority="29">
+    <cfRule type="expression" dxfId="191" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="182" priority="16">
+    <cfRule type="expression" dxfId="190" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="181" priority="1">
+    <cfRule type="expression" dxfId="189" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="180" priority="4">
+    <cfRule type="expression" dxfId="188" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="179" priority="5">
+    <cfRule type="expression" dxfId="187" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8978,10 +9076,10 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -9103,85 +9201,85 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="16" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E32" s="16"/>
       <c r="F32" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
       <c r="F33" s="16" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9210,32 +9308,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="178" priority="39">
+    <cfRule type="expression" dxfId="186" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="177" priority="38">
+    <cfRule type="expression" dxfId="185" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="176" priority="20">
+    <cfRule type="expression" dxfId="184" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="175" priority="1">
+    <cfRule type="expression" dxfId="183" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="174" priority="3">
+    <cfRule type="expression" dxfId="182" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="173" priority="2">
+    <cfRule type="expression" dxfId="181" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9328,10 +9426,10 @@
         <v>0.375</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F5" s="38"/>
       <c r="H5" s="11" t="s">
@@ -9355,10 +9453,10 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F7" s="38"/>
       <c r="H7" s="1" t="s">
@@ -9556,55 +9654,55 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9612,13 +9710,13 @@
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
       <c r="D32" s="19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -9655,37 +9753,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="172" priority="18">
+    <cfRule type="expression" dxfId="180" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="171" priority="2">
+    <cfRule type="expression" dxfId="179" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="170" priority="32">
+    <cfRule type="expression" dxfId="178" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="169" priority="31">
+    <cfRule type="expression" dxfId="177" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="168" priority="5">
+    <cfRule type="expression" dxfId="176" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="167" priority="1">
+    <cfRule type="expression" dxfId="175" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="166" priority="3">
+    <cfRule type="expression" dxfId="174" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9823,7 +9921,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -10010,44 +10108,44 @@
         <v>29</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="23" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="23"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -10101,22 +10199,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="304" priority="14">
+    <cfRule type="expression" dxfId="312" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="303" priority="6">
+    <cfRule type="expression" dxfId="311" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="302" priority="15">
+    <cfRule type="expression" dxfId="310" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="301" priority="1">
+    <cfRule type="expression" dxfId="309" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10282,7 +10380,7 @@
         <v>0.5</v>
       </c>
       <c r="C12" s="60" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D12" s="38"/>
       <c r="E12" s="36"/>
@@ -10293,7 +10391,7 @@
         <v>0.53125</v>
       </c>
       <c r="C13" s="63" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="36"/>
@@ -10304,7 +10402,7 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -10427,26 +10525,26 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="47" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -10456,7 +10554,7 @@
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -10466,7 +10564,7 @@
       <c r="A32" s="11"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
@@ -10476,7 +10574,7 @@
       <c r="A33" s="11"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
@@ -10486,7 +10584,7 @@
       <c r="A34" s="11"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
@@ -10496,7 +10594,7 @@
       <c r="A35" s="11"/>
       <c r="B35" s="17"/>
       <c r="C35" s="17" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
@@ -10506,7 +10604,7 @@
       <c r="A36" s="11"/>
       <c r="B36" s="17"/>
       <c r="C36" s="19" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
@@ -10514,22 +10612,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="165" priority="32">
+    <cfRule type="expression" dxfId="173" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="164" priority="31">
+    <cfRule type="expression" dxfId="172" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="163" priority="12">
+    <cfRule type="expression" dxfId="171" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="1">
+    <cfRule type="expression" dxfId="170" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10827,7 +10925,7 @@
       <c r="A29" s="11"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19" t="s">
@@ -10895,22 +10993,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="17">
+    <cfRule type="expression" dxfId="169" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="16">
+    <cfRule type="expression" dxfId="168" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="159" priority="2">
+    <cfRule type="expression" dxfId="167" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="158" priority="1">
+    <cfRule type="expression" dxfId="166" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10993,10 +11091,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11004,10 +11102,10 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -11025,7 +11123,7 @@
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="32" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -11036,7 +11134,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32"/>
@@ -11051,7 +11149,7 @@
         <v>0.4375</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C8" s="28"/>
       <c r="E8" s="28"/>
@@ -11069,7 +11167,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -11137,7 +11235,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -11148,7 +11246,7 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>27</v>
@@ -11255,30 +11353,30 @@
         <v>35</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E28" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>375</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="23" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -11287,7 +11385,7 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="23" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F30" s="17"/>
     </row>
@@ -11297,7 +11395,7 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="23" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F31" s="17"/>
     </row>
@@ -11307,7 +11405,7 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="23" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F32" s="17"/>
     </row>
@@ -11345,47 +11443,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="157" priority="32">
+    <cfRule type="expression" dxfId="165" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="156" priority="31">
+    <cfRule type="expression" dxfId="164" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="155" priority="1">
+    <cfRule type="expression" dxfId="163" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="154" priority="3">
+    <cfRule type="expression" dxfId="162" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="153" priority="5">
+    <cfRule type="expression" dxfId="161" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="152" priority="12">
+    <cfRule type="expression" dxfId="160" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="151" priority="18">
+    <cfRule type="expression" dxfId="159" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="150" priority="27">
+    <cfRule type="expression" dxfId="158" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="149" priority="33">
+    <cfRule type="expression" dxfId="157" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11469,11 +11567,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11481,7 +11579,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -11529,7 +11627,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -11545,7 +11643,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -11556,7 +11654,7 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -11723,53 +11821,53 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="16"/>
       <c r="F28" s="22" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="23" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="19"/>
       <c r="C30" s="23" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="23" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="19"/>
       <c r="C31" s="22" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
       <c r="F31" s="23" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -11779,7 +11877,7 @@
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
       <c r="F32" s="23" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -11816,47 +11914,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="148" priority="12">
+    <cfRule type="expression" dxfId="156" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="147" priority="29">
+    <cfRule type="expression" dxfId="155" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="146" priority="28">
+    <cfRule type="expression" dxfId="154" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="145" priority="27">
+    <cfRule type="expression" dxfId="153" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="144" priority="1">
+    <cfRule type="expression" dxfId="152" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="143" priority="3">
+    <cfRule type="expression" dxfId="151" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="142" priority="9">
+    <cfRule type="expression" dxfId="150" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="141" priority="24">
+    <cfRule type="expression" dxfId="149" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="140" priority="30">
+    <cfRule type="expression" dxfId="148" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11940,10 +12038,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -11954,7 +12052,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -11968,11 +12066,11 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -11983,7 +12081,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
@@ -12017,7 +12115,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D9" s="34"/>
       <c r="E9" s="30"/>
@@ -12085,7 +12183,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -12200,35 +12298,35 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D28" s="22" t="s">
         <v>36</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="22" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -12237,7 +12335,7 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="47" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F30" s="17"/>
     </row>
@@ -12291,52 +12389,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="139" priority="4">
+    <cfRule type="expression" dxfId="147" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="138" priority="27">
+    <cfRule type="expression" dxfId="146" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="137" priority="26">
+    <cfRule type="expression" dxfId="145" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="136" priority="1">
+    <cfRule type="expression" dxfId="144" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="135" priority="2">
+    <cfRule type="expression" dxfId="143" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="134" priority="28">
+    <cfRule type="expression" dxfId="142" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="133" priority="5">
+    <cfRule type="expression" dxfId="141" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="132" priority="8">
+    <cfRule type="expression" dxfId="140" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="131" priority="18">
+    <cfRule type="expression" dxfId="139" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="130" priority="22">
+    <cfRule type="expression" dxfId="138" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12419,11 +12517,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -12431,7 +12529,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -12479,7 +12577,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -12495,7 +12593,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -12506,7 +12604,7 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -12674,53 +12772,53 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="22" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="22" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="22" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="22" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="22" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="22" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -12765,47 +12863,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="129" priority="13">
+    <cfRule type="expression" dxfId="137" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="128" priority="22">
+    <cfRule type="expression" dxfId="136" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="127" priority="21">
+    <cfRule type="expression" dxfId="135" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="126" priority="1">
+    <cfRule type="expression" dxfId="134" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="125" priority="3">
+    <cfRule type="expression" dxfId="133" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="124" priority="5">
+    <cfRule type="expression" dxfId="132" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="123" priority="8">
+    <cfRule type="expression" dxfId="131" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="122" priority="17">
+    <cfRule type="expression" dxfId="130" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="121" priority="23">
+    <cfRule type="expression" dxfId="129" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12889,10 +12987,10 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -12903,7 +13001,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
@@ -12917,11 +13015,11 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C6" s="28"/>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -12932,7 +13030,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C7" s="28"/>
       <c r="E7" s="32" t="s">
@@ -12965,7 +13063,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -13030,7 +13128,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -13145,17 +13243,17 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13165,7 +13263,7 @@
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="47" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13175,7 +13273,7 @@
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="22" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13228,52 +13326,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="120" priority="5">
+    <cfRule type="expression" dxfId="128" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="119" priority="28">
+    <cfRule type="expression" dxfId="127" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="118" priority="27">
+    <cfRule type="expression" dxfId="126" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="117" priority="1">
+    <cfRule type="expression" dxfId="125" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="116" priority="3">
+    <cfRule type="expression" dxfId="124" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="115" priority="29">
+    <cfRule type="expression" dxfId="123" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="114" priority="22">
+    <cfRule type="expression" dxfId="122" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="113" priority="8">
+    <cfRule type="expression" dxfId="121" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="112" priority="19">
+    <cfRule type="expression" dxfId="120" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="111" priority="23">
+    <cfRule type="expression" dxfId="119" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13356,11 +13454,11 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -13368,7 +13466,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -13416,7 +13514,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -13432,7 +13530,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -13443,7 +13541,7 @@
       </c>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -13609,40 +13707,40 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="22" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="47" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -13651,10 +13749,10 @@
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="22" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -13702,47 +13800,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="110" priority="11">
+    <cfRule type="expression" dxfId="118" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="109" priority="22">
+    <cfRule type="expression" dxfId="117" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="108" priority="21">
+    <cfRule type="expression" dxfId="116" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="107" priority="1">
+    <cfRule type="expression" dxfId="115" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="106" priority="3">
+    <cfRule type="expression" dxfId="114" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="105" priority="23">
+    <cfRule type="expression" dxfId="113" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="104" priority="5">
+    <cfRule type="expression" dxfId="112" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="103" priority="7">
+    <cfRule type="expression" dxfId="111" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="102" priority="17">
+    <cfRule type="expression" dxfId="110" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13826,7 +13924,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -13848,10 +13946,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -13862,7 +13960,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -13893,7 +13991,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -13958,7 +14056,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -14073,48 +14171,48 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C28" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="D28" s="47" t="s">
         <v>453</v>
       </c>
-      <c r="D28" s="47" t="s">
-        <v>456</v>
-      </c>
       <c r="E28" s="22" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D29" s="47" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="22" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="22" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F30" s="17"/>
     </row>
@@ -14124,7 +14222,7 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="22" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F31" s="17"/>
     </row>
@@ -14170,52 +14268,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="101" priority="6">
+    <cfRule type="expression" dxfId="109" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="100" priority="27">
+    <cfRule type="expression" dxfId="108" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="99" priority="26">
+    <cfRule type="expression" dxfId="107" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="98" priority="1">
+    <cfRule type="expression" dxfId="106" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="97" priority="4">
+    <cfRule type="expression" dxfId="105" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="96" priority="28">
+    <cfRule type="expression" dxfId="104" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="95" priority="21">
+    <cfRule type="expression" dxfId="103" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="94" priority="9">
+    <cfRule type="expression" dxfId="102" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="93" priority="19">
+    <cfRule type="expression" dxfId="101" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="92" priority="22">
+    <cfRule type="expression" dxfId="100" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14298,8 +14396,11 @@
       <c r="A4" s="3">
         <v>0.35416666666666669</v>
       </c>
+      <c r="E4" s="29" t="s">
+        <v>472</v>
+      </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -14309,6 +14410,9 @@
       <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="E5" s="32" t="s">
+        <v>23</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -14323,9 +14427,7 @@
       <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>108</v>
-      </c>
+      <c r="E6" s="29"/>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -14337,9 +14439,7 @@
       <c r="B7" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
+      <c r="E7" s="32"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -14366,7 +14466,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -14383,7 +14483,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
@@ -14395,7 +14495,7 @@
       <c r="B11" s="5"/>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
@@ -14435,14 +14535,17 @@
       <c r="A16" s="3">
         <v>0.58333333333333304</v>
       </c>
+      <c r="B16" s="6" t="s">
+        <v>469</v>
+      </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>26</v>
+        <v>469</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>472</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -14452,11 +14555,14 @@
       <c r="A17" s="3">
         <v>0.60416666666666696</v>
       </c>
+      <c r="B17" s="5" t="s">
+        <v>470</v>
+      </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E17" s="32" t="s">
         <v>23</v>
@@ -14469,6 +14575,7 @@
       <c r="A18" s="3">
         <v>0.625</v>
       </c>
+      <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="31"/>
@@ -14478,6 +14585,7 @@
       <c r="A19" s="3">
         <v>0.64583333333333304</v>
       </c>
+      <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="31"/>
@@ -14487,6 +14595,7 @@
       <c r="A20" s="3">
         <v>0.66666666666666696</v>
       </c>
+      <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="31"/>
@@ -14496,10 +14605,8 @@
       <c r="A21" s="3">
         <v>0.67708333333333337</v>
       </c>
+      <c r="B21" s="5"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="E21" s="28"/>
       <c r="F21" s="5"/>
     </row>
@@ -14507,10 +14614,8 @@
       <c r="A22" s="3">
         <v>0.70833333333333304</v>
       </c>
+      <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="E22" s="28"/>
       <c r="F22" s="5"/>
     </row>
@@ -14518,8 +14623,8 @@
       <c r="A23" s="3">
         <v>0.72916666666666696</v>
       </c>
+      <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
       <c r="E23" s="28"/>
       <c r="F23" s="5"/>
     </row>
@@ -14527,8 +14632,8 @@
       <c r="A24" s="3">
         <v>0.75</v>
       </c>
+      <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
       <c r="E24" s="28"/>
       <c r="F24" s="5"/>
     </row>
@@ -14537,7 +14642,6 @@
         <v>0.76041666666666663</v>
       </c>
       <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
       <c r="E25" s="28"/>
       <c r="F25" s="5"/>
     </row>
@@ -14556,71 +14660,69 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>98</v>
+      <c r="B28" s="47" t="s">
+        <v>430</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>389</v>
+        <v>471</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>397</v>
+        <v>259</v>
+      </c>
+      <c r="F28" s="64" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="16" t="s">
-        <v>412</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>440</v>
+      <c r="B29" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>437</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>450</v>
+        <v>436</v>
+      </c>
+      <c r="F29" s="64" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>450</v>
+      <c r="B30" s="65" t="s">
+        <v>464</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>447</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="16" t="s">
-        <v>458</v>
+      <c r="F30" s="64" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="16" t="s">
-        <v>467</v>
-      </c>
+      <c r="B31" s="17"/>
       <c r="C31" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="F31" s="64" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="64" t="s">
-        <v>468</v>
-      </c>
+      <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
@@ -14660,38 +14762,48 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="91" priority="2">
+    <cfRule type="expression" dxfId="99" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="90" priority="25">
+    <cfRule type="expression" dxfId="98" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="89" priority="24">
+    <cfRule type="expression" dxfId="97" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F31 B33:F36 C32:F32">
-    <cfRule type="expression" dxfId="88" priority="4">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="96" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E7">
-    <cfRule type="expression" dxfId="87" priority="20">
+  <conditionalFormatting sqref="E4:E7">
+    <cfRule type="expression" dxfId="95" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F6 E7:F25 C16:D25">
-    <cfRule type="expression" dxfId="86" priority="11">
+  <conditionalFormatting sqref="F5:F6 E7:F15 C16:D25 E18:F25 F16:F17">
+    <cfRule type="expression" dxfId="94" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
-    <cfRule type="expression" dxfId="85" priority="1">
-      <formula>NOT(ISBLANK(B32))</formula>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="expression" dxfId="93" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16:E17">
+    <cfRule type="expression" dxfId="92" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" dxfId="91" priority="1">
+      <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14773,7 +14885,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
@@ -14867,7 +14979,7 @@
         <v>0.53125</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="31"/>
@@ -14894,7 +15006,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -14922,7 +15034,7 @@
         <v>0.625</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="31"/>
@@ -14999,26 +15111,26 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="22" t="s">
         <v>111</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -15027,10 +15139,10 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
@@ -15039,7 +15151,7 @@
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -15049,7 +15161,7 @@
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
@@ -15059,7 +15171,7 @@
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
@@ -15069,7 +15181,7 @@
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -15094,30 +15206,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="300" priority="3">
+    <cfRule type="expression" dxfId="308" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="299" priority="14">
+    <cfRule type="expression" dxfId="307" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="298" priority="15">
+    <cfRule type="expression" dxfId="306" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="297" priority="7">
+    <cfRule type="expression" dxfId="305" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="296" priority="9">
+    <cfRule type="expression" dxfId="304" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="295" priority="12">
+    <cfRule type="expression" dxfId="303" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15202,7 +15314,7 @@
       </c>
       <c r="B4" s="11"/>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -15224,10 +15336,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -15267,7 +15379,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15334,7 +15446,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -15479,7 +15591,9 @@
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="D29" s="17" t="s">
+        <v>467</v>
+      </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
     </row>
@@ -15541,27 +15655,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="84" priority="1">
+    <cfRule type="expression" dxfId="90" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="83" priority="21">
+    <cfRule type="expression" dxfId="89" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="82" priority="20">
+    <cfRule type="expression" dxfId="88" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="81" priority="19">
+    <cfRule type="expression" dxfId="87" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="80" priority="6">
+    <cfRule type="expression" dxfId="86" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15644,7 +15758,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -15666,10 +15780,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -15709,7 +15823,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15776,7 +15890,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -15924,7 +16038,7 @@
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="17" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15985,27 +16099,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="85" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="78" priority="27">
+    <cfRule type="expression" dxfId="84" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="77" priority="26">
+    <cfRule type="expression" dxfId="83" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="76" priority="3">
+    <cfRule type="expression" dxfId="82" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="75" priority="7">
+    <cfRule type="expression" dxfId="81" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16088,7 +16202,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -16107,7 +16221,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -16144,7 +16258,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16204,7 +16318,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -16337,40 +16451,44 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>465</v>
+      </c>
       <c r="C30" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="17" t="s">
+        <v>466</v>
+      </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -16418,37 +16536,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="74" priority="2">
+    <cfRule type="expression" dxfId="80" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="73" priority="31">
+    <cfRule type="expression" dxfId="79" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="72" priority="30">
+    <cfRule type="expression" dxfId="78" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="77" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="70" priority="10">
+    <cfRule type="expression" dxfId="76" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="69" priority="8">
+    <cfRule type="expression" dxfId="75" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="68" priority="14">
+    <cfRule type="expression" dxfId="74" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16531,13 +16649,16 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="B5" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -16549,6 +16670,9 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="B6" s="7" t="s">
+        <v>361</v>
+      </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
@@ -16557,6 +16681,7 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="B7" s="7"/>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -16567,6 +16692,7 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="B8" s="7"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -16579,8 +16705,9 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -16591,11 +16718,12 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="B10" s="7"/>
       <c r="C10" s="28" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F10" s="5"/>
     </row>
@@ -16603,9 +16731,10 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="B11" s="7"/>
       <c r="C11" s="28"/>
       <c r="D11" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F11" s="5"/>
     </row>
@@ -16613,6 +16742,7 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
+      <c r="B12" s="7"/>
       <c r="C12" s="28"/>
       <c r="D12" s="5"/>
       <c r="F12" s="5"/>
@@ -16621,6 +16751,7 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
+      <c r="B13" s="7"/>
       <c r="C13" s="28"/>
       <c r="D13" s="5"/>
       <c r="F13" s="5"/>
@@ -16629,6 +16760,7 @@
       <c r="A14" s="3">
         <v>0.54166666666666696</v>
       </c>
+      <c r="B14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -16748,26 +16880,26 @@
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>40</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16829,33 +16961,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:D25">
-    <cfRule type="expression" dxfId="67" priority="2">
+  <conditionalFormatting sqref="B15:D25 C4:D14">
+    <cfRule type="expression" dxfId="73" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="66" priority="36">
+    <cfRule type="expression" dxfId="72" priority="37">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="65" priority="35">
+    <cfRule type="expression" dxfId="71" priority="36">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="70" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="63" priority="14">
+    <cfRule type="expression" dxfId="69" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="62" priority="11">
+    <cfRule type="expression" dxfId="68" priority="12">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B14">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16938,16 +17075,13 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>11</v>
-      </c>
       <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
@@ -16959,11 +17093,8 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>363</v>
-      </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -16973,7 +17104,6 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B7" s="7"/>
       <c r="E7" s="32" t="s">
         <v>23</v>
       </c>
@@ -16987,7 +17117,6 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
-      <c r="B8" s="7"/>
       <c r="E8" s="28"/>
       <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
@@ -17001,9 +17130,8 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
-      <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -17012,7 +17140,6 @@
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
-      <c r="B10" s="7"/>
       <c r="C10" s="28" t="s">
         <v>13</v>
       </c>
@@ -17023,7 +17150,6 @@
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
-      <c r="B11" s="7"/>
       <c r="C11" s="28"/>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
@@ -17032,7 +17158,6 @@
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
-      <c r="B12" s="7"/>
       <c r="C12" s="28"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
@@ -17041,7 +17166,6 @@
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
-      <c r="B13" s="7"/>
       <c r="C13" s="28"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
@@ -17067,7 +17191,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -17189,39 +17313,39 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -17277,38 +17401,43 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="61" priority="8">
+  <conditionalFormatting sqref="B13:B14">
+    <cfRule type="expression" dxfId="66" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="60" priority="39">
+    <cfRule type="expression" dxfId="65" priority="40">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="59" priority="38">
+    <cfRule type="expression" dxfId="64" priority="39">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="58" priority="1">
+    <cfRule type="expression" dxfId="63" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="57" priority="2">
+    <cfRule type="expression" dxfId="62" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="56" priority="32">
+    <cfRule type="expression" dxfId="61" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="55" priority="31">
+    <cfRule type="expression" dxfId="60" priority="32">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:B13">
+    <cfRule type="expression" dxfId="59" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17392,7 +17521,7 @@
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -17415,7 +17544,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -17426,7 +17555,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
@@ -17453,7 +17582,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -17470,7 +17599,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -17482,7 +17611,7 @@
       <c r="B11" s="7"/>
       <c r="C11" s="28"/>
       <c r="D11" s="68" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="5"/>
@@ -17521,9 +17650,6 @@
       <c r="A16" s="3">
         <v>0.58333333333333304</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
@@ -17539,9 +17665,6 @@
       <c r="A17" s="3">
         <v>0.60416666666666696</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
       </c>
@@ -17556,9 +17679,6 @@
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>0.625</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -17569,7 +17689,6 @@
       <c r="A19" s="3">
         <v>0.64583333333333304</v>
       </c>
-      <c r="B19" s="5"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="36"/>
@@ -17579,7 +17698,6 @@
       <c r="A20" s="3">
         <v>0.66666666666666696</v>
       </c>
-      <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="36"/>
@@ -17589,7 +17707,6 @@
       <c r="A21" s="3">
         <v>0.67708333333333337</v>
       </c>
-      <c r="B21" s="5"/>
       <c r="C21" s="5"/>
       <c r="D21" s="6" t="s">
         <v>28</v>
@@ -17600,7 +17717,6 @@
       <c r="A22" s="3">
         <v>0.70833333333333304</v>
       </c>
-      <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5" t="s">
         <v>27</v>
@@ -17611,7 +17727,6 @@
       <c r="A23" s="3">
         <v>0.72916666666666696</v>
       </c>
-      <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="F23" s="5"/>
@@ -17620,7 +17735,6 @@
       <c r="A24" s="3">
         <v>0.75</v>
       </c>
-      <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="F24" s="5"/>
@@ -17629,7 +17743,6 @@
       <c r="A25" s="3">
         <v>0.76041666666666663</v>
       </c>
-      <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="F25" s="5"/>
@@ -17651,26 +17764,26 @@
       <c r="A28" s="15"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -17680,7 +17793,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17735,42 +17848,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="54" priority="7">
+    <cfRule type="expression" dxfId="58" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="53" priority="41">
+    <cfRule type="expression" dxfId="57" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="52" priority="40">
+    <cfRule type="expression" dxfId="56" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="51" priority="1">
+    <cfRule type="expression" dxfId="55" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="50" priority="2">
+    <cfRule type="expression" dxfId="54" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="49" priority="11">
+    <cfRule type="expression" dxfId="53" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 B15:D25">
-    <cfRule type="expression" dxfId="48" priority="34">
+  <conditionalFormatting sqref="F5:F14 B15:D16 B18:B19 B21 C17:D25 B23 B25:B26">
+    <cfRule type="expression" dxfId="52" priority="38">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="47" priority="33">
+    <cfRule type="expression" dxfId="51" priority="37">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="expression" dxfId="50" priority="4">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="expression" dxfId="49" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B22">
+    <cfRule type="expression" dxfId="48" priority="2">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24">
+    <cfRule type="expression" dxfId="47" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17853,7 +17986,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -17875,10 +18008,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -17918,7 +18051,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -17985,7 +18118,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -18114,30 +18247,30 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="16" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -18312,7 +18445,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -18334,10 +18467,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -18377,7 +18510,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18444,7 +18577,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -18573,7 +18706,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16" t="s">
@@ -18586,7 +18719,7 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="16" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -18596,7 +18729,7 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -18771,7 +18904,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -18793,10 +18926,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -18836,7 +18969,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18903,7 +19036,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -19032,7 +19165,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -19222,7 +19355,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -19244,10 +19377,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -19287,7 +19420,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19354,7 +19487,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -19501,10 +19634,10 @@
         <v>43</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
@@ -19685,7 +19818,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
@@ -19726,7 +19859,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="28"/>
       <c r="F7" s="5"/>
@@ -19788,7 +19921,7 @@
       </c>
       <c r="B13" s="5"/>
       <c r="E13" s="36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F13" s="5"/>
     </row>
@@ -19838,7 +19971,7 @@
         <v>0.625</v>
       </c>
       <c r="C18" s="43" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="36"/>
@@ -19849,7 +19982,7 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="36"/>
@@ -19890,7 +20023,7 @@
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F23" s="5"/>
     </row>
@@ -19926,67 +20059,67 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
       <c r="F31" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="19"/>
@@ -20027,22 +20160,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="294" priority="10">
+    <cfRule type="expression" dxfId="302" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="293" priority="9">
+    <cfRule type="expression" dxfId="301" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="292" priority="1">
+    <cfRule type="expression" dxfId="300" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="291" priority="7">
+    <cfRule type="expression" dxfId="299" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20126,7 +20259,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -20148,10 +20281,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -20191,7 +20324,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -20258,7 +20391,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -20585,7 +20718,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -20607,10 +20740,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -20650,7 +20783,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -20717,7 +20850,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -21035,7 +21168,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
@@ -21067,7 +21200,7 @@
       </c>
       <c r="C6" s="45"/>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -21078,7 +21211,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" s="45"/>
       <c r="E7" s="32">
@@ -21168,7 +21301,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -21280,85 +21413,85 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>91</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C29" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" s="23" t="s">
         <v>135</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E31" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="E31" s="23" t="s">
-        <v>147</v>
-      </c>
       <c r="F31" s="23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="23" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -21367,7 +21500,7 @@
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
       <c r="E33" s="23" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F33" s="19"/>
     </row>
@@ -21397,42 +21530,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="290" priority="15">
+    <cfRule type="expression" dxfId="298" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="289" priority="13">
+    <cfRule type="expression" dxfId="297" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="288" priority="30">
+    <cfRule type="expression" dxfId="296" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="287" priority="29">
+    <cfRule type="expression" dxfId="295" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="286" priority="7">
+    <cfRule type="expression" dxfId="294" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="285" priority="24">
+    <cfRule type="expression" dxfId="293" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="284" priority="20">
+    <cfRule type="expression" dxfId="292" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="283" priority="25">
+    <cfRule type="expression" dxfId="291" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21516,7 +21649,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
@@ -21548,7 +21681,7 @@
       </c>
       <c r="C7" s="28"/>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -21613,7 +21746,7 @@
         <v>0.5625</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -21650,7 +21783,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
@@ -21724,37 +21857,37 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C29" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="23" t="s">
         <v>157</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -21762,13 +21895,13 @@
       <c r="B30" s="19"/>
       <c r="C30" s="17"/>
       <c r="D30" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -21776,13 +21909,13 @@
       <c r="B31" s="19"/>
       <c r="C31" s="17"/>
       <c r="D31" s="47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -21790,11 +21923,11 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="47" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -21804,7 +21937,7 @@
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -21833,32 +21966,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="282" priority="8">
+    <cfRule type="expression" dxfId="290" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="281" priority="13">
+    <cfRule type="expression" dxfId="289" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="280" priority="12">
+    <cfRule type="expression" dxfId="288" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="279" priority="1">
+    <cfRule type="expression" dxfId="287" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="278" priority="4">
+    <cfRule type="expression" dxfId="286" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="277" priority="7">
+    <cfRule type="expression" dxfId="285" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21958,7 +22091,7 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -22036,7 +22169,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -22158,16 +22291,16 @@
       <c r="A29" s="11"/>
       <c r="B29" s="19"/>
       <c r="C29" s="23" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22175,13 +22308,13 @@
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="23" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22190,10 +22323,10 @@
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="23" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22203,7 +22336,7 @@
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
       <c r="F32" s="23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22213,7 +22346,7 @@
       <c r="D33" s="19"/>
       <c r="E33" s="19"/>
       <c r="F33" s="23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22242,52 +22375,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="276" priority="22">
+    <cfRule type="expression" dxfId="284" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="275" priority="23">
+    <cfRule type="expression" dxfId="283" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="274" priority="45">
+    <cfRule type="expression" dxfId="282" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="273" priority="44">
+    <cfRule type="expression" dxfId="281" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="272" priority="1">
+    <cfRule type="expression" dxfId="280" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="271" priority="35">
+    <cfRule type="expression" dxfId="279" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="270" priority="36">
+    <cfRule type="expression" dxfId="278" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="269" priority="16">
+    <cfRule type="expression" dxfId="277" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="268" priority="34">
+    <cfRule type="expression" dxfId="276" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="267" priority="5">
+    <cfRule type="expression" dxfId="275" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22371,7 +22504,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E4" s="33"/>
       <c r="H4" s="7" t="s">
@@ -22386,7 +22519,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="6" t="s">
@@ -22440,7 +22573,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="5"/>
@@ -22451,7 +22584,7 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="5"/>
@@ -22611,31 +22744,31 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="22" t="s">
         <v>179</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>181</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22645,7 +22778,7 @@
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22655,7 +22788,7 @@
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
       <c r="F31" s="23" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -22700,47 +22833,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="266" priority="16">
+    <cfRule type="expression" dxfId="274" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="265" priority="19">
+    <cfRule type="expression" dxfId="273" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="264" priority="18">
+    <cfRule type="expression" dxfId="272" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="263" priority="1">
+    <cfRule type="expression" dxfId="271" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="262" priority="15">
+    <cfRule type="expression" dxfId="270" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="261" priority="12">
+    <cfRule type="expression" dxfId="269" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="260" priority="11">
+    <cfRule type="expression" dxfId="268" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="259" priority="14">
+    <cfRule type="expression" dxfId="267" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="258" priority="5">
+    <cfRule type="expression" dxfId="266" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22824,7 +22957,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>10</v>
@@ -22835,7 +22968,7 @@
         <v>0.375</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>24</v>
@@ -22856,7 +22989,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -22868,7 +23001,7 @@
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -22899,7 +23032,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="30"/>
@@ -22910,7 +23043,7 @@
         <v>0.45833333333333398</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="31"/>
@@ -22961,7 +23094,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -23079,30 +23212,30 @@
         <v>32</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="23" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="23" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -23163,32 +23296,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="257" priority="2">
+    <cfRule type="expression" dxfId="265" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="256" priority="4">
+    <cfRule type="expression" dxfId="264" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="255" priority="16">
+    <cfRule type="expression" dxfId="263" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="254" priority="15">
+    <cfRule type="expression" dxfId="262" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="253" priority="1">
+    <cfRule type="expression" dxfId="261" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="252" priority="7">
+    <cfRule type="expression" dxfId="260" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82CAA52-9F1C-430E-8626-3390C3C054F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498FFF9E-51F0-4503-B8B0-B49BD1CE1ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="25" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="473">
   <si>
     <t>Week</t>
   </si>
@@ -1508,9 +1508,6 @@
   </si>
   <si>
     <t>Lokaal 303</t>
-  </si>
-  <si>
-    <t>Is er nog communicatie?</t>
   </si>
   <si>
     <t>Creatief &amp; Ondernemend</t>
@@ -1844,7 +1841,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="313">
+  <dxfs count="307">
     <dxf>
       <font>
         <color theme="1"/>
@@ -2320,6 +2317,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2360,6 +2381,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2424,6 +2455,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2434,6 +2489,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2478,6 +2563,30 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color theme="1"/>
       </font>
@@ -2518,178 +2627,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5446,47 +5383,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="259" priority="17">
+    <cfRule type="expression" dxfId="253" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="258" priority="25">
+    <cfRule type="expression" dxfId="252" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="257" priority="24">
+    <cfRule type="expression" dxfId="251" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="256" priority="5">
+    <cfRule type="expression" dxfId="250" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="255" priority="9">
+    <cfRule type="expression" dxfId="249" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="254" priority="8">
+    <cfRule type="expression" dxfId="248" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="253" priority="11">
+    <cfRule type="expression" dxfId="247" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="252" priority="15">
+    <cfRule type="expression" dxfId="246" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="251" priority="2">
+    <cfRule type="expression" dxfId="245" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5945,42 +5882,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="250" priority="15">
+    <cfRule type="expression" dxfId="244" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="249" priority="10">
+    <cfRule type="expression" dxfId="243" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="248" priority="24">
+    <cfRule type="expression" dxfId="242" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="247" priority="23">
+    <cfRule type="expression" dxfId="241" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="246" priority="1">
+    <cfRule type="expression" dxfId="240" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="245" priority="7">
+    <cfRule type="expression" dxfId="239" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="244" priority="3">
+    <cfRule type="expression" dxfId="238" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="243" priority="14">
+    <cfRule type="expression" dxfId="237" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6419,47 +6356,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="242" priority="10">
+    <cfRule type="expression" dxfId="236" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="241" priority="1">
+    <cfRule type="expression" dxfId="235" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="240" priority="25">
+    <cfRule type="expression" dxfId="234" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="239" priority="24">
+    <cfRule type="expression" dxfId="233" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="238" priority="4">
+    <cfRule type="expression" dxfId="232" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="237" priority="3">
+    <cfRule type="expression" dxfId="231" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="236" priority="6">
+    <cfRule type="expression" dxfId="230" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="235" priority="9">
+    <cfRule type="expression" dxfId="229" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="234" priority="11">
+    <cfRule type="expression" dxfId="228" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6922,57 +6859,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="233" priority="36">
+    <cfRule type="expression" dxfId="227" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="232" priority="51">
+    <cfRule type="expression" dxfId="226" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="231" priority="50">
+    <cfRule type="expression" dxfId="225" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="230" priority="9">
+    <cfRule type="expression" dxfId="224" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="229" priority="28">
+    <cfRule type="expression" dxfId="223" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="228" priority="11">
+    <cfRule type="expression" dxfId="222" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="227" priority="24">
+    <cfRule type="expression" dxfId="221" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="226" priority="31">
+    <cfRule type="expression" dxfId="220" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="225" priority="7">
+    <cfRule type="expression" dxfId="219" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="224" priority="35">
+    <cfRule type="expression" dxfId="218" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="223" priority="1">
+    <cfRule type="expression" dxfId="217" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7404,59 +7341,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="222" priority="35">
+    <cfRule type="expression" dxfId="216" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="221" priority="42">
+    <cfRule type="expression" dxfId="215" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="220" priority="54">
+    <cfRule type="expression" dxfId="214" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="219" priority="53">
+    <cfRule type="expression" dxfId="213" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="218" priority="5">
+    <cfRule type="expression" dxfId="212" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="217" priority="30">
+    <cfRule type="expression" dxfId="211" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="216" priority="33">
+    <cfRule type="expression" dxfId="210" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="215" priority="37">
+    <cfRule type="expression" dxfId="209" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="214" priority="41">
+    <cfRule type="expression" dxfId="208" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="213" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="211" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="210" priority="1">
+    <cfRule type="expression" dxfId="204" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7922,57 +7859,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="209" priority="1">
+    <cfRule type="expression" dxfId="203" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="208" priority="18">
+    <cfRule type="expression" dxfId="202" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="207" priority="41">
+    <cfRule type="expression" dxfId="201" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="206" priority="40">
+    <cfRule type="expression" dxfId="200" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="205" priority="13">
+    <cfRule type="expression" dxfId="199" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="204" priority="3">
+    <cfRule type="expression" dxfId="198" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="203" priority="5">
+    <cfRule type="expression" dxfId="197" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="202" priority="19">
+    <cfRule type="expression" dxfId="196" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="201" priority="7">
+    <cfRule type="expression" dxfId="195" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="200" priority="27">
+    <cfRule type="expression" dxfId="194" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="199" priority="8">
+    <cfRule type="expression" dxfId="193" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8432,32 +8369,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="198" priority="21">
+    <cfRule type="expression" dxfId="192" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="197" priority="43">
+    <cfRule type="expression" dxfId="191" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="196" priority="42">
+    <cfRule type="expression" dxfId="190" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="195" priority="1">
+    <cfRule type="expression" dxfId="189" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="194" priority="16">
+    <cfRule type="expression" dxfId="188" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="193" priority="24">
+    <cfRule type="expression" dxfId="187" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8873,32 +8810,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="192" priority="30">
+    <cfRule type="expression" dxfId="186" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="191" priority="29">
+    <cfRule type="expression" dxfId="185" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="190" priority="16">
+    <cfRule type="expression" dxfId="184" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="189" priority="1">
+    <cfRule type="expression" dxfId="183" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="188" priority="4">
+    <cfRule type="expression" dxfId="182" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="187" priority="5">
+    <cfRule type="expression" dxfId="181" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9308,32 +9245,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="186" priority="39">
+    <cfRule type="expression" dxfId="180" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="185" priority="38">
+    <cfRule type="expression" dxfId="179" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="184" priority="20">
+    <cfRule type="expression" dxfId="178" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="183" priority="1">
+    <cfRule type="expression" dxfId="177" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="182" priority="3">
+    <cfRule type="expression" dxfId="176" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="181" priority="2">
+    <cfRule type="expression" dxfId="175" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9753,37 +9690,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="180" priority="18">
+    <cfRule type="expression" dxfId="174" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="179" priority="2">
+    <cfRule type="expression" dxfId="173" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="178" priority="32">
+    <cfRule type="expression" dxfId="172" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="177" priority="31">
+    <cfRule type="expression" dxfId="171" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="176" priority="5">
+    <cfRule type="expression" dxfId="170" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="175" priority="1">
+    <cfRule type="expression" dxfId="169" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="174" priority="3">
+    <cfRule type="expression" dxfId="168" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10199,22 +10136,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="312" priority="14">
+    <cfRule type="expression" dxfId="306" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="311" priority="6">
+    <cfRule type="expression" dxfId="305" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="310" priority="15">
+    <cfRule type="expression" dxfId="304" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="309" priority="1">
+    <cfRule type="expression" dxfId="303" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10612,22 +10549,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="173" priority="32">
+    <cfRule type="expression" dxfId="167" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="172" priority="31">
+    <cfRule type="expression" dxfId="166" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="171" priority="12">
+    <cfRule type="expression" dxfId="165" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="170" priority="1">
+    <cfRule type="expression" dxfId="164" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10993,22 +10930,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="169" priority="17">
+    <cfRule type="expression" dxfId="163" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="168" priority="16">
+    <cfRule type="expression" dxfId="162" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="167" priority="2">
+    <cfRule type="expression" dxfId="161" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="166" priority="1">
+    <cfRule type="expression" dxfId="160" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11443,47 +11380,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="165" priority="32">
+    <cfRule type="expression" dxfId="159" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="164" priority="31">
+    <cfRule type="expression" dxfId="158" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="163" priority="1">
+    <cfRule type="expression" dxfId="157" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="162" priority="3">
+    <cfRule type="expression" dxfId="156" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="161" priority="5">
+    <cfRule type="expression" dxfId="155" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="160" priority="12">
+    <cfRule type="expression" dxfId="154" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="159" priority="18">
+    <cfRule type="expression" dxfId="153" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="158" priority="27">
+    <cfRule type="expression" dxfId="152" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="157" priority="33">
+    <cfRule type="expression" dxfId="151" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11914,47 +11851,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="156" priority="12">
+    <cfRule type="expression" dxfId="150" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="155" priority="29">
+    <cfRule type="expression" dxfId="149" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="154" priority="28">
+    <cfRule type="expression" dxfId="148" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="153" priority="27">
+    <cfRule type="expression" dxfId="147" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="152" priority="1">
+    <cfRule type="expression" dxfId="146" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="151" priority="3">
+    <cfRule type="expression" dxfId="145" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="150" priority="9">
+    <cfRule type="expression" dxfId="144" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="149" priority="24">
+    <cfRule type="expression" dxfId="143" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="148" priority="30">
+    <cfRule type="expression" dxfId="142" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12389,52 +12326,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="147" priority="4">
+    <cfRule type="expression" dxfId="141" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="146" priority="27">
+    <cfRule type="expression" dxfId="140" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="145" priority="26">
+    <cfRule type="expression" dxfId="139" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="144" priority="1">
+    <cfRule type="expression" dxfId="138" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="143" priority="2">
+    <cfRule type="expression" dxfId="137" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="142" priority="28">
+    <cfRule type="expression" dxfId="136" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="141" priority="5">
+    <cfRule type="expression" dxfId="135" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="140" priority="8">
+    <cfRule type="expression" dxfId="134" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="139" priority="18">
+    <cfRule type="expression" dxfId="133" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="138" priority="22">
+    <cfRule type="expression" dxfId="132" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12863,47 +12800,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="137" priority="13">
+    <cfRule type="expression" dxfId="131" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="136" priority="22">
+    <cfRule type="expression" dxfId="130" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="135" priority="21">
+    <cfRule type="expression" dxfId="129" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="134" priority="1">
+    <cfRule type="expression" dxfId="128" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="133" priority="3">
+    <cfRule type="expression" dxfId="127" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="132" priority="5">
+    <cfRule type="expression" dxfId="126" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="131" priority="8">
+    <cfRule type="expression" dxfId="125" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="130" priority="17">
+    <cfRule type="expression" dxfId="124" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="129" priority="23">
+    <cfRule type="expression" dxfId="123" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13326,52 +13263,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="128" priority="5">
+    <cfRule type="expression" dxfId="122" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="127" priority="28">
+    <cfRule type="expression" dxfId="121" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="126" priority="27">
+    <cfRule type="expression" dxfId="120" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="125" priority="1">
+    <cfRule type="expression" dxfId="119" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="124" priority="3">
+    <cfRule type="expression" dxfId="118" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="123" priority="29">
+    <cfRule type="expression" dxfId="117" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="122" priority="22">
+    <cfRule type="expression" dxfId="116" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="121" priority="8">
+    <cfRule type="expression" dxfId="115" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="120" priority="19">
+    <cfRule type="expression" dxfId="114" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="119" priority="23">
+    <cfRule type="expression" dxfId="113" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13800,47 +13737,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="118" priority="11">
+    <cfRule type="expression" dxfId="112" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="117" priority="22">
+    <cfRule type="expression" dxfId="111" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="116" priority="21">
+    <cfRule type="expression" dxfId="110" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="115" priority="1">
+    <cfRule type="expression" dxfId="109" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="114" priority="3">
+    <cfRule type="expression" dxfId="108" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="113" priority="23">
+    <cfRule type="expression" dxfId="107" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="112" priority="5">
+    <cfRule type="expression" dxfId="106" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="111" priority="7">
+    <cfRule type="expression" dxfId="105" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="110" priority="17">
+    <cfRule type="expression" dxfId="104" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14268,52 +14205,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="109" priority="6">
+    <cfRule type="expression" dxfId="103" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="108" priority="27">
+    <cfRule type="expression" dxfId="102" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="107" priority="26">
+    <cfRule type="expression" dxfId="101" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="106" priority="1">
+    <cfRule type="expression" dxfId="100" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="105" priority="4">
+    <cfRule type="expression" dxfId="99" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="104" priority="28">
+    <cfRule type="expression" dxfId="98" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="103" priority="21">
+    <cfRule type="expression" dxfId="97" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="102" priority="9">
+    <cfRule type="expression" dxfId="96" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="101" priority="19">
+    <cfRule type="expression" dxfId="95" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="100" priority="22">
+    <cfRule type="expression" dxfId="94" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14397,7 +14334,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>360</v>
@@ -14468,9 +14405,6 @@
       <c r="C9" s="29" t="s">
         <v>449</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
     </row>
@@ -14482,9 +14416,6 @@
       <c r="C10" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>354</v>
-      </c>
       <c r="E10" s="31"/>
       <c r="F10" s="5"/>
     </row>
@@ -14494,9 +14425,6 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="28"/>
-      <c r="D11" s="5" t="s">
-        <v>357</v>
-      </c>
       <c r="E11" s="31"/>
       <c r="F11" s="5"/>
     </row>
@@ -14506,7 +14434,6 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="28"/>
-      <c r="D12" s="5"/>
       <c r="E12" s="31"/>
       <c r="F12" s="5"/>
     </row>
@@ -14516,7 +14443,6 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="28"/>
-      <c r="D13" s="5"/>
       <c r="E13" s="31"/>
       <c r="F13" s="5"/>
     </row>
@@ -14545,7 +14471,7 @@
         <v>469</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -14663,11 +14589,11 @@
       <c r="B28" s="47" t="s">
         <v>430</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>395</v>
+      <c r="C28" s="47" t="s">
+        <v>437</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>259</v>
@@ -14681,12 +14607,10 @@
       <c r="B29" s="22" t="s">
         <v>463</v>
       </c>
-      <c r="C29" s="47" t="s">
-        <v>437</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>473</v>
-      </c>
+      <c r="C29" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="D29" s="17"/>
       <c r="E29" s="19" t="s">
         <v>436</v>
       </c>
@@ -14700,7 +14624,7 @@
         <v>464</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -14711,9 +14635,7 @@
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="16" t="s">
-        <v>454</v>
-      </c>
+      <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="64" t="s">
@@ -14762,47 +14684,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="99" priority="5">
+    <cfRule type="expression" dxfId="93" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="98" priority="28">
+    <cfRule type="expression" dxfId="92" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="97" priority="27">
+    <cfRule type="expression" dxfId="91" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="96" priority="4">
+    <cfRule type="expression" dxfId="90" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E7">
-    <cfRule type="expression" dxfId="95" priority="23">
+    <cfRule type="expression" dxfId="89" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F6 E7:F15 C16:D25 E18:F25 F16:F17">
-    <cfRule type="expression" dxfId="94" priority="14">
+  <conditionalFormatting sqref="E7:F25">
+    <cfRule type="expression" dxfId="88" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="expression" dxfId="93" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E16:E17">
-    <cfRule type="expression" dxfId="92" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
-    <cfRule type="expression" dxfId="91" priority="1">
+  <conditionalFormatting sqref="F5:F6 C16:D25">
+    <cfRule type="expression" dxfId="87" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15206,30 +15118,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="308" priority="3">
+    <cfRule type="expression" dxfId="302" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="307" priority="14">
+    <cfRule type="expression" dxfId="301" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="306" priority="15">
+    <cfRule type="expression" dxfId="300" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="305" priority="7">
+    <cfRule type="expression" dxfId="299" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="304" priority="9">
+    <cfRule type="expression" dxfId="298" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="303" priority="12">
+    <cfRule type="expression" dxfId="297" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15655,27 +15567,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="90" priority="1">
+    <cfRule type="expression" dxfId="86" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="89" priority="21">
+    <cfRule type="expression" dxfId="85" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="88" priority="20">
+    <cfRule type="expression" dxfId="84" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="87" priority="19">
+    <cfRule type="expression" dxfId="83" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="86" priority="6">
+    <cfRule type="expression" dxfId="82" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16099,27 +16011,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="85" priority="1">
+    <cfRule type="expression" dxfId="81" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="84" priority="27">
+    <cfRule type="expression" dxfId="80" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="83" priority="26">
+    <cfRule type="expression" dxfId="79" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="82" priority="3">
+    <cfRule type="expression" dxfId="78" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="81" priority="7">
+    <cfRule type="expression" dxfId="77" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16536,37 +16448,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="80" priority="2">
+    <cfRule type="expression" dxfId="76" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="79" priority="31">
+    <cfRule type="expression" dxfId="75" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="78" priority="30">
+    <cfRule type="expression" dxfId="74" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="77" priority="1">
+    <cfRule type="expression" dxfId="73" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="76" priority="10">
+    <cfRule type="expression" dxfId="72" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="75" priority="8">
+    <cfRule type="expression" dxfId="71" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="74" priority="14">
+    <cfRule type="expression" dxfId="70" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16961,38 +16873,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B15:D25 C4:D14">
-    <cfRule type="expression" dxfId="73" priority="3">
+  <conditionalFormatting sqref="B5:B14">
+    <cfRule type="expression" dxfId="69" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="72" priority="37">
+    <cfRule type="expression" dxfId="68" priority="37">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="71" priority="36">
+    <cfRule type="expression" dxfId="67" priority="36">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="70" priority="2">
+    <cfRule type="expression" dxfId="66" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C4:D14 B15:D25">
+    <cfRule type="expression" dxfId="65" priority="3">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="69" priority="15">
+    <cfRule type="expression" dxfId="64" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="68" priority="12">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="67" priority="1">
+    <cfRule type="expression" dxfId="63" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17401,43 +17313,38 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B13:B14">
-    <cfRule type="expression" dxfId="66" priority="9">
+  <conditionalFormatting sqref="B5:B14">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="65" priority="40">
+    <cfRule type="expression" dxfId="61" priority="40">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="64" priority="39">
+    <cfRule type="expression" dxfId="60" priority="39">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="63" priority="2">
+    <cfRule type="expression" dxfId="59" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="62" priority="3">
+    <cfRule type="expression" dxfId="58" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="61" priority="33">
+    <cfRule type="expression" dxfId="57" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="60" priority="32">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="59" priority="1">
+    <cfRule type="expression" dxfId="56" priority="32">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17848,62 +17755,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="58" priority="11">
+    <cfRule type="expression" dxfId="55" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B17:B26">
+    <cfRule type="expression" dxfId="54" priority="1">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="57" priority="45">
+    <cfRule type="expression" dxfId="53" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="56" priority="44">
+    <cfRule type="expression" dxfId="52" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="55" priority="5">
+    <cfRule type="expression" dxfId="51" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="54" priority="6">
+    <cfRule type="expression" dxfId="50" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="53" priority="15">
+    <cfRule type="expression" dxfId="49" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 B15:D16 B18:B19 B21 C17:D25 B23 B25:B26">
-    <cfRule type="expression" dxfId="52" priority="38">
+  <conditionalFormatting sqref="F5:F14 B15:D16 C17:D25">
+    <cfRule type="expression" dxfId="48" priority="38">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="51" priority="37">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="expression" dxfId="50" priority="4">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="expression" dxfId="49" priority="3">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22">
-    <cfRule type="expression" dxfId="48" priority="2">
-      <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="expression" dxfId="47" priority="1">
+    <cfRule type="expression" dxfId="47" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20160,22 +20052,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="302" priority="10">
+    <cfRule type="expression" dxfId="296" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="301" priority="9">
+    <cfRule type="expression" dxfId="295" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="300" priority="1">
+    <cfRule type="expression" dxfId="294" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="299" priority="7">
+    <cfRule type="expression" dxfId="293" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21530,42 +21422,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="298" priority="15">
+    <cfRule type="expression" dxfId="292" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="297" priority="13">
+    <cfRule type="expression" dxfId="291" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="296" priority="30">
+    <cfRule type="expression" dxfId="290" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="295" priority="29">
+    <cfRule type="expression" dxfId="289" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="294" priority="7">
+    <cfRule type="expression" dxfId="288" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="293" priority="24">
+    <cfRule type="expression" dxfId="287" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="292" priority="20">
+    <cfRule type="expression" dxfId="286" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="291" priority="25">
+    <cfRule type="expression" dxfId="285" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21966,32 +21858,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="290" priority="8">
+    <cfRule type="expression" dxfId="284" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="289" priority="13">
+    <cfRule type="expression" dxfId="283" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="288" priority="12">
+    <cfRule type="expression" dxfId="282" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="287" priority="1">
+    <cfRule type="expression" dxfId="281" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="286" priority="4">
+    <cfRule type="expression" dxfId="280" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="285" priority="7">
+    <cfRule type="expression" dxfId="279" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22375,52 +22267,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="284" priority="22">
+    <cfRule type="expression" dxfId="278" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="283" priority="23">
+    <cfRule type="expression" dxfId="277" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="282" priority="45">
+    <cfRule type="expression" dxfId="276" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="281" priority="44">
+    <cfRule type="expression" dxfId="275" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="280" priority="1">
+    <cfRule type="expression" dxfId="274" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="279" priority="35">
+    <cfRule type="expression" dxfId="273" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="278" priority="36">
+    <cfRule type="expression" dxfId="272" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="277" priority="16">
+    <cfRule type="expression" dxfId="271" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="276" priority="34">
+    <cfRule type="expression" dxfId="270" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="275" priority="5">
+    <cfRule type="expression" dxfId="269" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22833,47 +22725,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="274" priority="16">
+    <cfRule type="expression" dxfId="268" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="273" priority="19">
+    <cfRule type="expression" dxfId="267" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="272" priority="18">
+    <cfRule type="expression" dxfId="266" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="271" priority="1">
+    <cfRule type="expression" dxfId="265" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="270" priority="15">
+    <cfRule type="expression" dxfId="264" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="269" priority="12">
+    <cfRule type="expression" dxfId="263" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="268" priority="11">
+    <cfRule type="expression" dxfId="262" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="267" priority="14">
+    <cfRule type="expression" dxfId="261" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="266" priority="5">
+    <cfRule type="expression" dxfId="260" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23296,32 +23188,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="265" priority="2">
+    <cfRule type="expression" dxfId="259" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="264" priority="4">
+    <cfRule type="expression" dxfId="258" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="263" priority="16">
+    <cfRule type="expression" dxfId="257" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="262" priority="15">
+    <cfRule type="expression" dxfId="256" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="261" priority="1">
+    <cfRule type="expression" dxfId="255" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="260" priority="7">
+    <cfRule type="expression" dxfId="254" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498FFF9E-51F0-4503-B8B0-B49BD1CE1ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31E8304-21AA-41F1-90DB-4C4066B057CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="25" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="485">
   <si>
     <t>Week</t>
   </si>
@@ -1514,6 +1514,48 @@
   </si>
   <si>
     <t>Checken crossmedia's punten</t>
+  </si>
+  <si>
+    <t>Designgeschiedenis: les thema 4</t>
+  </si>
+  <si>
+    <t>Van 18.15—20.30u in auditorium A3. Meer info zie aparte mededeling. De les in de namiddag valt weg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Afsluitend panel gesprek in het kader van het vak (Graphic) Designgeschiedenis. Iedereen aanwezig.
+</t>
+  </si>
+  <si>
+    <t>Laatste les, thema 5.
+In deze les overlopen we ook kort de examenleerstof en bekijken we enkele potentiële examenvragen.</t>
+  </si>
+  <si>
+    <t>Examen designgeschiedenis</t>
+  </si>
+  <si>
+    <t>Let op Plus 2 vraag is enkel geldig als je een (half) A4 pdf document doorstuurt als bijlage
+met korte beschrijving, foto van de cover van het boek en je eigen naam. Indien niet in orde, geen plus 2 uiteraard!
+Deadline 14 Mei voor 18.00u.</t>
+  </si>
+  <si>
+    <t>Voor 18:00 met korte beschrijving, foto van de cover van het boek en je eigen naam. Indien niet in orde, geen plus 2 uiteraard!</t>
+  </si>
+  <si>
+    <t>Tegen morgen moet book ingediend zijn design geschiedenis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+BREAK OUT 1 : Creatief én slim ondernemen: Haal meer uit je auteursrechten! - Creative shelter – Jorg Raman – C23 -  14:45 tot 15:45 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+BREAK OUT 2: AI &amp; auteursrecht - consey.legal - Kris Seyen - C 23 - 16:00 tot 16:50 </t>
+  </si>
+  <si>
+    <t>Lokaal C23 - 9:20</t>
+  </si>
+  <si>
+    <t>minecrafft x McDo dus nice fit</t>
   </si>
 </sst>
 </file>
@@ -2527,6 +2569,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
       </font>
@@ -2539,16 +2591,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -14592,9 +14634,7 @@
       <c r="C28" s="47" t="s">
         <v>437</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>472</v>
-      </c>
+      <c r="D28" s="17"/>
       <c r="E28" s="16" t="s">
         <v>259</v>
       </c>
@@ -14614,7 +14654,7 @@
       <c r="E29" s="19" t="s">
         <v>436</v>
       </c>
-      <c r="F29" s="64" t="s">
+      <c r="F29" s="65" t="s">
         <v>447</v>
       </c>
     </row>
@@ -14627,7 +14667,9 @@
         <v>454</v>
       </c>
       <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
+      <c r="E30" s="16" t="s">
+        <v>481</v>
+      </c>
       <c r="F30" s="64" t="s">
         <v>455</v>
       </c>
@@ -14637,7 +14679,9 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="E31" s="16" t="s">
+        <v>482</v>
+      </c>
       <c r="F31" s="64" t="s">
         <v>468</v>
       </c>
@@ -14647,8 +14691,12 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="E32" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
@@ -14656,7 +14704,9 @@
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="F33" s="16" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
@@ -14719,6 +14769,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -16121,9 +16172,6 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="H5" s="11" t="s">
         <v>22</v>
       </c>
@@ -16132,21 +16180,11 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
       </c>
@@ -16156,8 +16194,6 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
@@ -16169,45 +16205,26 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>449</v>
-      </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -16223,111 +16240,51 @@
       <c r="A16" s="3">
         <v>0.58333333333333304</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>0.60416666666666696</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>0.625</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>0.64583333333333304</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>0.66666666666666696</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>0.67708333333333337</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>0.70833333333333304</v>
       </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>0.72916666666666696</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>0.75</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>0.76041666666666663</v>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
@@ -16447,19 +16404,19 @@
       <c r="F36" s="17"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="76" priority="2">
+  <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="76" priority="31">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
+    <cfRule type="expression" dxfId="75" priority="30">
+      <formula>B3 = TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:F25">
+    <cfRule type="expression" dxfId="74" priority="2">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="75" priority="31">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="74" priority="30">
-      <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
@@ -16820,7 +16777,9 @@
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
+      <c r="D30" s="17" t="s">
+        <v>473</v>
+      </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>
@@ -17260,7 +17219,9 @@
         <v>433</v>
       </c>
       <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
+      <c r="D30" s="17" t="s">
+        <v>475</v>
+      </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>
@@ -17268,7 +17229,9 @@
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
+      <c r="D31" s="17" t="s">
+        <v>474</v>
+      </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
     </row>
@@ -17698,7 +17661,9 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="C30" s="17" t="s">
+        <v>480</v>
+      </c>
       <c r="D30" s="17" t="s">
         <v>441</v>
       </c>
@@ -17709,7 +17674,9 @@
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
+      <c r="D31" s="17" t="s">
+        <v>476</v>
+      </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
     </row>
@@ -17717,7 +17684,9 @@
       <c r="A32" s="11"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
+      <c r="D32" s="17" t="s">
+        <v>479</v>
+      </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
     </row>
@@ -19254,12 +19223,6 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="H5" s="11" t="s">
         <v>22</v>
       </c>
@@ -19268,25 +19231,11 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
       </c>
@@ -19296,9 +19245,6 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
@@ -19310,50 +19256,26 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="29" t="s">
-        <v>449</v>
-      </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -19369,125 +19291,51 @@
       <c r="A16" s="3">
         <v>0.58333333333333304</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>0.60416666666666696</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>0.625</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>0.64583333333333304</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>0.66666666666666696</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>0.67708333333333337</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>0.70833333333333304</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>0.72916666666666696</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>0.75</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>0.76041666666666663</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
@@ -19532,7 +19380,9 @@
         <v>445</v>
       </c>
       <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="F29" s="19" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
@@ -19540,7 +19390,9 @@
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="F30" s="19" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -19616,7 +19468,7 @@
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D13">
+  <conditionalFormatting sqref="C4:D13 B5:F25">
     <cfRule type="expression" dxfId="17" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31E8304-21AA-41F1-90DB-4C4066B057CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9C030F-295E-4F52-9DB8-5C5F0ACF1938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14635,7 +14635,7 @@
         <v>437</v>
       </c>
       <c r="D28" s="17"/>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="22" t="s">
         <v>259</v>
       </c>
       <c r="F28" s="64" t="s">
@@ -14651,7 +14651,7 @@
         <v>447</v>
       </c>
       <c r="D29" s="17"/>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="22" t="s">
         <v>436</v>
       </c>
       <c r="F29" s="65" t="s">
@@ -14667,7 +14667,7 @@
         <v>454</v>
       </c>
       <c r="D30" s="17"/>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="22" t="s">
         <v>481</v>
       </c>
       <c r="F30" s="64" t="s">
@@ -14679,7 +14679,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="22" t="s">
         <v>482</v>
       </c>
       <c r="F31" s="64" t="s">
@@ -14691,7 +14691,7 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="22" t="s">
         <v>483</v>
       </c>
       <c r="F32" s="16" t="s">

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9C030F-295E-4F52-9DB8-5C5F0ACF1938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F09795-BE6E-4E04-A366-145B18906374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="23" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="509">
   <si>
     <t>Week</t>
   </si>
@@ -1556,6 +1556,78 @@
   </si>
   <si>
     <t>minecrafft x McDo dus nice fit</t>
+  </si>
+  <si>
+    <t>Examen</t>
+  </si>
+  <si>
+    <t>Design Geschiedenis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:00 - 11:00 - A2 </t>
+  </si>
+  <si>
+    <t>09:00 - 11:45 - A2</t>
+  </si>
+  <si>
+    <t>Tekenen op locatie (skatepark - bij regen krijgen jullie een bericht met de nieuwe locatie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de les perspectief valt daardoor weg voor de groepen A en B (er is een huistaak geformuleerd voor de groep C en D zie FAQ) </t>
+  </si>
+  <si>
+    <t>Op 12 mei ben ik de hele dag beschikbaar (lesuren) voor feedback en inhaalmogelijkheden van de gemiste lessen alsook voor de begeleiding van de opdracht Diorama - verdieping.</t>
+  </si>
+  <si>
+    <t>Inschrijven lijst bourse de commerce</t>
+  </si>
+  <si>
+    <t>Alles in apparte files steken enzo</t>
+  </si>
+  <si>
+    <t>Actoren systeem beginnen</t>
+  </si>
+  <si>
+    <t>Kaart met icoontjes</t>
+  </si>
+  <si>
+    <t>Actoren manager + order changen</t>
+  </si>
+  <si>
+    <t>Alles in functions steken voor handig te integraten met website uiteindelijk</t>
+  </si>
+  <si>
+    <t>Google doc updaten</t>
+  </si>
+  <si>
+    <t>Website mergen enzo!</t>
+  </si>
+  <si>
+    <t>Website indienen?</t>
+  </si>
+  <si>
+    <t>Elke ding 5 seconden maken</t>
+  </si>
+  <si>
+    <t>Scene 1 &amp; 2 maken</t>
+  </si>
+  <si>
+    <t>Scene 3 &amp; 4 maken</t>
+  </si>
+  <si>
+    <t>Scene 5 &amp; 6 maken</t>
+  </si>
+  <si>
+    <t>Scene 7 &amp; 8 maken</t>
+  </si>
+  <si>
+    <t>Scene 9 &amp; 10 maken</t>
+  </si>
+  <si>
+    <t>Scene 10 &amp; 11 maken</t>
+  </si>
+  <si>
+    <t>Scene 12 &amp; 13 maken</t>
   </si>
 </sst>
 </file>
@@ -1883,7 +1955,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="307">
+  <dxfs count="312">
     <dxf>
       <font>
         <color theme="1"/>
@@ -1987,6 +2059,16 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
       </font>
@@ -2053,6 +2135,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2591,6 +2683,27 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5425,47 +5538,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="253" priority="17">
+    <cfRule type="expression" dxfId="258" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="252" priority="25">
+    <cfRule type="expression" dxfId="257" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="251" priority="24">
+    <cfRule type="expression" dxfId="256" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="250" priority="5">
+    <cfRule type="expression" dxfId="255" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="249" priority="9">
+    <cfRule type="expression" dxfId="254" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="248" priority="8">
+    <cfRule type="expression" dxfId="253" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="247" priority="11">
+    <cfRule type="expression" dxfId="252" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="246" priority="15">
+    <cfRule type="expression" dxfId="251" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="245" priority="2">
+    <cfRule type="expression" dxfId="250" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5924,42 +6037,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="244" priority="15">
+    <cfRule type="expression" dxfId="249" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="243" priority="10">
+    <cfRule type="expression" dxfId="248" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="242" priority="24">
+    <cfRule type="expression" dxfId="247" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="241" priority="23">
+    <cfRule type="expression" dxfId="246" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="240" priority="1">
+    <cfRule type="expression" dxfId="245" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="239" priority="7">
+    <cfRule type="expression" dxfId="244" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="238" priority="3">
+    <cfRule type="expression" dxfId="243" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="237" priority="14">
+    <cfRule type="expression" dxfId="242" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6398,47 +6511,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="236" priority="10">
+    <cfRule type="expression" dxfId="241" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="235" priority="1">
+    <cfRule type="expression" dxfId="240" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="234" priority="25">
+    <cfRule type="expression" dxfId="239" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="233" priority="24">
+    <cfRule type="expression" dxfId="238" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="232" priority="4">
+    <cfRule type="expression" dxfId="237" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="231" priority="3">
+    <cfRule type="expression" dxfId="236" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="230" priority="6">
+    <cfRule type="expression" dxfId="235" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="229" priority="9">
+    <cfRule type="expression" dxfId="234" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="228" priority="11">
+    <cfRule type="expression" dxfId="233" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6901,57 +7014,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="227" priority="36">
+    <cfRule type="expression" dxfId="232" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="226" priority="51">
+    <cfRule type="expression" dxfId="231" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="225" priority="50">
+    <cfRule type="expression" dxfId="230" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="224" priority="9">
+    <cfRule type="expression" dxfId="229" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="223" priority="28">
+    <cfRule type="expression" dxfId="228" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="222" priority="11">
+    <cfRule type="expression" dxfId="227" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="221" priority="24">
+    <cfRule type="expression" dxfId="226" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="220" priority="31">
+    <cfRule type="expression" dxfId="225" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="219" priority="7">
+    <cfRule type="expression" dxfId="224" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="218" priority="35">
+    <cfRule type="expression" dxfId="223" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="217" priority="1">
+    <cfRule type="expression" dxfId="222" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7383,59 +7496,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="216" priority="35">
+    <cfRule type="expression" dxfId="221" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="215" priority="42">
+    <cfRule type="expression" dxfId="220" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="214" priority="54">
+    <cfRule type="expression" dxfId="219" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="213" priority="53">
+    <cfRule type="expression" dxfId="218" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="212" priority="5">
+    <cfRule type="expression" dxfId="217" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="211" priority="30">
+    <cfRule type="expression" dxfId="216" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="210" priority="33">
+    <cfRule type="expression" dxfId="215" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="209" priority="37">
+    <cfRule type="expression" dxfId="214" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="208" priority="41">
+    <cfRule type="expression" dxfId="213" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="207" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="205" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="204" priority="1">
+    <cfRule type="expression" dxfId="209" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7901,57 +8014,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="203" priority="1">
+    <cfRule type="expression" dxfId="208" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="202" priority="18">
+    <cfRule type="expression" dxfId="207" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="201" priority="41">
+    <cfRule type="expression" dxfId="206" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="200" priority="40">
+    <cfRule type="expression" dxfId="205" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="199" priority="13">
+    <cfRule type="expression" dxfId="204" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="198" priority="3">
+    <cfRule type="expression" dxfId="203" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="197" priority="5">
+    <cfRule type="expression" dxfId="202" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="196" priority="19">
+    <cfRule type="expression" dxfId="201" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="195" priority="7">
+    <cfRule type="expression" dxfId="200" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="194" priority="27">
+    <cfRule type="expression" dxfId="199" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="193" priority="8">
+    <cfRule type="expression" dxfId="198" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8411,32 +8524,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="192" priority="21">
+    <cfRule type="expression" dxfId="197" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="191" priority="43">
+    <cfRule type="expression" dxfId="196" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="190" priority="42">
+    <cfRule type="expression" dxfId="195" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="189" priority="1">
+    <cfRule type="expression" dxfId="194" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="188" priority="16">
+    <cfRule type="expression" dxfId="193" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="187" priority="24">
+    <cfRule type="expression" dxfId="192" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8852,32 +8965,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="186" priority="30">
+    <cfRule type="expression" dxfId="191" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="185" priority="29">
+    <cfRule type="expression" dxfId="190" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="184" priority="16">
+    <cfRule type="expression" dxfId="189" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="183" priority="1">
+    <cfRule type="expression" dxfId="188" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="182" priority="4">
+    <cfRule type="expression" dxfId="187" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="181" priority="5">
+    <cfRule type="expression" dxfId="186" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9287,32 +9400,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="180" priority="39">
+    <cfRule type="expression" dxfId="185" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="179" priority="38">
+    <cfRule type="expression" dxfId="184" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="178" priority="20">
+    <cfRule type="expression" dxfId="183" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="177" priority="1">
+    <cfRule type="expression" dxfId="182" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="176" priority="3">
+    <cfRule type="expression" dxfId="181" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="175" priority="2">
+    <cfRule type="expression" dxfId="180" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9732,37 +9845,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="174" priority="18">
+    <cfRule type="expression" dxfId="179" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="173" priority="2">
+    <cfRule type="expression" dxfId="178" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="172" priority="32">
+    <cfRule type="expression" dxfId="177" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="171" priority="31">
+    <cfRule type="expression" dxfId="176" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="170" priority="5">
+    <cfRule type="expression" dxfId="175" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="169" priority="1">
+    <cfRule type="expression" dxfId="174" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="168" priority="3">
+    <cfRule type="expression" dxfId="173" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10178,22 +10291,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="306" priority="14">
+    <cfRule type="expression" dxfId="311" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="305" priority="6">
+    <cfRule type="expression" dxfId="310" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="304" priority="15">
+    <cfRule type="expression" dxfId="309" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="303" priority="1">
+    <cfRule type="expression" dxfId="308" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10591,22 +10704,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="167" priority="32">
+    <cfRule type="expression" dxfId="172" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="166" priority="31">
+    <cfRule type="expression" dxfId="171" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="165" priority="12">
+    <cfRule type="expression" dxfId="170" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="164" priority="1">
+    <cfRule type="expression" dxfId="169" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10972,22 +11085,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="163" priority="17">
+    <cfRule type="expression" dxfId="168" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="162" priority="16">
+    <cfRule type="expression" dxfId="167" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="161" priority="2">
+    <cfRule type="expression" dxfId="166" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="160" priority="1">
+    <cfRule type="expression" dxfId="165" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11422,47 +11535,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="159" priority="32">
+    <cfRule type="expression" dxfId="164" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="158" priority="31">
+    <cfRule type="expression" dxfId="163" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="157" priority="1">
+    <cfRule type="expression" dxfId="162" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="156" priority="3">
+    <cfRule type="expression" dxfId="161" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="155" priority="5">
+    <cfRule type="expression" dxfId="160" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="154" priority="12">
+    <cfRule type="expression" dxfId="159" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="153" priority="18">
+    <cfRule type="expression" dxfId="158" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="152" priority="27">
+    <cfRule type="expression" dxfId="157" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="151" priority="33">
+    <cfRule type="expression" dxfId="156" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11893,47 +12006,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="150" priority="12">
+    <cfRule type="expression" dxfId="155" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="149" priority="29">
+    <cfRule type="expression" dxfId="154" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="148" priority="28">
+    <cfRule type="expression" dxfId="153" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="147" priority="27">
+    <cfRule type="expression" dxfId="152" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="146" priority="1">
+    <cfRule type="expression" dxfId="151" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="145" priority="3">
+    <cfRule type="expression" dxfId="150" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="144" priority="9">
+    <cfRule type="expression" dxfId="149" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="143" priority="24">
+    <cfRule type="expression" dxfId="148" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="142" priority="30">
+    <cfRule type="expression" dxfId="147" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12368,52 +12481,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="141" priority="4">
+    <cfRule type="expression" dxfId="146" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="140" priority="27">
+    <cfRule type="expression" dxfId="145" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="139" priority="26">
+    <cfRule type="expression" dxfId="144" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="138" priority="1">
+    <cfRule type="expression" dxfId="143" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="137" priority="2">
+    <cfRule type="expression" dxfId="142" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="136" priority="28">
+    <cfRule type="expression" dxfId="141" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="135" priority="5">
+    <cfRule type="expression" dxfId="140" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="134" priority="8">
+    <cfRule type="expression" dxfId="139" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="133" priority="18">
+    <cfRule type="expression" dxfId="138" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="132" priority="22">
+    <cfRule type="expression" dxfId="137" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12842,47 +12955,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="131" priority="13">
+    <cfRule type="expression" dxfId="136" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="130" priority="22">
+    <cfRule type="expression" dxfId="135" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="129" priority="21">
+    <cfRule type="expression" dxfId="134" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="128" priority="1">
+    <cfRule type="expression" dxfId="133" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="127" priority="3">
+    <cfRule type="expression" dxfId="132" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="126" priority="5">
+    <cfRule type="expression" dxfId="131" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="125" priority="8">
+    <cfRule type="expression" dxfId="130" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="124" priority="17">
+    <cfRule type="expression" dxfId="129" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="123" priority="23">
+    <cfRule type="expression" dxfId="128" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13305,52 +13418,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="122" priority="5">
+    <cfRule type="expression" dxfId="127" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="121" priority="28">
+    <cfRule type="expression" dxfId="126" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="120" priority="27">
+    <cfRule type="expression" dxfId="125" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="119" priority="1">
+    <cfRule type="expression" dxfId="124" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="118" priority="3">
+    <cfRule type="expression" dxfId="123" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="117" priority="29">
+    <cfRule type="expression" dxfId="122" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="116" priority="22">
+    <cfRule type="expression" dxfId="121" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="115" priority="8">
+    <cfRule type="expression" dxfId="120" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="114" priority="19">
+    <cfRule type="expression" dxfId="119" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="113" priority="23">
+    <cfRule type="expression" dxfId="118" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13779,47 +13892,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="112" priority="11">
+    <cfRule type="expression" dxfId="117" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="111" priority="22">
+    <cfRule type="expression" dxfId="116" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="110" priority="21">
+    <cfRule type="expression" dxfId="115" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="109" priority="1">
+    <cfRule type="expression" dxfId="114" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="108" priority="3">
+    <cfRule type="expression" dxfId="113" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="107" priority="23">
+    <cfRule type="expression" dxfId="112" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="106" priority="5">
+    <cfRule type="expression" dxfId="111" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="105" priority="7">
+    <cfRule type="expression" dxfId="110" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="104" priority="17">
+    <cfRule type="expression" dxfId="109" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14247,52 +14360,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="103" priority="6">
+    <cfRule type="expression" dxfId="108" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="102" priority="27">
+    <cfRule type="expression" dxfId="107" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="101" priority="26">
+    <cfRule type="expression" dxfId="106" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="100" priority="1">
+    <cfRule type="expression" dxfId="105" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="99" priority="4">
+    <cfRule type="expression" dxfId="104" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="98" priority="28">
+    <cfRule type="expression" dxfId="103" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="97" priority="21">
+    <cfRule type="expression" dxfId="102" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="96" priority="9">
+    <cfRule type="expression" dxfId="101" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="95" priority="19">
+    <cfRule type="expression" dxfId="100" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="94" priority="22">
+    <cfRule type="expression" dxfId="99" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14638,7 +14751,7 @@
       <c r="E28" s="22" t="s">
         <v>259</v>
       </c>
-      <c r="F28" s="64" t="s">
+      <c r="F28" s="65" t="s">
         <v>395</v>
       </c>
     </row>
@@ -14670,7 +14783,7 @@
       <c r="E30" s="22" t="s">
         <v>481</v>
       </c>
-      <c r="F30" s="64" t="s">
+      <c r="F30" s="65" t="s">
         <v>455</v>
       </c>
     </row>
@@ -14682,7 +14795,7 @@
       <c r="E31" s="22" t="s">
         <v>482</v>
       </c>
-      <c r="F31" s="64" t="s">
+      <c r="F31" s="65" t="s">
         <v>468</v>
       </c>
     </row>
@@ -14694,8 +14807,8 @@
       <c r="E32" s="22" t="s">
         <v>483</v>
       </c>
-      <c r="F32" s="16" t="s">
-        <v>472</v>
+      <c r="F32" s="22" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14704,9 +14817,7 @@
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="16" t="s">
-        <v>484</v>
-      </c>
+      <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
@@ -14734,37 +14845,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="93" priority="5">
+    <cfRule type="expression" dxfId="98" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="92" priority="28">
+    <cfRule type="expression" dxfId="97" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="91" priority="27">
+    <cfRule type="expression" dxfId="96" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="90" priority="4">
+    <cfRule type="expression" dxfId="95" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E7">
-    <cfRule type="expression" dxfId="89" priority="3">
+    <cfRule type="expression" dxfId="94" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F25">
-    <cfRule type="expression" dxfId="88" priority="1">
+    <cfRule type="expression" dxfId="93" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 C16:D25">
-    <cfRule type="expression" dxfId="87" priority="14">
+    <cfRule type="expression" dxfId="92" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15169,30 +15280,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="302" priority="3">
+    <cfRule type="expression" dxfId="307" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="301" priority="14">
+    <cfRule type="expression" dxfId="306" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="300" priority="15">
+    <cfRule type="expression" dxfId="305" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="299" priority="7">
+    <cfRule type="expression" dxfId="304" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="298" priority="9">
+    <cfRule type="expression" dxfId="303" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="297" priority="12">
+    <cfRule type="expression" dxfId="302" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15558,7 +15669,9 @@
         <v>467</v>
       </c>
       <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="F29" s="16" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
@@ -15566,7 +15679,9 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="16" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -15574,7 +15689,9 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="F31" s="17" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
@@ -15582,7 +15699,9 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="F32" s="16" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
@@ -15590,7 +15709,9 @@
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="F33" s="16" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
@@ -15598,7 +15719,9 @@
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+      <c r="F34" s="17" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
@@ -15606,7 +15729,9 @@
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+      <c r="F35" s="17" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
@@ -15618,27 +15743,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="86" priority="1">
+    <cfRule type="expression" dxfId="91" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="85" priority="21">
+    <cfRule type="expression" dxfId="90" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="84" priority="20">
+    <cfRule type="expression" dxfId="89" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="83" priority="19">
+    <cfRule type="expression" dxfId="88" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="82" priority="6">
+    <cfRule type="expression" dxfId="87" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15996,45 +16121,71 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>492</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>504</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>499</v>
+      </c>
       <c r="F29" s="17" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="16" t="s">
+        <v>472</v>
+      </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="E30" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="17" t="s">
+        <v>498</v>
+      </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="F31" s="17" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="17"/>
+      <c r="B32" s="17" t="s">
+        <v>501</v>
+      </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="F32" s="19" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="17"/>
+      <c r="B33" s="17" t="s">
+        <v>502</v>
+      </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="F33" s="19" t="s">
+        <v>507</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
@@ -16042,7 +16193,9 @@
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+      <c r="F34" s="19" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
@@ -16050,7 +16203,9 @@
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+      <c r="F35" s="19" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
@@ -16062,28 +16217,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="81" priority="1">
+    <cfRule type="expression" dxfId="86" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="80" priority="27">
+    <cfRule type="expression" dxfId="85" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="79" priority="26">
+    <cfRule type="expression" dxfId="84" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="78" priority="3">
+  <conditionalFormatting sqref="B28:F28 B31:F36 C29:F30">
+    <cfRule type="expression" dxfId="83" priority="6">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="77" priority="7">
+    <cfRule type="expression" dxfId="82" priority="10">
       <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="expression" dxfId="81" priority="3">
+      <formula>NOT(ISBLANK(B29))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="expression" dxfId="80" priority="2">
+      <formula>NOT(ISBLANK(B30))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="expression" dxfId="79" priority="1">
+      <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16301,75 +16471,73 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="C29" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>387</v>
-      </c>
-      <c r="E29" s="17" t="s">
+      <c r="D29" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="E29" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="F29" s="19" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="19" t="s">
         <v>454</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="E30" s="17" t="s">
+      <c r="D30" s="19"/>
+      <c r="E30" s="19" t="s">
         <v>458</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="19" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
@@ -16405,37 +16573,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="76" priority="31">
+    <cfRule type="expression" dxfId="78" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="75" priority="30">
+    <cfRule type="expression" dxfId="77" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="74" priority="2">
+    <cfRule type="expression" dxfId="76" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="73" priority="1">
+    <cfRule type="expression" dxfId="75" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="72" priority="10">
+    <cfRule type="expression" dxfId="74" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="71" priority="8">
+    <cfRule type="expression" dxfId="73" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="70" priority="14">
+    <cfRule type="expression" dxfId="72" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16550,7 +16718,9 @@
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>489</v>
+      </c>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -16747,7 +16917,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>489</v>
+      </c>
       <c r="C28" s="16" t="s">
         <v>420</v>
       </c>
@@ -16833,37 +17005,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="69" priority="1">
+    <cfRule type="expression" dxfId="71" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="68" priority="37">
+    <cfRule type="expression" dxfId="70" priority="37">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="67" priority="36">
+    <cfRule type="expression" dxfId="69" priority="36">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="66" priority="2">
+    <cfRule type="expression" dxfId="68" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14 B15:D25">
-    <cfRule type="expression" dxfId="65" priority="3">
+    <cfRule type="expression" dxfId="67" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="64" priority="15">
+    <cfRule type="expression" dxfId="66" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="63" priority="12">
+    <cfRule type="expression" dxfId="65" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17277,37 +17449,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="62" priority="1">
+    <cfRule type="expression" dxfId="64" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="61" priority="40">
+    <cfRule type="expression" dxfId="63" priority="40">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="60" priority="39">
+    <cfRule type="expression" dxfId="62" priority="39">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="59" priority="2">
+    <cfRule type="expression" dxfId="61" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="58" priority="3">
+    <cfRule type="expression" dxfId="60" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="57" priority="33">
+    <cfRule type="expression" dxfId="59" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="56" priority="32">
+    <cfRule type="expression" dxfId="58" priority="32">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17632,7 +17804,9 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="16" t="s">
+        <v>490</v>
+      </c>
       <c r="C28" s="16" t="s">
         <v>441</v>
       </c>
@@ -17648,7 +17822,9 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="17" t="s">
+        <v>491</v>
+      </c>
       <c r="C29" s="16" t="s">
         <v>454</v>
       </c>
@@ -17724,47 +17900,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="55" priority="11">
+    <cfRule type="expression" dxfId="57" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:B26">
-    <cfRule type="expression" dxfId="54" priority="1">
+    <cfRule type="expression" dxfId="56" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="53" priority="45">
+    <cfRule type="expression" dxfId="55" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="52" priority="44">
+    <cfRule type="expression" dxfId="54" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="51" priority="5">
+    <cfRule type="expression" dxfId="53" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="50" priority="6">
+    <cfRule type="expression" dxfId="52" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="49" priority="15">
+    <cfRule type="expression" dxfId="51" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B15:D16 C17:D25">
-    <cfRule type="expression" dxfId="48" priority="38">
+    <cfRule type="expression" dxfId="50" priority="38">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="47" priority="37">
+    <cfRule type="expression" dxfId="49" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18188,42 +18364,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="46" priority="6">
+    <cfRule type="expression" dxfId="48" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="45" priority="21">
+    <cfRule type="expression" dxfId="47" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="44" priority="20">
+    <cfRule type="expression" dxfId="46" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="43" priority="1">
+    <cfRule type="expression" dxfId="45" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="42" priority="2">
+    <cfRule type="expression" dxfId="44" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="41" priority="10">
+    <cfRule type="expression" dxfId="43" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B15:D25">
-    <cfRule type="expression" dxfId="40" priority="17">
+    <cfRule type="expression" dxfId="42" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="39" priority="16">
+    <cfRule type="expression" dxfId="41" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18647,42 +18823,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="38" priority="7">
+    <cfRule type="expression" dxfId="40" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D25">
-    <cfRule type="expression" dxfId="37" priority="8">
+    <cfRule type="expression" dxfId="39" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="36" priority="23">
+    <cfRule type="expression" dxfId="38" priority="23">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="35" priority="22">
+    <cfRule type="expression" dxfId="37" priority="22">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="34" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="33" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="32" priority="12">
+    <cfRule type="expression" dxfId="34" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="31" priority="18">
+    <cfRule type="expression" dxfId="33" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19098,42 +19274,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="30" priority="6">
+    <cfRule type="expression" dxfId="32" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="31" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="28" priority="22">
+    <cfRule type="expression" dxfId="30" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="27" priority="21">
+    <cfRule type="expression" dxfId="29" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="28" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="25" priority="2">
+    <cfRule type="expression" dxfId="27" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="24" priority="11">
+    <cfRule type="expression" dxfId="26" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="23" priority="17">
+    <cfRule type="expression" dxfId="25" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19223,6 +19399,12 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
+      <c r="C5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>486</v>
+      </c>
       <c r="H5" s="11" t="s">
         <v>22</v>
       </c>
@@ -19231,11 +19413,23 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
+      <c r="C6" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
+      <c r="C7" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>488</v>
+      </c>
       <c r="H7" s="1" t="s">
         <v>17</v>
       </c>
@@ -19245,6 +19439,8 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
+      <c r="C8" s="5"/>
+      <c r="F8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
@@ -19256,16 +19452,21 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
+      <c r="C9" s="5"/>
+      <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
+      <c r="C10" s="5"/>
+      <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -19444,46 +19645,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="22" priority="6">
+    <cfRule type="expression" dxfId="24" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="21" priority="7">
+    <cfRule type="expression" dxfId="23" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="20" priority="22">
+    <cfRule type="expression" dxfId="22" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="21" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="20" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13 B5:F25">
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="16" priority="11">
+    <cfRule type="expression" dxfId="18" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -19904,22 +20106,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="296" priority="10">
+    <cfRule type="expression" dxfId="301" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="295" priority="9">
+    <cfRule type="expression" dxfId="300" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="294" priority="1">
+    <cfRule type="expression" dxfId="299" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="293" priority="7">
+    <cfRule type="expression" dxfId="298" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20010,11 +20212,11 @@
       <c r="A5" s="3">
         <v>0.375</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>12</v>
+      <c r="C5" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>22</v>
@@ -20024,25 +20226,15 @@
       <c r="A6" s="3">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="E7" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
       <c r="H7" s="1" t="s">
         <v>17</v>
       </c>
@@ -20052,9 +20244,8 @@
       <c r="A8" s="3">
         <v>0.4375</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
       <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
@@ -20066,100 +20257,64 @@
       <c r="A9" s="10">
         <v>0.44791666666666669</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="29" t="s">
-        <v>449</v>
-      </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>0.45833333333333398</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>0.47916666666666702</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>0.5</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>0.53125</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>0.54166666666666696</v>
       </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>0.5625</v>
       </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>0.58333333333333304</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>0.60416666666666696</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -20167,9 +20322,6 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -20177,9 +20329,6 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -20187,9 +20336,6 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="5"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
@@ -20197,11 +20343,6 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -20209,41 +20350,21 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>0.72916666666666696</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="5"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>0.75</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="5"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>0.76041666666666663</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="5"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
@@ -20343,43 +20464,53 @@
       <c r="F36" s="19"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="14" priority="5">
+  <conditionalFormatting sqref="B4:B6">
+    <cfRule type="expression" dxfId="16" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="13" priority="6">
+  <conditionalFormatting sqref="B9:C12">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B7:D25">
+    <cfRule type="expression" dxfId="14" priority="7">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="12" priority="21">
+    <cfRule type="expression" dxfId="13" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="11" priority="20">
+    <cfRule type="expression" dxfId="12" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B4:F24">
+    <cfRule type="expression" dxfId="11" priority="5">
+      <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="10" priority="19">
+    <cfRule type="expression" dxfId="10" priority="28">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="9" priority="1">
+  <conditionalFormatting sqref="C5:C6">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="8" priority="10">
+  <conditionalFormatting sqref="E4:E26 F9:F25">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="7" priority="16">
+  <conditionalFormatting sqref="F4:F7">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21274,42 +21405,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="292" priority="15">
+    <cfRule type="expression" dxfId="297" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="291" priority="13">
+    <cfRule type="expression" dxfId="296" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="290" priority="30">
+    <cfRule type="expression" dxfId="295" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="289" priority="29">
+    <cfRule type="expression" dxfId="294" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="288" priority="7">
+    <cfRule type="expression" dxfId="293" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="287" priority="24">
+    <cfRule type="expression" dxfId="292" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="286" priority="20">
+    <cfRule type="expression" dxfId="291" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="285" priority="25">
+    <cfRule type="expression" dxfId="290" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21710,32 +21841,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="284" priority="8">
+    <cfRule type="expression" dxfId="289" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="283" priority="13">
+    <cfRule type="expression" dxfId="288" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="282" priority="12">
+    <cfRule type="expression" dxfId="287" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="281" priority="1">
+    <cfRule type="expression" dxfId="286" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="280" priority="4">
+    <cfRule type="expression" dxfId="285" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="279" priority="7">
+    <cfRule type="expression" dxfId="284" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22119,52 +22250,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="278" priority="22">
+    <cfRule type="expression" dxfId="283" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="277" priority="23">
+    <cfRule type="expression" dxfId="282" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="276" priority="45">
+    <cfRule type="expression" dxfId="281" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="275" priority="44">
+    <cfRule type="expression" dxfId="280" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="274" priority="1">
+    <cfRule type="expression" dxfId="279" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="273" priority="35">
+    <cfRule type="expression" dxfId="278" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="272" priority="36">
+    <cfRule type="expression" dxfId="277" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="271" priority="16">
+    <cfRule type="expression" dxfId="276" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="270" priority="34">
+    <cfRule type="expression" dxfId="275" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="269" priority="5">
+    <cfRule type="expression" dxfId="274" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22577,47 +22708,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="268" priority="16">
+    <cfRule type="expression" dxfId="273" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="267" priority="19">
+    <cfRule type="expression" dxfId="272" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="266" priority="18">
+    <cfRule type="expression" dxfId="271" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="265" priority="1">
+    <cfRule type="expression" dxfId="270" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="264" priority="15">
+    <cfRule type="expression" dxfId="269" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="263" priority="12">
+    <cfRule type="expression" dxfId="268" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="262" priority="11">
+    <cfRule type="expression" dxfId="267" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="261" priority="14">
+    <cfRule type="expression" dxfId="266" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="260" priority="5">
+    <cfRule type="expression" dxfId="265" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23040,32 +23171,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="259" priority="2">
+    <cfRule type="expression" dxfId="264" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="258" priority="4">
+    <cfRule type="expression" dxfId="263" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="257" priority="16">
+    <cfRule type="expression" dxfId="262" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="256" priority="15">
+    <cfRule type="expression" dxfId="261" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="255" priority="1">
+    <cfRule type="expression" dxfId="260" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="254" priority="7">
+    <cfRule type="expression" dxfId="259" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F09795-BE6E-4E04-A366-145B18906374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804330E6-F49F-4F56-9BD1-BA797E515397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1360,9 +1360,6 @@
     <t>OVERLAP WEEK! (mogelijkheid tot afwerken en laatste feedback)</t>
   </si>
   <si>
-    <t>14:00 DEADLINE</t>
-  </si>
-  <si>
     <t>boek net + lijm meedoen</t>
   </si>
   <si>
@@ -1628,6 +1625,9 @@
   </si>
   <si>
     <t>Scene 12 &amp; 13 maken</t>
+  </si>
+  <si>
+    <t>14:00 DEADLINE - Art of the title</t>
   </si>
 </sst>
 </file>
@@ -1955,7 +1955,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="312">
+  <dxfs count="309">
     <dxf>
       <font>
         <color theme="1"/>
@@ -2683,27 +2683,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5538,47 +5517,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="258" priority="17">
+    <cfRule type="expression" dxfId="255" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="257" priority="25">
+    <cfRule type="expression" dxfId="254" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="256" priority="24">
+    <cfRule type="expression" dxfId="253" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="255" priority="5">
+    <cfRule type="expression" dxfId="252" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="254" priority="9">
+    <cfRule type="expression" dxfId="251" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="253" priority="8">
+    <cfRule type="expression" dxfId="250" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="252" priority="11">
+    <cfRule type="expression" dxfId="249" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="251" priority="15">
+    <cfRule type="expression" dxfId="248" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="250" priority="2">
+    <cfRule type="expression" dxfId="247" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6037,42 +6016,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="249" priority="15">
+    <cfRule type="expression" dxfId="246" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="248" priority="10">
+    <cfRule type="expression" dxfId="245" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="247" priority="24">
+    <cfRule type="expression" dxfId="244" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="246" priority="23">
+    <cfRule type="expression" dxfId="243" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="245" priority="1">
+    <cfRule type="expression" dxfId="242" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="244" priority="7">
+    <cfRule type="expression" dxfId="241" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="243" priority="3">
+    <cfRule type="expression" dxfId="240" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="242" priority="14">
+    <cfRule type="expression" dxfId="239" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6511,47 +6490,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="241" priority="10">
+    <cfRule type="expression" dxfId="238" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="240" priority="1">
+    <cfRule type="expression" dxfId="237" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="239" priority="25">
+    <cfRule type="expression" dxfId="236" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="238" priority="24">
+    <cfRule type="expression" dxfId="235" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="237" priority="4">
+    <cfRule type="expression" dxfId="234" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="236" priority="3">
+    <cfRule type="expression" dxfId="233" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="235" priority="6">
+    <cfRule type="expression" dxfId="232" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="234" priority="9">
+    <cfRule type="expression" dxfId="231" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="233" priority="11">
+    <cfRule type="expression" dxfId="230" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7014,57 +6993,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="232" priority="36">
+    <cfRule type="expression" dxfId="229" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="231" priority="51">
+    <cfRule type="expression" dxfId="228" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="230" priority="50">
+    <cfRule type="expression" dxfId="227" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="229" priority="9">
+    <cfRule type="expression" dxfId="226" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="228" priority="28">
+    <cfRule type="expression" dxfId="225" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="227" priority="11">
+    <cfRule type="expression" dxfId="224" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="226" priority="24">
+    <cfRule type="expression" dxfId="223" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="225" priority="31">
+    <cfRule type="expression" dxfId="222" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="224" priority="7">
+    <cfRule type="expression" dxfId="221" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="223" priority="35">
+    <cfRule type="expression" dxfId="220" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="222" priority="1">
+    <cfRule type="expression" dxfId="219" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7496,59 +7475,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="221" priority="35">
+    <cfRule type="expression" dxfId="218" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="220" priority="42">
+    <cfRule type="expression" dxfId="217" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="219" priority="54">
+    <cfRule type="expression" dxfId="216" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="218" priority="53">
+    <cfRule type="expression" dxfId="215" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="217" priority="5">
+    <cfRule type="expression" dxfId="214" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="216" priority="30">
+    <cfRule type="expression" dxfId="213" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="215" priority="33">
+    <cfRule type="expression" dxfId="212" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="214" priority="37">
+    <cfRule type="expression" dxfId="211" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="213" priority="41">
+    <cfRule type="expression" dxfId="210" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="212" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="210" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="209" priority="1">
+    <cfRule type="expression" dxfId="206" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8014,57 +7993,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="208" priority="1">
+    <cfRule type="expression" dxfId="205" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="207" priority="18">
+    <cfRule type="expression" dxfId="204" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="206" priority="41">
+    <cfRule type="expression" dxfId="203" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="205" priority="40">
+    <cfRule type="expression" dxfId="202" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="204" priority="13">
+    <cfRule type="expression" dxfId="201" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="203" priority="3">
+    <cfRule type="expression" dxfId="200" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="202" priority="5">
+    <cfRule type="expression" dxfId="199" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="201" priority="19">
+    <cfRule type="expression" dxfId="198" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="200" priority="7">
+    <cfRule type="expression" dxfId="197" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="199" priority="27">
+    <cfRule type="expression" dxfId="196" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="198" priority="8">
+    <cfRule type="expression" dxfId="195" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8524,32 +8503,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="197" priority="21">
+    <cfRule type="expression" dxfId="194" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="196" priority="43">
+    <cfRule type="expression" dxfId="193" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="195" priority="42">
+    <cfRule type="expression" dxfId="192" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="194" priority="1">
+    <cfRule type="expression" dxfId="191" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="193" priority="16">
+    <cfRule type="expression" dxfId="190" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="192" priority="24">
+    <cfRule type="expression" dxfId="189" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8965,32 +8944,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="191" priority="30">
+    <cfRule type="expression" dxfId="188" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="190" priority="29">
+    <cfRule type="expression" dxfId="187" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="189" priority="16">
+    <cfRule type="expression" dxfId="186" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="188" priority="1">
+    <cfRule type="expression" dxfId="185" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="187" priority="4">
+    <cfRule type="expression" dxfId="184" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="186" priority="5">
+    <cfRule type="expression" dxfId="183" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9400,32 +9379,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="185" priority="39">
+    <cfRule type="expression" dxfId="182" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="184" priority="38">
+    <cfRule type="expression" dxfId="181" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="183" priority="20">
+    <cfRule type="expression" dxfId="180" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="182" priority="1">
+    <cfRule type="expression" dxfId="179" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="181" priority="3">
+    <cfRule type="expression" dxfId="178" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="180" priority="2">
+    <cfRule type="expression" dxfId="177" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9845,37 +9824,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="179" priority="18">
+    <cfRule type="expression" dxfId="176" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="178" priority="2">
+    <cfRule type="expression" dxfId="175" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="177" priority="32">
+    <cfRule type="expression" dxfId="174" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="176" priority="31">
+    <cfRule type="expression" dxfId="173" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="175" priority="5">
+    <cfRule type="expression" dxfId="172" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="174" priority="1">
+    <cfRule type="expression" dxfId="171" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="173" priority="3">
+    <cfRule type="expression" dxfId="170" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10291,22 +10270,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="311" priority="14">
+    <cfRule type="expression" dxfId="308" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="310" priority="6">
+    <cfRule type="expression" dxfId="307" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="309" priority="15">
+    <cfRule type="expression" dxfId="306" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="308" priority="1">
+    <cfRule type="expression" dxfId="305" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10704,22 +10683,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="172" priority="32">
+    <cfRule type="expression" dxfId="169" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="171" priority="31">
+    <cfRule type="expression" dxfId="168" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="170" priority="12">
+    <cfRule type="expression" dxfId="167" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="169" priority="1">
+    <cfRule type="expression" dxfId="166" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11085,22 +11064,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="168" priority="17">
+    <cfRule type="expression" dxfId="165" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="167" priority="16">
+    <cfRule type="expression" dxfId="164" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="166" priority="2">
+    <cfRule type="expression" dxfId="163" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="165" priority="1">
+    <cfRule type="expression" dxfId="162" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11535,47 +11514,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="164" priority="32">
+    <cfRule type="expression" dxfId="161" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="163" priority="31">
+    <cfRule type="expression" dxfId="160" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="1">
+    <cfRule type="expression" dxfId="159" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="161" priority="3">
+    <cfRule type="expression" dxfId="158" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="160" priority="5">
+    <cfRule type="expression" dxfId="157" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="159" priority="12">
+    <cfRule type="expression" dxfId="156" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="158" priority="18">
+    <cfRule type="expression" dxfId="155" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="157" priority="27">
+    <cfRule type="expression" dxfId="154" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="156" priority="33">
+    <cfRule type="expression" dxfId="153" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12006,47 +11985,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="155" priority="12">
+    <cfRule type="expression" dxfId="152" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="154" priority="29">
+    <cfRule type="expression" dxfId="151" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="153" priority="28">
+    <cfRule type="expression" dxfId="150" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="152" priority="27">
+    <cfRule type="expression" dxfId="149" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="151" priority="1">
+    <cfRule type="expression" dxfId="148" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="150" priority="3">
+    <cfRule type="expression" dxfId="147" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="149" priority="9">
+    <cfRule type="expression" dxfId="146" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="148" priority="24">
+    <cfRule type="expression" dxfId="145" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="147" priority="30">
+    <cfRule type="expression" dxfId="144" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12481,52 +12460,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="146" priority="4">
+    <cfRule type="expression" dxfId="143" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="145" priority="27">
+    <cfRule type="expression" dxfId="142" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="144" priority="26">
+    <cfRule type="expression" dxfId="141" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="143" priority="1">
+    <cfRule type="expression" dxfId="140" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="142" priority="2">
+    <cfRule type="expression" dxfId="139" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="141" priority="28">
+    <cfRule type="expression" dxfId="138" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="140" priority="5">
+    <cfRule type="expression" dxfId="137" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="139" priority="8">
+    <cfRule type="expression" dxfId="136" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="138" priority="18">
+    <cfRule type="expression" dxfId="135" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="137" priority="22">
+    <cfRule type="expression" dxfId="134" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12955,47 +12934,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="136" priority="13">
+    <cfRule type="expression" dxfId="133" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="135" priority="22">
+    <cfRule type="expression" dxfId="132" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="134" priority="21">
+    <cfRule type="expression" dxfId="131" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="133" priority="1">
+    <cfRule type="expression" dxfId="130" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="132" priority="3">
+    <cfRule type="expression" dxfId="129" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="131" priority="5">
+    <cfRule type="expression" dxfId="128" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="130" priority="8">
+    <cfRule type="expression" dxfId="127" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="129" priority="17">
+    <cfRule type="expression" dxfId="126" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="128" priority="23">
+    <cfRule type="expression" dxfId="125" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13342,7 +13321,7 @@
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>417</v>
@@ -13355,7 +13334,7 @@
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="47" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13365,7 +13344,7 @@
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -13418,52 +13397,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="127" priority="5">
+    <cfRule type="expression" dxfId="124" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="126" priority="28">
+    <cfRule type="expression" dxfId="123" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="125" priority="27">
+    <cfRule type="expression" dxfId="122" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="124" priority="1">
+    <cfRule type="expression" dxfId="121" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="123" priority="3">
+    <cfRule type="expression" dxfId="120" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="122" priority="29">
+    <cfRule type="expression" dxfId="119" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="121" priority="22">
+    <cfRule type="expression" dxfId="118" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="120" priority="8">
+    <cfRule type="expression" dxfId="117" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="119" priority="19">
+    <cfRule type="expression" dxfId="116" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="118" priority="23">
+    <cfRule type="expression" dxfId="115" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13806,7 +13785,7 @@
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>419</v>
@@ -13818,11 +13797,11 @@
         <v>409</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F29" s="17"/>
     </row>
@@ -13832,7 +13811,7 @@
         <v>415</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -13844,7 +13823,7 @@
         <v>302</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -13892,47 +13871,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="117" priority="11">
+    <cfRule type="expression" dxfId="114" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="116" priority="22">
+    <cfRule type="expression" dxfId="113" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="115" priority="21">
+    <cfRule type="expression" dxfId="112" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="114" priority="1">
+    <cfRule type="expression" dxfId="111" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="113" priority="3">
+    <cfRule type="expression" dxfId="110" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="112" priority="23">
+    <cfRule type="expression" dxfId="109" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="111" priority="5">
+    <cfRule type="expression" dxfId="108" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="110" priority="7">
+    <cfRule type="expression" dxfId="107" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="109" priority="17">
+    <cfRule type="expression" dxfId="106" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14052,7 +14031,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="69" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E7" s="32" t="s">
         <v>23</v>
@@ -14083,7 +14062,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -14263,16 +14242,16 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F28" s="22" t="s">
         <v>395</v>
@@ -14281,30 +14260,30 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="C29" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="C29" s="47" t="s">
-        <v>452</v>
-      </c>
       <c r="D29" s="47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="22" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="22" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F30" s="17"/>
     </row>
@@ -14314,7 +14293,7 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="22" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F31" s="17"/>
     </row>
@@ -14360,52 +14339,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="108" priority="6">
+    <cfRule type="expression" dxfId="105" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="107" priority="27">
+    <cfRule type="expression" dxfId="104" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="106" priority="26">
+    <cfRule type="expression" dxfId="103" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="105" priority="1">
+    <cfRule type="expression" dxfId="102" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="104" priority="4">
+    <cfRule type="expression" dxfId="101" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="103" priority="28">
+    <cfRule type="expression" dxfId="100" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="102" priority="21">
+    <cfRule type="expression" dxfId="99" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="101" priority="9">
+    <cfRule type="expression" dxfId="98" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="100" priority="19">
+    <cfRule type="expression" dxfId="97" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="99" priority="22">
+    <cfRule type="expression" dxfId="96" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14489,7 +14468,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>360</v>
@@ -14558,7 +14537,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -14617,16 +14596,16 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -14637,7 +14616,7 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
@@ -14742,10 +14721,10 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="47" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
@@ -14758,33 +14737,33 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="22" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F29" s="65" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="65" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="22" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F30" s="65" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14793,10 +14772,10 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="22" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F31" s="65" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14805,10 +14784,10 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="F32" s="22" t="s">
         <v>483</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14845,37 +14824,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="98" priority="5">
+    <cfRule type="expression" dxfId="95" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="97" priority="28">
+    <cfRule type="expression" dxfId="94" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="96" priority="27">
+    <cfRule type="expression" dxfId="93" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="95" priority="4">
+    <cfRule type="expression" dxfId="92" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E7">
-    <cfRule type="expression" dxfId="94" priority="3">
+    <cfRule type="expression" dxfId="91" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F25">
-    <cfRule type="expression" dxfId="93" priority="1">
+    <cfRule type="expression" dxfId="90" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 C16:D25">
-    <cfRule type="expression" dxfId="92" priority="14">
+    <cfRule type="expression" dxfId="89" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15280,30 +15259,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="307" priority="3">
+    <cfRule type="expression" dxfId="304" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="306" priority="14">
+    <cfRule type="expression" dxfId="303" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="305" priority="15">
+    <cfRule type="expression" dxfId="302" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="304" priority="7">
+    <cfRule type="expression" dxfId="301" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="303" priority="9">
+    <cfRule type="expression" dxfId="300" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="302" priority="12">
+    <cfRule type="expression" dxfId="299" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15453,7 +15432,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15666,11 +15645,11 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="16" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15680,7 +15659,7 @@
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="16" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15700,7 +15679,7 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15710,7 +15689,7 @@
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="16" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15730,7 +15709,7 @@
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
       <c r="F35" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15743,27 +15722,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="91" priority="2">
+    <cfRule type="expression" dxfId="88" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="90" priority="22">
+    <cfRule type="expression" dxfId="87" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="89" priority="21">
+    <cfRule type="expression" dxfId="86" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="88" priority="20">
+    <cfRule type="expression" dxfId="85" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="87" priority="7">
+    <cfRule type="expression" dxfId="84" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15911,7 +15890,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16122,16 +16101,16 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C29" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>503</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>504</v>
-      </c>
       <c r="E29" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>401</v>
@@ -16140,33 +16119,33 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -16178,13 +16157,13 @@
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="19" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -16204,7 +16183,7 @@
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
       <c r="F35" s="19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -16217,43 +16196,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="86" priority="4">
+    <cfRule type="expression" dxfId="83" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="85" priority="30">
+    <cfRule type="expression" dxfId="82" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="84" priority="29">
+    <cfRule type="expression" dxfId="81" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F28 B31:F36 C29:F30">
-    <cfRule type="expression" dxfId="83" priority="6">
+  <conditionalFormatting sqref="B28:F36">
+    <cfRule type="expression" dxfId="80" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="82" priority="10">
+    <cfRule type="expression" dxfId="79" priority="10">
       <formula>$I$8 = TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="expression" dxfId="81" priority="3">
-      <formula>NOT(ISBLANK(B29))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="expression" dxfId="80" priority="2">
-      <formula>NOT(ISBLANK(B30))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="expression" dxfId="79" priority="1">
-      <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16508,23 +16472,23 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="19" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="F30" s="19" t="s">
         <v>458</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="19" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -16719,7 +16683,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
@@ -16746,7 +16710,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -16918,7 +16882,7 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>420</v>
@@ -16937,10 +16901,10 @@
       <c r="A29" s="11"/>
       <c r="B29" s="17"/>
       <c r="C29" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
@@ -16950,7 +16914,7 @@
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17174,7 +17138,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -17359,40 +17323,40 @@
         <v>410</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>421</v>
+        <v>508</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>385</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>387</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17402,7 +17366,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -17624,7 +17588,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -17805,28 +17769,28 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>384</v>
       </c>
       <c r="E28" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="F28" s="16" t="s">
         <v>441</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>386</v>
@@ -17838,10 +17802,10 @@
       <c r="A30" s="11"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17851,7 +17815,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -17861,7 +17825,7 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
@@ -18088,7 +18052,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18284,12 +18248,12 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -18301,13 +18265,13 @@
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -18547,7 +18511,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18743,7 +18707,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16" t="s">
@@ -18756,7 +18720,7 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="16" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -18766,7 +18730,7 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -19006,7 +18970,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19202,7 +19166,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -19403,7 +19367,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>22</v>
@@ -19414,10 +19378,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -19425,10 +19389,10 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>487</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>488</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -19575,14 +19539,14 @@
         <v>43</v>
       </c>
       <c r="C29" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="D29" s="19" t="s">
         <v>444</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>445</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -19592,7 +19556,7 @@
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="19" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -20106,22 +20070,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="301" priority="10">
+    <cfRule type="expression" dxfId="298" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="300" priority="9">
+    <cfRule type="expression" dxfId="297" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="299" priority="1">
+    <cfRule type="expression" dxfId="296" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="298" priority="7">
+    <cfRule type="expression" dxfId="295" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20658,7 +20622,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -21405,42 +21369,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="297" priority="15">
+    <cfRule type="expression" dxfId="294" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="296" priority="13">
+    <cfRule type="expression" dxfId="293" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="295" priority="30">
+    <cfRule type="expression" dxfId="292" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="294" priority="29">
+    <cfRule type="expression" dxfId="291" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="293" priority="7">
+    <cfRule type="expression" dxfId="290" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="292" priority="24">
+    <cfRule type="expression" dxfId="289" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="291" priority="20">
+    <cfRule type="expression" dxfId="288" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="290" priority="25">
+    <cfRule type="expression" dxfId="287" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21841,32 +21805,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="289" priority="8">
+    <cfRule type="expression" dxfId="286" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="288" priority="13">
+    <cfRule type="expression" dxfId="285" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="287" priority="12">
+    <cfRule type="expression" dxfId="284" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="286" priority="1">
+    <cfRule type="expression" dxfId="283" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="285" priority="4">
+    <cfRule type="expression" dxfId="282" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="284" priority="7">
+    <cfRule type="expression" dxfId="281" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22250,52 +22214,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="283" priority="22">
+    <cfRule type="expression" dxfId="280" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="282" priority="23">
+    <cfRule type="expression" dxfId="279" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="281" priority="45">
+    <cfRule type="expression" dxfId="278" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="280" priority="44">
+    <cfRule type="expression" dxfId="277" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="279" priority="1">
+    <cfRule type="expression" dxfId="276" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="278" priority="35">
+    <cfRule type="expression" dxfId="275" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="277" priority="36">
+    <cfRule type="expression" dxfId="274" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="276" priority="16">
+    <cfRule type="expression" dxfId="273" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="275" priority="34">
+    <cfRule type="expression" dxfId="272" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="274" priority="5">
+    <cfRule type="expression" dxfId="271" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22708,47 +22672,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="273" priority="16">
+    <cfRule type="expression" dxfId="270" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="272" priority="19">
+    <cfRule type="expression" dxfId="269" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="271" priority="18">
+    <cfRule type="expression" dxfId="268" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="270" priority="1">
+    <cfRule type="expression" dxfId="267" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="269" priority="15">
+    <cfRule type="expression" dxfId="266" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="268" priority="12">
+    <cfRule type="expression" dxfId="265" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="267" priority="11">
+    <cfRule type="expression" dxfId="264" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="266" priority="14">
+    <cfRule type="expression" dxfId="263" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="265" priority="5">
+    <cfRule type="expression" dxfId="262" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23171,32 +23135,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="264" priority="2">
+    <cfRule type="expression" dxfId="261" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="263" priority="4">
+    <cfRule type="expression" dxfId="260" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="262" priority="16">
+    <cfRule type="expression" dxfId="259" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="261" priority="15">
+    <cfRule type="expression" dxfId="258" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="260" priority="1">
+    <cfRule type="expression" dxfId="257" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="259" priority="7">
+    <cfRule type="expression" dxfId="256" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804330E6-F49F-4F56-9BD1-BA797E515397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F28800-3B04-4DA1-A84C-36AE3F2C4C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1710" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="511">
   <si>
     <t>Week</t>
   </si>
@@ -1628,6 +1628,12 @@
   </si>
   <si>
     <t>14:00 DEADLINE - Art of the title</t>
+  </si>
+  <si>
+    <t>Deadline studiereis opdracht!!!</t>
+  </si>
+  <si>
+    <t>Morgen naar rommelmarkt met theo</t>
   </si>
 </sst>
 </file>
@@ -18276,7 +18282,9 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="17" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -18709,7 +18717,9 @@
       <c r="C28" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="D28" s="16"/>
+      <c r="D28" s="16" t="s">
+        <v>509</v>
+      </c>
       <c r="E28" s="16" t="s">
         <v>42</v>
       </c>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F28800-3B04-4DA1-A84C-36AE3F2C4C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9E87D1-E323-47F2-8FC0-61D03561ABD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="29" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1723" uniqueCount="522">
   <si>
     <t>Week</t>
   </si>
@@ -1390,12 +1390,6 @@
     <t>Perspectief - praktische toepassing in interieurs</t>
   </si>
   <si>
-    <t>Skatepark watersportbaan tekenen op locatie</t>
-  </si>
-  <si>
-    <t>Laatste les tekenen denk ik</t>
-  </si>
-  <si>
     <t>DEADLINE TEKENEN GISTEREN</t>
   </si>
   <si>
@@ -1511,9 +1505,6 @@
   </si>
   <si>
     <t>Checken crossmedia's punten</t>
-  </si>
-  <si>
-    <t>Designgeschiedenis: les thema 4</t>
   </si>
   <si>
     <t>Van 18.15—20.30u in auditorium A3. Meer info zie aparte mededeling. De les in de namiddag valt weg.</t>
@@ -1634,6 +1625,51 @@
   </si>
   <si>
     <t>Morgen naar rommelmarkt met theo</t>
+  </si>
+  <si>
+    <t>WERKEN PRESENTATIE COMMUNICATIE???</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Designgeschiedenis: </t>
+  </si>
+  <si>
+    <t>les thema 4</t>
+  </si>
+  <si>
+    <t>crossmedia punten checken</t>
+  </si>
+  <si>
+    <t>mes terug theo?</t>
+  </si>
+  <si>
+    <t>zwarte hemd met kwallen waar?</t>
+  </si>
+  <si>
+    <t>09u00: BRIEFING LAATSTE OPDRACHT!!
+10u briefing rush opdracht
+18u rush inleveren
+ANALOOG MOGELIJKHEID TOT FEEDBACK TITLE SEQUENCE (lijst)</t>
+  </si>
+  <si>
+    <t>14u00 – 15u30: WORKSHOP DYNAMIC MOTION DESIGN door een oud student!</t>
+  </si>
+  <si>
+    <t>15u45-17u00: Info sessie stage – LOKAAL D303</t>
+  </si>
+  <si>
+    <t>17u00-18u30: VERVOLG WORKSHOP</t>
+  </si>
+  <si>
+    <t>09u00: BRIEFING LAATSTE OPDRACHT!!</t>
+  </si>
+  <si>
+    <t>10u briefing rush opdracht</t>
+  </si>
+  <si>
+    <t>18u rush inleveren</t>
+  </si>
+  <si>
+    <t>ilaria vertrekt naar london</t>
   </si>
 </sst>
 </file>
@@ -13807,7 +13843,7 @@
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="22" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F29" s="17"/>
     </row>
@@ -14068,7 +14104,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -14248,13 +14284,13 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="22" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D28" s="47" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E28" s="22" t="s">
         <v>424</v>
@@ -14266,30 +14302,30 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C29" s="47" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D29" s="47" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="C30" s="22" t="s">
         <v>451</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>453</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="22" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F30" s="17"/>
     </row>
@@ -14299,7 +14335,7 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="22" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F31" s="17"/>
     </row>
@@ -14474,7 +14510,7 @@
         <v>0.35416666666666669</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>360</v>
@@ -14543,7 +14579,7 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -14602,16 +14638,16 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E16" s="29" t="s">
         <v>468</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>470</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>12</v>
@@ -14622,7 +14658,7 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>13</v>
@@ -14730,7 +14766,7 @@
         <v>429</v>
       </c>
       <c r="C28" s="47" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D28" s="17"/>
       <c r="E28" s="22" t="s">
@@ -14743,33 +14779,33 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="22" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D29" s="17"/>
       <c r="E29" s="22" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F29" s="65" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="65" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D30" s="17"/>
       <c r="E30" s="22" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F30" s="65" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14778,10 +14814,10 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="22" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F31" s="65" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -14790,10 +14826,10 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="22" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15438,7 +15474,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -15651,11 +15687,11 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E29" s="17"/>
       <c r="F29" s="16" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15665,7 +15701,7 @@
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="16" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15685,7 +15721,7 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15695,7 +15731,7 @@
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="16" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15715,7 +15751,7 @@
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
       <c r="F35" s="17" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -15896,7 +15932,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -16107,16 +16143,16 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>401</v>
@@ -16125,33 +16161,33 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
       <c r="F31" s="17" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="17" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -16163,13 +16199,13 @@
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="17" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="19" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -16189,7 +16225,7 @@
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
       <c r="F35" s="19" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -16478,23 +16514,23 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="19" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="19" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -16689,7 +16725,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F7" s="5"/>
       <c r="H7" s="1" t="s">
@@ -16716,7 +16752,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -16809,7 +16845,9 @@
         <v>0.625</v>
       </c>
       <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="D18" s="5" t="s">
+        <v>510</v>
+      </c>
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -16887,8 +16925,8 @@
     </row>
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
-      <c r="B28" s="16" t="s">
-        <v>488</v>
+      <c r="B28" s="22" t="s">
+        <v>485</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>420</v>
@@ -16905,65 +16943,87 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>445</v>
-      </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+        <v>451</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>514</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16" t="s">
+        <v>519</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16" t="s">
+        <v>520</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
     </row>
     <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
@@ -17144,7 +17204,7 @@
         <v>0.44791666666666669</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -17329,40 +17389,36 @@
         <v>410</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>385</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17" t="s">
-        <v>431</v>
-      </c>
+      <c r="B29" s="17"/>
       <c r="C29" s="16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>387</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17" t="s">
-        <v>432</v>
-      </c>
+      <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17372,7 +17428,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -17594,7 +17650,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -17775,28 +17831,28 @@
     <row r="28" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>384</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D29" s="16" t="s">
         <v>386</v>
@@ -17806,12 +17862,14 @@
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="17" t="s">
+        <v>513</v>
+      </c>
       <c r="C30" s="17" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
@@ -17821,7 +17879,7 @@
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E31" s="17"/>
       <c r="F31" s="17"/>
@@ -17831,7 +17889,7 @@
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
@@ -18058,7 +18116,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18254,12 +18312,12 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -18271,19 +18329,19 @@
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
       <c r="F29" s="16" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -18519,7 +18577,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -18715,10 +18773,10 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>42</v>
@@ -18730,7 +18788,7 @@
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="16" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -18740,7 +18798,7 @@
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="16" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -18980,7 +19038,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>
@@ -19176,7 +19234,7 @@
         <v>41</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
@@ -19377,7 +19435,7 @@
         <v>28</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>22</v>
@@ -19388,10 +19446,10 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -19399,10 +19457,10 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>17</v>
@@ -19549,14 +19607,14 @@
         <v>43</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -19566,7 +19624,7 @@
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="19" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -20632,7 +20690,7 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="29" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="5"/>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sethv\Documents\GitHub\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B748BF-2062-4162-BC39-DDA21C06775E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96DA231-DFC0-44D2-A8EB-2CA55ECEB758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="25" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-60" windowWidth="21720" windowHeight="12900" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="526">
   <si>
     <t>Week</t>
   </si>
@@ -1667,6 +1667,21 @@
   </si>
   <si>
     <t>ilaria vertrekt naar london</t>
+  </si>
+  <si>
+    <t>VISO REUNION VANAF 18!!!</t>
+  </si>
+  <si>
+    <t>Presentatie thema 4 heeft info hierover</t>
+  </si>
+  <si>
+    <t>Vragen doorsturen jens aan leerkrachten VOOR 17U!, related aan vakgebied (bv. Hoe blijf je origineel in deze creatieve wereld waar er al zo veel bestaat?, is ons vakgebied visual design subjectief, waarom is niet regels vormen positief in de geschiedenis maar niet in atelier) vraag idee: welke vraag zou jij gesteld hebben toen je de opleiding volgde en is die nog relevant</t>
+  </si>
+  <si>
+    <t>Laatste les design geschiedenis ofzo</t>
+  </si>
+  <si>
+    <t>geen les ofzo van laatste vak</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +2009,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="309">
+  <dxfs count="310">
     <dxf>
       <font>
         <color theme="1"/>
@@ -2594,6 +2609,13 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5556,47 +5578,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="255" priority="17">
+    <cfRule type="expression" dxfId="256" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="254" priority="25">
+    <cfRule type="expression" dxfId="255" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="253" priority="24">
+    <cfRule type="expression" dxfId="254" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="252" priority="5">
+    <cfRule type="expression" dxfId="253" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="251" priority="9">
+    <cfRule type="expression" dxfId="252" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="250" priority="8">
+    <cfRule type="expression" dxfId="251" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="249" priority="11">
+    <cfRule type="expression" dxfId="250" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="248" priority="15">
+    <cfRule type="expression" dxfId="249" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="247" priority="2">
+    <cfRule type="expression" dxfId="248" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6055,42 +6077,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="246" priority="15">
+    <cfRule type="expression" dxfId="247" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="245" priority="10">
+    <cfRule type="expression" dxfId="246" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="244" priority="24">
+    <cfRule type="expression" dxfId="245" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="243" priority="23">
+    <cfRule type="expression" dxfId="244" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="242" priority="1">
+    <cfRule type="expression" dxfId="243" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="241" priority="7">
+    <cfRule type="expression" dxfId="242" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="240" priority="3">
+    <cfRule type="expression" dxfId="241" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="239" priority="14">
+    <cfRule type="expression" dxfId="240" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6529,47 +6551,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="238" priority="10">
+    <cfRule type="expression" dxfId="239" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="237" priority="1">
+    <cfRule type="expression" dxfId="238" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="236" priority="25">
+    <cfRule type="expression" dxfId="237" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="235" priority="24">
+    <cfRule type="expression" dxfId="236" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="234" priority="4">
+    <cfRule type="expression" dxfId="235" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="233" priority="3">
+    <cfRule type="expression" dxfId="234" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="232" priority="6">
+    <cfRule type="expression" dxfId="233" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="231" priority="9">
+    <cfRule type="expression" dxfId="232" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="230" priority="11">
+    <cfRule type="expression" dxfId="231" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7032,57 +7054,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="229" priority="36">
+    <cfRule type="expression" dxfId="230" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="228" priority="51">
+    <cfRule type="expression" dxfId="229" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="227" priority="50">
+    <cfRule type="expression" dxfId="228" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="226" priority="9">
+    <cfRule type="expression" dxfId="227" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="225" priority="28">
+    <cfRule type="expression" dxfId="226" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="224" priority="11">
+    <cfRule type="expression" dxfId="225" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="223" priority="24">
+    <cfRule type="expression" dxfId="224" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="222" priority="31">
+    <cfRule type="expression" dxfId="223" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="221" priority="7">
+    <cfRule type="expression" dxfId="222" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="220" priority="35">
+    <cfRule type="expression" dxfId="221" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="219" priority="1">
+    <cfRule type="expression" dxfId="220" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7514,59 +7536,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="218" priority="35">
+    <cfRule type="expression" dxfId="219" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="217" priority="42">
+    <cfRule type="expression" dxfId="218" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="216" priority="54">
+    <cfRule type="expression" dxfId="217" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="215" priority="53">
+    <cfRule type="expression" dxfId="216" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="214" priority="5">
+    <cfRule type="expression" dxfId="215" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="213" priority="30">
+    <cfRule type="expression" dxfId="214" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="212" priority="33">
+    <cfRule type="expression" dxfId="213" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="211" priority="37">
+    <cfRule type="expression" dxfId="212" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="210" priority="41">
+    <cfRule type="expression" dxfId="211" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="209" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="207" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="206" priority="1">
+    <cfRule type="expression" dxfId="207" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8032,57 +8054,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="205" priority="1">
+    <cfRule type="expression" dxfId="206" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="204" priority="18">
+    <cfRule type="expression" dxfId="205" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="203" priority="41">
+    <cfRule type="expression" dxfId="204" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="202" priority="40">
+    <cfRule type="expression" dxfId="203" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="201" priority="13">
+    <cfRule type="expression" dxfId="202" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="200" priority="3">
+    <cfRule type="expression" dxfId="201" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="199" priority="5">
+    <cfRule type="expression" dxfId="200" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="198" priority="19">
+    <cfRule type="expression" dxfId="199" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="197" priority="7">
+    <cfRule type="expression" dxfId="198" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="196" priority="27">
+    <cfRule type="expression" dxfId="197" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="195" priority="8">
+    <cfRule type="expression" dxfId="196" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8542,32 +8564,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="194" priority="21">
+    <cfRule type="expression" dxfId="195" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="193" priority="43">
+    <cfRule type="expression" dxfId="194" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="192" priority="42">
+    <cfRule type="expression" dxfId="193" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="191" priority="1">
+    <cfRule type="expression" dxfId="192" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="190" priority="16">
+    <cfRule type="expression" dxfId="191" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="189" priority="24">
+    <cfRule type="expression" dxfId="190" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8983,32 +9005,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="188" priority="30">
+    <cfRule type="expression" dxfId="189" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="187" priority="29">
+    <cfRule type="expression" dxfId="188" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="186" priority="16">
+    <cfRule type="expression" dxfId="187" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="185" priority="1">
+    <cfRule type="expression" dxfId="186" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="184" priority="4">
+    <cfRule type="expression" dxfId="185" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="183" priority="5">
+    <cfRule type="expression" dxfId="184" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9418,32 +9440,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="182" priority="39">
+    <cfRule type="expression" dxfId="183" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="181" priority="38">
+    <cfRule type="expression" dxfId="182" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="180" priority="20">
+    <cfRule type="expression" dxfId="181" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="179" priority="1">
+    <cfRule type="expression" dxfId="180" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="178" priority="3">
+    <cfRule type="expression" dxfId="179" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="177" priority="2">
+    <cfRule type="expression" dxfId="178" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9863,37 +9885,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="176" priority="18">
+    <cfRule type="expression" dxfId="177" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="175" priority="2">
+    <cfRule type="expression" dxfId="176" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="174" priority="32">
+    <cfRule type="expression" dxfId="175" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="173" priority="31">
+    <cfRule type="expression" dxfId="174" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="172" priority="5">
+    <cfRule type="expression" dxfId="173" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="171" priority="1">
+    <cfRule type="expression" dxfId="172" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="170" priority="3">
+    <cfRule type="expression" dxfId="171" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10309,22 +10331,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="308" priority="14">
+    <cfRule type="expression" dxfId="309" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="307" priority="6">
+    <cfRule type="expression" dxfId="308" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="306" priority="15">
+    <cfRule type="expression" dxfId="307" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="305" priority="1">
+    <cfRule type="expression" dxfId="306" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10722,22 +10744,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="169" priority="32">
+    <cfRule type="expression" dxfId="170" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="168" priority="31">
+    <cfRule type="expression" dxfId="169" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="167" priority="12">
+    <cfRule type="expression" dxfId="168" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="166" priority="1">
+    <cfRule type="expression" dxfId="167" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11103,22 +11125,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="165" priority="17">
+    <cfRule type="expression" dxfId="166" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="164" priority="16">
+    <cfRule type="expression" dxfId="165" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="163" priority="2">
+    <cfRule type="expression" dxfId="164" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="1">
+    <cfRule type="expression" dxfId="163" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11553,47 +11575,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="32">
+    <cfRule type="expression" dxfId="162" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="31">
+    <cfRule type="expression" dxfId="161" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="159" priority="1">
+    <cfRule type="expression" dxfId="160" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="158" priority="3">
+    <cfRule type="expression" dxfId="159" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="157" priority="5">
+    <cfRule type="expression" dxfId="158" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="156" priority="12">
+    <cfRule type="expression" dxfId="157" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="155" priority="18">
+    <cfRule type="expression" dxfId="156" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="154" priority="27">
+    <cfRule type="expression" dxfId="155" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="153" priority="33">
+    <cfRule type="expression" dxfId="154" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12024,47 +12046,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="152" priority="12">
+    <cfRule type="expression" dxfId="153" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="151" priority="29">
+    <cfRule type="expression" dxfId="152" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="150" priority="28">
+    <cfRule type="expression" dxfId="151" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="149" priority="27">
+    <cfRule type="expression" dxfId="150" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="148" priority="1">
+    <cfRule type="expression" dxfId="149" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="147" priority="3">
+    <cfRule type="expression" dxfId="148" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="146" priority="9">
+    <cfRule type="expression" dxfId="147" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="145" priority="24">
+    <cfRule type="expression" dxfId="146" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="144" priority="30">
+    <cfRule type="expression" dxfId="145" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12499,52 +12521,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="143" priority="4">
+    <cfRule type="expression" dxfId="144" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="142" priority="27">
+    <cfRule type="expression" dxfId="143" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="141" priority="26">
+    <cfRule type="expression" dxfId="142" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="140" priority="1">
+    <cfRule type="expression" dxfId="141" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="139" priority="2">
+    <cfRule type="expression" dxfId="140" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="138" priority="28">
+    <cfRule type="expression" dxfId="139" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="137" priority="5">
+    <cfRule type="expression" dxfId="138" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="136" priority="8">
+    <cfRule type="expression" dxfId="137" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="135" priority="18">
+    <cfRule type="expression" dxfId="136" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="134" priority="22">
+    <cfRule type="expression" dxfId="135" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12973,47 +12995,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="133" priority="13">
+    <cfRule type="expression" dxfId="134" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="132" priority="22">
+    <cfRule type="expression" dxfId="133" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="131" priority="21">
+    <cfRule type="expression" dxfId="132" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="130" priority="1">
+    <cfRule type="expression" dxfId="131" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="129" priority="3">
+    <cfRule type="expression" dxfId="130" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="128" priority="5">
+    <cfRule type="expression" dxfId="129" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="127" priority="8">
+    <cfRule type="expression" dxfId="128" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="126" priority="17">
+    <cfRule type="expression" dxfId="127" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="125" priority="23">
+    <cfRule type="expression" dxfId="126" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13436,52 +13458,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="124" priority="5">
+    <cfRule type="expression" dxfId="125" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="123" priority="28">
+    <cfRule type="expression" dxfId="124" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="122" priority="27">
+    <cfRule type="expression" dxfId="123" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="121" priority="1">
+    <cfRule type="expression" dxfId="122" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="120" priority="3">
+    <cfRule type="expression" dxfId="121" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="119" priority="29">
+    <cfRule type="expression" dxfId="120" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="118" priority="22">
+    <cfRule type="expression" dxfId="119" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="117" priority="8">
+    <cfRule type="expression" dxfId="118" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="116" priority="19">
+    <cfRule type="expression" dxfId="117" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="115" priority="23">
+    <cfRule type="expression" dxfId="116" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13910,47 +13932,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="114" priority="11">
+    <cfRule type="expression" dxfId="115" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="113" priority="22">
+    <cfRule type="expression" dxfId="114" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="112" priority="21">
+    <cfRule type="expression" dxfId="113" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="111" priority="1">
+    <cfRule type="expression" dxfId="112" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="110" priority="3">
+    <cfRule type="expression" dxfId="111" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="109" priority="23">
+    <cfRule type="expression" dxfId="110" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="108" priority="5">
+    <cfRule type="expression" dxfId="109" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="107" priority="7">
+    <cfRule type="expression" dxfId="108" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="106" priority="17">
+    <cfRule type="expression" dxfId="107" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14378,52 +14400,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="105" priority="6">
+    <cfRule type="expression" dxfId="106" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="104" priority="27">
+    <cfRule type="expression" dxfId="105" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="103" priority="26">
+    <cfRule type="expression" dxfId="104" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="102" priority="1">
+    <cfRule type="expression" dxfId="103" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="101" priority="4">
+    <cfRule type="expression" dxfId="102" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="100" priority="28">
+    <cfRule type="expression" dxfId="101" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="99" priority="21">
+    <cfRule type="expression" dxfId="100" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="98" priority="9">
+    <cfRule type="expression" dxfId="99" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="97" priority="19">
+    <cfRule type="expression" dxfId="98" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="97" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14863,37 +14885,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="95" priority="5">
+    <cfRule type="expression" dxfId="96" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="94" priority="28">
+    <cfRule type="expression" dxfId="95" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="93" priority="27">
+    <cfRule type="expression" dxfId="94" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="92" priority="4">
+    <cfRule type="expression" dxfId="93" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E7">
-    <cfRule type="expression" dxfId="91" priority="3">
+    <cfRule type="expression" dxfId="92" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F25">
-    <cfRule type="expression" dxfId="90" priority="1">
+    <cfRule type="expression" dxfId="91" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 C16:D25">
-    <cfRule type="expression" dxfId="89" priority="14">
+    <cfRule type="expression" dxfId="90" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15298,30 +15320,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="304" priority="3">
+    <cfRule type="expression" dxfId="305" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="303" priority="14">
+    <cfRule type="expression" dxfId="304" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="302" priority="15">
+    <cfRule type="expression" dxfId="303" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="301" priority="7">
+    <cfRule type="expression" dxfId="302" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="300" priority="9">
+    <cfRule type="expression" dxfId="301" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="299" priority="12">
+    <cfRule type="expression" dxfId="300" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15761,27 +15783,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="88" priority="2">
+    <cfRule type="expression" dxfId="89" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="87" priority="22">
+    <cfRule type="expression" dxfId="88" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="86" priority="21">
+    <cfRule type="expression" dxfId="87" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="85" priority="20">
+    <cfRule type="expression" dxfId="86" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="84" priority="7">
+    <cfRule type="expression" dxfId="85" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16235,27 +16257,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="83" priority="4">
+    <cfRule type="expression" dxfId="84" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="82" priority="30">
+    <cfRule type="expression" dxfId="83" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="81" priority="29">
+    <cfRule type="expression" dxfId="82" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="80" priority="1">
+    <cfRule type="expression" dxfId="81" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="79" priority="10">
+    <cfRule type="expression" dxfId="80" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16576,37 +16598,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="78" priority="31">
+    <cfRule type="expression" dxfId="79" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="77" priority="30">
+    <cfRule type="expression" dxfId="78" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="76" priority="2">
+    <cfRule type="expression" dxfId="77" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="75" priority="1">
+    <cfRule type="expression" dxfId="76" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="74" priority="10">
+    <cfRule type="expression" dxfId="75" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="73" priority="8">
+    <cfRule type="expression" dxfId="74" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="72" priority="14">
+    <cfRule type="expression" dxfId="73" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17000,7 +17022,9 @@
       </c>
       <c r="D33" s="16"/>
       <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
+      <c r="F33" s="16" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="11"/>
@@ -17028,38 +17052,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="71" priority="1">
+    <cfRule type="expression" dxfId="72" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
+    <cfRule type="expression" dxfId="71" priority="38">
+      <formula>B$3 &lt; TODAY()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:F3">
     <cfRule type="expression" dxfId="70" priority="37">
-      <formula>B$3 &lt; TODAY()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="69" priority="36">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="68" priority="2">
+  <conditionalFormatting sqref="B28:F32 B34:F36 B33:E33">
+    <cfRule type="expression" dxfId="69" priority="3">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14 B15:D25">
-    <cfRule type="expression" dxfId="67" priority="3">
+    <cfRule type="expression" dxfId="68" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="66" priority="15">
+    <cfRule type="expression" dxfId="67" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="65" priority="12">
+    <cfRule type="expression" dxfId="66" priority="13">
       <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F33">
+    <cfRule type="expression" dxfId="65" priority="1">
+      <formula>NOT(ISBLANK(F33))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17430,7 +17459,9 @@
       <c r="A32" s="11"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
+      <c r="D32" s="16" t="s">
+        <v>522</v>
+      </c>
       <c r="E32" s="17"/>
       <c r="F32" s="17"/>
     </row>
@@ -17438,7 +17469,9 @@
       <c r="A33" s="11"/>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
+      <c r="D33" s="17" t="s">
+        <v>524</v>
+      </c>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
     </row>
@@ -17446,7 +17479,9 @@
       <c r="A34" s="11"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
+      <c r="D34" s="16" t="s">
+        <v>525</v>
+      </c>
       <c r="E34" s="17"/>
       <c r="F34" s="17"/>
     </row>
@@ -18315,25 +18350,25 @@
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="11"/>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="16" t="s">
         <v>98</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="16" t="s">
+      <c r="F29" s="19" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="11"/>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>440</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="16" t="s">
         <v>507</v>
       </c>
     </row>
@@ -18343,7 +18378,9 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="F31" s="16" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="11"/>
@@ -20131,22 +20168,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="298" priority="10">
+    <cfRule type="expression" dxfId="299" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="297" priority="9">
+    <cfRule type="expression" dxfId="298" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="296" priority="1">
+    <cfRule type="expression" dxfId="297" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="295" priority="7">
+    <cfRule type="expression" dxfId="296" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21430,42 +21467,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="294" priority="15">
+    <cfRule type="expression" dxfId="295" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="293" priority="13">
+    <cfRule type="expression" dxfId="294" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="292" priority="30">
+    <cfRule type="expression" dxfId="293" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="291" priority="29">
+    <cfRule type="expression" dxfId="292" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="290" priority="7">
+    <cfRule type="expression" dxfId="291" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="289" priority="24">
+    <cfRule type="expression" dxfId="290" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="288" priority="20">
+    <cfRule type="expression" dxfId="289" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="287" priority="25">
+    <cfRule type="expression" dxfId="288" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21866,32 +21903,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="286" priority="8">
+    <cfRule type="expression" dxfId="287" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="285" priority="13">
+    <cfRule type="expression" dxfId="286" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="284" priority="12">
+    <cfRule type="expression" dxfId="285" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="283" priority="1">
+    <cfRule type="expression" dxfId="284" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="282" priority="4">
+    <cfRule type="expression" dxfId="283" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="281" priority="7">
+    <cfRule type="expression" dxfId="282" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22275,52 +22312,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="280" priority="22">
+    <cfRule type="expression" dxfId="281" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="279" priority="23">
+    <cfRule type="expression" dxfId="280" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="278" priority="45">
+    <cfRule type="expression" dxfId="279" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="277" priority="44">
+    <cfRule type="expression" dxfId="278" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="276" priority="1">
+    <cfRule type="expression" dxfId="277" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="275" priority="35">
+    <cfRule type="expression" dxfId="276" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="274" priority="36">
+    <cfRule type="expression" dxfId="275" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="273" priority="16">
+    <cfRule type="expression" dxfId="274" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="272" priority="34">
+    <cfRule type="expression" dxfId="273" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="271" priority="5">
+    <cfRule type="expression" dxfId="272" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22733,47 +22770,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="270" priority="16">
+    <cfRule type="expression" dxfId="271" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="269" priority="19">
+    <cfRule type="expression" dxfId="270" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="268" priority="18">
+    <cfRule type="expression" dxfId="269" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="267" priority="1">
+    <cfRule type="expression" dxfId="268" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="266" priority="15">
+    <cfRule type="expression" dxfId="267" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="265" priority="12">
+    <cfRule type="expression" dxfId="266" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="264" priority="11">
+    <cfRule type="expression" dxfId="265" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="263" priority="14">
+    <cfRule type="expression" dxfId="264" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="262" priority="5">
+    <cfRule type="expression" dxfId="263" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23196,32 +23233,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="261" priority="2">
+    <cfRule type="expression" dxfId="262" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="260" priority="4">
+    <cfRule type="expression" dxfId="261" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="259" priority="16">
+    <cfRule type="expression" dxfId="260" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="258" priority="15">
+    <cfRule type="expression" dxfId="259" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="257" priority="1">
+    <cfRule type="expression" dxfId="258" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="256" priority="7">
+    <cfRule type="expression" dxfId="257" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B6E14F-60E4-4620-B663-D9DDE04555B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAB64A2-2AF8-4901-AB54-DBFB847E64F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="32" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="546">
   <si>
     <t>Week</t>
   </si>
@@ -1712,6 +1712,36 @@
   </si>
   <si>
     <t>WERKEN DIGITAAL!!!!!</t>
+  </si>
+  <si>
+    <t>NAAR MOM ALS GEEN BERLIJN 16 mei</t>
+  </si>
+  <si>
+    <t>7 mei hema kalendar ook school</t>
+  </si>
+  <si>
+    <t>6 mei - feedback: 3 first ideas &amp; concepts</t>
+  </si>
+  <si>
+    <t>09 mei - feedback 1 concept + moodboard</t>
+  </si>
+  <si>
+    <t>13 mei - feedback: first sketches and trials</t>
+  </si>
+  <si>
+    <t>16 mei - feedback: refined sketches and trials/final key elements</t>
+  </si>
+  <si>
+    <t>20 mei - feedback on deliverables</t>
+  </si>
+  <si>
+    <t>27 mei - final feedback</t>
+  </si>
+  <si>
+    <t>04 june - jury!</t>
+  </si>
+  <si>
+    <t>typo en afwerken title sequence</t>
   </si>
 </sst>
 </file>
@@ -1900,7 +1930,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2027,9 +2057,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="6" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="20% - Accent2" xfId="3" builtinId="34"/>
@@ -2042,7 +2069,77 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="309">
+  <dxfs count="319">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -5604,47 +5701,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="255" priority="17">
+    <cfRule type="expression" dxfId="265" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="254" priority="25">
+    <cfRule type="expression" dxfId="264" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="253" priority="24">
+    <cfRule type="expression" dxfId="263" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="252" priority="5">
+    <cfRule type="expression" dxfId="262" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="251" priority="9">
+    <cfRule type="expression" dxfId="261" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="250" priority="8">
+    <cfRule type="expression" dxfId="260" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="249" priority="11">
+    <cfRule type="expression" dxfId="259" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="248" priority="15">
+    <cfRule type="expression" dxfId="258" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="247" priority="2">
+    <cfRule type="expression" dxfId="257" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6103,42 +6200,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="246" priority="15">
+    <cfRule type="expression" dxfId="256" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="245" priority="10">
+    <cfRule type="expression" dxfId="255" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="244" priority="24">
+    <cfRule type="expression" dxfId="254" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="243" priority="23">
+    <cfRule type="expression" dxfId="253" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="242" priority="1">
+    <cfRule type="expression" dxfId="252" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="241" priority="7">
+    <cfRule type="expression" dxfId="251" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="240" priority="3">
+    <cfRule type="expression" dxfId="250" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="239" priority="14">
+    <cfRule type="expression" dxfId="249" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6577,47 +6674,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="238" priority="10">
+    <cfRule type="expression" dxfId="248" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="237" priority="1">
+    <cfRule type="expression" dxfId="247" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="236" priority="25">
+    <cfRule type="expression" dxfId="246" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="235" priority="24">
+    <cfRule type="expression" dxfId="245" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="234" priority="4">
+    <cfRule type="expression" dxfId="244" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="233" priority="3">
+    <cfRule type="expression" dxfId="243" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="232" priority="6">
+    <cfRule type="expression" dxfId="242" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="231" priority="9">
+    <cfRule type="expression" dxfId="241" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="230" priority="11">
+    <cfRule type="expression" dxfId="240" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7080,57 +7177,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="229" priority="36">
+    <cfRule type="expression" dxfId="239" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="228" priority="51">
+    <cfRule type="expression" dxfId="238" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="227" priority="50">
+    <cfRule type="expression" dxfId="237" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="226" priority="9">
+    <cfRule type="expression" dxfId="236" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="225" priority="28">
+    <cfRule type="expression" dxfId="235" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="224" priority="11">
+    <cfRule type="expression" dxfId="234" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="223" priority="24">
+    <cfRule type="expression" dxfId="233" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="222" priority="31">
+    <cfRule type="expression" dxfId="232" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="221" priority="7">
+    <cfRule type="expression" dxfId="231" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="220" priority="35">
+    <cfRule type="expression" dxfId="230" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="219" priority="1">
+    <cfRule type="expression" dxfId="229" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7562,59 +7659,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="218" priority="35">
+    <cfRule type="expression" dxfId="228" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="217" priority="42">
+    <cfRule type="expression" dxfId="227" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="216" priority="54">
+    <cfRule type="expression" dxfId="226" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="215" priority="53">
+    <cfRule type="expression" dxfId="225" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="214" priority="5">
+    <cfRule type="expression" dxfId="224" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="213" priority="30">
+    <cfRule type="expression" dxfId="223" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="212" priority="33">
+    <cfRule type="expression" dxfId="222" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="211" priority="37">
+    <cfRule type="expression" dxfId="221" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="210" priority="41">
+    <cfRule type="expression" dxfId="220" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="209" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="207" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="206" priority="1">
+    <cfRule type="expression" dxfId="216" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8080,57 +8177,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="205" priority="1">
+    <cfRule type="expression" dxfId="215" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="204" priority="18">
+    <cfRule type="expression" dxfId="214" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="203" priority="41">
+    <cfRule type="expression" dxfId="213" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="202" priority="40">
+    <cfRule type="expression" dxfId="212" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="201" priority="13">
+    <cfRule type="expression" dxfId="211" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="200" priority="3">
+    <cfRule type="expression" dxfId="210" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="199" priority="5">
+    <cfRule type="expression" dxfId="209" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="198" priority="19">
+    <cfRule type="expression" dxfId="208" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="197" priority="7">
+    <cfRule type="expression" dxfId="207" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="196" priority="27">
+    <cfRule type="expression" dxfId="206" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="195" priority="8">
+    <cfRule type="expression" dxfId="205" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8590,32 +8687,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="194" priority="21">
+    <cfRule type="expression" dxfId="204" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="193" priority="43">
+    <cfRule type="expression" dxfId="203" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="192" priority="42">
+    <cfRule type="expression" dxfId="202" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="191" priority="1">
+    <cfRule type="expression" dxfId="201" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="190" priority="16">
+    <cfRule type="expression" dxfId="200" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="189" priority="24">
+    <cfRule type="expression" dxfId="199" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9031,32 +9128,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="188" priority="30">
+    <cfRule type="expression" dxfId="198" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="187" priority="29">
+    <cfRule type="expression" dxfId="197" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="186" priority="16">
+    <cfRule type="expression" dxfId="196" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="185" priority="1">
+    <cfRule type="expression" dxfId="195" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="184" priority="4">
+    <cfRule type="expression" dxfId="194" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="183" priority="5">
+    <cfRule type="expression" dxfId="193" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9466,32 +9563,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="182" priority="39">
+    <cfRule type="expression" dxfId="192" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="181" priority="38">
+    <cfRule type="expression" dxfId="191" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="180" priority="20">
+    <cfRule type="expression" dxfId="190" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="179" priority="1">
+    <cfRule type="expression" dxfId="189" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="178" priority="3">
+    <cfRule type="expression" dxfId="188" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="177" priority="2">
+    <cfRule type="expression" dxfId="187" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9911,37 +10008,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="176" priority="18">
+    <cfRule type="expression" dxfId="186" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="175" priority="2">
+    <cfRule type="expression" dxfId="185" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="174" priority="32">
+    <cfRule type="expression" dxfId="184" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="173" priority="31">
+    <cfRule type="expression" dxfId="183" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="172" priority="5">
+    <cfRule type="expression" dxfId="182" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="171" priority="1">
+    <cfRule type="expression" dxfId="181" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="170" priority="3">
+    <cfRule type="expression" dxfId="180" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10357,22 +10454,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="308" priority="14">
+    <cfRule type="expression" dxfId="318" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="307" priority="6">
+    <cfRule type="expression" dxfId="317" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="306" priority="15">
+    <cfRule type="expression" dxfId="316" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="305" priority="1">
+    <cfRule type="expression" dxfId="315" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10770,22 +10867,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="169" priority="32">
+    <cfRule type="expression" dxfId="179" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="168" priority="31">
+    <cfRule type="expression" dxfId="178" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="167" priority="12">
+    <cfRule type="expression" dxfId="177" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="166" priority="1">
+    <cfRule type="expression" dxfId="176" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11151,22 +11248,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="165" priority="17">
+    <cfRule type="expression" dxfId="175" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="164" priority="16">
+    <cfRule type="expression" dxfId="174" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="163" priority="2">
+    <cfRule type="expression" dxfId="173" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="162" priority="1">
+    <cfRule type="expression" dxfId="172" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11601,47 +11698,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="32">
+    <cfRule type="expression" dxfId="171" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="31">
+    <cfRule type="expression" dxfId="170" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="159" priority="1">
+    <cfRule type="expression" dxfId="169" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="158" priority="3">
+    <cfRule type="expression" dxfId="168" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="157" priority="5">
+    <cfRule type="expression" dxfId="167" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="156" priority="12">
+    <cfRule type="expression" dxfId="166" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="155" priority="18">
+    <cfRule type="expression" dxfId="165" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="154" priority="27">
+    <cfRule type="expression" dxfId="164" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="153" priority="33">
+    <cfRule type="expression" dxfId="163" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12072,47 +12169,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="152" priority="12">
+    <cfRule type="expression" dxfId="162" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="151" priority="29">
+    <cfRule type="expression" dxfId="161" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="150" priority="28">
+    <cfRule type="expression" dxfId="160" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="149" priority="27">
+    <cfRule type="expression" dxfId="159" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="148" priority="1">
+    <cfRule type="expression" dxfId="158" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="147" priority="3">
+    <cfRule type="expression" dxfId="157" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="146" priority="9">
+    <cfRule type="expression" dxfId="156" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="145" priority="24">
+    <cfRule type="expression" dxfId="155" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="144" priority="30">
+    <cfRule type="expression" dxfId="154" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12547,52 +12644,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="143" priority="4">
+    <cfRule type="expression" dxfId="153" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="142" priority="27">
+    <cfRule type="expression" dxfId="152" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="141" priority="26">
+    <cfRule type="expression" dxfId="151" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="140" priority="1">
+    <cfRule type="expression" dxfId="150" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="139" priority="2">
+    <cfRule type="expression" dxfId="149" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="138" priority="28">
+    <cfRule type="expression" dxfId="148" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="137" priority="5">
+    <cfRule type="expression" dxfId="147" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="136" priority="8">
+    <cfRule type="expression" dxfId="146" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="135" priority="18">
+    <cfRule type="expression" dxfId="145" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="134" priority="22">
+    <cfRule type="expression" dxfId="144" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13021,47 +13118,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="133" priority="13">
+    <cfRule type="expression" dxfId="143" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="132" priority="22">
+    <cfRule type="expression" dxfId="142" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="131" priority="21">
+    <cfRule type="expression" dxfId="141" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="130" priority="1">
+    <cfRule type="expression" dxfId="140" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="129" priority="3">
+    <cfRule type="expression" dxfId="139" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="128" priority="5">
+    <cfRule type="expression" dxfId="138" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="127" priority="8">
+    <cfRule type="expression" dxfId="137" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="126" priority="17">
+    <cfRule type="expression" dxfId="136" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="125" priority="23">
+    <cfRule type="expression" dxfId="135" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13484,52 +13581,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="124" priority="5">
+    <cfRule type="expression" dxfId="134" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="123" priority="28">
+    <cfRule type="expression" dxfId="133" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="122" priority="27">
+    <cfRule type="expression" dxfId="132" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="121" priority="1">
+    <cfRule type="expression" dxfId="131" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="120" priority="3">
+    <cfRule type="expression" dxfId="130" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="119" priority="29">
+    <cfRule type="expression" dxfId="129" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="118" priority="22">
+    <cfRule type="expression" dxfId="128" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="117" priority="8">
+    <cfRule type="expression" dxfId="127" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="116" priority="19">
+    <cfRule type="expression" dxfId="126" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="115" priority="23">
+    <cfRule type="expression" dxfId="125" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13958,47 +14055,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="114" priority="11">
+    <cfRule type="expression" dxfId="124" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="113" priority="22">
+    <cfRule type="expression" dxfId="123" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="112" priority="21">
+    <cfRule type="expression" dxfId="122" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="111" priority="1">
+    <cfRule type="expression" dxfId="121" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="110" priority="3">
+    <cfRule type="expression" dxfId="120" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="109" priority="23">
+    <cfRule type="expression" dxfId="119" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D14">
-    <cfRule type="expression" dxfId="108" priority="5">
+    <cfRule type="expression" dxfId="118" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="107" priority="7">
+    <cfRule type="expression" dxfId="117" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="106" priority="17">
+    <cfRule type="expression" dxfId="116" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14426,52 +14523,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="105" priority="6">
+    <cfRule type="expression" dxfId="115" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="104" priority="27">
+    <cfRule type="expression" dxfId="114" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="103" priority="26">
+    <cfRule type="expression" dxfId="113" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="102" priority="1">
+    <cfRule type="expression" dxfId="112" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C14">
-    <cfRule type="expression" dxfId="101" priority="4">
+    <cfRule type="expression" dxfId="111" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="100" priority="28">
+    <cfRule type="expression" dxfId="110" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="99" priority="21">
+    <cfRule type="expression" dxfId="109" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="98" priority="9">
+    <cfRule type="expression" dxfId="108" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="97" priority="19">
+    <cfRule type="expression" dxfId="107" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="96" priority="22">
+    <cfRule type="expression" dxfId="106" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14911,37 +15008,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D15">
-    <cfRule type="expression" dxfId="95" priority="5">
+    <cfRule type="expression" dxfId="105" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="94" priority="28">
+    <cfRule type="expression" dxfId="104" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="93" priority="27">
+    <cfRule type="expression" dxfId="103" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="92" priority="4">
+    <cfRule type="expression" dxfId="102" priority="4">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E7">
-    <cfRule type="expression" dxfId="91" priority="3">
+    <cfRule type="expression" dxfId="101" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F25">
-    <cfRule type="expression" dxfId="90" priority="1">
+    <cfRule type="expression" dxfId="100" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 C16:D25">
-    <cfRule type="expression" dxfId="89" priority="14">
+    <cfRule type="expression" dxfId="99" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15346,30 +15443,30 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:D12">
-    <cfRule type="expression" dxfId="304" priority="3">
+    <cfRule type="expression" dxfId="314" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="303" priority="14">
+    <cfRule type="expression" dxfId="313" priority="14">
       <formula>B$3 = TODAY()</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="302" priority="15">
+    <cfRule type="expression" dxfId="312" priority="15">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="301" priority="7">
+    <cfRule type="expression" dxfId="311" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="300" priority="9">
+    <cfRule type="expression" dxfId="310" priority="9">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 B4:B13 F5:F6 E7:F25 D13 B14:D15 C16:D25">
-    <cfRule type="expression" dxfId="299" priority="12">
+    <cfRule type="expression" dxfId="309" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15809,27 +15906,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="88" priority="2">
+    <cfRule type="expression" dxfId="98" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="87" priority="22">
+    <cfRule type="expression" dxfId="97" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="86" priority="21">
+    <cfRule type="expression" dxfId="96" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="85" priority="20">
+    <cfRule type="expression" dxfId="95" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="84" priority="7">
+    <cfRule type="expression" dxfId="94" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16283,27 +16380,27 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="83" priority="4">
+    <cfRule type="expression" dxfId="93" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="82" priority="30">
+    <cfRule type="expression" dxfId="92" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="81" priority="29">
+    <cfRule type="expression" dxfId="91" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="80" priority="1">
+    <cfRule type="expression" dxfId="90" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D6 F5:F6 E6:E7 D7:F13 B14:F25">
-    <cfRule type="expression" dxfId="79" priority="10">
+    <cfRule type="expression" dxfId="89" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16624,37 +16721,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="78" priority="31">
+    <cfRule type="expression" dxfId="88" priority="31">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="77" priority="30">
+    <cfRule type="expression" dxfId="87" priority="30">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="76" priority="2">
+    <cfRule type="expression" dxfId="86" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="75" priority="1">
+    <cfRule type="expression" dxfId="85" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D5 F5:F13 B14:E25">
-    <cfRule type="expression" dxfId="74" priority="10">
+    <cfRule type="expression" dxfId="84" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E13">
-    <cfRule type="expression" dxfId="73" priority="8">
+    <cfRule type="expression" dxfId="83" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="72" priority="14">
+    <cfRule type="expression" dxfId="82" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17056,7 +17153,7 @@
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
-      <c r="F34" s="70" t="s">
+      <c r="F34" s="16" t="s">
         <v>510</v>
       </c>
     </row>
@@ -17078,37 +17175,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="71" priority="2">
+    <cfRule type="expression" dxfId="81" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="70" priority="38">
+    <cfRule type="expression" dxfId="80" priority="38">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="69" priority="37">
+    <cfRule type="expression" dxfId="79" priority="37">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="78" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14 B15:D25">
-    <cfRule type="expression" dxfId="67" priority="4">
+    <cfRule type="expression" dxfId="77" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="66" priority="16">
+    <cfRule type="expression" dxfId="76" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="65" priority="13">
+    <cfRule type="expression" dxfId="75" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17440,13 +17537,13 @@
       <c r="E28" s="16" t="s">
         <v>457</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="19" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="19" t="s">
         <v>534</v>
       </c>
       <c r="C29" s="16" t="s">
@@ -17455,72 +17552,80 @@
       <c r="D29" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="19" t="s">
         <v>458</v>
       </c>
-      <c r="F29" s="17"/>
+      <c r="F29" s="19" t="s">
+        <v>539</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17" t="s">
+      <c r="B30" s="19" t="s">
+        <v>545</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>528</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="19" t="s">
         <v>526</v>
       </c>
-      <c r="F30" s="17"/>
+      <c r="F30" s="19"/>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17" t="s">
+      <c r="B31" s="19"/>
+      <c r="C31" s="19" t="s">
+        <v>538</v>
+      </c>
+      <c r="D31" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
       <c r="D32" s="16" t="s">
         <v>522</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
     </row>
     <row r="33" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17" t="s">
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19" t="s">
         <v>524</v>
       </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
     </row>
     <row r="34" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
       <c r="D34" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
     </row>
     <row r="35" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
     </row>
     <row r="36" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
@@ -17532,37 +17637,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="64" priority="1">
+    <cfRule type="expression" dxfId="74" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="63" priority="40">
+    <cfRule type="expression" dxfId="73" priority="40">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="62" priority="39">
+    <cfRule type="expression" dxfId="72" priority="39">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="61" priority="2">
+    <cfRule type="expression" dxfId="71" priority="2">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="60" priority="3">
+    <cfRule type="expression" dxfId="70" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26 B15:D25">
-    <cfRule type="expression" dxfId="59" priority="33">
+    <cfRule type="expression" dxfId="69" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="58" priority="32">
+    <cfRule type="expression" dxfId="68" priority="32">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17915,7 +18020,9 @@
         <v>386</v>
       </c>
       <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="F29" s="17" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
@@ -17929,12 +18036,16 @@
         <v>438</v>
       </c>
       <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="17" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="C31" s="17" t="s">
+        <v>540</v>
+      </c>
       <c r="D31" s="17" t="s">
         <v>472</v>
       </c>
@@ -17985,47 +18096,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="57" priority="11">
+    <cfRule type="expression" dxfId="67" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:B26">
-    <cfRule type="expression" dxfId="56" priority="1">
+    <cfRule type="expression" dxfId="66" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="55" priority="45">
+    <cfRule type="expression" dxfId="65" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="54" priority="44">
+    <cfRule type="expression" dxfId="64" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="53" priority="5">
+    <cfRule type="expression" dxfId="63" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="52" priority="6">
+    <cfRule type="expression" dxfId="62" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26">
-    <cfRule type="expression" dxfId="51" priority="15">
+    <cfRule type="expression" dxfId="61" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 B15:D16 C17:D25">
-    <cfRule type="expression" dxfId="50" priority="38">
+    <cfRule type="expression" dxfId="60" priority="38">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="49" priority="37">
+    <cfRule type="expression" dxfId="59" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18400,7 +18511,9 @@
       <c r="B30" s="16" t="s">
         <v>440</v>
       </c>
-      <c r="C30" s="17"/>
+      <c r="C30" s="17" t="s">
+        <v>542</v>
+      </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="16" t="s">
@@ -18463,42 +18576,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="48" priority="6">
+    <cfRule type="expression" dxfId="58" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="47" priority="21">
+    <cfRule type="expression" dxfId="57" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="46" priority="20">
+    <cfRule type="expression" dxfId="56" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="45" priority="1">
+    <cfRule type="expression" dxfId="55" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="44" priority="2">
+    <cfRule type="expression" dxfId="54" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E26">
-    <cfRule type="expression" dxfId="43" priority="10">
+    <cfRule type="expression" dxfId="53" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13 B15:D25">
-    <cfRule type="expression" dxfId="42" priority="17">
+    <cfRule type="expression" dxfId="52" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="41" priority="16">
+    <cfRule type="expression" dxfId="51" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18859,9 +18972,15 @@
       <c r="B29" s="16" t="s">
         <v>431</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
+      <c r="C29" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="F29" s="17" t="s">
         <v>531</v>
       </c>
@@ -18871,14 +18990,20 @@
       <c r="B30" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="C30" s="17"/>
+      <c r="C30" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="F30" s="19" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
-      <c r="B31" s="17"/>
+      <c r="B31" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -18926,43 +19051,68 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14">
-    <cfRule type="expression" dxfId="40" priority="7">
+    <cfRule type="expression" dxfId="50" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D25">
-    <cfRule type="expression" dxfId="39" priority="8">
+    <cfRule type="expression" dxfId="49" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="38" priority="23">
+    <cfRule type="expression" dxfId="48" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="37" priority="22">
+    <cfRule type="expression" dxfId="47" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="36" priority="1">
+  <conditionalFormatting sqref="B28:F28 B32:F36 B30 B29:C29 F29 D30:E30 C31:F31">
+    <cfRule type="expression" dxfId="46" priority="6">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D14">
-    <cfRule type="expression" dxfId="35" priority="2">
+    <cfRule type="expression" dxfId="45" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="34" priority="12">
+    <cfRule type="expression" dxfId="44" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="33" priority="18">
+    <cfRule type="expression" dxfId="43" priority="23">
       <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>NOT(ISBLANK(F30))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>NOT(ISBLANK(E29))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>NOT(ISBLANK(D29))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C30">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>NOT(ISBLANK(C30))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19307,23 +19457,35 @@
       <c r="C28" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
+      <c r="D28" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="17" t="s">
         <v>533</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
+      <c r="C29" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="E29" s="17"/>
       <c r="F29" s="17"/>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="17"/>
+      <c r="B30" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
@@ -19379,43 +19541,68 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="32" priority="6">
+    <cfRule type="expression" dxfId="42" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="31" priority="7">
+    <cfRule type="expression" dxfId="41" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="30" priority="22">
+    <cfRule type="expression" dxfId="40" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="29" priority="21">
+    <cfRule type="expression" dxfId="39" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="28" priority="1">
+  <conditionalFormatting sqref="B31:F36 B28:D28 B29 E29:F29 C30:F30">
+    <cfRule type="expression" dxfId="38" priority="6">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="27" priority="2">
+    <cfRule type="expression" dxfId="37" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="26" priority="11">
+    <cfRule type="expression" dxfId="36" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="25" priority="17">
+    <cfRule type="expression" dxfId="35" priority="22">
       <formula>$I$8 = TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28">
+    <cfRule type="expression" dxfId="9" priority="5">
+      <formula>NOT(ISBLANK(F28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28">
+    <cfRule type="expression" dxfId="8" priority="4">
+      <formula>NOT(ISBLANK(E28))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29">
+    <cfRule type="expression" dxfId="7" priority="3">
+      <formula>NOT(ISBLANK(D29))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>NOT(ISBLANK(C29))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19685,16 +19872,24 @@
       <c r="D29" s="19" t="s">
         <v>442</v>
       </c>
-      <c r="E29" s="19"/>
+      <c r="E29" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="F29" s="19" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
+      <c r="B30" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="E30" s="19"/>
       <c r="F30" s="19" t="s">
         <v>474</v>
@@ -19706,7 +19901,9 @@
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
       <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
+      <c r="F31" s="19" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
@@ -19750,42 +19947,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="24" priority="6">
+    <cfRule type="expression" dxfId="34" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="23" priority="7">
+    <cfRule type="expression" dxfId="33" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="32" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="21" priority="21">
+    <cfRule type="expression" dxfId="31" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="30" priority="20">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13 B5:F25">
-    <cfRule type="expression" dxfId="19" priority="2">
+    <cfRule type="expression" dxfId="29" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14 E6:E26">
-    <cfRule type="expression" dxfId="18" priority="11">
+    <cfRule type="expression" dxfId="28" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="17" priority="17">
+    <cfRule type="expression" dxfId="27" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20211,22 +20408,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="298" priority="10">
+    <cfRule type="expression" dxfId="308" priority="10">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="297" priority="9">
+    <cfRule type="expression" dxfId="307" priority="9">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="296" priority="1">
+    <cfRule type="expression" dxfId="306" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E6 F5:F6 B5:B14 C7:F8 C9:C13 E9:F13 C14:F14 B15:F15 C16:F25">
-    <cfRule type="expression" dxfId="295" priority="7">
+    <cfRule type="expression" dxfId="305" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20570,52 +20767,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:B6">
-    <cfRule type="expression" dxfId="16" priority="6">
+    <cfRule type="expression" dxfId="26" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:C12">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="25" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D25">
-    <cfRule type="expression" dxfId="14" priority="7">
+    <cfRule type="expression" dxfId="24" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="13" priority="30">
+    <cfRule type="expression" dxfId="23" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="12" priority="29">
+    <cfRule type="expression" dxfId="22" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F24">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="21" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="10" priority="28">
+    <cfRule type="expression" dxfId="20" priority="28">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5:C6">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E26 F9:F25">
-    <cfRule type="expression" dxfId="8" priority="8">
+    <cfRule type="expression" dxfId="18" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F7">
-    <cfRule type="expression" dxfId="7" priority="3">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21035,37 +21232,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B13">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="16" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="15" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="4" priority="21">
+    <cfRule type="expression" dxfId="14" priority="21">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="3" priority="20">
+    <cfRule type="expression" dxfId="13" priority="20">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="2" priority="19">
+    <cfRule type="expression" dxfId="12" priority="19">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D13">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25 E6:E26">
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="10" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21510,42 +21707,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B28 D28:E28 F28:F33 B29:E29 D30:E33 B34:F36">
-    <cfRule type="expression" dxfId="294" priority="15">
+    <cfRule type="expression" dxfId="304" priority="15">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30:B33">
-    <cfRule type="expression" dxfId="293" priority="13">
+    <cfRule type="expression" dxfId="303" priority="13">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="292" priority="30">
+    <cfRule type="expression" dxfId="302" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="291" priority="29">
+    <cfRule type="expression" dxfId="301" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:C33">
-    <cfRule type="expression" dxfId="290" priority="7">
+    <cfRule type="expression" dxfId="300" priority="7">
       <formula>NOT(ISBLANK(C28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 E6:E7 C9:C13 C14:D14">
-    <cfRule type="expression" dxfId="289" priority="24">
+    <cfRule type="expression" dxfId="299" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="288" priority="20">
+    <cfRule type="expression" dxfId="298" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 B5:B14 E7:F25 B15:D15 C16:C20 B16:B26 C21:D25">
-    <cfRule type="expression" dxfId="287" priority="25">
+    <cfRule type="expression" dxfId="297" priority="25">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21946,32 +22143,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 C5:C14 D7:F7 E9:F22 D14:D15 B15:C25 E23 E24:F25 F26">
-    <cfRule type="expression" dxfId="286" priority="8">
+    <cfRule type="expression" dxfId="296" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="285" priority="13">
+    <cfRule type="expression" dxfId="295" priority="13">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="284" priority="12">
+    <cfRule type="expression" dxfId="294" priority="12">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="283" priority="1">
+    <cfRule type="expression" dxfId="293" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="282" priority="4">
+    <cfRule type="expression" dxfId="292" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6">
-    <cfRule type="expression" dxfId="281" priority="7">
+    <cfRule type="expression" dxfId="291" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22355,52 +22552,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B15:B25">
-    <cfRule type="expression" dxfId="280" priority="22">
+    <cfRule type="expression" dxfId="290" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:C13">
-    <cfRule type="expression" dxfId="279" priority="23">
+    <cfRule type="expression" dxfId="289" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="278" priority="45">
+    <cfRule type="expression" dxfId="288" priority="45">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="277" priority="44">
+    <cfRule type="expression" dxfId="287" priority="44">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="276" priority="1">
+    <cfRule type="expression" dxfId="286" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:D8 B14:D14">
-    <cfRule type="expression" dxfId="275" priority="35">
+    <cfRule type="expression" dxfId="285" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 C16:C20 C21:D25">
-    <cfRule type="expression" dxfId="274" priority="36">
+    <cfRule type="expression" dxfId="284" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D13">
-    <cfRule type="expression" dxfId="273" priority="16">
+    <cfRule type="expression" dxfId="283" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D16:D25">
-    <cfRule type="expression" dxfId="272" priority="34">
+    <cfRule type="expression" dxfId="282" priority="34">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:F25">
-    <cfRule type="expression" dxfId="271" priority="5">
+    <cfRule type="expression" dxfId="281" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22813,47 +23010,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 B15:C15 C16:C25">
-    <cfRule type="expression" dxfId="270" priority="16">
+    <cfRule type="expression" dxfId="280" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="269" priority="19">
+    <cfRule type="expression" dxfId="279" priority="19">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="268" priority="18">
+    <cfRule type="expression" dxfId="278" priority="18">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="267" priority="1">
+    <cfRule type="expression" dxfId="277" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="266" priority="15">
+    <cfRule type="expression" dxfId="276" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D8">
-    <cfRule type="expression" dxfId="265" priority="12">
+    <cfRule type="expression" dxfId="275" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="264" priority="11">
+    <cfRule type="expression" dxfId="274" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="263" priority="14">
+    <cfRule type="expression" dxfId="273" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F25">
-    <cfRule type="expression" dxfId="262" priority="5">
+    <cfRule type="expression" dxfId="272" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23276,32 +23473,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C13 D5:D10 E7:F25">
-    <cfRule type="expression" dxfId="261" priority="2">
+    <cfRule type="expression" dxfId="271" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="260" priority="4">
+    <cfRule type="expression" dxfId="270" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="259" priority="16">
+    <cfRule type="expression" dxfId="269" priority="16">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="258" priority="15">
+    <cfRule type="expression" dxfId="268" priority="15">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="257" priority="1">
+    <cfRule type="expression" dxfId="267" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="256" priority="7">
+    <cfRule type="expression" dxfId="266" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/uurrooster.xlsx
+++ b/uurrooster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\LUCA-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BAB64A2-2AF8-4901-AB54-DBFB847E64F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F55376-5FB7-4B1D-ACC3-6F63F056DD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="32" activeTab="34" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="4" r:id="rId1"/>
@@ -2069,7 +2069,27 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="319">
+  <dxfs count="314">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2078,6 +2098,73 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2085,6 +2172,93 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2092,6 +2266,73 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2099,6 +2340,43 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2106,6 +2384,26 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2113,6 +2411,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2120,6 +2428,23 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2127,6 +2452,16 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2134,6 +2469,56 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2142,6 +2527,23 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -2161,6 +2563,36 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -2205,476 +2637,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5701,47 +5666,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 B15:C25">
-    <cfRule type="expression" dxfId="265" priority="17">
+    <cfRule type="expression" dxfId="260" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="264" priority="25">
+    <cfRule type="expression" dxfId="259" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="263" priority="24">
+    <cfRule type="expression" dxfId="258" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="262" priority="5">
+    <cfRule type="expression" dxfId="257" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="261" priority="9">
+    <cfRule type="expression" dxfId="256" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="260" priority="8">
+    <cfRule type="expression" dxfId="255" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="259" priority="11">
+    <cfRule type="expression" dxfId="254" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="258" priority="15">
+    <cfRule type="expression" dxfId="253" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="expression" dxfId="257" priority="2">
+    <cfRule type="expression" dxfId="252" priority="2">
       <formula>NOT(ISBLANK(E29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6200,42 +6165,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 F15:F25">
-    <cfRule type="expression" dxfId="256" priority="15">
+    <cfRule type="expression" dxfId="251" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D25">
-    <cfRule type="expression" dxfId="255" priority="10">
+    <cfRule type="expression" dxfId="250" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="254" priority="24">
+    <cfRule type="expression" dxfId="249" priority="24">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="253" priority="23">
+    <cfRule type="expression" dxfId="248" priority="23">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="252" priority="1">
+    <cfRule type="expression" dxfId="247" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C13">
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="246" priority="7">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D10">
-    <cfRule type="expression" dxfId="250" priority="3">
+    <cfRule type="expression" dxfId="245" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="249" priority="14">
+    <cfRule type="expression" dxfId="244" priority="14">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6674,47 +6639,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:C25">
-    <cfRule type="expression" dxfId="248" priority="10">
+    <cfRule type="expression" dxfId="243" priority="10">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:C28 E28:F28 D28:D30 F28:F34 B29:E34 B35:F36">
-    <cfRule type="expression" dxfId="247" priority="1">
+    <cfRule type="expression" dxfId="242" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="246" priority="25">
+    <cfRule type="expression" dxfId="241" priority="25">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="245" priority="24">
+    <cfRule type="expression" dxfId="240" priority="24">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="244" priority="4">
+    <cfRule type="expression" dxfId="239" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="243" priority="3">
+    <cfRule type="expression" dxfId="238" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="242" priority="6">
+    <cfRule type="expression" dxfId="237" priority="6">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="241" priority="9">
+    <cfRule type="expression" dxfId="236" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="240" priority="11">
+    <cfRule type="expression" dxfId="235" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7177,57 +7142,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B14 E6:E25 B15:C25 F16:F25">
-    <cfRule type="expression" dxfId="239" priority="36">
+    <cfRule type="expression" dxfId="234" priority="36">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="238" priority="51">
+    <cfRule type="expression" dxfId="233" priority="51">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="237" priority="50">
+    <cfRule type="expression" dxfId="232" priority="50">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F28 B35:E35 B36:F36">
-    <cfRule type="expression" dxfId="236" priority="9">
+    <cfRule type="expression" dxfId="231" priority="9">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C12 C14">
-    <cfRule type="expression" dxfId="235" priority="28">
+    <cfRule type="expression" dxfId="230" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="234" priority="11">
+    <cfRule type="expression" dxfId="229" priority="11">
       <formula>NOT(ISBLANK(C13))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="233" priority="24">
+    <cfRule type="expression" dxfId="228" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="232" priority="31">
+    <cfRule type="expression" dxfId="227" priority="31">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E28:E34 B29:D34">
-    <cfRule type="expression" dxfId="231" priority="7">
+    <cfRule type="expression" dxfId="226" priority="7">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="230" priority="35">
+    <cfRule type="expression" dxfId="225" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F29:F35">
-    <cfRule type="expression" dxfId="229" priority="1">
+    <cfRule type="expression" dxfId="224" priority="1">
       <formula>NOT(ISBLANK(F29))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7659,59 +7624,59 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4">
-    <cfRule type="expression" dxfId="228" priority="35">
+    <cfRule type="expression" dxfId="223" priority="35">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C25">
-    <cfRule type="expression" dxfId="227" priority="42">
+    <cfRule type="expression" dxfId="222" priority="42">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="226" priority="54">
+    <cfRule type="expression" dxfId="221" priority="54">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="225" priority="53">
+    <cfRule type="expression" dxfId="220" priority="53">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="224" priority="5">
+    <cfRule type="expression" dxfId="219" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="223" priority="30">
+    <cfRule type="expression" dxfId="218" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="222" priority="33">
+    <cfRule type="expression" dxfId="217" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D25">
-    <cfRule type="expression" dxfId="221" priority="37">
+    <cfRule type="expression" dxfId="216" priority="37">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E6 F5:F6 E7:F25">
-    <cfRule type="expression" dxfId="220" priority="41">
+    <cfRule type="expression" dxfId="215" priority="41">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F34">
-    <cfRule type="duplicateValues" dxfId="219" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F34">
-    <cfRule type="duplicateValues" dxfId="217" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35">
-    <cfRule type="expression" dxfId="216" priority="1">
+    <cfRule type="expression" dxfId="211" priority="1">
       <formula>NOT(ISBLANK(F35))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8177,57 +8142,57 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B30:B36">
-    <cfRule type="expression" dxfId="215" priority="1">
+    <cfRule type="expression" dxfId="210" priority="1">
       <formula>NOT(ISBLANK(B30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:D10">
-    <cfRule type="expression" dxfId="214" priority="18">
+    <cfRule type="expression" dxfId="209" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="213" priority="41">
+    <cfRule type="expression" dxfId="208" priority="41">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="212" priority="40">
+    <cfRule type="expression" dxfId="207" priority="40">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="211" priority="13">
+    <cfRule type="expression" dxfId="206" priority="13">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C30:D34">
-    <cfRule type="expression" dxfId="210" priority="3">
+    <cfRule type="expression" dxfId="205" priority="3">
       <formula>NOT(ISBLANK(C30))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E33 C35:F36">
-    <cfRule type="expression" dxfId="209" priority="5">
+    <cfRule type="expression" dxfId="204" priority="5">
       <formula>NOT(ISBLANK(C31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7:F10 B11:F25">
-    <cfRule type="expression" dxfId="208" priority="19">
+    <cfRule type="expression" dxfId="203" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:F34">
-    <cfRule type="expression" dxfId="207" priority="7">
+    <cfRule type="expression" dxfId="202" priority="7">
       <formula>NOT(ISBLANK(E33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="206" priority="27">
+    <cfRule type="expression" dxfId="201" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31:F32">
-    <cfRule type="expression" dxfId="205" priority="8">
+    <cfRule type="expression" dxfId="200" priority="8">
       <formula>NOT(ISBLANK(F31))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8687,32 +8652,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C11 E7:F11 B12:F25">
-    <cfRule type="expression" dxfId="204" priority="21">
+    <cfRule type="expression" dxfId="199" priority="21">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="203" priority="43">
+    <cfRule type="expression" dxfId="198" priority="43">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="202" priority="42">
+    <cfRule type="expression" dxfId="197" priority="42">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="201" priority="1">
+    <cfRule type="expression" dxfId="196" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D10">
-    <cfRule type="expression" dxfId="200" priority="16">
+    <cfRule type="expression" dxfId="195" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F6 E6:E7">
-    <cfRule type="expression" dxfId="199" priority="24">
+    <cfRule type="expression" dxfId="194" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9128,32 +9093,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="198" priority="30">
+    <cfRule type="expression" dxfId="193" priority="30">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="197" priority="29">
+    <cfRule type="expression" dxfId="192" priority="29">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F16 B17 D17:E17 B18:F25">
-    <cfRule type="expression" dxfId="196" priority="16">
+    <cfRule type="expression" dxfId="191" priority="16">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="195" priority="1">
+    <cfRule type="expression" dxfId="190" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17">
-    <cfRule type="expression" dxfId="194" priority="4">
+    <cfRule type="expression" dxfId="189" priority="4">
       <formula>NOT(ISBLANK(C17))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="expression" dxfId="193" priority="5">
+    <cfRule type="expression" dxfId="188" priority="5">
       <formula>NOT(ISBLANK(F17))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9563,32 +9528,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="192" priority="39">
+    <cfRule type="expression" dxfId="187" priority="39">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="191" priority="38">
+    <cfRule type="expression" dxfId="186" priority="38">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F13 B14 D14:E14 B15:F25">
-    <cfRule type="expression" dxfId="190" priority="20">
+    <cfRule type="expression" dxfId="185" priority="20">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="189" priority="1">
+    <cfRule type="expression" dxfId="184" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="188" priority="3">
+    <cfRule type="expression" dxfId="183" priority="3">
       <formula>NOT(ISBLANK(C14))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="expression" dxfId="187" priority="2">
+    <cfRule type="expression" dxfId="182" priority="2">
       <formula>NOT(ISBLANK(F14))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10008,37 +9973,37 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4:C4 F4 B5:F25">
-    <cfRule type="expression" dxfId="186" priority="18">
+    <cfRule type="expression" dxfId="181" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:E32">
-    <cfRule type="expression" dxfId="185" priority="2">
+    <cfRule type="expression" dxfId="180" priority="2">
       <formula>NOT(ISBLANK(B31))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="184" priority="32">
+    <cfRule type="expression" dxfId="179" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="183" priority="31">
+    <cfRule type="expression" dxfId="178" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F30">
-    <cfRule type="expression" dxfId="182" priority="5">
+    <cfRule type="expression" dxfId="177" priority="5">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:F36">
-    <cfRule type="expression" dxfId="181" priority="1">
+    <cfRule type="expression" dxfId="176" priority="1">
       <formula>NOT(ISBLANK(B33))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F32">
-    <cfRule type="expression" dxfId="180" priority="3">
+    <cfRule type="expression" dxfId="175" priority="3">
       <formula>NOT(ISBLANK(F30))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10454,22 +10419,22 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="318" priority="14">
+    <cfRule type="expression" dxfId="313" priority="14">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="317" priority="6">
+    <cfRule type="expression" dxfId="312" priority="6">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="316" priority="15">
+    <cfRule type="expression" dxfId="311" priority="15">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="315" priority="1">
+    <cfRule type="expression" dxfId="310" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10867,22 +10832,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="179" priority="32">
+    <cfRule type="expression" dxfId="174" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="178" priority="31">
+    <cfRule type="expression" dxfId="173" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F4 B5:B7 D5:F7 B8:F25">
-    <cfRule type="expression" dxfId="177" priority="12">
+    <cfRule type="expression" dxfId="172" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="176" priority="1">
+    <cfRule type="expression" dxfId="171" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11248,22 +11213,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="175" priority="17">
+    <cfRule type="expression" dxfId="170" priority="17">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="174" priority="16">
+    <cfRule type="expression" dxfId="169" priority="16">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:F25">
-    <cfRule type="expression" dxfId="173" priority="2">
+    <cfRule type="expression" dxfId="168" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="172" priority="1">
+    <cfRule type="expression" dxfId="167" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11698,47 +11663,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="171" priority="32">
+    <cfRule type="expression" dxfId="166" priority="32">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="170" priority="31">
+    <cfRule type="expression" dxfId="165" priority="31">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="169" priority="1">
+    <cfRule type="expression" dxfId="164" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25 B6:B25">
-    <cfRule type="expression" dxfId="168" priority="3">
+    <cfRule type="expression" dxfId="163" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14:D15">
-    <cfRule type="expression" dxfId="167" priority="5">
+    <cfRule type="expression" dxfId="162" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E25">
-    <cfRule type="expression" dxfId="166" priority="12">
+    <cfRule type="expression" dxfId="161" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="165" priority="18">
+    <cfRule type="expression" dxfId="160" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="164" priority="27">
+    <cfRule type="expression" dxfId="159" priority="27">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="163" priority="33">
+    <cfRule type="expression" dxfId="158" priority="33">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12169,47 +12134,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="162" priority="12">
+    <cfRule type="expression" dxfId="157" priority="12">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="161" priority="29">
+    <cfRule type="expression" dxfId="156" priority="29">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="160" priority="28">
+    <cfRule type="expression" dxfId="155" priority="28">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="159" priority="27">
+    <cfRule type="expression" dxfId="154" priority="27">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="158" priority="1">
+    <cfRule type="expression" dxfId="153" priority="1">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="157" priority="3">
+    <cfRule type="expression" dxfId="152" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="156" priority="9">
+    <cfRule type="expression" dxfId="151" priority="9">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="155" priority="24">
+    <cfRule type="expression" dxfId="150" priority="24">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="154" priority="30">
+    <cfRule type="expression" dxfId="149" priority="30">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12644,52 +12609,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="153" priority="4">
+    <cfRule type="expression" dxfId="148" priority="4">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="152" priority="27">
+    <cfRule type="expression" dxfId="147" priority="27">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="151" priority="26">
+    <cfRule type="expression" dxfId="146" priority="26">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="150" priority="1">
+    <cfRule type="expression" dxfId="145" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="149" priority="2">
+    <cfRule type="expression" dxfId="144" priority="2">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="148" priority="28">
+    <cfRule type="expression" dxfId="143" priority="28">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D8:D14">
-    <cfRule type="expression" dxfId="147" priority="5">
+    <cfRule type="expression" dxfId="142" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="146" priority="8">
+    <cfRule type="expression" dxfId="141" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F13">
-    <cfRule type="expression" dxfId="145" priority="18">
+    <cfRule type="expression" dxfId="140" priority="18">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F25">
-    <cfRule type="expression" dxfId="144" priority="22">
+    <cfRule type="expression" dxfId="139" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13118,47 +13083,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F14 B15:B25">
-    <cfRule type="expression" dxfId="143" priority="13">
+    <cfRule type="expression" dxfId="138" priority="13">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="142" priority="22">
+    <cfRule type="expression" dxfId="137" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="141" priority="21">
+    <cfRule type="expression" dxfId="136" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="140" priority="1">
+    <cfRule type="expression" dxfId="135" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="expression" dxfId="139" priority="3">
+    <cfRule type="expression" dxfId="134" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D9:D15">
-    <cfRule type="expression" dxfId="138" priority="5">
+    <cfRule type="expression" dxfId="133" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E25">
-    <cfRule type="expression" dxfId="137" priority="8">
+    <cfRule type="expression" dxfId="132" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="136" priority="17">
+    <cfRule type="expression" dxfId="131" priority="17">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:H19 J17:J21">
-    <cfRule type="expression" dxfId="135" priority="23">
+    <cfRule type="expression" dxfId="130" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13581,52 +13546,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5:B25">
-    <cfRule type="expression" dxfId="134" priority="5">
+    <cfRule type="expression" dxfId="129" priority="5">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="133" priority="28">
+    <cfRule type="expression" dxfId="128" priority="28">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="132" priority="27">
+    <cfRule type="expression" dxfId="127" priority="27">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="131" priority="1">
+    <cfRule type="expression" dxfId="126" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="130" priority="3">
+    <cfRule type="expression" dxfId="125" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="129" priority="29">
+    <cfRule type="expression" dxfId="124" priority="29">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="128" priority="22">
+    <cfRule type="expression" dxfId="123" priority="22">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E25">
-    <cfRule type="expression" dxfId="127" priority="8">
+    <cfRule type="expression" dxfId="122" priority="8">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="126" priority="19">
+    <cfRule type="expression" dxfId="121" priority="19">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F25">
-    <cfRule type="expression" dxfId="125" priority="23">
+    <cfRule type="expression" dxfId="120" priority="23">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14055,47 +14020,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B4 F5:F13 B15:B25">
-    <cfRule type="expression" dxfId="124" priority="11">
+    <cfRule type="expression" dxfId="119" priority="11">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:F3">
-    <cfRule type="expression" dxfId="123" priority="22">
+    <cfRule type="expression" dxfId="118" priority="22">
       <formula>B$3 &lt; TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:F3">
-    <cfRule type="expression" dxfId="122" priority="21">
+    <cfRule type="expression" dxfId="117" priority="21">
       <formula>B3 = TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28:F36">
-    <cfRule type="expression" dxfId="121" priority="1">
+    <cfRule type="expression" dxfId="116" priority="1">
       <formula>NOT(ISBLANK(B28))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:C14">
-    <cfRule type="expression" dxfId="120" priority="3">
+    <cfRule type="expression" dxfId="115" priority="3">
       <formula>$I$8 = TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:D15 H15:H19 C16:C25 J17:J21">
-    <cfRule type="expression" dxfId="